--- a/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
+++ b/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.2 Informe agregados\INFORME ACREDITADO-E ISO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Informes agregado\Gran agregado AG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0666828B-34BE-49E2-8413-A5C1F5C5A1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA20EC9-9FBB-4FA3-9B9E-196904C680B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="598" activeTab="3" xr2:uid="{21CE8C7D-CFC7-4B7D-B46A-F41F71EC9170}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="598" firstSheet="2" activeTab="3" xr2:uid="{21CE8C7D-CFC7-4B7D-B46A-F41F71EC9170}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="105" r:id="rId1"/>
@@ -3509,7 +3509,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1009">
+  <cellXfs count="1008">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
@@ -6007,25 +6007,22 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="12" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="12" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="12" fillId="7" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6046,13 +6043,88 @@
     <xf numFmtId="0" fontId="42" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -6080,80 +6152,59 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="22" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="22" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6166,10 +6217,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6188,87 +6235,37 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="22" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="22" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="181" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -6427,6 +6424,78 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6467,101 +6536,23 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6571,23 +6562,35 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6606,9 +6609,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -6617,23 +6617,17 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6671,6 +6665,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="12" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="12" fontId="12" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="12" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -6683,30 +6698,6 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -6719,26 +6710,32 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="12" fontId="12" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="12" fontId="12" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="12" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -21207,8 +21204,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="428625" y="7210425"/>
-          <a:ext cx="6791325" cy="2457450"/>
+          <a:off x="428625" y="7149465"/>
+          <a:ext cx="6991350" cy="2396490"/>
           <a:chOff x="442633" y="7244603"/>
           <a:chExt cx="6781240" cy="2474258"/>
         </a:xfrm>
@@ -24159,7 +24156,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -24218,7 +24215,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -24260,7 +24257,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -24302,7 +24299,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="SUCS (2)"/>
@@ -24353,7 +24350,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -25151,7 +25148,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -25270,7 +25267,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -25321,7 +25318,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Hoja1"/>
@@ -25343,7 +25340,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -25395,7 +25392,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -25425,7 +25422,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -25457,7 +25454,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="TABLA"/>
@@ -25723,7 +25720,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Hoja1"/>
@@ -31448,22 +31445,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6DE5C0-9D5B-45C2-900A-E8F19CDB3B1B}">
   <dimension ref="A1:N57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" style="200" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" style="200" customWidth="1"/>
-    <col min="3" max="3" width="2.5703125" style="200" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" style="200" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="200" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" style="200" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="200" customWidth="1"/>
+    <col min="3" max="3" width="2.5546875" style="200" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" style="200" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="200" customWidth="1"/>
     <col min="6" max="6" width="5" style="200" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="200" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="200" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="200" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" style="200" customWidth="1"/>
-    <col min="11" max="16384" width="10.28515625" style="200"/>
+    <col min="7" max="7" width="12.5546875" style="200" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="200" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" style="200" customWidth="1"/>
+    <col min="10" max="10" width="6.44140625" style="200" customWidth="1"/>
+    <col min="11" max="16384" width="10.33203125" style="200"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="9.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="9.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="727"/>
       <c r="B1" s="728"/>
       <c r="C1" s="729"/>
@@ -31474,7 +31471,7 @@
       <c r="H1" s="729"/>
       <c r="I1" s="730"/>
     </row>
-    <row r="2" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="731"/>
       <c r="B2" s="176"/>
       <c r="C2" s="177"/>
@@ -31489,7 +31486,7 @@
       </c>
       <c r="M2" s="776"/>
     </row>
-    <row r="3" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="731"/>
       <c r="B3" s="176"/>
       <c r="C3" s="177"/>
@@ -31504,7 +31501,7 @@
       </c>
       <c r="M3" s="777"/>
     </row>
-    <row r="4" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="731"/>
       <c r="B4" s="176"/>
       <c r="C4" s="177"/>
@@ -31519,7 +31516,7 @@
       </c>
       <c r="M4" s="777"/>
     </row>
-    <row r="5" spans="1:14" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="733"/>
       <c r="B5" s="734"/>
       <c r="C5" s="734"/>
@@ -31534,7 +31531,7 @@
       </c>
       <c r="M5" s="777"/>
     </row>
-    <row r="6" spans="1:14" ht="6" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="6" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="736"/>
       <c r="B6" s="736"/>
       <c r="C6" s="736"/>
@@ -31547,41 +31544,41 @@
       <c r="L6" s="778"/>
       <c r="M6" s="779"/>
     </row>
-    <row r="7" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="831" t="s">
+    <row r="7" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="806" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="831"/>
-      <c r="C7" s="831"/>
-      <c r="D7" s="831"/>
-      <c r="E7" s="831"/>
-      <c r="F7" s="831"/>
-      <c r="G7" s="831"/>
-      <c r="H7" s="831"/>
-      <c r="I7" s="831"/>
+      <c r="B7" s="806"/>
+      <c r="C7" s="806"/>
+      <c r="D7" s="806"/>
+      <c r="E7" s="806"/>
+      <c r="F7" s="806"/>
+      <c r="G7" s="806"/>
+      <c r="H7" s="806"/>
+      <c r="I7" s="806"/>
       <c r="L7" s="285" t="s">
         <v>447</v>
       </c>
       <c r="M7" s="779"/>
     </row>
-    <row r="8" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="832" t="s">
+    <row r="8" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="807" t="s">
         <v>385</v>
       </c>
-      <c r="B8" s="832"/>
-      <c r="C8" s="832"/>
-      <c r="D8" s="832"/>
-      <c r="E8" s="832"/>
-      <c r="F8" s="832"/>
-      <c r="G8" s="832"/>
-      <c r="H8" s="832"/>
-      <c r="I8" s="832"/>
+      <c r="B8" s="807"/>
+      <c r="C8" s="807"/>
+      <c r="D8" s="807"/>
+      <c r="E8" s="807"/>
+      <c r="F8" s="807"/>
+      <c r="G8" s="807"/>
+      <c r="H8" s="807"/>
+      <c r="I8" s="807"/>
       <c r="L8" s="285" t="s">
         <v>448</v>
       </c>
       <c r="M8" s="780"/>
     </row>
-    <row r="9" spans="1:14" ht="9.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="726"/>
       <c r="B9" s="726"/>
       <c r="C9" s="726"/>
@@ -31596,20 +31593,20 @@
       </c>
       <c r="M9" s="779"/>
     </row>
-    <row r="10" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="726"/>
-      <c r="B10" s="826" t="s">
+      <c r="B10" s="808" t="s">
         <v>386</v>
       </c>
-      <c r="C10" s="826"/>
-      <c r="D10" s="833" t="s">
+      <c r="C10" s="808"/>
+      <c r="D10" s="809" t="s">
         <v>387</v>
       </c>
-      <c r="E10" s="834"/>
-      <c r="F10" s="833" t="s">
+      <c r="E10" s="810"/>
+      <c r="F10" s="809" t="s">
         <v>388</v>
       </c>
-      <c r="G10" s="834"/>
+      <c r="G10" s="810"/>
       <c r="H10" s="737" t="s">
         <v>389</v>
       </c>
@@ -31617,14 +31614,14 @@
       <c r="L10" s="778"/>
       <c r="M10" s="779"/>
     </row>
-    <row r="11" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="726"/>
-      <c r="B11" s="828"/>
-      <c r="C11" s="828"/>
-      <c r="D11" s="829"/>
-      <c r="E11" s="830"/>
-      <c r="F11" s="829"/>
-      <c r="G11" s="830"/>
+      <c r="B11" s="803"/>
+      <c r="C11" s="803"/>
+      <c r="D11" s="804"/>
+      <c r="E11" s="805"/>
+      <c r="F11" s="804"/>
+      <c r="G11" s="805"/>
       <c r="H11" s="738"/>
       <c r="I11" s="726"/>
       <c r="L11" s="285" t="s">
@@ -31632,7 +31629,7 @@
       </c>
       <c r="M11" s="779"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="726"/>
       <c r="B12" s="726"/>
       <c r="C12" s="726"/>
@@ -31647,18 +31644,18 @@
       </c>
       <c r="M12" s="780"/>
     </row>
-    <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="818" t="s">
+    <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="812" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="819"/>
-      <c r="C13" s="819"/>
-      <c r="D13" s="819"/>
-      <c r="E13" s="819"/>
-      <c r="F13" s="819"/>
-      <c r="G13" s="819"/>
-      <c r="H13" s="819"/>
-      <c r="I13" s="820"/>
+      <c r="B13" s="813"/>
+      <c r="C13" s="813"/>
+      <c r="D13" s="813"/>
+      <c r="E13" s="813"/>
+      <c r="F13" s="813"/>
+      <c r="G13" s="813"/>
+      <c r="H13" s="813"/>
+      <c r="I13" s="814"/>
       <c r="J13" s="166"/>
       <c r="L13" s="285" t="s">
         <v>452</v>
@@ -31666,23 +31663,23 @@
       <c r="M13" s="780"/>
       <c r="N13"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="821" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="815" t="s">
         <v>390</v>
       </c>
-      <c r="B14" s="822"/>
-      <c r="C14" s="822"/>
-      <c r="D14" s="822"/>
-      <c r="E14" s="822"/>
-      <c r="F14" s="822"/>
-      <c r="G14" s="822"/>
-      <c r="H14" s="822"/>
-      <c r="I14" s="823"/>
+      <c r="B14" s="816"/>
+      <c r="C14" s="816"/>
+      <c r="D14" s="816"/>
+      <c r="E14" s="816"/>
+      <c r="F14" s="816"/>
+      <c r="G14" s="816"/>
+      <c r="H14" s="816"/>
+      <c r="I14" s="817"/>
       <c r="J14" s="166"/>
       <c r="L14" s="778"/>
       <c r="M14" s="779"/>
     </row>
-    <row r="15" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="739"/>
       <c r="B15" s="195"/>
       <c r="C15" s="195"/>
@@ -31698,14 +31695,14 @@
       </c>
       <c r="M15" s="781"/>
     </row>
-    <row r="16" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="740" t="s">
         <v>391</v>
       </c>
-      <c r="B16" s="805"/>
-      <c r="C16" s="805"/>
-      <c r="D16" s="805"/>
-      <c r="E16" s="805"/>
+      <c r="B16" s="818"/>
+      <c r="C16" s="818"/>
+      <c r="D16" s="818"/>
+      <c r="E16" s="818"/>
       <c r="F16" s="231"/>
       <c r="G16" s="213" t="s">
         <v>9</v>
@@ -31721,14 +31718,14 @@
       </c>
       <c r="M16" s="781"/>
     </row>
-    <row r="17" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="824" t="s">
+    <row r="17" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="819" t="s">
         <v>394</v>
       </c>
-      <c r="B17" s="824"/>
-      <c r="C17" s="824"/>
-      <c r="D17" s="825"/>
-      <c r="E17" s="825"/>
+      <c r="B17" s="819"/>
+      <c r="C17" s="819"/>
+      <c r="D17" s="820"/>
+      <c r="E17" s="820"/>
       <c r="F17" s="231"/>
       <c r="G17" s="213" t="s">
         <v>11</v>
@@ -31744,14 +31741,14 @@
       </c>
       <c r="M17" s="782"/>
     </row>
-    <row r="18" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="740" t="s">
         <v>397</v>
       </c>
-      <c r="B18" s="805"/>
-      <c r="C18" s="805"/>
-      <c r="D18" s="805"/>
-      <c r="E18" s="805"/>
+      <c r="B18" s="818"/>
+      <c r="C18" s="818"/>
+      <c r="D18" s="818"/>
+      <c r="E18" s="818"/>
       <c r="F18" s="741"/>
       <c r="G18" s="77" t="s">
         <v>398</v>
@@ -31761,7 +31758,7 @@
       </c>
       <c r="I18" s="69"/>
     </row>
-    <row r="19" spans="1:13" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E19" s="231"/>
       <c r="F19" s="231"/>
       <c r="G19" s="220" t="s">
@@ -31772,14 +31769,14 @@
       </c>
       <c r="I19" s="69"/>
     </row>
-    <row r="20" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="826" t="s">
+    <row r="20" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="808" t="s">
         <v>400</v>
       </c>
-      <c r="B20" s="826"/>
-      <c r="C20" s="826"/>
-      <c r="D20" s="826"/>
-      <c r="E20" s="826"/>
+      <c r="B20" s="808"/>
+      <c r="C20" s="808"/>
+      <c r="D20" s="808"/>
+      <c r="E20" s="808"/>
       <c r="F20" s="743"/>
       <c r="G20" s="77" t="s">
         <v>401</v>
@@ -31790,7 +31787,7 @@
       <c r="I20" s="69"/>
       <c r="J20" s="774"/>
     </row>
-    <row r="21" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="744" t="s">
         <v>402</v>
       </c>
@@ -31798,8 +31795,8 @@
       <c r="C21" s="746" t="s">
         <v>403</v>
       </c>
-      <c r="D21" s="827"/>
-      <c r="E21" s="827"/>
+      <c r="D21" s="821"/>
+      <c r="E21" s="821"/>
       <c r="F21" s="747"/>
       <c r="G21" s="77" t="s">
         <v>404</v>
@@ -31810,7 +31807,7 @@
       <c r="I21" s="69"/>
       <c r="J21" s="166"/>
     </row>
-    <row r="22" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="744" t="s">
         <v>405</v>
       </c>
@@ -31818,8 +31815,8 @@
       <c r="C22" s="746" t="s">
         <v>403</v>
       </c>
-      <c r="D22" s="827"/>
-      <c r="E22" s="827"/>
+      <c r="D22" s="821"/>
+      <c r="E22" s="821"/>
       <c r="F22" s="747"/>
       <c r="G22" s="77" t="s">
         <v>406</v>
@@ -31829,7 +31826,7 @@
       </c>
       <c r="I22" s="69"/>
     </row>
-    <row r="23" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="744" t="s">
         <v>407</v>
       </c>
@@ -31837,8 +31834,8 @@
       <c r="C23" s="746" t="s">
         <v>403</v>
       </c>
-      <c r="D23" s="827"/>
-      <c r="E23" s="827"/>
+      <c r="D23" s="821"/>
+      <c r="E23" s="821"/>
       <c r="F23" s="747"/>
       <c r="G23" s="77" t="s">
         <v>408</v>
@@ -31848,7 +31845,7 @@
       </c>
       <c r="I23" s="69"/>
     </row>
-    <row r="24" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="744" t="s">
         <v>409</v>
       </c>
@@ -31856,8 +31853,8 @@
       <c r="C24" s="746" t="s">
         <v>403</v>
       </c>
-      <c r="D24" s="827"/>
-      <c r="E24" s="827"/>
+      <c r="D24" s="821"/>
+      <c r="E24" s="821"/>
       <c r="F24" s="747"/>
       <c r="G24" s="220" t="s">
         <v>410</v>
@@ -31867,7 +31864,7 @@
       </c>
       <c r="I24" s="69"/>
     </row>
-    <row r="25" spans="1:13" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
       <c r="B25" s="743"/>
       <c r="C25" s="748"/>
@@ -31882,14 +31879,14 @@
       </c>
       <c r="I25" s="69"/>
     </row>
-    <row r="26" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="817" t="s">
+    <row r="26" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="811" t="s">
         <v>412</v>
       </c>
-      <c r="B26" s="817"/>
-      <c r="C26" s="817"/>
-      <c r="D26" s="817"/>
-      <c r="E26" s="817"/>
+      <c r="B26" s="811"/>
+      <c r="C26" s="811"/>
+      <c r="D26" s="811"/>
+      <c r="E26" s="811"/>
       <c r="F26" s="5"/>
       <c r="G26" s="77" t="s">
         <v>413</v>
@@ -31899,7 +31896,7 @@
       </c>
       <c r="I26" s="69"/>
     </row>
-    <row r="27" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="749" t="s">
         <v>402</v>
       </c>
@@ -31907,8 +31904,8 @@
       <c r="C27" s="751" t="s">
         <v>403</v>
       </c>
-      <c r="D27" s="813"/>
-      <c r="E27" s="813"/>
+      <c r="D27" s="822"/>
+      <c r="E27" s="822"/>
       <c r="G27" s="220" t="s">
         <v>414</v>
       </c>
@@ -31917,7 +31914,7 @@
       </c>
       <c r="I27" s="69"/>
     </row>
-    <row r="28" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="749" t="s">
         <v>415</v>
       </c>
@@ -31925,8 +31922,8 @@
       <c r="C28" s="753" t="s">
         <v>403</v>
       </c>
-      <c r="D28" s="805"/>
-      <c r="E28" s="805"/>
+      <c r="D28" s="818"/>
+      <c r="E28" s="818"/>
       <c r="G28" s="77" t="s">
         <v>416</v>
       </c>
@@ -31935,14 +31932,14 @@
       </c>
       <c r="I28" s="69"/>
     </row>
-    <row r="29" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="814" t="s">
+    <row r="29" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="823" t="s">
         <v>417</v>
       </c>
-      <c r="B29" s="815"/>
-      <c r="C29" s="815"/>
-      <c r="D29" s="815"/>
-      <c r="E29" s="816"/>
+      <c r="B29" s="824"/>
+      <c r="C29" s="824"/>
+      <c r="D29" s="824"/>
+      <c r="E29" s="825"/>
       <c r="G29" s="220" t="s">
         <v>418</v>
       </c>
@@ -31952,7 +31949,7 @@
       <c r="I29" s="69"/>
       <c r="J29" s="166"/>
     </row>
-    <row r="30" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="744" t="s">
         <v>405</v>
       </c>
@@ -31960,8 +31957,8 @@
       <c r="C30" s="753" t="s">
         <v>403</v>
       </c>
-      <c r="D30" s="805"/>
-      <c r="E30" s="805"/>
+      <c r="D30" s="818"/>
+      <c r="E30" s="818"/>
       <c r="G30" s="220" t="s">
         <v>161</v>
       </c>
@@ -31971,7 +31968,7 @@
       <c r="I30" s="69"/>
       <c r="J30" s="166"/>
     </row>
-    <row r="31" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="749" t="s">
         <v>407</v>
       </c>
@@ -31979,8 +31976,8 @@
       <c r="C31" s="753" t="s">
         <v>403</v>
       </c>
-      <c r="D31" s="805"/>
-      <c r="E31" s="805"/>
+      <c r="D31" s="818"/>
+      <c r="E31" s="818"/>
       <c r="G31" s="220" t="s">
         <v>419</v>
       </c>
@@ -31990,14 +31987,14 @@
       <c r="I31" s="69"/>
       <c r="J31" s="166"/>
     </row>
-    <row r="32" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="814" t="s">
+    <row r="32" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="823" t="s">
         <v>420</v>
       </c>
-      <c r="B32" s="815"/>
-      <c r="C32" s="815"/>
-      <c r="D32" s="815"/>
-      <c r="E32" s="816"/>
+      <c r="B32" s="824"/>
+      <c r="C32" s="824"/>
+      <c r="D32" s="824"/>
+      <c r="E32" s="825"/>
       <c r="G32" s="220" t="s">
         <v>421</v>
       </c>
@@ -32007,7 +32004,7 @@
       <c r="I32" s="69"/>
       <c r="J32" s="166"/>
     </row>
-    <row r="33" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="744" t="s">
         <v>422</v>
       </c>
@@ -32015,8 +32012,8 @@
       <c r="C33" s="753" t="s">
         <v>403</v>
       </c>
-      <c r="D33" s="805"/>
-      <c r="E33" s="805"/>
+      <c r="D33" s="818"/>
+      <c r="E33" s="818"/>
       <c r="F33" s="741"/>
       <c r="G33" s="220" t="s">
         <v>423</v>
@@ -32027,15 +32024,15 @@
       <c r="I33" s="69"/>
       <c r="J33" s="166"/>
     </row>
-    <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="755" t="s">
         <v>424</v>
       </c>
       <c r="C34" s="748" t="s">
         <v>403</v>
       </c>
-      <c r="D34" s="805"/>
-      <c r="E34" s="805"/>
+      <c r="D34" s="818"/>
+      <c r="E34" s="818"/>
       <c r="F34" s="741"/>
       <c r="G34" s="220" t="s">
         <v>425</v>
@@ -32046,7 +32043,7 @@
       <c r="I34" s="69"/>
       <c r="J34" s="166"/>
     </row>
-    <row r="35" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="744" t="s">
         <v>426</v>
       </c>
@@ -32054,8 +32051,8 @@
       <c r="C35" s="753" t="s">
         <v>403</v>
       </c>
-      <c r="D35" s="805"/>
-      <c r="E35" s="805"/>
+      <c r="D35" s="818"/>
+      <c r="E35" s="818"/>
       <c r="F35" s="741"/>
       <c r="G35" s="230" t="s">
         <v>34</v>
@@ -32066,22 +32063,22 @@
       <c r="I35" s="230"/>
       <c r="J35" s="166"/>
     </row>
-    <row r="36" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="755" t="s">
         <v>427</v>
       </c>
       <c r="C36" s="748" t="s">
         <v>403</v>
       </c>
-      <c r="D36" s="805"/>
-      <c r="E36" s="805"/>
+      <c r="D36" s="818"/>
+      <c r="E36" s="818"/>
       <c r="F36" s="741"/>
       <c r="H36" s="756" t="s">
         <v>428</v>
       </c>
       <c r="J36" s="166"/>
     </row>
-    <row r="37" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="744" t="s">
         <v>429</v>
       </c>
@@ -32089,12 +32086,12 @@
       <c r="C37" s="753" t="s">
         <v>403</v>
       </c>
-      <c r="D37" s="805"/>
-      <c r="E37" s="805"/>
+      <c r="D37" s="818"/>
+      <c r="E37" s="818"/>
       <c r="F37" s="741"/>
       <c r="J37" s="166"/>
     </row>
-    <row r="38" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="749" t="s">
         <v>430</v>
       </c>
@@ -32102,13 +32099,13 @@
       <c r="C38" s="751" t="s">
         <v>431</v>
       </c>
-      <c r="D38" s="805"/>
-      <c r="E38" s="805"/>
+      <c r="D38" s="818"/>
+      <c r="E38" s="818"/>
       <c r="F38" s="741"/>
       <c r="I38" s="758"/>
       <c r="J38" s="166"/>
     </row>
-    <row r="39" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="749" t="s">
         <v>432</v>
       </c>
@@ -32116,15 +32113,15 @@
       <c r="C39" s="751" t="s">
         <v>403</v>
       </c>
-      <c r="D39" s="805"/>
-      <c r="E39" s="805"/>
+      <c r="D39" s="818"/>
+      <c r="E39" s="818"/>
       <c r="F39" s="741"/>
       <c r="G39" s="759"/>
       <c r="H39" s="760"/>
       <c r="I39" s="758"/>
       <c r="J39" s="166"/>
     </row>
-    <row r="40" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E40" s="741"/>
       <c r="F40" s="741"/>
       <c r="G40" s="759"/>
@@ -32132,54 +32129,54 @@
       <c r="I40" s="758"/>
       <c r="J40" s="166"/>
     </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="806" t="s">
+    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="827" t="s">
         <v>433</v>
       </c>
-      <c r="B41" s="806"/>
-      <c r="C41" s="806"/>
-      <c r="D41" s="806"/>
+      <c r="B41" s="827"/>
+      <c r="C41" s="827"/>
+      <c r="D41" s="827"/>
       <c r="E41" s="761"/>
       <c r="F41" s="761"/>
       <c r="J41" s="166"/>
     </row>
-    <row r="42" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="762" t="s">
         <v>434</v>
       </c>
       <c r="B42" s="763"/>
-      <c r="C42" s="807"/>
-      <c r="D42" s="807"/>
-      <c r="E42" s="808"/>
-      <c r="F42" s="808"/>
+      <c r="C42" s="828"/>
+      <c r="D42" s="828"/>
+      <c r="E42" s="829"/>
+      <c r="F42" s="829"/>
       <c r="J42" s="166"/>
     </row>
-    <row r="43" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="762" t="s">
         <v>435</v>
       </c>
       <c r="B43" s="764"/>
-      <c r="C43" s="807"/>
-      <c r="D43" s="807"/>
-      <c r="E43" s="808"/>
-      <c r="F43" s="808"/>
+      <c r="C43" s="828"/>
+      <c r="D43" s="828"/>
+      <c r="E43" s="829"/>
+      <c r="F43" s="829"/>
       <c r="J43" s="166"/>
     </row>
-    <row r="44" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="765" t="s">
         <v>436</v>
       </c>
       <c r="B44" s="764"/>
-      <c r="C44" s="807"/>
-      <c r="D44" s="807"/>
-      <c r="E44" s="808"/>
-      <c r="F44" s="808"/>
+      <c r="C44" s="828"/>
+      <c r="D44" s="828"/>
+      <c r="E44" s="829"/>
+      <c r="F44" s="829"/>
       <c r="J44" s="166"/>
     </row>
-    <row r="45" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J45" s="166"/>
     </row>
-    <row r="46" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="766" t="s">
         <v>437</v>
       </c>
@@ -32192,29 +32189,29 @@
       <c r="F46" s="281"/>
       <c r="J46" s="166"/>
     </row>
-    <row r="47" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="770" t="s">
         <v>439</v>
       </c>
-      <c r="B47" s="809"/>
-      <c r="C47" s="810"/>
-      <c r="D47" s="811"/>
+      <c r="B47" s="830"/>
+      <c r="C47" s="831"/>
+      <c r="D47" s="832"/>
       <c r="E47" s="247"/>
       <c r="F47" s="247"/>
-      <c r="G47" s="812" t="s">
+      <c r="G47" s="833" t="s">
         <v>440</v>
       </c>
-      <c r="H47" s="812"/>
-      <c r="I47" s="812"/>
+      <c r="H47" s="833"/>
+      <c r="I47" s="833"/>
       <c r="J47" s="166"/>
     </row>
-    <row r="48" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="771" t="s">
         <v>441</v>
       </c>
-      <c r="B48" s="809"/>
-      <c r="C48" s="810"/>
-      <c r="D48" s="811"/>
+      <c r="B48" s="830"/>
+      <c r="C48" s="831"/>
+      <c r="D48" s="832"/>
       <c r="E48" s="247"/>
       <c r="F48" s="247"/>
       <c r="G48" s="4" t="s">
@@ -32222,7 +32219,7 @@
       </c>
       <c r="J48" s="166"/>
     </row>
-    <row r="49" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="772" t="s">
         <v>443</v>
       </c>
@@ -32232,7 +32229,7 @@
       <c r="H49" s="247"/>
       <c r="J49" s="166"/>
     </row>
-    <row r="50" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="772"/>
       <c r="E50" s="247"/>
       <c r="F50" s="247"/>
@@ -32240,7 +32237,7 @@
       <c r="H50" s="247"/>
       <c r="J50" s="166"/>
     </row>
-    <row r="51" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="772"/>
       <c r="E51" s="247"/>
       <c r="F51" s="247"/>
@@ -32248,7 +32245,7 @@
       <c r="H51" s="247"/>
       <c r="J51" s="166"/>
     </row>
-    <row r="52" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
         <v>4</v>
       </c>
@@ -32261,7 +32258,7 @@
       <c r="H52" s="239"/>
       <c r="J52" s="166"/>
     </row>
-    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
         <v>444</v>
       </c>
@@ -32277,36 +32274,52 @@
       <c r="I53" s="239"/>
       <c r="J53" s="166"/>
     </row>
-    <row r="54" spans="1:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="804" t="s">
+    <row r="54" spans="1:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="826" t="s">
         <v>446</v>
       </c>
-      <c r="B55" s="804"/>
-      <c r="C55" s="804"/>
-      <c r="D55" s="804"/>
-      <c r="E55" s="804"/>
-      <c r="F55" s="804"/>
-      <c r="G55" s="804"/>
-      <c r="H55" s="804"/>
-      <c r="I55" s="804"/>
-    </row>
-    <row r="56" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B55" s="826"/>
+      <c r="C55" s="826"/>
+      <c r="D55" s="826"/>
+      <c r="E55" s="826"/>
+      <c r="F55" s="826"/>
+      <c r="G55" s="826"/>
+      <c r="H55" s="826"/>
+      <c r="I55" s="826"/>
+    </row>
+    <row r="56" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="mIWhJnxyN3XPvacsgWk9ewyIoJ34+YfI7gB/PE3y3zbMfMuX2E1GZruPXE95kMlpgXtXNntC/2FXyMKYR5LwLQ==" saltValue="wi9Lpn9BfQ3nbJB8EnVKXQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="B15" name="Rango3_3_1_1_1_1_1_1_1_1"/>
   </protectedRanges>
   <mergeCells count="44">
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A14:I14"/>
@@ -32319,30 +32332,14 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.59055118110236227" top="0.78740157480314965" bottom="0" header="0" footer="0"/>
@@ -32355,25 +32352,25 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3295A275-BCFD-46E8-B683-5F629FC3BD9F}">
   <dimension ref="B3:BC35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="5"/>
-    <col min="2" max="3" width="8.7109375" style="5" customWidth="1"/>
-    <col min="4" max="6" width="5.7109375" style="5" customWidth="1"/>
-    <col min="7" max="8" width="8.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="5" customWidth="1"/>
-    <col min="10" max="18" width="4.7109375" style="5" hidden="1" customWidth="1"/>
-    <col min="19" max="21" width="4.7109375" style="5" customWidth="1"/>
-    <col min="22" max="24" width="4.7109375" style="5" hidden="1" customWidth="1"/>
-    <col min="25" max="27" width="4.7109375" style="5" customWidth="1"/>
-    <col min="28" max="33" width="4.7109375" style="5" hidden="1" customWidth="1"/>
-    <col min="34" max="36" width="4.7109375" style="5" customWidth="1"/>
-    <col min="37" max="39" width="4.7109375" style="5" hidden="1" customWidth="1"/>
-    <col min="40" max="45" width="4.7109375" style="5" customWidth="1"/>
-    <col min="46" max="48" width="4.7109375" style="5" hidden="1" customWidth="1"/>
-    <col min="49" max="53" width="4.7109375" style="5" customWidth="1"/>
-    <col min="54" max="54" width="10.28515625" style="5" customWidth="1"/>
-    <col min="55" max="16384" width="10.28515625" style="5"/>
+    <col min="1" max="1" width="10.33203125" style="5"/>
+    <col min="2" max="3" width="8.6640625" style="5" customWidth="1"/>
+    <col min="4" max="6" width="5.6640625" style="5" customWidth="1"/>
+    <col min="7" max="8" width="8.6640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="5" customWidth="1"/>
+    <col min="10" max="18" width="4.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="19" max="21" width="4.6640625" style="5" customWidth="1"/>
+    <col min="22" max="24" width="4.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="25" max="27" width="4.6640625" style="5" customWidth="1"/>
+    <col min="28" max="33" width="4.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="34" max="36" width="4.6640625" style="5" customWidth="1"/>
+    <col min="37" max="39" width="4.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="40" max="45" width="4.6640625" style="5" customWidth="1"/>
+    <col min="46" max="48" width="4.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="49" max="53" width="4.6640625" style="5" customWidth="1"/>
+    <col min="54" max="54" width="10.33203125" style="5" customWidth="1"/>
+    <col min="55" max="16384" width="10.33203125" style="5"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -32395,117 +32392,117 @@
       <c r="T4" s="25"/>
     </row>
     <row r="5" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="997" t="s">
+      <c r="B5" s="975" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="998"/>
-      <c r="D5" s="998"/>
-      <c r="E5" s="998"/>
-      <c r="F5" s="999"/>
-      <c r="H5" s="997" t="s">
+      <c r="C5" s="976"/>
+      <c r="D5" s="976"/>
+      <c r="E5" s="976"/>
+      <c r="F5" s="977"/>
+      <c r="H5" s="975" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="998"/>
-      <c r="J5" s="998"/>
-      <c r="K5" s="998"/>
-      <c r="L5" s="998"/>
-      <c r="M5" s="998"/>
-      <c r="N5" s="998"/>
-      <c r="O5" s="998"/>
-      <c r="P5" s="998"/>
-      <c r="Q5" s="998"/>
-      <c r="R5" s="998"/>
-      <c r="S5" s="998"/>
-      <c r="T5" s="998"/>
-      <c r="U5" s="998"/>
-      <c r="V5" s="998"/>
-      <c r="W5" s="998"/>
-      <c r="X5" s="998"/>
-      <c r="Y5" s="998"/>
-      <c r="Z5" s="998"/>
-      <c r="AA5" s="998"/>
-      <c r="AB5" s="998"/>
-      <c r="AC5" s="998"/>
-      <c r="AD5" s="998"/>
-      <c r="AE5" s="998"/>
-      <c r="AF5" s="998"/>
-      <c r="AG5" s="998"/>
-      <c r="AH5" s="998"/>
-      <c r="AI5" s="998"/>
-      <c r="AJ5" s="998"/>
-      <c r="AK5" s="998"/>
-      <c r="AL5" s="998"/>
-      <c r="AM5" s="998"/>
-      <c r="AN5" s="998"/>
-      <c r="AO5" s="998"/>
-      <c r="AP5" s="998"/>
-      <c r="AQ5" s="998"/>
-      <c r="AR5" s="998"/>
-      <c r="AS5" s="999"/>
+      <c r="I5" s="976"/>
+      <c r="J5" s="976"/>
+      <c r="K5" s="976"/>
+      <c r="L5" s="976"/>
+      <c r="M5" s="976"/>
+      <c r="N5" s="976"/>
+      <c r="O5" s="976"/>
+      <c r="P5" s="976"/>
+      <c r="Q5" s="976"/>
+      <c r="R5" s="976"/>
+      <c r="S5" s="976"/>
+      <c r="T5" s="976"/>
+      <c r="U5" s="976"/>
+      <c r="V5" s="976"/>
+      <c r="W5" s="976"/>
+      <c r="X5" s="976"/>
+      <c r="Y5" s="976"/>
+      <c r="Z5" s="976"/>
+      <c r="AA5" s="976"/>
+      <c r="AB5" s="976"/>
+      <c r="AC5" s="976"/>
+      <c r="AD5" s="976"/>
+      <c r="AE5" s="976"/>
+      <c r="AF5" s="976"/>
+      <c r="AG5" s="976"/>
+      <c r="AH5" s="976"/>
+      <c r="AI5" s="976"/>
+      <c r="AJ5" s="976"/>
+      <c r="AK5" s="976"/>
+      <c r="AL5" s="976"/>
+      <c r="AM5" s="976"/>
+      <c r="AN5" s="976"/>
+      <c r="AO5" s="976"/>
+      <c r="AP5" s="976"/>
+      <c r="AQ5" s="976"/>
+      <c r="AR5" s="976"/>
+      <c r="AS5" s="977"/>
     </row>
     <row r="6" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="997" t="s">
+      <c r="B6" s="975" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="998"/>
-      <c r="D6" s="998"/>
-      <c r="E6" s="998"/>
-      <c r="F6" s="999"/>
-      <c r="H6" s="997" t="s">
+      <c r="C6" s="976"/>
+      <c r="D6" s="976"/>
+      <c r="E6" s="976"/>
+      <c r="F6" s="977"/>
+      <c r="H6" s="975" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="998"/>
-      <c r="J6" s="998"/>
-      <c r="K6" s="998"/>
-      <c r="L6" s="998"/>
-      <c r="M6" s="998"/>
-      <c r="N6" s="998"/>
-      <c r="O6" s="998"/>
-      <c r="P6" s="998"/>
-      <c r="Q6" s="998"/>
-      <c r="R6" s="998"/>
-      <c r="S6" s="998"/>
-      <c r="T6" s="998"/>
-      <c r="U6" s="998"/>
-      <c r="V6" s="998"/>
-      <c r="W6" s="998"/>
-      <c r="X6" s="998"/>
-      <c r="Y6" s="998"/>
-      <c r="Z6" s="998"/>
-      <c r="AA6" s="998"/>
-      <c r="AB6" s="998"/>
-      <c r="AC6" s="998"/>
-      <c r="AD6" s="998"/>
-      <c r="AE6" s="998"/>
-      <c r="AF6" s="998"/>
-      <c r="AG6" s="998"/>
-      <c r="AH6" s="998"/>
-      <c r="AI6" s="998"/>
-      <c r="AJ6" s="998"/>
-      <c r="AK6" s="998"/>
-      <c r="AL6" s="998"/>
-      <c r="AM6" s="998"/>
-      <c r="AN6" s="998"/>
-      <c r="AO6" s="998"/>
-      <c r="AP6" s="998"/>
-      <c r="AQ6" s="998"/>
-      <c r="AR6" s="998"/>
-      <c r="AS6" s="999"/>
-    </row>
-    <row r="7" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="977" t="s">
+      <c r="I6" s="976"/>
+      <c r="J6" s="976"/>
+      <c r="K6" s="976"/>
+      <c r="L6" s="976"/>
+      <c r="M6" s="976"/>
+      <c r="N6" s="976"/>
+      <c r="O6" s="976"/>
+      <c r="P6" s="976"/>
+      <c r="Q6" s="976"/>
+      <c r="R6" s="976"/>
+      <c r="S6" s="976"/>
+      <c r="T6" s="976"/>
+      <c r="U6" s="976"/>
+      <c r="V6" s="976"/>
+      <c r="W6" s="976"/>
+      <c r="X6" s="976"/>
+      <c r="Y6" s="976"/>
+      <c r="Z6" s="976"/>
+      <c r="AA6" s="976"/>
+      <c r="AB6" s="976"/>
+      <c r="AC6" s="976"/>
+      <c r="AD6" s="976"/>
+      <c r="AE6" s="976"/>
+      <c r="AF6" s="976"/>
+      <c r="AG6" s="976"/>
+      <c r="AH6" s="976"/>
+      <c r="AI6" s="976"/>
+      <c r="AJ6" s="976"/>
+      <c r="AK6" s="976"/>
+      <c r="AL6" s="976"/>
+      <c r="AM6" s="976"/>
+      <c r="AN6" s="976"/>
+      <c r="AO6" s="976"/>
+      <c r="AP6" s="976"/>
+      <c r="AQ6" s="976"/>
+      <c r="AR6" s="976"/>
+      <c r="AS6" s="977"/>
+    </row>
+    <row r="7" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1000" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="978"/>
-      <c r="D7" s="981" t="s">
+      <c r="C7" s="1001"/>
+      <c r="D7" s="978" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="982"/>
-      <c r="F7" s="983"/>
-      <c r="H7" s="993" t="s">
+      <c r="E7" s="979"/>
+      <c r="F7" s="980"/>
+      <c r="H7" s="1004" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="994"/>
+      <c r="I7" s="1005"/>
       <c r="J7" s="30"/>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
@@ -32515,201 +32512,201 @@
       <c r="P7" s="30"/>
       <c r="Q7" s="30"/>
       <c r="R7" s="14"/>
-      <c r="S7" s="1006">
+      <c r="S7" s="990">
         <v>2</v>
       </c>
-      <c r="T7" s="1007"/>
-      <c r="U7" s="1008"/>
-      <c r="V7" s="1000"/>
-      <c r="W7" s="1001"/>
-      <c r="X7" s="1002"/>
-      <c r="Y7" s="1006">
+      <c r="T7" s="991"/>
+      <c r="U7" s="992"/>
+      <c r="V7" s="996"/>
+      <c r="W7" s="997"/>
+      <c r="X7" s="998"/>
+      <c r="Y7" s="990">
         <v>1.5</v>
       </c>
-      <c r="Z7" s="1007"/>
-      <c r="AA7" s="1008"/>
-      <c r="AB7" s="1000"/>
-      <c r="AC7" s="1001"/>
-      <c r="AD7" s="1002"/>
-      <c r="AE7" s="1000"/>
-      <c r="AF7" s="1001"/>
-      <c r="AG7" s="1002"/>
-      <c r="AH7" s="1006">
+      <c r="Z7" s="991"/>
+      <c r="AA7" s="992"/>
+      <c r="AB7" s="996"/>
+      <c r="AC7" s="997"/>
+      <c r="AD7" s="998"/>
+      <c r="AE7" s="996"/>
+      <c r="AF7" s="997"/>
+      <c r="AG7" s="998"/>
+      <c r="AH7" s="990">
         <v>1</v>
       </c>
-      <c r="AI7" s="1007"/>
-      <c r="AJ7" s="1008"/>
-      <c r="AK7" s="1000"/>
-      <c r="AL7" s="1001"/>
-      <c r="AM7" s="1002"/>
-      <c r="AN7" s="1006">
+      <c r="AI7" s="991"/>
+      <c r="AJ7" s="992"/>
+      <c r="AK7" s="996"/>
+      <c r="AL7" s="997"/>
+      <c r="AM7" s="998"/>
+      <c r="AN7" s="990">
         <v>0.75</v>
       </c>
-      <c r="AO7" s="1007"/>
-      <c r="AP7" s="1008"/>
-      <c r="AQ7" s="1006">
+      <c r="AO7" s="991"/>
+      <c r="AP7" s="992"/>
+      <c r="AQ7" s="990">
         <v>0.5</v>
       </c>
-      <c r="AR7" s="1007"/>
-      <c r="AS7" s="1008"/>
-    </row>
-    <row r="8" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="979"/>
-      <c r="C8" s="980"/>
-      <c r="D8" s="984"/>
-      <c r="E8" s="985"/>
-      <c r="F8" s="986"/>
-      <c r="H8" s="995" t="s">
+      <c r="AR7" s="991"/>
+      <c r="AS7" s="992"/>
+    </row>
+    <row r="8" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1002"/>
+      <c r="C8" s="1003"/>
+      <c r="D8" s="981"/>
+      <c r="E8" s="982"/>
+      <c r="F8" s="983"/>
+      <c r="H8" s="1006" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="996"/>
-      <c r="J8" s="990">
+      <c r="I8" s="1007"/>
+      <c r="J8" s="993">
         <v>1</v>
       </c>
-      <c r="K8" s="991"/>
-      <c r="L8" s="992"/>
-      <c r="M8" s="990">
+      <c r="K8" s="994"/>
+      <c r="L8" s="995"/>
+      <c r="M8" s="993">
         <v>2</v>
       </c>
-      <c r="N8" s="991"/>
-      <c r="O8" s="992"/>
-      <c r="P8" s="990">
+      <c r="N8" s="994"/>
+      <c r="O8" s="995"/>
+      <c r="P8" s="993">
         <v>3</v>
       </c>
-      <c r="Q8" s="991"/>
-      <c r="R8" s="992"/>
-      <c r="S8" s="990">
+      <c r="Q8" s="994"/>
+      <c r="R8" s="995"/>
+      <c r="S8" s="993">
         <v>357</v>
       </c>
-      <c r="T8" s="991"/>
-      <c r="U8" s="992"/>
-      <c r="V8" s="990">
+      <c r="T8" s="994"/>
+      <c r="U8" s="995"/>
+      <c r="V8" s="993">
         <v>4</v>
       </c>
-      <c r="W8" s="991"/>
-      <c r="X8" s="992"/>
-      <c r="Y8" s="990">
+      <c r="W8" s="994"/>
+      <c r="X8" s="995"/>
+      <c r="Y8" s="993">
         <v>467</v>
       </c>
-      <c r="Z8" s="991"/>
-      <c r="AA8" s="992"/>
-      <c r="AB8" s="990">
+      <c r="Z8" s="994"/>
+      <c r="AA8" s="995"/>
+      <c r="AB8" s="993">
         <v>5</v>
       </c>
-      <c r="AC8" s="991"/>
-      <c r="AD8" s="992"/>
-      <c r="AE8" s="990">
+      <c r="AC8" s="994"/>
+      <c r="AD8" s="995"/>
+      <c r="AE8" s="993">
         <v>56</v>
       </c>
-      <c r="AF8" s="991"/>
-      <c r="AG8" s="992"/>
-      <c r="AH8" s="990">
+      <c r="AF8" s="994"/>
+      <c r="AG8" s="995"/>
+      <c r="AH8" s="993">
         <v>57</v>
       </c>
-      <c r="AI8" s="991"/>
-      <c r="AJ8" s="992"/>
-      <c r="AK8" s="990">
+      <c r="AI8" s="994"/>
+      <c r="AJ8" s="995"/>
+      <c r="AK8" s="993">
         <v>6</v>
       </c>
-      <c r="AL8" s="991"/>
-      <c r="AM8" s="992"/>
-      <c r="AN8" s="990">
+      <c r="AL8" s="994"/>
+      <c r="AM8" s="995"/>
+      <c r="AN8" s="993">
         <v>67</v>
       </c>
-      <c r="AO8" s="991"/>
-      <c r="AP8" s="992"/>
-      <c r="AQ8" s="990">
+      <c r="AO8" s="994"/>
+      <c r="AP8" s="995"/>
+      <c r="AQ8" s="993">
         <v>7</v>
       </c>
-      <c r="AR8" s="991"/>
-      <c r="AS8" s="992"/>
-      <c r="AT8" s="990">
+      <c r="AR8" s="994"/>
+      <c r="AS8" s="995"/>
+      <c r="AT8" s="993">
         <v>8</v>
       </c>
-      <c r="AU8" s="991"/>
-      <c r="AV8" s="992"/>
-    </row>
-    <row r="9" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AU8" s="994"/>
+      <c r="AV8" s="995"/>
+    </row>
+    <row r="9" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="987"/>
-      <c r="E9" s="988"/>
-      <c r="F9" s="989"/>
+      <c r="D9" s="984"/>
+      <c r="E9" s="985"/>
+      <c r="F9" s="986"/>
       <c r="H9" s="32" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="990" t="s">
+      <c r="J9" s="993" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="991"/>
-      <c r="L9" s="992"/>
-      <c r="M9" s="990" t="s">
+      <c r="K9" s="994"/>
+      <c r="L9" s="995"/>
+      <c r="M9" s="993" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="991"/>
-      <c r="O9" s="992"/>
-      <c r="P9" s="990" t="s">
+      <c r="N9" s="994"/>
+      <c r="O9" s="995"/>
+      <c r="P9" s="993" t="s">
         <v>53</v>
       </c>
-      <c r="Q9" s="991"/>
-      <c r="R9" s="992"/>
-      <c r="S9" s="990" t="s">
+      <c r="Q9" s="994"/>
+      <c r="R9" s="995"/>
+      <c r="S9" s="993" t="s">
         <v>54</v>
       </c>
-      <c r="T9" s="991"/>
-      <c r="U9" s="992"/>
-      <c r="V9" s="990" t="s">
+      <c r="T9" s="994"/>
+      <c r="U9" s="995"/>
+      <c r="V9" s="993" t="s">
         <v>55</v>
       </c>
-      <c r="W9" s="991"/>
-      <c r="X9" s="992"/>
-      <c r="Y9" s="990" t="s">
+      <c r="W9" s="994"/>
+      <c r="X9" s="995"/>
+      <c r="Y9" s="993" t="s">
         <v>56</v>
       </c>
-      <c r="Z9" s="991"/>
-      <c r="AA9" s="992"/>
-      <c r="AB9" s="990" t="s">
+      <c r="Z9" s="994"/>
+      <c r="AA9" s="995"/>
+      <c r="AB9" s="993" t="s">
         <v>57</v>
       </c>
-      <c r="AC9" s="991"/>
-      <c r="AD9" s="992"/>
-      <c r="AE9" s="990" t="s">
+      <c r="AC9" s="994"/>
+      <c r="AD9" s="995"/>
+      <c r="AE9" s="993" t="s">
         <v>58</v>
       </c>
-      <c r="AF9" s="991"/>
-      <c r="AG9" s="992"/>
-      <c r="AH9" s="990" t="s">
+      <c r="AF9" s="994"/>
+      <c r="AG9" s="995"/>
+      <c r="AH9" s="993" t="s">
         <v>59</v>
       </c>
-      <c r="AI9" s="991"/>
-      <c r="AJ9" s="992"/>
-      <c r="AK9" s="990" t="s">
+      <c r="AI9" s="994"/>
+      <c r="AJ9" s="995"/>
+      <c r="AK9" s="993" t="s">
         <v>60</v>
       </c>
-      <c r="AL9" s="991"/>
-      <c r="AM9" s="992"/>
-      <c r="AN9" s="990" t="s">
+      <c r="AL9" s="994"/>
+      <c r="AM9" s="995"/>
+      <c r="AN9" s="993" t="s">
         <v>61</v>
       </c>
-      <c r="AO9" s="991"/>
-      <c r="AP9" s="992"/>
-      <c r="AQ9" s="990" t="s">
+      <c r="AO9" s="994"/>
+      <c r="AP9" s="995"/>
+      <c r="AQ9" s="993" t="s">
         <v>62</v>
       </c>
-      <c r="AR9" s="991"/>
-      <c r="AS9" s="992"/>
-      <c r="AT9" s="990" t="s">
+      <c r="AR9" s="994"/>
+      <c r="AS9" s="995"/>
+      <c r="AT9" s="993" t="s">
         <v>63</v>
       </c>
-      <c r="AU9" s="991"/>
-      <c r="AV9" s="992"/>
+      <c r="AU9" s="994"/>
+      <c r="AV9" s="995"/>
     </row>
     <row r="10" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="33" t="s">
@@ -33268,7 +33265,7 @@
         <v>19.05</v>
       </c>
     </row>
-    <row r="17" spans="3:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="47"/>
       <c r="D17" s="48"/>
       <c r="E17" s="49"/>
@@ -33361,7 +33358,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="18" spans="3:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="47"/>
       <c r="D18" s="51"/>
       <c r="E18" s="52"/>
@@ -33841,11 +33838,11 @@
       <c r="I25" s="60">
         <v>0.75</v>
       </c>
-      <c r="J25" s="981" t="s">
+      <c r="J25" s="978" t="s">
         <v>46</v>
       </c>
-      <c r="K25" s="982"/>
-      <c r="L25" s="983"/>
+      <c r="K25" s="979"/>
+      <c r="L25" s="980"/>
       <c r="Q25" s="25"/>
       <c r="R25" s="25"/>
       <c r="S25" s="25"/>
@@ -33870,16 +33867,16 @@
       <c r="I26" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="J26" s="984"/>
-      <c r="K26" s="985"/>
-      <c r="L26" s="986"/>
+      <c r="J26" s="981"/>
+      <c r="K26" s="982"/>
+      <c r="L26" s="983"/>
       <c r="Q26" s="25"/>
       <c r="R26" s="25"/>
-      <c r="S26" s="1003" t="s">
+      <c r="S26" s="987" t="s">
         <v>43</v>
       </c>
-      <c r="T26" s="1004"/>
-      <c r="U26" s="1005"/>
+      <c r="T26" s="988"/>
+      <c r="U26" s="989"/>
       <c r="AI26" s="73">
         <v>1.5</v>
       </c>
@@ -33903,9 +33900,9 @@
         <f>H27*2.54*10</f>
         <v>25.4</v>
       </c>
-      <c r="J27" s="987"/>
-      <c r="K27" s="988"/>
-      <c r="L27" s="989"/>
+      <c r="J27" s="984"/>
+      <c r="K27" s="985"/>
+      <c r="L27" s="986"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25"/>
       <c r="S27" s="42"/>
@@ -34073,11 +34070,11 @@
       <c r="U32" s="54"/>
     </row>
     <row r="33" spans="3:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="976"/>
-      <c r="D33" s="976"/>
-      <c r="E33" s="976"/>
-      <c r="F33" s="976"/>
-      <c r="G33" s="976"/>
+      <c r="C33" s="999"/>
+      <c r="D33" s="999"/>
+      <c r="E33" s="999"/>
+      <c r="F33" s="999"/>
+      <c r="G33" s="999"/>
       <c r="H33" s="54"/>
       <c r="I33" s="54"/>
       <c r="J33" s="54"/>
@@ -34105,6 +34102,36 @@
     <row r="35" spans="3:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="D7:F9"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="AB9:AD9"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="S8:U8"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="AT8:AV8"/>
+    <mergeCell ref="AT9:AV9"/>
+    <mergeCell ref="AN8:AP8"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="AB7:AD7"/>
+    <mergeCell ref="AE7:AG7"/>
+    <mergeCell ref="AK7:AM7"/>
+    <mergeCell ref="AE8:AG8"/>
+    <mergeCell ref="AE9:AG9"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="AK8:AM8"/>
+    <mergeCell ref="AK9:AM9"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="H6:AS6"/>
     <mergeCell ref="H5:AS5"/>
@@ -34121,36 +34148,6 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AB8:AD8"/>
-    <mergeCell ref="AT8:AV8"/>
-    <mergeCell ref="AT9:AV9"/>
-    <mergeCell ref="AN8:AP8"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="V7:X7"/>
-    <mergeCell ref="AB7:AD7"/>
-    <mergeCell ref="AE7:AG7"/>
-    <mergeCell ref="AK7:AM7"/>
-    <mergeCell ref="AE8:AG8"/>
-    <mergeCell ref="AE9:AG9"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="AK8:AM8"/>
-    <mergeCell ref="AK9:AM9"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="AB9:AD9"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="P9:R9"/>
-    <mergeCell ref="S8:U8"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="D7:F9"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -34162,20 +34159,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8970878-9EC1-4D80-A674-4904E367EFB9}">
   <dimension ref="A1:AC69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="314" customWidth="1"/>
-    <col min="2" max="2" width="2.28515625" style="314" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="314" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" style="314" customWidth="1"/>
-    <col min="6" max="8" width="13.7109375" style="314" customWidth="1"/>
-    <col min="9" max="9" width="1.85546875" style="314" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" style="314" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" style="314" customWidth="1"/>
+    <col min="2" max="2" width="2.33203125" style="314" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" style="314" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" style="314" customWidth="1"/>
+    <col min="6" max="8" width="13.6640625" style="314" customWidth="1"/>
+    <col min="9" max="9" width="1.88671875" style="314" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" style="314" customWidth="1"/>
     <col min="11" max="11" width="10" style="314" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" style="314" customWidth="1"/>
+    <col min="12" max="12" width="6.88671875" style="314" customWidth="1"/>
     <col min="13" max="13" width="7" style="314" customWidth="1"/>
-    <col min="14" max="26" width="13.28515625" style="314" customWidth="1"/>
-    <col min="27" max="16384" width="10.28515625" style="314"/>
+    <col min="14" max="26" width="13.33203125" style="314" customWidth="1"/>
+    <col min="27" max="16384" width="10.33203125" style="314"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -34259,39 +34256,39 @@
       <c r="Z5" s="315"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="835" t="s">
+      <c r="A6" s="850" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="835"/>
-      <c r="C6" s="835"/>
-      <c r="D6" s="835"/>
-      <c r="E6" s="835"/>
-      <c r="F6" s="835"/>
-      <c r="G6" s="835"/>
-      <c r="H6" s="835"/>
-      <c r="I6" s="835"/>
-      <c r="J6" s="835"/>
-      <c r="K6" s="835"/>
-      <c r="L6" s="835"/>
-      <c r="M6" s="835"/>
+      <c r="B6" s="850"/>
+      <c r="C6" s="850"/>
+      <c r="D6" s="850"/>
+      <c r="E6" s="850"/>
+      <c r="F6" s="850"/>
+      <c r="G6" s="850"/>
+      <c r="H6" s="850"/>
+      <c r="I6" s="850"/>
+      <c r="J6" s="850"/>
+      <c r="K6" s="850"/>
+      <c r="L6" s="850"/>
+      <c r="M6" s="850"/>
       <c r="Z6" s="315"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="836">
+      <c r="A7" s="851">
         <v>1</v>
       </c>
-      <c r="B7" s="836"/>
-      <c r="C7" s="836"/>
-      <c r="D7" s="836"/>
-      <c r="E7" s="836"/>
-      <c r="F7" s="836"/>
-      <c r="G7" s="836"/>
-      <c r="H7" s="836"/>
-      <c r="I7" s="836"/>
-      <c r="J7" s="836"/>
-      <c r="K7" s="836"/>
-      <c r="L7" s="836"/>
-      <c r="M7" s="836"/>
+      <c r="B7" s="851"/>
+      <c r="C7" s="851"/>
+      <c r="D7" s="851"/>
+      <c r="E7" s="851"/>
+      <c r="F7" s="851"/>
+      <c r="G7" s="851"/>
+      <c r="H7" s="851"/>
+      <c r="I7" s="851"/>
+      <c r="J7" s="851"/>
+      <c r="K7" s="851"/>
+      <c r="L7" s="851"/>
+      <c r="M7" s="851"/>
     </row>
     <row r="8" spans="1:26" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34334,10 +34331,10 @@
       <c r="K10" s="285" t="s">
         <v>357</v>
       </c>
-      <c r="L10" s="837">
+      <c r="L10" s="852">
         <v>1</v>
       </c>
-      <c r="M10" s="837"/>
+      <c r="M10" s="852"/>
       <c r="N10" s="320"/>
       <c r="O10" s="320"/>
       <c r="P10" s="320"/>
@@ -34369,8 +34366,8 @@
       <c r="K11" s="285" t="s">
         <v>127</v>
       </c>
-      <c r="L11" s="838"/>
-      <c r="M11" s="838"/>
+      <c r="L11" s="848"/>
+      <c r="M11" s="848"/>
       <c r="N11" s="320"/>
       <c r="O11" s="320"/>
       <c r="P11" s="320"/>
@@ -34444,21 +34441,21 @@
       <c r="Y13" s="320"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="848" t="s">
+      <c r="A14" s="836" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="849"/>
-      <c r="C14" s="849"/>
-      <c r="D14" s="849"/>
-      <c r="E14" s="849"/>
-      <c r="F14" s="849"/>
-      <c r="G14" s="849"/>
-      <c r="H14" s="849"/>
-      <c r="I14" s="849"/>
-      <c r="J14" s="849"/>
-      <c r="K14" s="849"/>
-      <c r="L14" s="849"/>
-      <c r="M14" s="850"/>
+      <c r="B14" s="837"/>
+      <c r="C14" s="837"/>
+      <c r="D14" s="837"/>
+      <c r="E14" s="837"/>
+      <c r="F14" s="837"/>
+      <c r="G14" s="837"/>
+      <c r="H14" s="837"/>
+      <c r="I14" s="837"/>
+      <c r="J14" s="837"/>
+      <c r="K14" s="837"/>
+      <c r="L14" s="837"/>
+      <c r="M14" s="838"/>
       <c r="N14" s="320"/>
       <c r="O14" s="320"/>
       <c r="P14" s="320"/>
@@ -34473,21 +34470,21 @@
       <c r="Y14" s="320"/>
     </row>
     <row r="15" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="851" t="s">
+      <c r="A15" s="839" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="852"/>
-      <c r="C15" s="852"/>
-      <c r="D15" s="852"/>
-      <c r="E15" s="852"/>
-      <c r="F15" s="852"/>
-      <c r="G15" s="852"/>
-      <c r="H15" s="852"/>
-      <c r="I15" s="852"/>
-      <c r="J15" s="852"/>
-      <c r="K15" s="852"/>
-      <c r="L15" s="852"/>
-      <c r="M15" s="853"/>
+      <c r="B15" s="840"/>
+      <c r="C15" s="840"/>
+      <c r="D15" s="840"/>
+      <c r="E15" s="840"/>
+      <c r="F15" s="840"/>
+      <c r="G15" s="840"/>
+      <c r="H15" s="840"/>
+      <c r="I15" s="840"/>
+      <c r="J15" s="840"/>
+      <c r="K15" s="840"/>
+      <c r="L15" s="840"/>
+      <c r="M15" s="841"/>
       <c r="N15" s="320"/>
       <c r="O15" s="320"/>
       <c r="P15" s="320"/>
@@ -34562,10 +34559,10 @@
       <c r="K18" s="285" t="s">
         <v>153</v>
       </c>
-      <c r="L18" s="858">
+      <c r="L18" s="846">
         <v>1</v>
       </c>
-      <c r="M18" s="859"/>
+      <c r="M18" s="847"/>
       <c r="Y18" s="320"/>
     </row>
     <row r="19" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34584,8 +34581,8 @@
       <c r="K19" s="285" t="s">
         <v>125</v>
       </c>
-      <c r="L19" s="838"/>
-      <c r="M19" s="860"/>
+      <c r="L19" s="848"/>
+      <c r="M19" s="849"/>
       <c r="Y19" s="320"/>
     </row>
     <row r="20" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34604,8 +34601,8 @@
       <c r="K20" s="285" t="s">
         <v>126</v>
       </c>
-      <c r="L20" s="838"/>
-      <c r="M20" s="860"/>
+      <c r="L20" s="848"/>
+      <c r="M20" s="849"/>
       <c r="Y20" s="320"/>
     </row>
     <row r="21" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34628,7 +34625,7 @@
       <c r="M21" s="330"/>
       <c r="Y21" s="320"/>
     </row>
-    <row r="22" spans="1:29" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="353"/>
       <c r="B22" s="354"/>
       <c r="C22" s="354"/>
@@ -34660,24 +34657,24 @@
       <c r="A23" s="356"/>
       <c r="B23" s="364"/>
       <c r="C23" s="364"/>
-      <c r="D23" s="854" t="s">
+      <c r="D23" s="842" t="s">
         <v>354</v>
       </c>
-      <c r="E23" s="855"/>
-      <c r="F23" s="845" t="s">
+      <c r="E23" s="843"/>
+      <c r="F23" s="834" t="s">
         <v>277</v>
       </c>
-      <c r="G23" s="845" t="s">
+      <c r="G23" s="834" t="s">
         <v>347</v>
       </c>
-      <c r="H23" s="845" t="s">
+      <c r="H23" s="834" t="s">
         <v>276</v>
       </c>
       <c r="I23" s="337"/>
-      <c r="J23" s="840" t="s">
+      <c r="J23" s="854" t="s">
         <v>146</v>
       </c>
-      <c r="K23" s="841"/>
+      <c r="K23" s="855"/>
       <c r="L23" s="497"/>
       <c r="M23" s="357"/>
       <c r="N23" s="320"/>
@@ -34692,11 +34689,11 @@
       <c r="W23" s="320"/>
       <c r="X23" s="320"/>
       <c r="Y23" s="332"/>
-      <c r="AA23" s="856" t="s">
+      <c r="AA23" s="844" t="s">
         <v>279</v>
       </c>
-      <c r="AB23" s="857"/>
-      <c r="AC23" s="845" t="s">
+      <c r="AB23" s="845"/>
+      <c r="AC23" s="834" t="s">
         <v>276</v>
       </c>
     </row>
@@ -34710,12 +34707,12 @@
       <c r="E24" s="500" t="s">
         <v>381</v>
       </c>
-      <c r="F24" s="846"/>
-      <c r="G24" s="846"/>
-      <c r="H24" s="846"/>
+      <c r="F24" s="835"/>
+      <c r="G24" s="835"/>
+      <c r="H24" s="835"/>
       <c r="I24" s="337"/>
-      <c r="J24" s="842"/>
-      <c r="K24" s="843"/>
+      <c r="J24" s="856"/>
+      <c r="K24" s="857"/>
       <c r="L24" s="497"/>
       <c r="M24" s="358"/>
       <c r="N24" s="320"/>
@@ -34736,7 +34733,7 @@
       <c r="AB24" s="380" t="s">
         <v>12</v>
       </c>
-      <c r="AC24" s="846"/>
+      <c r="AC24" s="835"/>
     </row>
     <row r="25" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="356"/>
@@ -35144,7 +35141,7 @@
       <c r="J32" s="298"/>
       <c r="K32" s="298"/>
       <c r="L32" s="298"/>
-      <c r="M32" s="847"/>
+      <c r="M32" s="859"/>
       <c r="N32" s="320"/>
       <c r="O32" s="320"/>
       <c r="P32" s="320"/>
@@ -35194,7 +35191,7 @@
       <c r="J33" s="298"/>
       <c r="K33" s="298"/>
       <c r="L33" s="298"/>
-      <c r="M33" s="847"/>
+      <c r="M33" s="859"/>
       <c r="N33" s="320"/>
       <c r="O33" s="320"/>
       <c r="P33" s="320"/>
@@ -36056,21 +36053,21 @@
       <c r="Z59" s="480"/>
     </row>
     <row r="60" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="844" t="s">
+      <c r="A60" s="858" t="s">
         <v>297</v>
       </c>
-      <c r="B60" s="844"/>
-      <c r="C60" s="844"/>
-      <c r="D60" s="844"/>
-      <c r="E60" s="844"/>
-      <c r="F60" s="844"/>
-      <c r="G60" s="844"/>
-      <c r="H60" s="844"/>
-      <c r="I60" s="844"/>
-      <c r="J60" s="844"/>
-      <c r="K60" s="844"/>
-      <c r="L60" s="844"/>
-      <c r="M60" s="844"/>
+      <c r="B60" s="858"/>
+      <c r="C60" s="858"/>
+      <c r="D60" s="858"/>
+      <c r="E60" s="858"/>
+      <c r="F60" s="858"/>
+      <c r="G60" s="858"/>
+      <c r="H60" s="858"/>
+      <c r="I60" s="858"/>
+      <c r="J60" s="858"/>
+      <c r="K60" s="858"/>
+      <c r="L60" s="858"/>
+      <c r="M60" s="858"/>
       <c r="N60" s="483"/>
       <c r="O60" s="483"/>
       <c r="P60" s="483"/>
@@ -36116,21 +36113,21 @@
       <c r="Z61" s="480"/>
     </row>
     <row r="62" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="844" t="s">
+      <c r="A62" s="858" t="s">
         <v>356</v>
       </c>
-      <c r="B62" s="844"/>
-      <c r="C62" s="844"/>
-      <c r="D62" s="844"/>
-      <c r="E62" s="844"/>
-      <c r="F62" s="844"/>
-      <c r="G62" s="844"/>
-      <c r="H62" s="844"/>
-      <c r="I62" s="844"/>
-      <c r="J62" s="844"/>
-      <c r="K62" s="844"/>
-      <c r="L62" s="844"/>
-      <c r="M62" s="844"/>
+      <c r="B62" s="858"/>
+      <c r="C62" s="858"/>
+      <c r="D62" s="858"/>
+      <c r="E62" s="858"/>
+      <c r="F62" s="858"/>
+      <c r="G62" s="858"/>
+      <c r="H62" s="858"/>
+      <c r="I62" s="858"/>
+      <c r="J62" s="858"/>
+      <c r="K62" s="858"/>
+      <c r="L62" s="858"/>
+      <c r="M62" s="858"/>
       <c r="N62" s="319"/>
       <c r="O62" s="319"/>
       <c r="P62" s="319"/>
@@ -36201,12 +36198,12 @@
       <c r="Z64" s="482"/>
     </row>
     <row r="65" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="839" t="s">
+      <c r="A65" s="853" t="s">
         <v>363</v>
       </c>
-      <c r="B65" s="839"/>
-      <c r="C65" s="839"/>
-      <c r="D65" s="839"/>
+      <c r="B65" s="853"/>
+      <c r="C65" s="853"/>
+      <c r="D65" s="853"/>
       <c r="E65" s="337"/>
       <c r="F65" s="337"/>
       <c r="G65" s="337"/>
@@ -36288,15 +36285,6 @@
     <protectedRange sqref="D9:D10" name="Rango3_3_1_1_1_1_1_2_1_1_1"/>
   </protectedRanges>
   <mergeCells count="20">
-    <mergeCell ref="AC23:AC24"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A7:M7"/>
     <mergeCell ref="L10:M10"/>
@@ -36308,6 +36296,15 @@
     <mergeCell ref="H23:H24"/>
     <mergeCell ref="A62:M62"/>
     <mergeCell ref="M32:M33"/>
+    <mergeCell ref="AC23:AC24"/>
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -36324,19 +36321,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83178C66-EA7A-4253-9722-9A41637B80DE}">
   <dimension ref="A1:AB69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="314" customWidth="1"/>
-    <col min="2" max="2" width="2.28515625" style="314" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="314" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" style="314" customWidth="1"/>
-    <col min="6" max="8" width="13.7109375" style="314" customWidth="1"/>
-    <col min="9" max="9" width="1.85546875" style="314" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" style="314" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" style="314" customWidth="1"/>
+    <col min="2" max="2" width="2.33203125" style="314" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" style="314" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" style="314" customWidth="1"/>
+    <col min="6" max="8" width="13.6640625" style="314" customWidth="1"/>
+    <col min="9" max="9" width="1.88671875" style="314" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" style="314" customWidth="1"/>
     <col min="11" max="11" width="10" style="314" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" style="314" customWidth="1"/>
-    <col min="13" max="25" width="13.28515625" style="314" customWidth="1"/>
-    <col min="26" max="16384" width="10.28515625" style="314"/>
+    <col min="12" max="12" width="12.33203125" style="314" customWidth="1"/>
+    <col min="13" max="25" width="13.33203125" style="314" customWidth="1"/>
+    <col min="26" max="16384" width="10.33203125" style="314"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -36415,37 +36412,37 @@
       <c r="Y5" s="315"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="835" t="s">
+      <c r="A6" s="850" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="835"/>
-      <c r="C6" s="835"/>
-      <c r="D6" s="835"/>
-      <c r="E6" s="835"/>
-      <c r="F6" s="835"/>
-      <c r="G6" s="835"/>
-      <c r="H6" s="835"/>
-      <c r="I6" s="835"/>
-      <c r="J6" s="835"/>
-      <c r="K6" s="835"/>
-      <c r="L6" s="835"/>
+      <c r="B6" s="850"/>
+      <c r="C6" s="850"/>
+      <c r="D6" s="850"/>
+      <c r="E6" s="850"/>
+      <c r="F6" s="850"/>
+      <c r="G6" s="850"/>
+      <c r="H6" s="850"/>
+      <c r="I6" s="850"/>
+      <c r="J6" s="850"/>
+      <c r="K6" s="850"/>
+      <c r="L6" s="850"/>
       <c r="Y6" s="315"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="861">
+      <c r="A7" s="868">
         <v>1</v>
       </c>
-      <c r="B7" s="861"/>
-      <c r="C7" s="861"/>
-      <c r="D7" s="861"/>
-      <c r="E7" s="861"/>
-      <c r="F7" s="861"/>
-      <c r="G7" s="861"/>
-      <c r="H7" s="861"/>
-      <c r="I7" s="861"/>
-      <c r="J7" s="861"/>
-      <c r="K7" s="861"/>
-      <c r="L7" s="861"/>
+      <c r="B7" s="868"/>
+      <c r="C7" s="868"/>
+      <c r="D7" s="868"/>
+      <c r="E7" s="868"/>
+      <c r="F7" s="868"/>
+      <c r="G7" s="868"/>
+      <c r="H7" s="868"/>
+      <c r="I7" s="868"/>
+      <c r="J7" s="868"/>
+      <c r="K7" s="868"/>
+      <c r="L7" s="868"/>
     </row>
     <row r="8" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36616,20 +36613,20 @@
       <c r="X13" s="320"/>
     </row>
     <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="848" t="s">
+      <c r="A14" s="836" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="849"/>
-      <c r="C14" s="849"/>
-      <c r="D14" s="849"/>
-      <c r="E14" s="849"/>
-      <c r="F14" s="849"/>
-      <c r="G14" s="849"/>
-      <c r="H14" s="849"/>
-      <c r="I14" s="849"/>
-      <c r="J14" s="849"/>
-      <c r="K14" s="849"/>
-      <c r="L14" s="850"/>
+      <c r="B14" s="837"/>
+      <c r="C14" s="837"/>
+      <c r="D14" s="837"/>
+      <c r="E14" s="837"/>
+      <c r="F14" s="837"/>
+      <c r="G14" s="837"/>
+      <c r="H14" s="837"/>
+      <c r="I14" s="837"/>
+      <c r="J14" s="837"/>
+      <c r="K14" s="837"/>
+      <c r="L14" s="838"/>
       <c r="M14" s="320"/>
       <c r="N14" s="320"/>
       <c r="O14" s="320"/>
@@ -36644,20 +36641,20 @@
       <c r="X14" s="320"/>
     </row>
     <row r="15" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="851" t="s">
+      <c r="A15" s="839" t="s">
         <v>467</v>
       </c>
-      <c r="B15" s="852"/>
-      <c r="C15" s="852"/>
-      <c r="D15" s="852"/>
-      <c r="E15" s="852"/>
-      <c r="F15" s="852"/>
-      <c r="G15" s="852"/>
-      <c r="H15" s="852"/>
-      <c r="I15" s="852"/>
-      <c r="J15" s="852"/>
-      <c r="K15" s="852"/>
-      <c r="L15" s="853"/>
+      <c r="B15" s="840"/>
+      <c r="C15" s="840"/>
+      <c r="D15" s="840"/>
+      <c r="E15" s="840"/>
+      <c r="F15" s="840"/>
+      <c r="G15" s="840"/>
+      <c r="H15" s="840"/>
+      <c r="I15" s="840"/>
+      <c r="J15" s="840"/>
+      <c r="K15" s="840"/>
+      <c r="L15" s="841"/>
       <c r="M15" s="320"/>
       <c r="N15" s="320"/>
       <c r="O15" s="320"/>
@@ -36812,7 +36809,7 @@
       <c r="L21" s="369"/>
       <c r="X21" s="320"/>
     </row>
-    <row r="22" spans="1:28" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="353"/>
       <c r="B22" s="354"/>
       <c r="C22" s="354"/>
@@ -36843,30 +36840,30 @@
       <c r="A23" s="356"/>
       <c r="B23" s="364"/>
       <c r="C23" s="364"/>
-      <c r="D23" s="854" t="s">
+      <c r="D23" s="842" t="s">
         <v>354</v>
       </c>
-      <c r="E23" s="855"/>
-      <c r="F23" s="845" t="s">
+      <c r="E23" s="843"/>
+      <c r="F23" s="834" t="s">
         <v>277</v>
       </c>
-      <c r="G23" s="845" t="s">
+      <c r="G23" s="834" t="s">
         <v>347</v>
       </c>
-      <c r="H23" s="845" t="s">
+      <c r="H23" s="834" t="s">
         <v>276</v>
       </c>
       <c r="I23" s="337"/>
-      <c r="J23" s="840" t="s">
+      <c r="J23" s="854" t="s">
         <v>146</v>
       </c>
-      <c r="K23" s="841"/>
+      <c r="K23" s="855"/>
       <c r="L23" s="652"/>
       <c r="M23" s="320"/>
-      <c r="N23" s="840" t="s">
+      <c r="N23" s="854" t="s">
         <v>146</v>
       </c>
-      <c r="O23" s="841"/>
+      <c r="O23" s="855"/>
       <c r="P23" s="320"/>
       <c r="Q23" s="320"/>
       <c r="R23" s="320"/>
@@ -36876,11 +36873,11 @@
       <c r="V23" s="320"/>
       <c r="W23" s="320"/>
       <c r="X23" s="332"/>
-      <c r="Z23" s="856" t="s">
+      <c r="Z23" s="844" t="s">
         <v>279</v>
       </c>
-      <c r="AA23" s="857"/>
-      <c r="AB23" s="845" t="s">
+      <c r="AA23" s="845"/>
+      <c r="AB23" s="834" t="s">
         <v>276</v>
       </c>
     </row>
@@ -36894,16 +36891,16 @@
       <c r="E24" s="500" t="s">
         <v>381</v>
       </c>
-      <c r="F24" s="846"/>
-      <c r="G24" s="846"/>
-      <c r="H24" s="846"/>
+      <c r="F24" s="835"/>
+      <c r="G24" s="835"/>
+      <c r="H24" s="835"/>
       <c r="I24" s="337"/>
-      <c r="J24" s="842"/>
-      <c r="K24" s="843"/>
+      <c r="J24" s="856"/>
+      <c r="K24" s="857"/>
       <c r="L24" s="652"/>
       <c r="M24" s="320"/>
-      <c r="N24" s="842"/>
-      <c r="O24" s="843"/>
+      <c r="N24" s="856"/>
+      <c r="O24" s="857"/>
       <c r="P24" s="320"/>
       <c r="Q24" s="320"/>
       <c r="R24" s="320"/>
@@ -36919,7 +36916,7 @@
       <c r="AA24" s="380" t="s">
         <v>12</v>
       </c>
-      <c r="AB24" s="846"/>
+      <c r="AB24" s="835"/>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="356"/>
@@ -36944,10 +36941,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I25" s="337"/>
-      <c r="J25" s="863" t="s">
+      <c r="J25" s="861" t="s">
         <v>382</v>
       </c>
-      <c r="K25" s="866" t="e">
+      <c r="K25" s="864" t="e">
         <f>+datos!I21</f>
         <v>#DIV/0!</v>
       </c>
@@ -37003,8 +37000,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I26" s="337"/>
-      <c r="J26" s="864"/>
-      <c r="K26" s="867"/>
+      <c r="J26" s="862"/>
+      <c r="K26" s="865"/>
       <c r="L26" s="653"/>
       <c r="M26" s="320"/>
       <c r="N26" s="360" t="s">
@@ -37057,8 +37054,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="337"/>
-      <c r="J27" s="865"/>
-      <c r="K27" s="868"/>
+      <c r="J27" s="863"/>
+      <c r="K27" s="866"/>
       <c r="L27" s="649"/>
       <c r="M27" s="320"/>
       <c r="N27" s="360" t="s">
@@ -38158,37 +38155,37 @@
       <c r="Y57" s="386"/>
     </row>
     <row r="58" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="869" t="s">
+      <c r="A58" s="867" t="s">
         <v>468</v>
       </c>
-      <c r="B58" s="869"/>
-      <c r="C58" s="869"/>
-      <c r="D58" s="869"/>
-      <c r="E58" s="869"/>
-      <c r="F58" s="869"/>
-      <c r="G58" s="869"/>
-      <c r="H58" s="869"/>
-      <c r="I58" s="869"/>
-      <c r="J58" s="869"/>
-      <c r="K58" s="869"/>
-      <c r="L58" s="869"/>
+      <c r="B58" s="867"/>
+      <c r="C58" s="867"/>
+      <c r="D58" s="867"/>
+      <c r="E58" s="867"/>
+      <c r="F58" s="867"/>
+      <c r="G58" s="867"/>
+      <c r="H58" s="867"/>
+      <c r="I58" s="867"/>
+      <c r="J58" s="867"/>
+      <c r="K58" s="867"/>
+      <c r="L58" s="867"/>
       <c r="Y58" s="386"/>
     </row>
-    <row r="59" spans="1:25" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="862" t="s">
+    <row r="59" spans="1:25" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="860" t="s">
         <v>469</v>
       </c>
-      <c r="B59" s="862"/>
-      <c r="C59" s="862"/>
-      <c r="D59" s="862"/>
-      <c r="E59" s="862"/>
-      <c r="F59" s="862"/>
-      <c r="G59" s="862"/>
-      <c r="H59" s="862"/>
-      <c r="I59" s="862"/>
-      <c r="J59" s="862"/>
-      <c r="K59" s="862"/>
-      <c r="L59" s="862"/>
+      <c r="B59" s="860"/>
+      <c r="C59" s="860"/>
+      <c r="D59" s="860"/>
+      <c r="E59" s="860"/>
+      <c r="F59" s="860"/>
+      <c r="G59" s="860"/>
+      <c r="H59" s="860"/>
+      <c r="I59" s="860"/>
+      <c r="J59" s="860"/>
+      <c r="K59" s="860"/>
+      <c r="L59" s="860"/>
       <c r="M59" s="319"/>
       <c r="N59" s="319"/>
       <c r="O59" s="319"/>
@@ -38204,20 +38201,20 @@
       <c r="Y59" s="480"/>
     </row>
     <row r="60" spans="1:25" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="862" t="s">
+      <c r="A60" s="860" t="s">
         <v>470</v>
       </c>
-      <c r="B60" s="862"/>
-      <c r="C60" s="862"/>
-      <c r="D60" s="862"/>
-      <c r="E60" s="862"/>
-      <c r="F60" s="862"/>
-      <c r="G60" s="862"/>
-      <c r="H60" s="862"/>
-      <c r="I60" s="862"/>
-      <c r="J60" s="862"/>
-      <c r="K60" s="862"/>
-      <c r="L60" s="862"/>
+      <c r="B60" s="860"/>
+      <c r="C60" s="860"/>
+      <c r="D60" s="860"/>
+      <c r="E60" s="860"/>
+      <c r="F60" s="860"/>
+      <c r="G60" s="860"/>
+      <c r="H60" s="860"/>
+      <c r="I60" s="860"/>
+      <c r="J60" s="860"/>
+      <c r="K60" s="860"/>
+      <c r="L60" s="860"/>
       <c r="M60" s="483"/>
       <c r="N60" s="483"/>
       <c r="O60" s="483"/>
@@ -38232,21 +38229,21 @@
       <c r="X60" s="483"/>
       <c r="Y60" s="483"/>
     </row>
-    <row r="61" spans="1:25" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="862" t="s">
+    <row r="61" spans="1:25" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="860" t="s">
         <v>471</v>
       </c>
-      <c r="B61" s="862"/>
-      <c r="C61" s="862"/>
-      <c r="D61" s="862"/>
-      <c r="E61" s="862"/>
-      <c r="F61" s="862"/>
-      <c r="G61" s="862"/>
-      <c r="H61" s="862"/>
-      <c r="I61" s="862"/>
-      <c r="J61" s="862"/>
-      <c r="K61" s="862"/>
-      <c r="L61" s="862"/>
+      <c r="B61" s="860"/>
+      <c r="C61" s="860"/>
+      <c r="D61" s="860"/>
+      <c r="E61" s="860"/>
+      <c r="F61" s="860"/>
+      <c r="G61" s="860"/>
+      <c r="H61" s="860"/>
+      <c r="I61" s="860"/>
+      <c r="J61" s="860"/>
+      <c r="K61" s="860"/>
+      <c r="L61" s="860"/>
       <c r="M61" s="319"/>
       <c r="N61" s="319"/>
       <c r="O61" s="319"/>
@@ -38261,21 +38258,21 @@
       <c r="X61" s="480"/>
       <c r="Y61" s="480"/>
     </row>
-    <row r="62" spans="1:25" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="844" t="s">
+    <row r="62" spans="1:25" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="858" t="s">
         <v>472</v>
       </c>
-      <c r="B62" s="844"/>
-      <c r="C62" s="844"/>
-      <c r="D62" s="844"/>
-      <c r="E62" s="844"/>
-      <c r="F62" s="844"/>
-      <c r="G62" s="844"/>
-      <c r="H62" s="844"/>
-      <c r="I62" s="844"/>
-      <c r="J62" s="844"/>
-      <c r="K62" s="844"/>
-      <c r="L62" s="844"/>
+      <c r="B62" s="858"/>
+      <c r="C62" s="858"/>
+      <c r="D62" s="858"/>
+      <c r="E62" s="858"/>
+      <c r="F62" s="858"/>
+      <c r="G62" s="858"/>
+      <c r="H62" s="858"/>
+      <c r="I62" s="858"/>
+      <c r="J62" s="858"/>
+      <c r="K62" s="858"/>
+      <c r="L62" s="858"/>
       <c r="M62" s="319"/>
       <c r="N62" s="319"/>
       <c r="O62" s="319"/>
@@ -38345,12 +38342,12 @@
       <c r="Y64" s="482"/>
     </row>
     <row r="65" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="839" t="s">
+      <c r="A65" s="853" t="s">
         <v>473</v>
       </c>
-      <c r="B65" s="839"/>
-      <c r="C65" s="839"/>
-      <c r="D65" s="839"/>
+      <c r="B65" s="853"/>
+      <c r="C65" s="853"/>
+      <c r="D65" s="853"/>
       <c r="E65" s="337"/>
       <c r="F65" s="337"/>
       <c r="G65" s="337"/>
@@ -38419,7 +38416,7 @@
       <c r="L69" s="337"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kYEhBMpBR4A4hBDP8nVe+fkaAPDdKPZVLQdsDn27UTI5SW9m2Y+5D92W4wKhHAknMQUVToaGWb5F9zvawqmmWg==" saltValue="ArUihwcGijS44cDDSGldiA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <protectedRanges>
     <protectedRange sqref="E16" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E13" name="Rango3_3_1_1_1_1_1_1_1_1_2"/>
@@ -38428,6 +38425,11 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="20">
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="Z23:AA23"/>
     <mergeCell ref="AB23:AB24"/>
     <mergeCell ref="A60:L60"/>
     <mergeCell ref="A62:L62"/>
@@ -38443,11 +38445,6 @@
     <mergeCell ref="A61:L61"/>
     <mergeCell ref="A59:L59"/>
     <mergeCell ref="A58:L58"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="Z23:AA23"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
@@ -38464,48 +38461,48 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{070D23A9-A3B7-48A9-92EF-B48C66251EB4}">
   <dimension ref="A1:V89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="438" customWidth="1"/>
-    <col min="2" max="5" width="11.28515625" style="438" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="438" customWidth="1"/>
-    <col min="7" max="8" width="11.28515625" style="438" customWidth="1"/>
-    <col min="9" max="12" width="11.5703125" style="438" customWidth="1"/>
-    <col min="13" max="21" width="8.7109375" style="438" customWidth="1"/>
-    <col min="22" max="16384" width="10.28515625" style="438"/>
+    <col min="1" max="1" width="4.88671875" style="438" customWidth="1"/>
+    <col min="2" max="5" width="11.33203125" style="438" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="438" customWidth="1"/>
+    <col min="7" max="8" width="11.33203125" style="438" customWidth="1"/>
+    <col min="9" max="12" width="11.5546875" style="438" customWidth="1"/>
+    <col min="13" max="21" width="8.6640625" style="438" customWidth="1"/>
+    <col min="22" max="16384" width="10.33203125" style="438"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="470"/>
-      <c r="B1" s="848" t="s">
+      <c r="B1" s="836" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="849"/>
-      <c r="D1" s="849"/>
-      <c r="E1" s="849"/>
-      <c r="F1" s="849"/>
-      <c r="G1" s="849"/>
-      <c r="H1" s="849"/>
-      <c r="I1" s="849"/>
-      <c r="J1" s="849"/>
-      <c r="K1" s="849"/>
-      <c r="L1" s="850"/>
+      <c r="C1" s="837"/>
+      <c r="D1" s="837"/>
+      <c r="E1" s="837"/>
+      <c r="F1" s="837"/>
+      <c r="G1" s="837"/>
+      <c r="H1" s="837"/>
+      <c r="I1" s="837"/>
+      <c r="J1" s="837"/>
+      <c r="K1" s="837"/>
+      <c r="L1" s="838"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="470"/>
-      <c r="B2" s="851" t="s">
+      <c r="B2" s="839" t="s">
         <v>384</v>
       </c>
-      <c r="C2" s="852"/>
-      <c r="D2" s="852"/>
-      <c r="E2" s="852"/>
-      <c r="F2" s="852"/>
-      <c r="G2" s="852"/>
-      <c r="H2" s="852"/>
-      <c r="I2" s="852"/>
-      <c r="J2" s="852"/>
-      <c r="K2" s="852"/>
-      <c r="L2" s="853"/>
+      <c r="C2" s="840"/>
+      <c r="D2" s="840"/>
+      <c r="E2" s="840"/>
+      <c r="F2" s="840"/>
+      <c r="G2" s="840"/>
+      <c r="H2" s="840"/>
+      <c r="I2" s="840"/>
+      <c r="J2" s="840"/>
+      <c r="K2" s="840"/>
+      <c r="L2" s="841"/>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="470"/>
@@ -38529,14 +38526,14 @@
         <v>306</v>
       </c>
       <c r="C4" s="791"/>
-      <c r="D4" s="792"/>
+      <c r="D4" s="47"/>
       <c r="E4" s="791"/>
       <c r="F4" s="791"/>
-      <c r="G4" s="793"/>
+      <c r="G4" s="792"/>
       <c r="H4" s="791"/>
-      <c r="I4" s="794"/>
-      <c r="J4" s="794"/>
-      <c r="K4" s="794"/>
+      <c r="I4" s="793"/>
+      <c r="J4" s="793"/>
+      <c r="K4" s="793"/>
       <c r="L4" s="490"/>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -38545,17 +38542,17 @@
         <v>307</v>
       </c>
       <c r="C5" s="791"/>
-      <c r="D5" s="795">
+      <c r="D5" s="794">
         <f>+Balanza!B8</f>
         <v>-3.2899999999999998E-6</v>
       </c>
       <c r="E5" s="791"/>
       <c r="F5" s="791"/>
-      <c r="G5" s="793"/>
+      <c r="G5" s="792"/>
       <c r="H5" s="791"/>
-      <c r="I5" s="794"/>
-      <c r="J5" s="794"/>
-      <c r="K5" s="794"/>
+      <c r="I5" s="793"/>
+      <c r="J5" s="793"/>
+      <c r="K5" s="793"/>
       <c r="L5" s="490"/>
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -38563,18 +38560,18 @@
       <c r="B6" s="722" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="792"/>
-      <c r="D6" s="796" t="str">
+      <c r="C6" s="47"/>
+      <c r="D6" s="795" t="str">
         <f>+Balanza!B12</f>
         <v>EQP-0046</v>
       </c>
-      <c r="E6" s="797"/>
-      <c r="F6" s="797"/>
-      <c r="G6" s="792"/>
+      <c r="E6" s="796"/>
+      <c r="F6" s="796"/>
+      <c r="G6" s="47"/>
       <c r="H6" s="791"/>
-      <c r="I6" s="794"/>
-      <c r="J6" s="794"/>
-      <c r="K6" s="794"/>
+      <c r="I6" s="793"/>
+      <c r="J6" s="793"/>
+      <c r="K6" s="793"/>
       <c r="L6" s="490"/>
     </row>
     <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -38583,7 +38580,7 @@
         <v>105</v>
       </c>
       <c r="C7" s="611"/>
-      <c r="D7" s="798">
+      <c r="D7" s="797">
         <v>46132</v>
       </c>
       <c r="E7" s="612"/>
@@ -38595,7 +38592,7 @@
       <c r="K7" s="789"/>
       <c r="L7" s="790"/>
     </row>
-    <row r="8" spans="1:14" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="8.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="470"/>
       <c r="B8" s="470"/>
       <c r="C8" s="614"/>
@@ -38614,10 +38611,10 @@
       <c r="B9" s="439" t="s">
         <v>333</v>
       </c>
-      <c r="C9" s="885" t="s">
+      <c r="C9" s="884" t="s">
         <v>345</v>
       </c>
-      <c r="D9" s="886"/>
+      <c r="D9" s="885"/>
       <c r="F9" s="580" t="s">
         <v>355</v>
       </c>
@@ -38634,10 +38631,10 @@
       <c r="B10" s="439" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="885" t="s">
+      <c r="C10" s="884" t="s">
         <v>345</v>
       </c>
-      <c r="D10" s="886"/>
+      <c r="D10" s="885"/>
       <c r="F10" s="708" t="s">
         <v>345</v>
       </c>
@@ -38653,7 +38650,7 @@
       <c r="M10" s="440"/>
       <c r="N10" s="440"/>
     </row>
-    <row r="11" spans="1:14" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="470"/>
       <c r="B11" s="441"/>
       <c r="C11" s="616"/>
@@ -38671,18 +38668,18 @@
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="470"/>
-      <c r="B12" s="876" t="s">
+      <c r="B12" s="875" t="s">
         <v>283</v>
       </c>
-      <c r="C12" s="877"/>
-      <c r="D12" s="877"/>
-      <c r="E12" s="878"/>
+      <c r="C12" s="876"/>
+      <c r="D12" s="876"/>
+      <c r="E12" s="877"/>
       <c r="F12" s="470"/>
-      <c r="G12" s="879" t="s">
+      <c r="G12" s="878" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="880"/>
-      <c r="I12" s="881"/>
+      <c r="H12" s="879"/>
+      <c r="I12" s="880"/>
       <c r="J12" s="470"/>
       <c r="K12" s="470"/>
       <c r="L12" s="617"/>
@@ -38733,7 +38730,7 @@
       </c>
       <c r="F14" s="619">
         <f>SUM(E28:E45)</f>
-        <v>359.89881592899997</v>
+        <v>0</v>
       </c>
       <c r="G14" s="582" t="s">
         <v>285</v>
@@ -38833,18 +38830,18 @@
     </row>
     <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="623"/>
-      <c r="B18" s="876" t="s">
+      <c r="B18" s="875" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="877"/>
-      <c r="D18" s="877"/>
-      <c r="E18" s="878"/>
+      <c r="C18" s="876"/>
+      <c r="D18" s="876"/>
+      <c r="E18" s="877"/>
       <c r="F18" s="470"/>
       <c r="G18" s="470"/>
-      <c r="H18" s="883" t="s">
+      <c r="H18" s="882" t="s">
         <v>146</v>
       </c>
-      <c r="I18" s="884"/>
+      <c r="I18" s="883"/>
       <c r="J18" s="617"/>
       <c r="K18" s="622"/>
       <c r="L18" s="617"/>
@@ -38906,7 +38903,8 @@
       <c r="C21" s="589"/>
       <c r="D21" s="589"/>
       <c r="E21" s="537">
-        <v>359.9</v>
+        <f>+IF(C10="Global",FORMATO!D24,FORMATO!D39)</f>
+        <v>0</v>
       </c>
       <c r="F21" s="775"/>
       <c r="G21" s="470"/>
@@ -38930,7 +38928,7 @@
       <c r="D22" s="625"/>
       <c r="E22" s="457">
         <f>IF(C10="Global",SUM(E28:E45),SUM(E37:E45))</f>
-        <v>348.09885475099998</v>
+        <v>0</v>
       </c>
       <c r="F22" s="470"/>
       <c r="G22" s="470"/>
@@ -38954,7 +38952,7 @@
       <c r="D23" s="626"/>
       <c r="E23" s="627">
         <f>ABS(E21-E22)</f>
-        <v>11.801145249000001</v>
+        <v>0</v>
       </c>
       <c r="F23" s="470"/>
       <c r="G23" s="470"/>
@@ -38976,13 +38974,13 @@
       </c>
       <c r="C24" s="628"/>
       <c r="D24" s="628"/>
-      <c r="E24" s="629">
+      <c r="E24" s="629" t="e">
         <f>E23/E21*100</f>
-        <v>3.2790067377049184</v>
-      </c>
-      <c r="F24" s="630" t="str">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F24" s="630" t="e">
         <f>+IF(E24&lt;=0.3,"cumple","no cumple")</f>
-        <v>no cumple</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G24" s="470"/>
       <c r="H24" s="458" t="s">
@@ -38996,7 +38994,7 @@
       <c r="K24" s="470"/>
       <c r="L24" s="470"/>
     </row>
-    <row r="25" spans="1:22" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="8.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="623"/>
       <c r="B25" s="477"/>
       <c r="C25" s="470"/>
@@ -39012,23 +39010,23 @@
     </row>
     <row r="26" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="632"/>
-      <c r="B26" s="882" t="s">
+      <c r="B26" s="881" t="s">
         <v>279</v>
       </c>
-      <c r="C26" s="882"/>
+      <c r="C26" s="881"/>
       <c r="D26" s="633" t="s">
         <v>278</v>
       </c>
-      <c r="E26" s="875" t="s">
+      <c r="E26" s="874" t="s">
         <v>100</v>
       </c>
-      <c r="F26" s="873" t="s">
+      <c r="F26" s="872" t="s">
         <v>289</v>
       </c>
-      <c r="G26" s="873" t="s">
+      <c r="G26" s="872" t="s">
         <v>346</v>
       </c>
-      <c r="H26" s="873" t="s">
+      <c r="H26" s="872" t="s">
         <v>276</v>
       </c>
       <c r="I26" s="470"/>
@@ -39047,10 +39045,10 @@
       <c r="D27" s="476" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="875"/>
-      <c r="F27" s="874"/>
-      <c r="G27" s="874"/>
-      <c r="H27" s="874"/>
+      <c r="E27" s="874"/>
+      <c r="F27" s="873"/>
+      <c r="G27" s="873"/>
+      <c r="H27" s="873"/>
       <c r="I27" s="470"/>
       <c r="J27" s="636"/>
       <c r="K27" s="634"/>
@@ -39066,7 +39064,7 @@
       <c r="U27" s="710"/>
       <c r="V27" s="711"/>
     </row>
-    <row r="28" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="635"/>
       <c r="B28" s="465">
         <v>3</v>
@@ -39133,7 +39131,7 @@
       </c>
       <c r="V28" s="713"/>
     </row>
-    <row r="29" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="623"/>
       <c r="B29" s="466">
         <v>2.5</v>
@@ -39200,7 +39198,7 @@
       </c>
       <c r="V29" s="713"/>
     </row>
-    <row r="30" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="623"/>
       <c r="B30" s="465">
         <v>2</v>
@@ -39267,7 +39265,7 @@
       </c>
       <c r="V30" s="713"/>
     </row>
-    <row r="31" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="623"/>
       <c r="B31" s="466">
         <v>1.5</v>
@@ -39334,7 +39332,7 @@
       </c>
       <c r="V31" s="713"/>
     </row>
-    <row r="32" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="623"/>
       <c r="B32" s="465">
         <v>1</v>
@@ -39401,7 +39399,7 @@
       </c>
       <c r="V32" s="713"/>
     </row>
-    <row r="33" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="623"/>
       <c r="B33" s="466">
         <v>0.75</v>
@@ -39468,7 +39466,7 @@
       </c>
       <c r="V33" s="713"/>
     </row>
-    <row r="34" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="623"/>
       <c r="B34" s="466">
         <v>0.5</v>
@@ -39535,7 +39533,7 @@
       </c>
       <c r="V34" s="713"/>
     </row>
-    <row r="35" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="623"/>
       <c r="B35" s="466">
         <v>0.375</v>
@@ -39599,7 +39597,7 @@
       </c>
       <c r="V35" s="713"/>
     </row>
-    <row r="36" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="623"/>
       <c r="B36" s="465" t="s">
         <v>20</v>
@@ -39608,11 +39606,12 @@
         <v>4.75</v>
       </c>
       <c r="D36" s="540">
-        <v>11.8</v>
+        <f>+FORMATO!I26</f>
+        <v>0</v>
       </c>
       <c r="E36" s="449">
         <f t="shared" si="5"/>
-        <v>11.799961178</v>
+        <v>0</v>
       </c>
       <c r="F36" s="501" t="e">
         <f t="shared" si="0"/>
@@ -39662,7 +39661,7 @@
       </c>
       <c r="V36" s="713"/>
     </row>
-    <row r="37" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="623"/>
       <c r="B37" s="465">
         <v>8</v>
@@ -39671,11 +39670,12 @@
         <v>2.36</v>
       </c>
       <c r="D37" s="540">
-        <v>70.5</v>
+        <f>+FORMATO!I27</f>
+        <v>0</v>
       </c>
       <c r="E37" s="449">
         <f t="shared" si="5"/>
-        <v>70.499768055000004</v>
+        <v>0</v>
       </c>
       <c r="F37" s="501" t="b">
         <f>IF($C$10="Fraccionada",E37*$H$36/E$20,IF($C$10="Global",E37/$E$19*100))</f>
@@ -39707,7 +39707,7 @@
       <c r="U37" s="591"/>
       <c r="V37" s="713"/>
     </row>
-    <row r="38" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="623"/>
       <c r="B38" s="465">
         <v>10</v>
@@ -39716,11 +39716,12 @@
         <v>2</v>
       </c>
       <c r="D38" s="540">
-        <v>18.8</v>
+        <f>+FORMATO!I28</f>
+        <v>0</v>
       </c>
       <c r="E38" s="449">
         <f t="shared" si="5"/>
-        <v>18.799938147999999</v>
+        <v>0</v>
       </c>
       <c r="F38" s="501" t="b">
         <f>IF($C$10="Fraccionada",E38*$H$36/E$20,IF($C$10="Global",E38/$E$19*100))</f>
@@ -39759,7 +39760,7 @@
       <c r="U38" s="715"/>
       <c r="V38" s="713"/>
     </row>
-    <row r="39" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="623"/>
       <c r="B39" s="465">
         <v>16</v>
@@ -39768,11 +39769,12 @@
         <v>1.18</v>
       </c>
       <c r="D39" s="540">
-        <v>79.8</v>
+        <f>+FORMATO!I29</f>
+        <v>0</v>
       </c>
       <c r="E39" s="449">
         <f t="shared" si="5"/>
-        <v>79.799737457999996</v>
+        <v>0</v>
       </c>
       <c r="F39" s="501" t="b">
         <f t="shared" ref="F39:F45" si="13">IF($C$10="Fraccionada",E39*$H$36/E$20,IF($C$10="Global",E39/$E$19*100))</f>
@@ -39820,11 +39822,12 @@
         <v>0.6</v>
       </c>
       <c r="D40" s="540">
-        <v>80.8</v>
+        <f>+FORMATO!I30</f>
+        <v>0</v>
       </c>
       <c r="E40" s="449">
         <f t="shared" si="5"/>
-        <v>80.799734168000001</v>
+        <v>0</v>
       </c>
       <c r="F40" s="501" t="b">
         <f t="shared" si="13"/>
@@ -39847,7 +39850,7 @@
       <c r="Q40" s="717"/>
       <c r="V40" s="713"/>
     </row>
-    <row r="41" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="623"/>
       <c r="B41" s="465">
         <v>40</v>
@@ -39856,11 +39859,12 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="D41" s="540">
-        <v>31</v>
+        <f>+FORMATO!I31</f>
+        <v>0</v>
       </c>
       <c r="E41" s="449">
         <f t="shared" si="5"/>
-        <v>30.999898009999999</v>
+        <v>0</v>
       </c>
       <c r="F41" s="501" t="b">
         <f t="shared" si="13"/>
@@ -39898,11 +39902,12 @@
         <v>0.3</v>
       </c>
       <c r="D42" s="540">
-        <v>21.5</v>
+        <f>+FORMATO!I32</f>
+        <v>0</v>
       </c>
       <c r="E42" s="449">
         <f t="shared" si="5"/>
-        <v>21.499929264999999</v>
+        <v>0</v>
       </c>
       <c r="F42" s="501" t="b">
         <f t="shared" si="13"/>
@@ -39930,11 +39935,12 @@
         <v>0.15</v>
       </c>
       <c r="D43" s="540">
-        <v>30.8</v>
+        <f>+FORMATO!I33</f>
+        <v>0</v>
       </c>
       <c r="E43" s="449">
         <f t="shared" si="5"/>
-        <v>30.799898668000001</v>
+        <v>0</v>
       </c>
       <c r="F43" s="501" t="b">
         <f t="shared" si="13"/>
@@ -39962,11 +39968,12 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D44" s="540">
-        <v>14.9</v>
+        <f>+FORMATO!I34</f>
+        <v>0</v>
       </c>
       <c r="E44" s="449">
         <f t="shared" si="5"/>
-        <v>14.899950979</v>
+        <v>0</v>
       </c>
       <c r="F44" s="501" t="b">
         <f t="shared" si="13"/>
@@ -39992,6 +39999,7 @@
       </c>
       <c r="C45" s="465"/>
       <c r="D45" s="540">
+        <f>+FORMATO!I35</f>
         <v>0</v>
       </c>
       <c r="E45" s="449">
@@ -40029,11 +40037,11 @@
     <row r="47" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="451"/>
       <c r="B47" s="464"/>
-      <c r="C47" s="870" t="s">
+      <c r="C47" s="869" t="s">
         <v>294</v>
       </c>
-      <c r="D47" s="870"/>
-      <c r="E47" s="870"/>
+      <c r="D47" s="869"/>
+      <c r="E47" s="869"/>
       <c r="H47" s="469"/>
       <c r="I47" s="440"/>
       <c r="J47" s="440"/>
@@ -40244,10 +40252,10 @@
     </row>
     <row r="61" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="454"/>
-      <c r="C61" s="871" t="s">
+      <c r="C61" s="870" t="s">
         <v>295</v>
       </c>
-      <c r="D61" s="872"/>
+      <c r="D61" s="871"/>
       <c r="E61" s="607" t="str">
         <f>IF(E19&gt;=300,"Cumple","No cumple")</f>
         <v>Cumple</v>
@@ -40330,7 +40338,6 @@
     <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="rVx5rV3+cPVKGGVtiIc+8GRwN17UdcXICeoKaloQg6ha1ohISsMObtq/4m/tgD8Op5CeK+HySrHvKCXGRpKSgQ==" saltValue="+mwCAzhni0q5qX/2GOS1ew==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="15">
     <mergeCell ref="C47:E47"/>
     <mergeCell ref="C61:D61"/>
@@ -40375,31 +40382,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DDA032E-1F32-4934-885E-494CF4F3E44D}">
   <dimension ref="A1:N281"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" style="390" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="390" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="390" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="390"/>
-    <col min="5" max="8" width="11.5703125" style="390" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="390" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" style="390" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="390" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="390"/>
+    <col min="1" max="1" width="28.5546875" style="390" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="390" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="390" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="390"/>
+    <col min="5" max="8" width="11.5546875" style="390" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" style="390" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="390" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" style="390" customWidth="1"/>
+    <col min="12" max="16384" width="11.44140625" style="390"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="900"/>
-      <c r="B1" s="891" t="s">
+      <c r="A1" s="899"/>
+      <c r="B1" s="890" t="s">
         <v>235</v>
       </c>
-      <c r="C1" s="892"/>
-      <c r="D1" s="892"/>
-      <c r="E1" s="892"/>
-      <c r="F1" s="892"/>
-      <c r="G1" s="892"/>
-      <c r="H1" s="892"/>
-      <c r="I1" s="893"/>
+      <c r="C1" s="891"/>
+      <c r="D1" s="891"/>
+      <c r="E1" s="891"/>
+      <c r="F1" s="891"/>
+      <c r="G1" s="891"/>
+      <c r="H1" s="891"/>
+      <c r="I1" s="892"/>
       <c r="J1" s="400" t="s">
         <v>234</v>
       </c>
@@ -40408,15 +40415,15 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="901"/>
-      <c r="B2" s="894"/>
-      <c r="C2" s="895"/>
-      <c r="D2" s="895"/>
-      <c r="E2" s="895"/>
-      <c r="F2" s="895"/>
-      <c r="G2" s="895"/>
-      <c r="H2" s="895"/>
-      <c r="I2" s="896"/>
+      <c r="A2" s="900"/>
+      <c r="B2" s="893"/>
+      <c r="C2" s="894"/>
+      <c r="D2" s="894"/>
+      <c r="E2" s="894"/>
+      <c r="F2" s="894"/>
+      <c r="G2" s="894"/>
+      <c r="H2" s="894"/>
+      <c r="I2" s="895"/>
       <c r="J2" s="400" t="s">
         <v>232</v>
       </c>
@@ -40425,15 +40432,15 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="901"/>
-      <c r="B3" s="894"/>
-      <c r="C3" s="895"/>
-      <c r="D3" s="895"/>
-      <c r="E3" s="895"/>
-      <c r="F3" s="895"/>
-      <c r="G3" s="895"/>
-      <c r="H3" s="895"/>
-      <c r="I3" s="896"/>
+      <c r="A3" s="900"/>
+      <c r="B3" s="893"/>
+      <c r="C3" s="894"/>
+      <c r="D3" s="894"/>
+      <c r="E3" s="894"/>
+      <c r="F3" s="894"/>
+      <c r="G3" s="894"/>
+      <c r="H3" s="894"/>
+      <c r="I3" s="895"/>
       <c r="J3" s="400" t="s">
         <v>231</v>
       </c>
@@ -40442,15 +40449,15 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="902"/>
-      <c r="B4" s="897"/>
-      <c r="C4" s="898"/>
-      <c r="D4" s="898"/>
-      <c r="E4" s="898"/>
-      <c r="F4" s="898"/>
-      <c r="G4" s="898"/>
-      <c r="H4" s="898"/>
-      <c r="I4" s="899"/>
+      <c r="A4" s="901"/>
+      <c r="B4" s="896"/>
+      <c r="C4" s="897"/>
+      <c r="D4" s="897"/>
+      <c r="E4" s="897"/>
+      <c r="F4" s="897"/>
+      <c r="G4" s="897"/>
+      <c r="H4" s="897"/>
+      <c r="I4" s="898"/>
       <c r="J4" s="400" t="s">
         <v>230</v>
       </c>
@@ -40526,7 +40533,7 @@
       <c r="J9" s="388"/>
       <c r="K9" s="398"/>
     </row>
-    <row r="11" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="492" t="s">
         <v>465</v>
       </c>
@@ -40541,7 +40548,7 @@
       <c r="J11" s="491"/>
       <c r="K11" s="491"/>
     </row>
-    <row r="12" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="492"/>
       <c r="B12" s="491"/>
       <c r="C12" s="491"/>
@@ -40554,7 +40561,7 @@
       <c r="J12" s="491"/>
       <c r="K12" s="491"/>
     </row>
-    <row r="13" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="572" t="s">
         <v>311</v>
       </c>
@@ -40571,7 +40578,7 @@
       <c r="J13" s="491"/>
       <c r="K13" s="491"/>
     </row>
-    <row r="14" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="491"/>
       <c r="B14" s="503"/>
       <c r="C14" s="399"/>
@@ -40584,7 +40591,7 @@
       <c r="J14" s="491"/>
       <c r="K14" s="491"/>
     </row>
-    <row r="15" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="573" t="s">
         <v>350</v>
       </c>
@@ -40599,7 +40606,7 @@
       <c r="J15" s="491"/>
       <c r="K15" s="491"/>
     </row>
-    <row r="16" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="573" t="s">
         <v>351</v>
       </c>
@@ -40614,7 +40621,7 @@
       <c r="J16" s="491"/>
       <c r="K16" s="491"/>
     </row>
-    <row r="17" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="573" t="s">
         <v>352</v>
       </c>
@@ -40629,7 +40636,7 @@
       <c r="J17" s="491"/>
       <c r="K17" s="491"/>
     </row>
-    <row r="18" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="491"/>
       <c r="B18" s="491"/>
       <c r="C18" s="491"/>
@@ -40642,7 +40649,7 @@
       <c r="J18" s="491"/>
       <c r="K18" s="491"/>
     </row>
-    <row r="19" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="572" t="s">
         <v>314</v>
       </c>
@@ -40657,7 +40664,7 @@
       <c r="J19" s="491"/>
       <c r="K19" s="491"/>
     </row>
-    <row r="20" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="491"/>
       <c r="B20" s="491"/>
       <c r="C20" s="491"/>
@@ -40670,7 +40677,7 @@
       <c r="J20" s="491"/>
       <c r="K20" s="491"/>
     </row>
-    <row r="21" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="574" t="s">
         <v>316</v>
       </c>
@@ -40685,7 +40692,7 @@
       <c r="J21" s="491"/>
       <c r="K21" s="491"/>
     </row>
-    <row r="22" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="574" t="s">
         <v>317</v>
       </c>
@@ -40700,7 +40707,7 @@
       <c r="J22" s="491"/>
       <c r="K22" s="491"/>
     </row>
-    <row r="23" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="491"/>
       <c r="B23" s="491"/>
       <c r="C23" s="491"/>
@@ -40713,7 +40720,7 @@
       <c r="J23" s="491"/>
       <c r="K23" s="491"/>
     </row>
-    <row r="24" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="492" t="s">
         <v>315</v>
       </c>
@@ -40728,7 +40735,7 @@
       <c r="J24" s="491"/>
       <c r="K24" s="491"/>
     </row>
-    <row r="25" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="491"/>
       <c r="B25" s="491"/>
       <c r="C25" s="491"/>
@@ -40741,7 +40748,7 @@
       <c r="J25" s="491"/>
       <c r="K25" s="491"/>
     </row>
-    <row r="26" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="491"/>
       <c r="B26" s="491"/>
       <c r="C26" s="491"/>
@@ -40754,7 +40761,7 @@
       <c r="J26" s="491"/>
       <c r="K26" s="491"/>
     </row>
-    <row r="27" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="491"/>
       <c r="B27" s="491"/>
       <c r="C27" s="491"/>
@@ -40767,7 +40774,7 @@
       <c r="J27" s="491"/>
       <c r="K27" s="491"/>
     </row>
-    <row r="28" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="491"/>
       <c r="B28" s="491"/>
       <c r="C28" s="491"/>
@@ -40780,7 +40787,7 @@
       <c r="J28" s="491"/>
       <c r="K28" s="270"/>
     </row>
-    <row r="29" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="491"/>
       <c r="B29" s="491"/>
       <c r="C29" s="491"/>
@@ -40793,7 +40800,7 @@
       <c r="J29" s="491"/>
       <c r="K29" s="491"/>
     </row>
-    <row r="30" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="491"/>
       <c r="B30" s="491"/>
       <c r="C30" s="491"/>
@@ -40806,7 +40813,7 @@
       <c r="J30" s="491"/>
       <c r="K30" s="491"/>
     </row>
-    <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="491"/>
       <c r="B31" s="491"/>
       <c r="C31" s="491"/>
@@ -40819,7 +40826,7 @@
       <c r="J31" s="491"/>
       <c r="K31" s="491"/>
     </row>
-    <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="491"/>
       <c r="B32" s="491"/>
       <c r="C32" s="491"/>
@@ -40832,7 +40839,7 @@
       <c r="J32" s="491"/>
       <c r="K32" s="491"/>
     </row>
-    <row r="33" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="491"/>
       <c r="B33" s="491"/>
       <c r="C33" s="491"/>
@@ -40845,7 +40852,7 @@
       <c r="J33" s="491"/>
       <c r="K33" s="491"/>
     </row>
-    <row r="34" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="491"/>
       <c r="B34" s="491"/>
       <c r="C34" s="491"/>
@@ -40859,19 +40866,19 @@
       <c r="K34" s="491"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="890" t="s">
+      <c r="A35" s="889" t="s">
         <v>466</v>
       </c>
-      <c r="B35" s="890"/>
-      <c r="C35" s="890"/>
-      <c r="D35" s="890"/>
-      <c r="E35" s="890"/>
-      <c r="F35" s="890"/>
-      <c r="G35" s="890"/>
-      <c r="H35" s="890"/>
-      <c r="I35" s="890"/>
-    </row>
-    <row r="36" spans="1:14" ht="39" x14ac:dyDescent="0.2">
+      <c r="B35" s="889"/>
+      <c r="C35" s="889"/>
+      <c r="D35" s="889"/>
+      <c r="E35" s="889"/>
+      <c r="F35" s="889"/>
+      <c r="G35" s="889"/>
+      <c r="H35" s="889"/>
+      <c r="I35" s="889"/>
+    </row>
+    <row r="36" spans="1:14" ht="37.799999999999997" x14ac:dyDescent="0.25">
       <c r="A36" s="397" t="s">
         <v>225</v>
       </c>
@@ -40901,7 +40908,7 @@
       </c>
       <c r="N36" s="569"/>
     </row>
-    <row r="37" spans="1:14" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="387"/>
       <c r="B37" s="387"/>
       <c r="C37" s="387"/>
@@ -42176,7 +42183,7 @@
       <c r="I92" s="387"/>
       <c r="J92" s="387"/>
     </row>
-    <row r="93" spans="1:10" ht="12.75" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:10" ht="12" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="426" t="s">
         <v>210</v>
@@ -43454,9 +43461,9 @@
         <f>SQRT(G152*G152+(G160*G160)+(G156*G156)+(G162*G162))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I150" s="434" t="e">
+      <c r="I150" s="434" t="str">
         <f>IF(B152=0,"---",(H150*2))</f>
-        <v>#VALUE!</v>
+        <v>---</v>
       </c>
       <c r="J150" s="387"/>
     </row>
@@ -43478,7 +43485,7 @@
       </c>
       <c r="B152" s="525">
         <f>+Balanza!D38</f>
-        <v>11.799961178</v>
+        <v>0</v>
       </c>
       <c r="C152" s="404"/>
       <c r="D152" s="405" t="s">
@@ -43528,14 +43535,14 @@
       <c r="B154" s="410"/>
       <c r="C154" s="416">
         <f>2*(SQRT(Balanza!$B$9+Balanza!$C$9*(POWER(B152,2))))</f>
-        <v>0.12899664856262527</v>
+        <v>0.12899612397277679</v>
       </c>
       <c r="D154" s="412" t="s">
         <v>185</v>
       </c>
       <c r="E154" s="413">
         <f>C154/2</f>
-        <v>6.4498324281312636E-2</v>
+        <v>6.4498061986388397E-2</v>
       </c>
       <c r="F154" s="414"/>
       <c r="G154" s="415"/>
@@ -43752,7 +43759,7 @@
       <c r="I162" s="387"/>
       <c r="J162" s="387"/>
     </row>
-    <row r="163" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="516" t="str">
         <f>+datos!C10</f>
         <v>-</v>
@@ -43778,9 +43785,9 @@
         <f>IF($A$163="fraccionada",SQRT(G166*G166+(G174*G174)+(G170*G170)+(G176*G176)+(G165*G165)),SQRT(G166*G166+G170*G170+G174*G174+G176*G176))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I164" s="434" t="e">
+      <c r="I164" s="434" t="str">
         <f>IF(B166=0,"---",(H164*2))</f>
-        <v>#VALUE!</v>
+        <v>---</v>
       </c>
       <c r="J164" s="387"/>
     </row>
@@ -43817,7 +43824,7 @@
       </c>
       <c r="B166" s="525">
         <f>+Balanza!D39</f>
-        <v>82.299729233000008</v>
+        <v>0</v>
       </c>
       <c r="C166" s="404"/>
       <c r="D166" s="405" t="s">
@@ -43867,14 +43874,14 @@
       <c r="B168" s="410"/>
       <c r="C168" s="416">
         <f>2*(SQRT(Balanza!$B$9+Balanza!$C$9*(POWER(B166,2))))</f>
-        <v>0.12902164002429875</v>
+        <v>0.12899612397277679</v>
       </c>
       <c r="D168" s="412" t="s">
         <v>185</v>
       </c>
       <c r="E168" s="413">
         <f>C168/2</f>
-        <v>6.4510820012149375E-2</v>
+        <v>6.4498061986388397E-2</v>
       </c>
       <c r="F168" s="414"/>
       <c r="G168" s="415"/>
@@ -44110,9 +44117,9 @@
         <f>IF($A$163="fraccionada",SQRT(G180*G180+(G188*G188)+(G184*G184)+(G190*G190)+(G179*G179)),SQRT(G180*G180+G184*G184+G188*G188+G190*G190))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I178" s="434" t="e">
+      <c r="I178" s="434" t="str">
         <f>IF(B180=0,"---",(H178*2))</f>
-        <v>#VALUE!</v>
+        <v>---</v>
       </c>
       <c r="J178" s="387"/>
     </row>
@@ -44149,7 +44156,7 @@
       </c>
       <c r="B180" s="525">
         <f>Balanza!D40</f>
-        <v>101.099667381</v>
+        <v>0</v>
       </c>
       <c r="C180" s="404"/>
       <c r="D180" s="405" t="s">
@@ -44200,14 +44207,14 @@
       <c r="B182" s="410"/>
       <c r="C182" s="416">
         <f>2*(SQRT(Balanza!$B$9+Balanza!$C$9*(POWER(B180,2))))</f>
-        <v>0.12903462694466047</v>
+        <v>0.12899612397277679</v>
       </c>
       <c r="D182" s="412" t="s">
         <v>185</v>
       </c>
       <c r="E182" s="413">
         <f>C182/2</f>
-        <v>6.4517313472330237E-2</v>
+        <v>6.4498061986388397E-2</v>
       </c>
       <c r="F182" s="414"/>
       <c r="G182" s="415"/>
@@ -44462,9 +44469,9 @@
         <f>IF($A$163="fraccionada",SQRT(G194*G194+(G202*G202)+(G198*G198)+(G204*G204)+(G193*G193)),SQRT(G194*G194+G198*G198+G202*G202+G204*G204))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I192" s="434" t="e">
+      <c r="I192" s="434" t="str">
         <f>IF(B194=0,"---",(H192*2))</f>
-        <v>#VALUE!</v>
+        <v>---</v>
       </c>
       <c r="J192" s="387"/>
     </row>
@@ -44501,7 +44508,7 @@
       </c>
       <c r="B194" s="525">
         <f>Balanza!D41</f>
-        <v>180.899404839</v>
+        <v>0</v>
       </c>
       <c r="C194" s="404"/>
       <c r="D194" s="405" t="s">
@@ -44551,14 +44558,14 @@
       <c r="B196" s="410"/>
       <c r="C196" s="416">
         <f>2*(SQRT(Balanza!$B$9+Balanza!$C$9*(POWER(B194,2))))</f>
-        <v>0.12911935682158704</v>
+        <v>0.12899612397277679</v>
       </c>
       <c r="D196" s="412" t="s">
         <v>185</v>
       </c>
       <c r="E196" s="413">
         <f>C196/2</f>
-        <v>6.455967841079352E-2</v>
+        <v>6.4498061986388397E-2</v>
       </c>
       <c r="F196" s="414"/>
       <c r="G196" s="415"/>
@@ -44813,9 +44820,9 @@
         <f>IF($A$163="fraccionada",SQRT(G208*G208+(G216*G216)+(G212*G212)+(G218*G218)+(G207*G207)),SQRT(G208*G208+G212*G212+G216*G216+G218*G218))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I206" s="434" t="e">
+      <c r="I206" s="434" t="str">
         <f>IF(B208=0,"---",(H206*2))</f>
-        <v>#VALUE!</v>
+        <v>---</v>
       </c>
       <c r="J206" s="387"/>
     </row>
@@ -44852,7 +44859,7 @@
       </c>
       <c r="B208" s="525">
         <f>Balanza!D42</f>
-        <v>261.69913900699999</v>
+        <v>0</v>
       </c>
       <c r="C208" s="404"/>
       <c r="D208" s="405" t="s">
@@ -44902,14 +44909,14 @@
       <c r="B210" s="410"/>
       <c r="C210" s="416">
         <f>2*(SQRT(Balanza!$B$9+Balanza!$C$9*(POWER(B208,2))))</f>
-        <v>0.12925389285841649</v>
+        <v>0.12899612397277679</v>
       </c>
       <c r="D210" s="412" t="s">
         <v>185</v>
       </c>
       <c r="E210" s="413">
         <f>C210/2</f>
-        <v>6.4626946429208243E-2</v>
+        <v>6.4498061986388397E-2</v>
       </c>
       <c r="F210" s="414"/>
       <c r="G210" s="415"/>
@@ -45164,9 +45171,9 @@
         <f>IF($A$163="fraccionada",SQRT(G222*G222+(G230*G230)+(G226*G226)+(G232*G232)+(G221*G221)),SQRT(G222*G222+G226*G226+G230*G230+G232*G232))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I220" s="434" t="e">
+      <c r="I220" s="434" t="str">
         <f>IF(B222=0,"---",(H220*2))</f>
-        <v>#VALUE!</v>
+        <v>---</v>
       </c>
       <c r="J220" s="387"/>
     </row>
@@ -45203,7 +45210,7 @@
       </c>
       <c r="B222" s="525">
         <f>Balanza!D43</f>
-        <v>292.69903701699997</v>
+        <v>0</v>
       </c>
       <c r="C222" s="404"/>
       <c r="D222" s="405" t="s">
@@ -45253,14 +45260,14 @@
       <c r="B224" s="410"/>
       <c r="C224" s="416">
         <f>2*(SQRT(Balanza!$B$9+Balanza!$C$9*(POWER(B222,2))))</f>
-        <v>0.12931849786451705</v>
+        <v>0.12899612397277679</v>
       </c>
       <c r="D224" s="412" t="s">
         <v>185</v>
       </c>
       <c r="E224" s="413">
         <f>C224/2</f>
-        <v>6.4659248932258523E-2</v>
+        <v>6.4498061986388397E-2</v>
       </c>
       <c r="F224" s="414"/>
       <c r="G224" s="415"/>
@@ -45515,9 +45522,9 @@
         <f>IF($A$163="fraccionada",SQRT(G236*G236+(G244*G244)+(G240*G240)+(G246*G246)+(G235*G235)),SQRT(G236*G236+G240*G240+G244*G244+G246*G246))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I234" s="434" t="e">
+      <c r="I234" s="434" t="str">
         <f>IF(B236=0,"---",(H234*2))</f>
-        <v>#VALUE!</v>
+        <v>---</v>
       </c>
       <c r="J234" s="387"/>
     </row>
@@ -45554,7 +45561,7 @@
       </c>
       <c r="B236" s="525">
         <f>Balanza!D44</f>
-        <v>314.19896628199996</v>
+        <v>0</v>
       </c>
       <c r="C236" s="404"/>
       <c r="D236" s="405" t="s">
@@ -45604,14 +45611,14 @@
       <c r="B238" s="410"/>
       <c r="C238" s="416">
         <f>2*(SQRT(Balanza!$B$9+Balanza!$C$9*(POWER(B236,2))))</f>
-        <v>0.1293675260746727</v>
+        <v>0.12899612397277679</v>
       </c>
       <c r="D238" s="412" t="s">
         <v>185</v>
       </c>
       <c r="E238" s="413">
         <f>C238/2</f>
-        <v>6.4683763037336348E-2</v>
+        <v>6.4498061986388397E-2</v>
       </c>
       <c r="F238" s="414"/>
       <c r="G238" s="415"/>
@@ -45866,9 +45873,9 @@
         <f>IF($A$163="fraccionada",SQRT(G250*G250+(G258*G258)+(G254*G254)+(G260*G260)+(G249*G249)),SQRT(G250*G250+G254*G254+G258*G258+G260*G260))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I248" s="434" t="e">
+      <c r="I248" s="434" t="str">
         <f>IF(B250=0,"---",(H248*2))</f>
-        <v>#VALUE!</v>
+        <v>---</v>
       </c>
       <c r="J248" s="387"/>
     </row>
@@ -45905,7 +45912,7 @@
       </c>
       <c r="B250" s="525">
         <f>Balanza!D45</f>
-        <v>344.99886494999998</v>
+        <v>0</v>
       </c>
       <c r="C250" s="404"/>
       <c r="D250" s="405" t="s">
@@ -45955,14 +45962,14 @@
       <c r="B252" s="410"/>
       <c r="C252" s="416">
         <f>2*(SQRT(Balanza!$B$9+Balanza!$C$9*(POWER(B250,2))))</f>
-        <v>0.12944377752038108</v>
+        <v>0.12899612397277679</v>
       </c>
       <c r="D252" s="412" t="s">
         <v>185</v>
       </c>
       <c r="E252" s="413">
         <f>C252/2</f>
-        <v>6.4721888760190541E-2</v>
+        <v>6.4498061986388397E-2</v>
       </c>
       <c r="F252" s="414"/>
       <c r="G252" s="415"/>
@@ -46217,9 +46224,9 @@
         <f>IF($A$163="fraccionada",SQRT(G264*G264+(G272*G272)+(G268*G268)+(G274*G274)+(G263*G263)),SQRT(G264*G264+G268*G268+G272*G272+G274*G274))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I262" s="571" t="e">
+      <c r="I262" s="571" t="str">
         <f>IF(B264=0,"---",(H262*2))</f>
-        <v>#VALUE!</v>
+        <v>---</v>
       </c>
       <c r="J262" s="387"/>
     </row>
@@ -46256,7 +46263,7 @@
       </c>
       <c r="B264" s="525">
         <f>Balanza!D46</f>
-        <v>359.89881592899997</v>
+        <v>0</v>
       </c>
       <c r="C264" s="404"/>
       <c r="D264" s="405" t="s">
@@ -46306,14 +46313,14 @@
       <c r="B266" s="410"/>
       <c r="C266" s="416">
         <f>2*(SQRT(Balanza!$B$9+Balanza!$C$9*(POWER(B264,2))))</f>
-        <v>0.12948320507807681</v>
+        <v>0.12899612397277679</v>
       </c>
       <c r="D266" s="412" t="s">
         <v>185</v>
       </c>
       <c r="E266" s="413">
         <f>C266/2</f>
-        <v>6.4741602539038406E-2</v>
+        <v>6.4498061986388397E-2</v>
       </c>
       <c r="F266" s="414"/>
       <c r="G266" s="415"/>
@@ -46550,26 +46557,26 @@
       <c r="I274" s="387"/>
       <c r="J274" s="387"/>
     </row>
-    <row r="278" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:10" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A278" s="786" t="s">
         <v>458</v>
       </c>
-      <c r="B278" s="903" t="s">
+      <c r="B278" s="902" t="s">
         <v>459</v>
       </c>
-      <c r="C278" s="904"/>
+      <c r="C278" s="903"/>
       <c r="D278" s="787"/>
-      <c r="E278" s="905" t="s">
+      <c r="E278" s="904" t="s">
         <v>460</v>
       </c>
-      <c r="F278" s="905"/>
-      <c r="G278" s="906" t="s">
+      <c r="F278" s="904"/>
+      <c r="G278" s="905" t="s">
         <v>461</v>
       </c>
-      <c r="H278" s="907"/>
+      <c r="H278" s="906"/>
       <c r="I278" s="547"/>
     </row>
-    <row r="279" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:10" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A279" s="547"/>
       <c r="B279" s="547"/>
       <c r="C279" s="547"/>
@@ -46580,26 +46587,26 @@
       <c r="H279" s="547"/>
       <c r="I279" s="547"/>
     </row>
-    <row r="280" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:10" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A280" s="788" t="s">
         <v>462</v>
       </c>
-      <c r="B280" s="887">
+      <c r="B280" s="886">
         <v>44944</v>
       </c>
-      <c r="C280" s="888"/>
+      <c r="C280" s="887"/>
       <c r="D280" s="547"/>
-      <c r="E280" s="889" t="s">
+      <c r="E280" s="888" t="s">
         <v>463</v>
       </c>
-      <c r="F280" s="889"/>
-      <c r="G280" s="887">
+      <c r="F280" s="888"/>
+      <c r="G280" s="886">
         <v>44944</v>
       </c>
-      <c r="H280" s="888"/>
+      <c r="H280" s="887"/>
       <c r="I280" s="547"/>
     </row>
-    <row r="281" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:10" ht="13.2" x14ac:dyDescent="0.2">
       <c r="A281" s="547"/>
       <c r="B281" s="547"/>
       <c r="C281" s="547"/>
@@ -46632,19 +46639,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD6025B9-C381-4FB1-9FD5-743211BAA37E}">
   <dimension ref="A7:T69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="660"/>
-    <col min="2" max="3" width="12.5703125" style="660" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="660"/>
-    <col min="5" max="6" width="13.7109375" style="660" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" style="660" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="660"/>
-    <col min="9" max="9" width="11.85546875" style="660" customWidth="1"/>
-    <col min="10" max="16384" width="11.5703125" style="660"/>
+    <col min="1" max="1" width="11.5546875" style="660"/>
+    <col min="2" max="3" width="12.5546875" style="660" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="660"/>
+    <col min="5" max="6" width="13.6640625" style="660" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" style="660" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" style="660"/>
+    <col min="9" max="9" width="11.88671875" style="660" customWidth="1"/>
+    <col min="10" max="16384" width="11.5546875" style="660"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="658" t="s">
         <v>177</v>
       </c>
@@ -46655,7 +46662,7 @@
       <c r="F7" s="547"/>
       <c r="G7" s="547"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="783" t="s">
         <v>307</v>
       </c>
@@ -46676,7 +46683,7 @@
       <c r="S8" s="662"/>
       <c r="T8" s="662"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="492" t="s">
         <v>178</v>
       </c>
@@ -46691,7 +46698,7 @@
       <c r="F9" s="547"/>
       <c r="G9" s="547"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="492" t="s">
         <v>454</v>
       </c>
@@ -46704,7 +46711,7 @@
       <c r="F10" s="547"/>
       <c r="G10" s="547"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="492" t="s">
         <v>184</v>
       </c>
@@ -46719,7 +46726,7 @@
       <c r="F11" s="547"/>
       <c r="G11" s="547"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="492" t="s">
         <v>456</v>
       </c>
@@ -46732,7 +46739,7 @@
       <c r="F12" s="547"/>
       <c r="G12" s="547"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="492" t="s">
         <v>457</v>
       </c>
@@ -46745,7 +46752,7 @@
       <c r="F13" s="547"/>
       <c r="G13" s="547"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="495"/>
       <c r="B14" s="661"/>
       <c r="C14" s="547"/>
@@ -46754,7 +46761,7 @@
       <c r="F14" s="547"/>
       <c r="G14" s="547"/>
     </row>
-    <row r="15" spans="1:20" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="665" t="s">
         <v>271</v>
       </c>
@@ -46780,7 +46787,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="666"/>
       <c r="B16" s="667"/>
       <c r="C16" s="668"/>
@@ -46790,7 +46797,7 @@
       <c r="G16" s="703"/>
       <c r="H16" s="703"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="666"/>
       <c r="B17" s="667"/>
       <c r="C17" s="668"/>
@@ -46800,7 +46807,7 @@
       <c r="G17" s="703"/>
       <c r="H17" s="703"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="547"/>
       <c r="B18" s="547"/>
       <c r="C18" s="547"/>
@@ -46809,7 +46816,7 @@
       <c r="F18" s="547"/>
       <c r="G18" s="547"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="664"/>
       <c r="B19" s="663" t="s">
         <v>180</v>
@@ -46833,24 +46840,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:15" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="912" t="s">
+    <row r="20" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:15" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="911" t="s">
         <v>164</v>
       </c>
-      <c r="D21" s="913"/>
-      <c r="E21" s="913"/>
-      <c r="F21" s="913"/>
-      <c r="G21" s="913"/>
-      <c r="H21" s="914"/>
-    </row>
-    <row r="22" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="915"/>
-      <c r="D22" s="916"/>
-      <c r="E22" s="916"/>
-      <c r="F22" s="916"/>
-      <c r="G22" s="916"/>
-      <c r="H22" s="917"/>
+      <c r="D21" s="912"/>
+      <c r="E21" s="912"/>
+      <c r="F21" s="912"/>
+      <c r="G21" s="912"/>
+      <c r="H21" s="913"/>
+    </row>
+    <row r="22" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="914"/>
+      <c r="D22" s="915"/>
+      <c r="E22" s="915"/>
+      <c r="F22" s="915"/>
+      <c r="G22" s="915"/>
+      <c r="H22" s="916"/>
       <c r="J22" s="670"/>
       <c r="K22" s="671" t="s">
         <v>165</v>
@@ -46860,7 +46867,7 @@
       <c r="N22" s="671"/>
       <c r="O22" s="672"/>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="673">
         <f t="shared" ref="C23:H23" si="0">+C15</f>
         <v>20</v>
@@ -46888,7 +46895,7 @@
       <c r="J23" s="676"/>
       <c r="O23" s="677"/>
     </row>
-    <row r="24" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C24" s="678">
         <f t="shared" ref="C24:H24" si="1">C19</f>
         <v>0</v>
@@ -46924,13 +46931,13 @@
       <c r="N24" s="548"/>
       <c r="O24" s="677"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="494"/>
       <c r="B25" s="495"/>
       <c r="J25" s="676"/>
       <c r="O25" s="677"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="681"/>
       <c r="B26" s="682" t="s">
         <v>174</v>
@@ -46946,7 +46953,7 @@
       <c r="J26" s="676"/>
       <c r="O26" s="677"/>
     </row>
-    <row r="27" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="683" t="str">
         <f>+datos!C10</f>
         <v>-</v>
@@ -46972,21 +46979,21 @@
       <c r="N27" s="686"/>
       <c r="O27" s="677"/>
     </row>
-    <row r="28" spans="1:15" ht="13.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="908" t="s">
+    <row r="28" spans="1:15" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="907" t="s">
         <v>318</v>
       </c>
-      <c r="C28" s="918" t="s">
+      <c r="C28" s="917" t="s">
         <v>342</v>
       </c>
-      <c r="D28" s="918" t="s">
+      <c r="D28" s="917" t="s">
         <v>321</v>
       </c>
-      <c r="E28" s="910" t="s">
+      <c r="E28" s="909" t="s">
         <v>320</v>
       </c>
-      <c r="G28" s="920"/>
-      <c r="H28" s="920"/>
+      <c r="G28" s="919"/>
+      <c r="H28" s="919"/>
       <c r="J28" s="676"/>
       <c r="K28" s="551" t="s">
         <v>170</v>
@@ -47003,14 +47010,14 @@
       </c>
       <c r="O28" s="677"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="681"/>
-      <c r="B29" s="909"/>
-      <c r="C29" s="919"/>
-      <c r="D29" s="919"/>
-      <c r="E29" s="911"/>
-      <c r="G29" s="920"/>
-      <c r="H29" s="920"/>
+      <c r="B29" s="908"/>
+      <c r="C29" s="918"/>
+      <c r="D29" s="918"/>
+      <c r="E29" s="910"/>
+      <c r="G29" s="919"/>
+      <c r="H29" s="919"/>
       <c r="J29" s="676"/>
       <c r="K29" s="551" t="s">
         <v>237</v>
@@ -47027,7 +47034,7 @@
       </c>
       <c r="O29" s="677"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="681"/>
       <c r="B30" s="544" t="s">
         <v>170</v>
@@ -47062,7 +47069,7 @@
       </c>
       <c r="O30" s="677"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="681"/>
       <c r="B31" s="544" t="s">
         <v>237</v>
@@ -47097,7 +47104,7 @@
       </c>
       <c r="O31" s="677"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="681"/>
       <c r="B32" s="544" t="s">
         <v>172</v>
@@ -47132,7 +47139,7 @@
       </c>
       <c r="O32" s="677"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="681"/>
       <c r="B33" s="544" t="s">
         <v>173</v>
@@ -47167,7 +47174,7 @@
       </c>
       <c r="O33" s="677"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="681"/>
       <c r="B34" s="544" t="s">
         <v>175</v>
@@ -47202,7 +47209,7 @@
       </c>
       <c r="O34" s="677"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="681"/>
       <c r="B35" s="544" t="s">
         <v>18</v>
@@ -47237,7 +47244,7 @@
       </c>
       <c r="O35" s="677"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="681"/>
       <c r="B36" s="544" t="s">
         <v>32</v>
@@ -47272,7 +47279,7 @@
       </c>
       <c r="O36" s="677"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="681"/>
       <c r="B37" s="544" t="s">
         <v>19</v>
@@ -47307,18 +47314,18 @@
       </c>
       <c r="O37" s="677"/>
     </row>
-    <row r="38" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="681"/>
       <c r="B38" s="545" t="s">
         <v>155</v>
       </c>
       <c r="C38" s="693">
         <f>+datos!E36</f>
-        <v>11.799961178</v>
+        <v>0</v>
       </c>
       <c r="D38" s="693">
         <f t="shared" si="3"/>
-        <v>11.799961178</v>
+        <v>0</v>
       </c>
       <c r="E38" s="694">
         <f t="shared" si="4"/>
@@ -47342,18 +47349,18 @@
       </c>
       <c r="O38" s="677"/>
     </row>
-    <row r="39" spans="1:15" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="13.8" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A39" s="681"/>
       <c r="B39" s="546" t="s">
         <v>156</v>
       </c>
       <c r="C39" s="695">
         <f>+datos!E37</f>
-        <v>70.499768055000004</v>
+        <v>0</v>
       </c>
       <c r="D39" s="695">
         <f>IF(B27="Fraccionada",C39,D38+C39)</f>
-        <v>82.299729233000008</v>
+        <v>0</v>
       </c>
       <c r="E39" s="696">
         <f t="shared" si="4"/>
@@ -47377,18 +47384,18 @@
       </c>
       <c r="O39" s="677"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="681"/>
       <c r="B40" s="544" t="s">
         <v>160</v>
       </c>
       <c r="C40" s="689">
         <f>+datos!E38</f>
-        <v>18.799938147999999</v>
+        <v>0</v>
       </c>
       <c r="D40" s="689">
         <f t="shared" ref="D40:D46" si="6">D39+C40</f>
-        <v>101.099667381</v>
+        <v>0</v>
       </c>
       <c r="E40" s="690">
         <f t="shared" si="4"/>
@@ -47412,18 +47419,18 @@
       </c>
       <c r="O40" s="677"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="681"/>
       <c r="B41" s="544" t="s">
         <v>157</v>
       </c>
       <c r="C41" s="689">
         <f>+datos!E39</f>
-        <v>79.799737457999996</v>
+        <v>0</v>
       </c>
       <c r="D41" s="689">
         <f t="shared" si="6"/>
-        <v>180.899404839</v>
+        <v>0</v>
       </c>
       <c r="E41" s="690">
         <f t="shared" si="4"/>
@@ -47447,18 +47454,18 @@
       </c>
       <c r="O41" s="677"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="681"/>
       <c r="B42" s="544" t="s">
         <v>161</v>
       </c>
       <c r="C42" s="689">
         <f>+datos!E40</f>
-        <v>80.799734168000001</v>
+        <v>0</v>
       </c>
       <c r="D42" s="689">
         <f t="shared" si="6"/>
-        <v>261.69913900699999</v>
+        <v>0</v>
       </c>
       <c r="E42" s="690">
         <f t="shared" si="4"/>
@@ -47482,18 +47489,18 @@
       </c>
       <c r="O42" s="677"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="681"/>
       <c r="B43" s="544" t="s">
         <v>162</v>
       </c>
       <c r="C43" s="689">
         <f>+datos!E41</f>
-        <v>30.999898009999999</v>
+        <v>0</v>
       </c>
       <c r="D43" s="689">
         <f t="shared" si="6"/>
-        <v>292.69903701699997</v>
+        <v>0</v>
       </c>
       <c r="E43" s="690">
         <f t="shared" si="4"/>
@@ -47517,18 +47524,18 @@
       </c>
       <c r="O43" s="677"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="681"/>
       <c r="B44" s="544" t="s">
         <v>158</v>
       </c>
       <c r="C44" s="689">
         <f>+datos!E42</f>
-        <v>21.499929264999999</v>
+        <v>0</v>
       </c>
       <c r="D44" s="689">
         <f t="shared" si="6"/>
-        <v>314.19896628199996</v>
+        <v>0</v>
       </c>
       <c r="E44" s="690">
         <f t="shared" si="4"/>
@@ -47550,18 +47557,18 @@
       <c r="N44" s="697"/>
       <c r="O44" s="677"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="681"/>
       <c r="B45" s="544" t="s">
         <v>159</v>
       </c>
       <c r="C45" s="689">
         <f>+datos!E43</f>
-        <v>30.799898668000001</v>
+        <v>0</v>
       </c>
       <c r="D45" s="689">
         <f>D44+C45</f>
-        <v>344.99886494999998</v>
+        <v>0</v>
       </c>
       <c r="E45" s="690">
         <f t="shared" si="4"/>
@@ -47572,18 +47579,18 @@
       <c r="J45" s="681"/>
       <c r="O45" s="677"/>
     </row>
-    <row r="46" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="681"/>
       <c r="B46" s="545" t="s">
         <v>163</v>
       </c>
       <c r="C46" s="693">
         <f>+datos!E44</f>
-        <v>14.899950979</v>
+        <v>0</v>
       </c>
       <c r="D46" s="693">
         <f t="shared" si="6"/>
-        <v>359.89881592899997</v>
+        <v>0</v>
       </c>
       <c r="E46" s="690">
         <f t="shared" si="4"/>
@@ -47598,32 +47605,32 @@
       <c r="N46" s="554"/>
       <c r="O46" s="698"/>
     </row>
-    <row r="47" spans="1:15" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" ht="13.8" thickTop="1" x14ac:dyDescent="0.25">
       <c r="H47" s="493"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H48" s="493"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="802" t="s">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="801" t="s">
         <v>176</v>
       </c>
-      <c r="C49" s="803"/>
+      <c r="C49" s="802"/>
       <c r="H49" s="555"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="800" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="799" t="s">
         <v>474</v>
       </c>
-      <c r="D50" s="801">
+      <c r="D50" s="800">
         <v>46142</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="53.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" ht="53.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="556" t="s">
         <v>167</v>
       </c>
-      <c r="B52" s="799" t="s">
+      <c r="B52" s="798" t="s">
         <v>348</v>
       </c>
       <c r="C52" s="567" t="s">
@@ -47632,7 +47639,7 @@
       <c r="D52" s="579"/>
       <c r="E52" s="557"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="558" t="s">
         <v>170</v>
       </c>
@@ -47645,7 +47652,7 @@
       <c r="D53" s="700"/>
       <c r="E53" s="700"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="558" t="s">
         <v>237</v>
       </c>
@@ -47658,7 +47665,7 @@
       <c r="D54" s="700"/>
       <c r="E54" s="700"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="558" t="s">
         <v>172</v>
       </c>
@@ -47671,7 +47678,7 @@
       <c r="D55" s="700"/>
       <c r="E55" s="700"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="558" t="s">
         <v>173</v>
       </c>
@@ -47684,7 +47691,7 @@
       <c r="D56" s="700"/>
       <c r="E56" s="700"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="558" t="s">
         <v>175</v>
       </c>
@@ -47697,7 +47704,7 @@
       <c r="D57" s="700"/>
       <c r="E57" s="700"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="558" t="s">
         <v>18</v>
       </c>
@@ -47710,7 +47717,7 @@
       <c r="D58" s="700"/>
       <c r="E58" s="700"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="558" t="s">
         <v>32</v>
       </c>
@@ -47723,7 +47730,7 @@
       <c r="D59" s="700"/>
       <c r="E59" s="700"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="558" t="s">
         <v>19</v>
       </c>
@@ -47736,7 +47743,7 @@
       <c r="D60" s="700"/>
       <c r="E60" s="700"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="558" t="s">
         <v>155</v>
       </c>
@@ -47749,7 +47756,7 @@
       <c r="D61" s="700"/>
       <c r="E61" s="700"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="558" t="s">
         <v>156</v>
       </c>
@@ -47762,7 +47769,7 @@
       <c r="D62" s="700"/>
       <c r="E62" s="700"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="558" t="s">
         <v>160</v>
       </c>
@@ -47775,7 +47782,7 @@
       <c r="D63" s="700"/>
       <c r="E63" s="700"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="558" t="s">
         <v>157</v>
       </c>
@@ -47788,7 +47795,7 @@
       <c r="D64" s="700"/>
       <c r="E64" s="700"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="558" t="s">
         <v>238</v>
       </c>
@@ -47801,7 +47808,7 @@
       <c r="D65" s="700"/>
       <c r="E65" s="700"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="558" t="s">
         <v>162</v>
       </c>
@@ -47814,7 +47821,7 @@
       <c r="D66" s="700"/>
       <c r="E66" s="700"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="558" t="s">
         <v>158</v>
       </c>
@@ -47827,7 +47834,7 @@
       <c r="D67" s="700"/>
       <c r="E67" s="700"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="558" t="s">
         <v>159</v>
       </c>
@@ -47840,7 +47847,7 @@
       <c r="D68" s="700"/>
       <c r="E68" s="700"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="558" t="s">
         <v>163</v>
       </c>
@@ -47873,70 +47880,70 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20AEEFE-47A3-4B0A-A4E5-DEA5C4050938}">
   <dimension ref="A1:AE75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.28515625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" style="87" customWidth="1"/>
-    <col min="2" max="7" width="8.28515625" style="87" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" style="87" customWidth="1"/>
-    <col min="9" max="10" width="10.5703125" style="87" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="86" customWidth="1"/>
-    <col min="12" max="12" width="2.85546875" style="86" customWidth="1"/>
-    <col min="13" max="13" width="6.28515625" style="86" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="87" customWidth="1"/>
+    <col min="2" max="7" width="8.33203125" style="87" customWidth="1"/>
+    <col min="8" max="8" width="4.6640625" style="87" customWidth="1"/>
+    <col min="9" max="10" width="10.5546875" style="87" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="86" customWidth="1"/>
+    <col min="12" max="12" width="2.88671875" style="86" customWidth="1"/>
+    <col min="13" max="13" width="6.33203125" style="86" customWidth="1"/>
     <col min="14" max="15" width="7" style="87" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" style="87" customWidth="1"/>
-    <col min="17" max="17" width="11.28515625" style="87" customWidth="1"/>
-    <col min="18" max="18" width="4.42578125" style="87" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" style="87" customWidth="1"/>
-    <col min="20" max="20" width="5.5703125" style="87" customWidth="1"/>
-    <col min="21" max="22" width="8.5703125" style="87" customWidth="1"/>
-    <col min="23" max="23" width="11.85546875" style="87" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" style="87" customWidth="1"/>
+    <col min="17" max="17" width="11.33203125" style="87" customWidth="1"/>
+    <col min="18" max="18" width="4.44140625" style="87" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" style="87" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" style="87" customWidth="1"/>
+    <col min="21" max="22" width="8.5546875" style="87" customWidth="1"/>
+    <col min="23" max="23" width="11.88671875" style="87" customWidth="1"/>
     <col min="24" max="24" width="8" style="87" customWidth="1"/>
-    <col min="25" max="255" width="11.42578125" style="87" customWidth="1"/>
-    <col min="256" max="16384" width="12.28515625" style="87"/>
+    <col min="25" max="255" width="11.44140625" style="87" customWidth="1"/>
+    <col min="256" max="16384" width="12.33203125" style="87"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K1" s="87"/>
     </row>
-    <row r="2" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="934" t="s">
+    <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="921" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="934"/>
-      <c r="C5" s="934"/>
-      <c r="D5" s="934"/>
-      <c r="E5" s="934"/>
-      <c r="F5" s="934"/>
-      <c r="G5" s="934"/>
-      <c r="H5" s="934"/>
-      <c r="I5" s="934"/>
-      <c r="J5" s="934"/>
-      <c r="K5" s="934"/>
-    </row>
-    <row r="6" spans="1:31" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="941">
+      <c r="B5" s="921"/>
+      <c r="C5" s="921"/>
+      <c r="D5" s="921"/>
+      <c r="E5" s="921"/>
+      <c r="F5" s="921"/>
+      <c r="G5" s="921"/>
+      <c r="H5" s="921"/>
+      <c r="I5" s="921"/>
+      <c r="J5" s="921"/>
+      <c r="K5" s="921"/>
+    </row>
+    <row r="6" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="928">
         <f>+K12</f>
         <v>32</v>
       </c>
-      <c r="B6" s="941"/>
-      <c r="C6" s="941"/>
-      <c r="D6" s="941"/>
-      <c r="E6" s="941"/>
-      <c r="F6" s="941"/>
-      <c r="G6" s="941"/>
-      <c r="H6" s="941"/>
-      <c r="I6" s="941"/>
-      <c r="J6" s="941"/>
-      <c r="K6" s="941"/>
+      <c r="B6" s="928"/>
+      <c r="C6" s="928"/>
+      <c r="D6" s="928"/>
+      <c r="E6" s="928"/>
+      <c r="F6" s="928"/>
+      <c r="G6" s="928"/>
+      <c r="H6" s="928"/>
+      <c r="I6" s="928"/>
+      <c r="J6" s="928"/>
+      <c r="K6" s="928"/>
       <c r="S6" s="259" t="s">
         <v>101</v>
       </c>
@@ -47951,7 +47958,7 @@
       <c r="AB6" s="264"/>
       <c r="AC6" s="265"/>
     </row>
-    <row r="7" spans="1:31" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R7" s="88"/>
       <c r="S7" s="266" t="s">
         <v>102</v>
@@ -47971,7 +47978,7 @@
       <c r="AD7" s="88"/>
       <c r="AE7" s="88"/>
     </row>
-    <row r="8" spans="1:31" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R8" s="88"/>
       <c r="S8" s="272" t="s">
         <v>104</v>
@@ -47991,7 +47998,7 @@
       <c r="AD8" s="88"/>
       <c r="AE8" s="88"/>
     </row>
-    <row r="9" spans="1:31" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="281" t="s">
         <v>106</v>
       </c>
@@ -48013,10 +48020,10 @@
       <c r="S9" s="275" t="s">
         <v>105</v>
       </c>
-      <c r="T9" s="945">
+      <c r="T9" s="932">
         <v>44090</v>
       </c>
-      <c r="U9" s="945"/>
+      <c r="U9" s="932"/>
       <c r="V9" s="276"/>
       <c r="W9" s="277"/>
       <c r="X9" s="276"/>
@@ -48028,7 +48035,7 @@
       <c r="AD9" s="89"/>
       <c r="AE9" s="89"/>
     </row>
-    <row r="10" spans="1:31" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="281" t="s">
         <v>107</v>
       </c>
@@ -48065,7 +48072,7 @@
       <c r="AD10" s="89"/>
       <c r="AE10" s="89"/>
     </row>
-    <row r="11" spans="1:31" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="281" t="s">
         <v>109</v>
       </c>
@@ -48102,7 +48109,7 @@
       <c r="AD11" s="89"/>
       <c r="AE11" s="89"/>
     </row>
-    <row r="12" spans="1:31" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="281" t="s">
         <v>110</v>
       </c>
@@ -48139,7 +48146,7 @@
       <c r="AD12" s="89"/>
       <c r="AE12" s="89"/>
     </row>
-    <row r="13" spans="1:31" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="282" t="s">
         <v>111</v>
       </c>
@@ -48160,20 +48167,20 @@
       <c r="R13" s="86"/>
       <c r="S13" s="86"/>
     </row>
-    <row r="14" spans="1:31" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="942" t="s">
+    <row r="14" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="929" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="943"/>
-      <c r="C14" s="943"/>
-      <c r="D14" s="943"/>
-      <c r="E14" s="943"/>
-      <c r="F14" s="943"/>
-      <c r="G14" s="943"/>
-      <c r="H14" s="943"/>
-      <c r="I14" s="943"/>
-      <c r="J14" s="943"/>
-      <c r="K14" s="944"/>
+      <c r="B14" s="930"/>
+      <c r="C14" s="930"/>
+      <c r="D14" s="930"/>
+      <c r="E14" s="930"/>
+      <c r="F14" s="930"/>
+      <c r="G14" s="930"/>
+      <c r="H14" s="930"/>
+      <c r="I14" s="930"/>
+      <c r="J14" s="930"/>
+      <c r="K14" s="931"/>
       <c r="L14" s="87"/>
       <c r="M14" s="87"/>
       <c r="P14" s="86"/>
@@ -48181,20 +48188,20 @@
       <c r="R14" s="86"/>
       <c r="S14" s="86"/>
     </row>
-    <row r="15" spans="1:31" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="949" t="s">
+    <row r="15" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="936" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="950"/>
-      <c r="C15" s="950"/>
-      <c r="D15" s="950"/>
-      <c r="E15" s="950"/>
-      <c r="F15" s="950"/>
-      <c r="G15" s="950"/>
-      <c r="H15" s="950"/>
-      <c r="I15" s="950"/>
-      <c r="J15" s="950"/>
-      <c r="K15" s="951"/>
+      <c r="B15" s="937"/>
+      <c r="C15" s="937"/>
+      <c r="D15" s="937"/>
+      <c r="E15" s="937"/>
+      <c r="F15" s="937"/>
+      <c r="G15" s="937"/>
+      <c r="H15" s="937"/>
+      <c r="I15" s="937"/>
+      <c r="J15" s="937"/>
+      <c r="K15" s="938"/>
       <c r="L15" s="87"/>
       <c r="M15" s="87"/>
       <c r="P15" s="86"/>
@@ -48202,7 +48209,7 @@
       <c r="R15" s="86"/>
       <c r="S15" s="86"/>
     </row>
-    <row r="16" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="194"/>
       <c r="B16" s="195"/>
       <c r="C16" s="195"/>
@@ -48221,18 +48228,18 @@
       <c r="R16" s="86"/>
       <c r="S16" s="86"/>
     </row>
-    <row r="17" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="939" t="s">
+    <row r="17" spans="1:27" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="926" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="940"/>
-      <c r="C17" s="940"/>
-      <c r="D17" s="940"/>
-      <c r="E17" s="940"/>
-      <c r="F17" s="940"/>
-      <c r="G17" s="940"/>
-      <c r="H17" s="940"/>
-      <c r="I17" s="940"/>
+      <c r="B17" s="927"/>
+      <c r="C17" s="927"/>
+      <c r="D17" s="927"/>
+      <c r="E17" s="927"/>
+      <c r="F17" s="927"/>
+      <c r="G17" s="927"/>
+      <c r="H17" s="927"/>
+      <c r="I17" s="927"/>
       <c r="J17" s="1"/>
       <c r="K17" s="199"/>
       <c r="L17" s="87"/>
@@ -48242,7 +48249,7 @@
       <c r="R17" s="86"/>
       <c r="S17" s="86"/>
     </row>
-    <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="286" t="s">
         <v>113</v>
       </c>
@@ -48272,7 +48279,7 @@
       <c r="S18" s="86"/>
       <c r="Z18" s="157"/>
     </row>
-    <row r="19" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="286" t="s">
         <v>115</v>
       </c>
@@ -48300,27 +48307,27 @@
       <c r="Q19" s="86"/>
       <c r="R19" s="86"/>
       <c r="S19" s="86"/>
-      <c r="U19" s="922" t="s">
+      <c r="U19" s="940" t="s">
         <v>9</v>
       </c>
-      <c r="V19" s="923"/>
-      <c r="W19" s="933" t="s">
+      <c r="V19" s="941"/>
+      <c r="W19" s="920" t="s">
         <v>100</v>
       </c>
-      <c r="X19" s="845" t="s">
+      <c r="X19" s="834" t="s">
         <v>45</v>
       </c>
-      <c r="Y19" s="845" t="s">
+      <c r="Y19" s="834" t="s">
         <v>41</v>
       </c>
-      <c r="Z19" s="845" t="s">
+      <c r="Z19" s="834" t="s">
         <v>42</v>
       </c>
-      <c r="AA19" s="845" t="s">
+      <c r="AA19" s="834" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="286" t="s">
         <v>116</v>
       </c>
@@ -48354,13 +48361,13 @@
       <c r="V20" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="W20" s="933"/>
-      <c r="X20" s="846"/>
-      <c r="Y20" s="846"/>
-      <c r="Z20" s="846"/>
-      <c r="AA20" s="846"/>
-    </row>
-    <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W20" s="920"/>
+      <c r="X20" s="835"/>
+      <c r="Y20" s="835"/>
+      <c r="Z20" s="835"/>
+      <c r="AA20" s="835"/>
+    </row>
+    <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="288" t="s">
         <v>118</v>
       </c>
@@ -48411,7 +48418,7 @@
       <c r="Z21" s="153"/>
       <c r="AA21" s="163"/>
     </row>
-    <row r="22" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="141"/>
       <c r="B22" s="247"/>
       <c r="C22" s="226"/>
@@ -48449,29 +48456,29 @@
       <c r="Z22" s="154"/>
       <c r="AA22" s="97"/>
     </row>
-    <row r="23" spans="1:27" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="140"/>
-      <c r="B23" s="922" t="s">
+      <c r="B23" s="940" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="923"/>
-      <c r="D23" s="845" t="s">
+      <c r="C23" s="941"/>
+      <c r="D23" s="834" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="845" t="s">
+      <c r="E23" s="834" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="845" t="s">
+      <c r="F23" s="834" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="845" t="s">
+      <c r="G23" s="834" t="s">
         <v>43</v>
       </c>
       <c r="H23" s="138"/>
-      <c r="I23" s="927" t="s">
+      <c r="I23" s="945" t="s">
         <v>36</v>
       </c>
-      <c r="J23" s="928"/>
+      <c r="J23" s="946"/>
       <c r="K23" s="139"/>
       <c r="L23" s="91"/>
       <c r="M23" s="91"/>
@@ -48512,16 +48519,16 @@
       <c r="C24" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="846"/>
-      <c r="E24" s="846"/>
-      <c r="F24" s="846"/>
-      <c r="G24" s="846"/>
+      <c r="D24" s="835"/>
+      <c r="E24" s="835"/>
+      <c r="F24" s="835"/>
+      <c r="G24" s="835"/>
       <c r="H24" s="156"/>
-      <c r="I24" s="930">
+      <c r="I24" s="948">
         <f>+Q23</f>
         <v>23983.979695431473</v>
       </c>
-      <c r="J24" s="931"/>
+      <c r="J24" s="949"/>
       <c r="K24" s="139"/>
       <c r="L24" s="91"/>
       <c r="M24" s="91"/>
@@ -48552,7 +48559,7 @@
         <v>88.092057449531538</v>
       </c>
     </row>
-    <row r="25" spans="1:27" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="140"/>
       <c r="B25" s="153" t="s">
         <v>75</v>
@@ -48613,7 +48620,7 @@
         <v>76.984648852035747</v>
       </c>
     </row>
-    <row r="26" spans="1:27" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="140"/>
       <c r="B26" s="93" t="s">
         <v>76</v>
@@ -48635,10 +48642,10 @@
       </c>
       <c r="G26" s="97"/>
       <c r="H26" s="142"/>
-      <c r="I26" s="929" t="s">
+      <c r="I26" s="947" t="s">
         <v>92</v>
       </c>
-      <c r="J26" s="929"/>
+      <c r="J26" s="947"/>
       <c r="K26" s="143"/>
       <c r="L26" s="91"/>
       <c r="M26" s="91"/>
@@ -48679,7 +48686,7 @@
         <v>57.746817294661284</v>
       </c>
     </row>
-    <row r="27" spans="1:27" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="140"/>
       <c r="B27" s="93" t="s">
         <v>77</v>
@@ -48889,16 +48896,16 @@
         <v>57.746817294661284</v>
       </c>
       <c r="H30" s="142"/>
-      <c r="I30" s="938"/>
-      <c r="J30" s="938"/>
+      <c r="I30" s="925"/>
+      <c r="J30" s="925"/>
       <c r="K30" s="143"/>
       <c r="L30" s="91"/>
-      <c r="M30" s="946" t="s">
+      <c r="M30" s="933" t="s">
         <v>74</v>
       </c>
-      <c r="N30" s="947"/>
-      <c r="O30" s="947"/>
-      <c r="P30" s="948"/>
+      <c r="N30" s="934"/>
+      <c r="O30" s="934"/>
+      <c r="P30" s="935"/>
       <c r="T30" s="99"/>
       <c r="U30" s="93" t="s">
         <v>88</v>
@@ -48951,16 +48958,16 @@
         <v>38.462771103509866</v>
       </c>
       <c r="H31" s="142"/>
-      <c r="I31" s="938"/>
-      <c r="J31" s="938"/>
+      <c r="I31" s="925"/>
+      <c r="J31" s="925"/>
       <c r="K31" s="143"/>
       <c r="L31" s="91"/>
-      <c r="M31" s="935" t="s">
+      <c r="M31" s="922" t="s">
         <v>82</v>
       </c>
-      <c r="N31" s="936"/>
-      <c r="O31" s="936"/>
-      <c r="P31" s="937"/>
+      <c r="N31" s="923"/>
+      <c r="O31" s="923"/>
+      <c r="P31" s="924"/>
       <c r="T31" s="99"/>
       <c r="U31" s="147" t="s">
         <v>90</v>
@@ -49125,11 +49132,11 @@
         <f t="shared" ref="U34:U42" si="10">+T34</f>
         <v>25.4</v>
       </c>
-      <c r="Z34" s="924" t="s">
+      <c r="Z34" s="942" t="s">
         <v>89</v>
       </c>
-      <c r="AA34" s="925"/>
-      <c r="AB34" s="925"/>
+      <c r="AA34" s="943"/>
+      <c r="AB34" s="943"/>
     </row>
     <row r="35" spans="1:28" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="140"/>
@@ -49192,7 +49199,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="125"/>
       <c r="I36" s="90"/>
       <c r="J36" s="90"/>
@@ -49228,7 +49235,7 @@
       </c>
       <c r="AB36" s="107"/>
     </row>
-    <row r="37" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="108"/>
       <c r="B37" s="109"/>
       <c r="C37" s="109"/>
@@ -49268,7 +49275,7 @@
       </c>
       <c r="AB37" s="107"/>
     </row>
-    <row r="38" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="112"/>
       <c r="K38" s="256"/>
       <c r="M38" s="101" t="str">
@@ -49302,7 +49309,7 @@
       </c>
       <c r="AB38" s="107"/>
     </row>
-    <row r="39" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="112"/>
       <c r="K39" s="256"/>
       <c r="M39" s="101" t="str">
@@ -49336,7 +49343,7 @@
       </c>
       <c r="AB39" s="107"/>
     </row>
-    <row r="40" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="112"/>
       <c r="K40" s="256"/>
       <c r="M40" s="101" t="str">
@@ -49370,7 +49377,7 @@
       </c>
       <c r="AB40" s="107"/>
     </row>
-    <row r="41" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="112"/>
       <c r="K41" s="256"/>
       <c r="M41" s="101" t="str">
@@ -49404,7 +49411,7 @@
       </c>
       <c r="AB41" s="107"/>
     </row>
-    <row r="42" spans="1:28" ht="14.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="14.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="112"/>
       <c r="K42" s="256"/>
       <c r="M42" s="113" t="str">
@@ -49438,7 +49445,7 @@
       </c>
       <c r="AB42" s="107"/>
     </row>
-    <row r="43" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="112"/>
       <c r="K43" s="256"/>
       <c r="M43" s="91"/>
@@ -49453,7 +49460,7 @@
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
     </row>
-    <row r="44" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="112"/>
       <c r="K44" s="256"/>
       <c r="M44" s="91"/>
@@ -49468,7 +49475,7 @@
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
     </row>
-    <row r="45" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="112"/>
       <c r="K45" s="256"/>
       <c r="M45" s="91"/>
@@ -49483,7 +49490,7 @@
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
     </row>
-    <row r="46" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="112"/>
       <c r="K46" s="256"/>
       <c r="M46" s="91"/>
@@ -49498,7 +49505,7 @@
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
     </row>
-    <row r="47" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="112"/>
       <c r="K47" s="256"/>
       <c r="M47" s="91"/>
@@ -49513,7 +49520,7 @@
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
     </row>
-    <row r="48" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="112"/>
       <c r="K48" s="256"/>
       <c r="M48" s="122"/>
@@ -49528,7 +49535,7 @@
       <c r="V48" s="123"/>
       <c r="W48" s="123"/>
     </row>
-    <row r="49" spans="1:24" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="112"/>
       <c r="K49" s="256"/>
       <c r="M49" s="122"/>
@@ -49543,7 +49550,7 @@
       <c r="V49" s="123"/>
       <c r="W49" s="123"/>
     </row>
-    <row r="50" spans="1:24" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="112"/>
       <c r="K50" s="256"/>
       <c r="M50" s="122"/>
@@ -49558,7 +49565,7 @@
       <c r="V50" s="123"/>
       <c r="W50" s="123"/>
     </row>
-    <row r="51" spans="1:24" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="125"/>
       <c r="B51" s="90"/>
       <c r="C51" s="90"/>
@@ -49582,7 +49589,7 @@
       <c r="V51" s="123"/>
       <c r="W51" s="123"/>
     </row>
-    <row r="52" spans="1:24" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="238" t="s">
         <v>3</v>
       </c>
@@ -49608,7 +49615,7 @@
       <c r="V52" s="123"/>
       <c r="W52" s="123"/>
     </row>
-    <row r="53" spans="1:24" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K53" s="87"/>
       <c r="M53" s="122"/>
       <c r="N53" s="123"/>
@@ -49622,7 +49629,7 @@
       <c r="V53" s="123"/>
       <c r="W53" s="123"/>
     </row>
-    <row r="54" spans="1:24" s="4" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" s="4" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -49646,7 +49653,7 @@
       <c r="V54" s="123"/>
       <c r="W54" s="123"/>
     </row>
-    <row r="55" spans="1:24" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24" s="5" customFormat="1" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="87"/>
       <c r="E55" s="87"/>
       <c r="F55" s="87"/>
@@ -49668,7 +49675,7 @@
       <c r="V55" s="123"/>
       <c r="W55" s="123"/>
     </row>
-    <row r="56" spans="1:24" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
         <v>4</v>
       </c>
@@ -49687,20 +49694,20 @@
       <c r="V56" s="123"/>
       <c r="W56" s="123"/>
     </row>
-    <row r="57" spans="1:24" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
         <v>99</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="926"/>
-      <c r="E57" s="926"/>
-      <c r="F57" s="926"/>
-      <c r="G57" s="926"/>
-      <c r="H57" s="926"/>
-      <c r="I57" s="926"/>
-      <c r="J57" s="926"/>
-      <c r="K57" s="926"/>
+      <c r="D57" s="944"/>
+      <c r="E57" s="944"/>
+      <c r="F57" s="944"/>
+      <c r="G57" s="944"/>
+      <c r="H57" s="944"/>
+      <c r="I57" s="944"/>
+      <c r="J57" s="944"/>
+      <c r="K57" s="944"/>
       <c r="M57" s="91"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
@@ -49739,7 +49746,7 @@
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="296" t="s">
         <v>121</v>
       </c>
@@ -49765,20 +49772,20 @@
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
     </row>
-    <row r="60" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="932" t="s">
+    <row r="60" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="950" t="s">
         <v>122</v>
       </c>
-      <c r="B60" s="932"/>
-      <c r="C60" s="932"/>
-      <c r="D60" s="932"/>
-      <c r="E60" s="932"/>
-      <c r="F60" s="932"/>
-      <c r="G60" s="932"/>
-      <c r="H60" s="932"/>
-      <c r="I60" s="932"/>
-      <c r="J60" s="932"/>
-      <c r="K60" s="932"/>
+      <c r="B60" s="950"/>
+      <c r="C60" s="950"/>
+      <c r="D60" s="950"/>
+      <c r="E60" s="950"/>
+      <c r="F60" s="950"/>
+      <c r="G60" s="950"/>
+      <c r="H60" s="950"/>
+      <c r="I60" s="950"/>
+      <c r="J60" s="950"/>
+      <c r="K60" s="950"/>
       <c r="M60" s="91"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
@@ -49791,7 +49798,7 @@
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
     </row>
-    <row r="61" spans="1:24" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -49799,12 +49806,12 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="921" t="s">
+      <c r="H61" s="939" t="s">
         <v>123</v>
       </c>
-      <c r="I61" s="921"/>
-      <c r="J61" s="921"/>
-      <c r="K61" s="921"/>
+      <c r="I61" s="939"/>
+      <c r="J61" s="939"/>
+      <c r="K61" s="939"/>
       <c r="M61" s="91"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
@@ -49817,7 +49824,7 @@
       <c r="V61" s="4"/>
       <c r="W61" s="4"/>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="86"/>
       <c r="B62" s="86"/>
       <c r="C62" s="86"/>
@@ -49840,7 +49847,7 @@
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
     </row>
-    <row r="63" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="86"/>
       <c r="B63" s="86"/>
       <c r="C63" s="86"/>
@@ -49866,7 +49873,7 @@
       <c r="W63" s="4"/>
       <c r="X63" s="87"/>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="129"/>
       <c r="B64" s="86"/>
       <c r="C64" s="86"/>
@@ -49889,7 +49896,7 @@
       <c r="V64" s="4"/>
       <c r="W64" s="4"/>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="86"/>
       <c r="B65" s="86"/>
       <c r="C65" s="86"/>
@@ -49913,7 +49920,7 @@
       <c r="W65" s="132"/>
       <c r="X65" s="133"/>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="86"/>
       <c r="B66" s="86"/>
       <c r="C66" s="86"/>
@@ -49936,7 +49943,7 @@
       <c r="V66" s="4"/>
       <c r="W66" s="4"/>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="86"/>
       <c r="B67" s="86"/>
       <c r="C67" s="86"/>
@@ -49959,7 +49966,7 @@
       <c r="V67" s="4"/>
       <c r="W67" s="4"/>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="86"/>
       <c r="B68" s="86"/>
       <c r="C68" s="86"/>
@@ -49983,7 +49990,7 @@
       <c r="V68" s="4"/>
       <c r="W68" s="4"/>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="86"/>
       <c r="B69" s="86"/>
       <c r="C69" s="86"/>
@@ -50006,7 +50013,7 @@
       <c r="V69" s="4"/>
       <c r="W69" s="4"/>
     </row>
-    <row r="70" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="127"/>
       <c r="B70" s="127"/>
       <c r="C70" s="127"/>
@@ -50029,7 +50036,7 @@
       <c r="V70" s="4"/>
       <c r="W70" s="4"/>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="86"/>
       <c r="B71" s="86"/>
       <c r="C71" s="86"/>
@@ -50053,7 +50060,7 @@
       <c r="W71" s="4"/>
       <c r="X71" s="5"/>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="86"/>
       <c r="B72" s="86"/>
       <c r="C72" s="86"/>
@@ -50076,7 +50083,7 @@
       <c r="V72" s="4"/>
       <c r="W72" s="4"/>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="86"/>
       <c r="B73" s="86"/>
       <c r="C73" s="86"/>
@@ -50099,7 +50106,7 @@
       <c r="V73" s="4"/>
       <c r="W73" s="4"/>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" s="129"/>
       <c r="B74" s="86"/>
       <c r="C74" s="86"/>
@@ -50122,7 +50129,7 @@
       <c r="V74" s="4"/>
       <c r="W74" s="4"/>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" s="86"/>
       <c r="B75" s="86"/>
       <c r="C75" s="86"/>
@@ -50153,20 +50160,6 @@
     <protectedRange sqref="C9:C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="30">
-    <mergeCell ref="Z19:Z20"/>
-    <mergeCell ref="AA19:AA20"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="M30:P30"/>
-    <mergeCell ref="A15:K15"/>
     <mergeCell ref="H61:K61"/>
     <mergeCell ref="U19:V19"/>
     <mergeCell ref="X19:X20"/>
@@ -50183,6 +50176,20 @@
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="F23:F24"/>
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="A15:K15"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -50201,22 +50208,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AG92"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
-    <col min="2" max="7" width="8.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="7.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="14" width="7.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" customWidth="1"/>
-    <col min="16" max="19" width="7.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
+    <col min="2" max="7" width="8.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="7.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="1" customWidth="1"/>
+    <col min="13" max="14" width="7.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" style="1" customWidth="1"/>
+    <col min="16" max="19" width="7.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5546875" style="1" customWidth="1"/>
     <col min="22" max="22" width="17" style="1" customWidth="1"/>
-    <col min="23" max="24" width="10.5703125" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="10.28515625" style="1"/>
+    <col min="23" max="24" width="10.5546875" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="10.33203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -50303,35 +50310,35 @@
       <c r="X6" s="178"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="934" t="s">
+      <c r="A7" s="921" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="934"/>
-      <c r="C7" s="934"/>
-      <c r="D7" s="934"/>
-      <c r="E7" s="934"/>
-      <c r="F7" s="934"/>
-      <c r="G7" s="934"/>
-      <c r="H7" s="934"/>
-      <c r="I7" s="934"/>
-      <c r="J7" s="934"/>
-      <c r="K7" s="934"/>
+      <c r="B7" s="921"/>
+      <c r="C7" s="921"/>
+      <c r="D7" s="921"/>
+      <c r="E7" s="921"/>
+      <c r="F7" s="921"/>
+      <c r="G7" s="921"/>
+      <c r="H7" s="921"/>
+      <c r="I7" s="921"/>
+      <c r="J7" s="921"/>
+      <c r="K7" s="921"/>
       <c r="X7" s="178"/>
     </row>
     <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="961">
+      <c r="A8" s="957">
         <v>1</v>
       </c>
-      <c r="B8" s="961"/>
-      <c r="C8" s="961"/>
-      <c r="D8" s="961"/>
-      <c r="E8" s="961"/>
-      <c r="F8" s="961"/>
-      <c r="G8" s="961"/>
-      <c r="H8" s="961"/>
-      <c r="I8" s="961"/>
-      <c r="J8" s="961"/>
-      <c r="K8" s="961"/>
+      <c r="B8" s="957"/>
+      <c r="C8" s="957"/>
+      <c r="D8" s="957"/>
+      <c r="E8" s="957"/>
+      <c r="F8" s="957"/>
+      <c r="G8" s="957"/>
+      <c r="H8" s="957"/>
+      <c r="I8" s="957"/>
+      <c r="J8" s="957"/>
+      <c r="K8" s="957"/>
       <c r="X8" s="178"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -50407,15 +50414,15 @@
       <c r="K13" s="308">
         <v>43845</v>
       </c>
-      <c r="M13" s="922" t="s">
+      <c r="M13" s="940" t="s">
         <v>9</v>
       </c>
-      <c r="N13" s="923"/>
-      <c r="O13" s="954" t="s">
+      <c r="N13" s="941"/>
+      <c r="O13" s="960" t="s">
         <v>69</v>
       </c>
-      <c r="P13" s="955"/>
-      <c r="Q13" s="956"/>
+      <c r="P13" s="961"/>
+      <c r="Q13" s="962"/>
       <c r="W13" s="178"/>
       <c r="X13" s="178"/>
     </row>
@@ -50439,26 +50446,26 @@
       <c r="N14" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="O14" s="957"/>
-      <c r="P14" s="958"/>
-      <c r="Q14" s="959"/>
+      <c r="O14" s="963"/>
+      <c r="P14" s="964"/>
+      <c r="Q14" s="965"/>
       <c r="W14" s="178"/>
       <c r="X14" s="178"/>
     </row>
-    <row r="15" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="942" t="s">
+    <row r="15" spans="1:24" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A15" s="929" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="943"/>
-      <c r="C15" s="943"/>
-      <c r="D15" s="943"/>
-      <c r="E15" s="943"/>
-      <c r="F15" s="943"/>
-      <c r="G15" s="943"/>
-      <c r="H15" s="943"/>
-      <c r="I15" s="943"/>
-      <c r="J15" s="943"/>
-      <c r="K15" s="944"/>
+      <c r="B15" s="930"/>
+      <c r="C15" s="930"/>
+      <c r="D15" s="930"/>
+      <c r="E15" s="930"/>
+      <c r="F15" s="930"/>
+      <c r="G15" s="930"/>
+      <c r="H15" s="930"/>
+      <c r="I15" s="930"/>
+      <c r="J15" s="930"/>
+      <c r="K15" s="931"/>
       <c r="M15" s="77" t="s">
         <v>19</v>
       </c>
@@ -50472,19 +50479,19 @@
       <c r="X15" s="178"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="949" t="s">
+      <c r="A16" s="936" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="950"/>
-      <c r="C16" s="950"/>
-      <c r="D16" s="950"/>
-      <c r="E16" s="950"/>
-      <c r="F16" s="950"/>
-      <c r="G16" s="950"/>
-      <c r="H16" s="950"/>
-      <c r="I16" s="950"/>
-      <c r="J16" s="950"/>
-      <c r="K16" s="951"/>
+      <c r="B16" s="937"/>
+      <c r="C16" s="937"/>
+      <c r="D16" s="937"/>
+      <c r="E16" s="937"/>
+      <c r="F16" s="937"/>
+      <c r="G16" s="937"/>
+      <c r="H16" s="937"/>
+      <c r="I16" s="937"/>
+      <c r="J16" s="937"/>
+      <c r="K16" s="938"/>
       <c r="L16" s="18"/>
       <c r="M16" s="77" t="s">
         <v>20</v>
@@ -50523,17 +50530,17 @@
       <c r="X17" s="178"/>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="939" t="s">
+      <c r="A18" s="926" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="940"/>
-      <c r="C18" s="940"/>
-      <c r="D18" s="940"/>
-      <c r="E18" s="940"/>
-      <c r="F18" s="940"/>
-      <c r="G18" s="940"/>
-      <c r="H18" s="940"/>
-      <c r="I18" s="940"/>
+      <c r="B18" s="927"/>
+      <c r="C18" s="927"/>
+      <c r="D18" s="927"/>
+      <c r="E18" s="927"/>
+      <c r="F18" s="927"/>
+      <c r="G18" s="927"/>
+      <c r="H18" s="927"/>
+      <c r="I18" s="927"/>
       <c r="J18" s="291"/>
       <c r="K18" s="292"/>
       <c r="M18" s="77">
@@ -50682,15 +50689,15 @@
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
       <c r="K24" s="144"/>
-      <c r="M24" s="922" t="s">
+      <c r="M24" s="940" t="s">
         <v>71</v>
       </c>
-      <c r="N24" s="923"/>
+      <c r="N24" s="941"/>
       <c r="O24" s="294"/>
-      <c r="P24" s="952">
+      <c r="P24" s="958">
         <v>762</v>
       </c>
-      <c r="Q24" s="953"/>
+      <c r="Q24" s="959"/>
       <c r="R24" s="202"/>
       <c r="S24" s="202"/>
       <c r="V24" s="201"/>
@@ -50699,33 +50706,33 @@
     </row>
     <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20"/>
-      <c r="B25" s="922" t="s">
+      <c r="B25" s="940" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="923"/>
-      <c r="D25" s="845" t="s">
+      <c r="C25" s="941"/>
+      <c r="D25" s="834" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="845" t="s">
+      <c r="E25" s="834" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="845" t="s">
+      <c r="F25" s="834" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="845" t="s">
+      <c r="G25" s="834" t="s">
         <v>43</v>
       </c>
       <c r="H25" s="209"/>
-      <c r="I25" s="927" t="s">
+      <c r="I25" s="945" t="s">
         <v>36</v>
       </c>
-      <c r="J25" s="928"/>
+      <c r="J25" s="946"/>
       <c r="K25" s="144"/>
       <c r="M25" s="210" t="s">
         <v>9</v>
       </c>
       <c r="N25" s="211"/>
-      <c r="O25" s="933" t="s">
+      <c r="O25" s="920" t="s">
         <v>100</v>
       </c>
       <c r="P25" s="212" t="s">
@@ -50752,16 +50759,16 @@
       <c r="C26" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="846"/>
-      <c r="E26" s="846"/>
-      <c r="F26" s="846"/>
-      <c r="G26" s="846"/>
+      <c r="D26" s="835"/>
+      <c r="E26" s="835"/>
+      <c r="F26" s="835"/>
+      <c r="G26" s="835"/>
       <c r="H26" s="209"/>
-      <c r="I26" s="930">
+      <c r="I26" s="948">
         <f>+P24</f>
         <v>762</v>
       </c>
-      <c r="J26" s="931"/>
+      <c r="J26" s="949"/>
       <c r="K26" s="144"/>
       <c r="M26" s="213" t="s">
         <v>11</v>
@@ -50769,7 +50776,7 @@
       <c r="N26" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="O26" s="933"/>
+      <c r="O26" s="920"/>
       <c r="P26" s="187" t="s">
         <v>28</v>
       </c>
@@ -50869,10 +50876,10 @@
         <v>#REF!</v>
       </c>
       <c r="H28" s="218"/>
-      <c r="I28" s="963" t="s">
+      <c r="I28" s="952" t="s">
         <v>37</v>
       </c>
-      <c r="J28" s="964"/>
+      <c r="J28" s="953"/>
       <c r="K28" s="144"/>
       <c r="M28" s="220" t="s">
         <v>31</v>
@@ -50928,11 +50935,11 @@
         <v>#REF!</v>
       </c>
       <c r="H29" s="218"/>
-      <c r="I29" s="965" t="e">
+      <c r="I29" s="954" t="e">
         <f>(R30+R32+R34+R36+R37+R39+R40+R42+R43)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="J29" s="966"/>
+      <c r="J29" s="955"/>
       <c r="K29" s="144"/>
       <c r="M29" s="220" t="s">
         <v>15</v>
@@ -51048,8 +51055,8 @@
         <v>#REF!</v>
       </c>
       <c r="H31" s="218"/>
-      <c r="I31" s="938"/>
-      <c r="J31" s="938"/>
+      <c r="I31" s="925"/>
+      <c r="J31" s="925"/>
       <c r="K31" s="144"/>
       <c r="L31" s="19"/>
       <c r="M31" s="220" t="s">
@@ -51106,8 +51113,8 @@
         <v>#REF!</v>
       </c>
       <c r="H32" s="218"/>
-      <c r="I32" s="938"/>
-      <c r="J32" s="938"/>
+      <c r="I32" s="925"/>
+      <c r="J32" s="925"/>
       <c r="K32" s="144"/>
       <c r="L32" s="19"/>
       <c r="M32" s="220" t="s">
@@ -51164,8 +51171,8 @@
         <v>#REF!</v>
       </c>
       <c r="H33" s="218"/>
-      <c r="I33" s="960"/>
-      <c r="J33" s="960"/>
+      <c r="I33" s="956"/>
+      <c r="J33" s="956"/>
       <c r="K33" s="144"/>
       <c r="L33" s="19"/>
       <c r="M33" s="220" t="s">
@@ -51983,10 +51990,10 @@
       <c r="W54" s="275" t="s">
         <v>105</v>
       </c>
-      <c r="X54" s="945">
+      <c r="X54" s="932">
         <v>44090</v>
       </c>
-      <c r="Y54" s="945"/>
+      <c r="Y54" s="932"/>
       <c r="Z54" s="276"/>
       <c r="AA54" s="277"/>
       <c r="AB54" s="276"/>
@@ -52015,19 +52022,19 @@
       <c r="X57" s="178"/>
     </row>
     <row r="58" spans="1:33" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="962" t="s">
+      <c r="A58" s="951" t="s">
         <v>120</v>
       </c>
-      <c r="B58" s="962"/>
-      <c r="C58" s="962"/>
-      <c r="D58" s="962"/>
-      <c r="E58" s="962"/>
-      <c r="F58" s="962"/>
-      <c r="G58" s="962"/>
-      <c r="H58" s="962"/>
-      <c r="I58" s="962"/>
-      <c r="J58" s="962"/>
-      <c r="K58" s="962"/>
+      <c r="B58" s="951"/>
+      <c r="C58" s="951"/>
+      <c r="D58" s="951"/>
+      <c r="E58" s="951"/>
+      <c r="F58" s="951"/>
+      <c r="G58" s="951"/>
+      <c r="H58" s="951"/>
+      <c r="I58" s="951"/>
+      <c r="J58" s="951"/>
+      <c r="K58" s="951"/>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" s="310" t="s">
@@ -52045,19 +52052,19 @@
       <c r="K59" s="311"/>
     </row>
     <row r="60" spans="1:33" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="962" t="s">
+      <c r="A60" s="951" t="s">
         <v>122</v>
       </c>
-      <c r="B60" s="962"/>
-      <c r="C60" s="962"/>
-      <c r="D60" s="962"/>
-      <c r="E60" s="962"/>
-      <c r="F60" s="962"/>
-      <c r="G60" s="962"/>
-      <c r="H60" s="962"/>
-      <c r="I60" s="962"/>
-      <c r="J60" s="962"/>
-      <c r="K60" s="962"/>
+      <c r="B60" s="951"/>
+      <c r="C60" s="951"/>
+      <c r="D60" s="951"/>
+      <c r="E60" s="951"/>
+      <c r="F60" s="951"/>
+      <c r="G60" s="951"/>
+      <c r="H60" s="951"/>
+      <c r="I60" s="951"/>
+      <c r="J60" s="951"/>
+      <c r="K60" s="951"/>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B63" s="5"/>
@@ -52091,21 +52098,6 @@
     <protectedRange sqref="B10:B11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="25">
-    <mergeCell ref="X54:Y54"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A18:I18"/>
     <mergeCell ref="M24:N24"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="F25:F26"/>
@@ -52116,6 +52108,21 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="X54:Y54"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="I31:J31"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -52131,21 +52138,21 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34371A01-7980-4798-897B-47E25DE845CD}">
   <dimension ref="A1:AA56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
-    <col min="2" max="7" width="8.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="7.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="14" width="7.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" style="1" customWidth="1"/>
-    <col min="16" max="18" width="7.7109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.42578125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="10.28515625" style="1"/>
+    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
+    <col min="2" max="7" width="8.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="7.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="1" customWidth="1"/>
+    <col min="13" max="14" width="7.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.33203125" style="1" customWidth="1"/>
+    <col min="16" max="18" width="7.6640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.44140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5546875" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="10.33203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -52198,35 +52205,35 @@
       <c r="H4" s="177"/>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="934" t="s">
+      <c r="A5" s="921" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="934"/>
-      <c r="C5" s="934"/>
-      <c r="D5" s="934"/>
-      <c r="E5" s="934"/>
-      <c r="F5" s="934"/>
-      <c r="G5" s="934"/>
-      <c r="H5" s="934"/>
-      <c r="I5" s="934"/>
-      <c r="J5" s="934"/>
-      <c r="K5" s="934"/>
+      <c r="B5" s="921"/>
+      <c r="C5" s="921"/>
+      <c r="D5" s="921"/>
+      <c r="E5" s="921"/>
+      <c r="F5" s="921"/>
+      <c r="G5" s="921"/>
+      <c r="H5" s="921"/>
+      <c r="I5" s="921"/>
+      <c r="J5" s="921"/>
+      <c r="K5" s="921"/>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="941">
+      <c r="A6" s="928">
         <f>+K12</f>
         <v>44</v>
       </c>
-      <c r="B6" s="941"/>
-      <c r="C6" s="941"/>
-      <c r="D6" s="941"/>
-      <c r="E6" s="941"/>
-      <c r="F6" s="941"/>
-      <c r="G6" s="941"/>
-      <c r="H6" s="941"/>
-      <c r="I6" s="941"/>
-      <c r="J6" s="941"/>
-      <c r="K6" s="941"/>
+      <c r="B6" s="928"/>
+      <c r="C6" s="928"/>
+      <c r="D6" s="928"/>
+      <c r="E6" s="928"/>
+      <c r="F6" s="928"/>
+      <c r="G6" s="928"/>
+      <c r="H6" s="928"/>
+      <c r="I6" s="928"/>
+      <c r="J6" s="928"/>
+      <c r="K6" s="928"/>
       <c r="Q6" s="259" t="s">
         <v>101</v>
       </c>
@@ -52292,10 +52299,10 @@
       <c r="Q9" s="275" t="s">
         <v>105</v>
       </c>
-      <c r="R9" s="945">
+      <c r="R9" s="932">
         <v>44090</v>
       </c>
-      <c r="S9" s="945"/>
+      <c r="S9" s="932"/>
       <c r="T9" s="276"/>
       <c r="U9" s="277"/>
       <c r="V9" s="276"/>
@@ -52376,37 +52383,37 @@
       <c r="U13" s="3"/>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="942" t="s">
+      <c r="A14" s="929" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="943"/>
-      <c r="C14" s="943"/>
-      <c r="D14" s="943"/>
-      <c r="E14" s="943"/>
-      <c r="F14" s="943"/>
-      <c r="G14" s="943"/>
-      <c r="H14" s="943"/>
-      <c r="I14" s="943"/>
-      <c r="J14" s="943"/>
-      <c r="K14" s="944"/>
+      <c r="B14" s="930"/>
+      <c r="C14" s="930"/>
+      <c r="D14" s="930"/>
+      <c r="E14" s="930"/>
+      <c r="F14" s="930"/>
+      <c r="G14" s="930"/>
+      <c r="H14" s="930"/>
+      <c r="I14" s="930"/>
+      <c r="J14" s="930"/>
+      <c r="K14" s="931"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
       <c r="U14" s="70"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="949" t="s">
+      <c r="A15" s="936" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="950"/>
-      <c r="C15" s="950"/>
-      <c r="D15" s="950"/>
-      <c r="E15" s="950"/>
-      <c r="F15" s="950"/>
-      <c r="G15" s="950"/>
-      <c r="H15" s="950"/>
-      <c r="I15" s="950"/>
-      <c r="J15" s="950"/>
-      <c r="K15" s="951"/>
+      <c r="B15" s="937"/>
+      <c r="C15" s="937"/>
+      <c r="D15" s="937"/>
+      <c r="E15" s="937"/>
+      <c r="F15" s="937"/>
+      <c r="G15" s="937"/>
+      <c r="H15" s="937"/>
+      <c r="I15" s="937"/>
+      <c r="J15" s="937"/>
+      <c r="K15" s="938"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
       <c r="U15" s="71"/>
@@ -52428,17 +52435,17 @@
       <c r="U16" s="70"/>
     </row>
     <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="939" t="s">
+      <c r="A17" s="926" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="940"/>
-      <c r="C17" s="940"/>
-      <c r="D17" s="940"/>
-      <c r="E17" s="940"/>
-      <c r="F17" s="940"/>
-      <c r="G17" s="940"/>
-      <c r="H17" s="940"/>
-      <c r="I17" s="940"/>
+      <c r="B17" s="927"/>
+      <c r="C17" s="927"/>
+      <c r="D17" s="927"/>
+      <c r="E17" s="927"/>
+      <c r="F17" s="927"/>
+      <c r="G17" s="927"/>
+      <c r="H17" s="927"/>
+      <c r="I17" s="927"/>
       <c r="J17" s="291" t="s">
         <v>124</v>
       </c>
@@ -52534,16 +52541,16 @@
       <c r="I22" s="242"/>
       <c r="J22" s="18"/>
       <c r="K22" s="243"/>
-      <c r="M22" s="967" t="s">
+      <c r="M22" s="968" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="968"/>
+      <c r="N22" s="969"/>
       <c r="O22" s="280"/>
-      <c r="P22" s="969">
+      <c r="P22" s="970">
         <f>SUM(O25:O42)</f>
         <v>9543.9950657520003</v>
       </c>
-      <c r="Q22" s="953"/>
+      <c r="Q22" s="959"/>
       <c r="R22" s="77" t="s">
         <v>73</v>
       </c>
@@ -52558,33 +52565,33 @@
     </row>
     <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
-      <c r="B23" s="975" t="s">
+      <c r="B23" s="966" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="975"/>
-      <c r="D23" s="972" t="s">
+      <c r="C23" s="966"/>
+      <c r="D23" s="967" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="972" t="s">
+      <c r="E23" s="967" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="972" t="s">
+      <c r="F23" s="967" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="972" t="s">
+      <c r="G23" s="967" t="s">
         <v>43</v>
       </c>
       <c r="H23" s="18"/>
-      <c r="I23" s="927" t="s">
+      <c r="I23" s="945" t="s">
         <v>36</v>
       </c>
-      <c r="J23" s="928"/>
+      <c r="J23" s="946"/>
       <c r="K23" s="144"/>
       <c r="M23" s="67" t="s">
         <v>9</v>
       </c>
       <c r="N23" s="68"/>
-      <c r="O23" s="933" t="s">
+      <c r="O23" s="920" t="s">
         <v>100</v>
       </c>
       <c r="P23" s="9" t="s">
@@ -52615,16 +52622,16 @@
       <c r="C24" s="244" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="972"/>
-      <c r="E24" s="972"/>
-      <c r="F24" s="972"/>
-      <c r="G24" s="972"/>
+      <c r="D24" s="967"/>
+      <c r="E24" s="967"/>
+      <c r="F24" s="967"/>
+      <c r="G24" s="967"/>
       <c r="H24" s="245"/>
-      <c r="I24" s="930">
+      <c r="I24" s="948">
         <f>+P22</f>
         <v>9543.9950657520003</v>
       </c>
-      <c r="J24" s="931"/>
+      <c r="J24" s="949"/>
       <c r="K24" s="144"/>
       <c r="M24" s="65" t="s">
         <v>11</v>
@@ -52632,7 +52639,7 @@
       <c r="N24" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O24" s="933"/>
+      <c r="O24" s="920"/>
       <c r="P24" s="10" t="s">
         <v>28</v>
       </c>
@@ -52650,7 +52657,7 @@
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20"/>
       <c r="B25" s="77" t="s">
         <v>31</v>
@@ -52728,7 +52735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20"/>
       <c r="B26" s="77" t="s">
         <v>15</v>
@@ -52753,10 +52760,10 @@
         <v>100</v>
       </c>
       <c r="H26" s="245"/>
-      <c r="I26" s="963" t="s">
+      <c r="I26" s="952" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="964"/>
+      <c r="J26" s="953"/>
       <c r="K26" s="144"/>
       <c r="M26" s="74">
         <v>2.5</v>
@@ -52808,7 +52815,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="20"/>
       <c r="B27" s="77" t="s">
         <v>16</v>
@@ -52889,7 +52896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20"/>
       <c r="B28" s="77" t="s">
         <v>17</v>
@@ -52967,7 +52974,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20"/>
       <c r="B29" s="77" t="s">
         <v>18</v>
@@ -52992,10 +52999,10 @@
         <v>98.973176865046099</v>
       </c>
       <c r="H29" s="245"/>
-      <c r="I29" s="963" t="s">
+      <c r="I29" s="952" t="s">
         <v>65</v>
       </c>
-      <c r="J29" s="964"/>
+      <c r="J29" s="953"/>
       <c r="K29" s="144"/>
       <c r="L29" s="19"/>
       <c r="M29" s="74">
@@ -53048,7 +53055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20"/>
       <c r="B30" s="77" t="s">
         <v>32</v>
@@ -53073,11 +53080,11 @@
         <v>44.991617770326911</v>
       </c>
       <c r="H30" s="245"/>
-      <c r="I30" s="970">
+      <c r="I30" s="971">
         <f>+Z38</f>
         <v>0.5</v>
       </c>
-      <c r="J30" s="971"/>
+      <c r="J30" s="972"/>
       <c r="K30" s="144"/>
       <c r="L30" s="19"/>
       <c r="M30" s="74">
@@ -53130,7 +53137,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20"/>
       <c r="B31" s="77" t="s">
         <v>19</v>
@@ -53209,7 +53216,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20"/>
       <c r="B32" s="77" t="s">
         <v>47</v>
@@ -53234,8 +53241,8 @@
         <v>0.20955574182733017</v>
       </c>
       <c r="H32" s="245"/>
-      <c r="I32" s="938"/>
-      <c r="J32" s="938"/>
+      <c r="I32" s="925"/>
+      <c r="J32" s="925"/>
       <c r="K32" s="144"/>
       <c r="L32" s="19"/>
       <c r="M32" s="74">
@@ -53288,7 +53295,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20"/>
       <c r="B33" s="77" t="s">
         <v>70</v>
@@ -53313,8 +53320,8 @@
         <v>0</v>
       </c>
       <c r="H33" s="245"/>
-      <c r="I33" s="938"/>
-      <c r="J33" s="938"/>
+      <c r="I33" s="925"/>
+      <c r="J33" s="925"/>
       <c r="K33" s="144"/>
       <c r="L33" s="19"/>
       <c r="M33" s="74">
@@ -53367,7 +53374,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20"/>
       <c r="B34" s="77" t="s">
         <v>44</v>
@@ -53387,8 +53394,8 @@
       </c>
       <c r="G34" s="303"/>
       <c r="H34" s="245"/>
-      <c r="I34" s="960"/>
-      <c r="J34" s="960"/>
+      <c r="I34" s="956"/>
+      <c r="J34" s="956"/>
       <c r="K34" s="144"/>
       <c r="L34" s="19"/>
       <c r="M34" s="23" t="s">
@@ -53477,7 +53484,7 @@
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
     </row>
-    <row r="36" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="21"/>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -53526,7 +53533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20"/>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
@@ -53575,7 +53582,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="20"/>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -54036,27 +54043,27 @@
       <c r="K54" s="297"/>
     </row>
     <row r="55" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="932" t="s">
+      <c r="A55" s="950" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="932"/>
-      <c r="C55" s="932"/>
-      <c r="D55" s="932"/>
-      <c r="E55" s="932"/>
-      <c r="F55" s="932"/>
-      <c r="G55" s="932"/>
-      <c r="H55" s="932"/>
-      <c r="I55" s="932"/>
-      <c r="J55" s="932"/>
-      <c r="K55" s="932"/>
+      <c r="B55" s="950"/>
+      <c r="C55" s="950"/>
+      <c r="D55" s="950"/>
+      <c r="E55" s="950"/>
+      <c r="F55" s="950"/>
+      <c r="G55" s="950"/>
+      <c r="H55" s="950"/>
+      <c r="I55" s="950"/>
+      <c r="J55" s="950"/>
+      <c r="K55" s="950"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="H56" s="921" t="s">
+      <c r="H56" s="939" t="s">
         <v>123</v>
       </c>
-      <c r="I56" s="921"/>
-      <c r="J56" s="921"/>
-      <c r="K56" s="921"/>
+      <c r="I56" s="939"/>
+      <c r="J56" s="939"/>
+      <c r="K56" s="939"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -54066,15 +54073,6 @@
     <protectedRange sqref="B9:B10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="25">
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="G23:G24"/>
     <mergeCell ref="A55:K55"/>
     <mergeCell ref="H56:K56"/>
     <mergeCell ref="O23:O24"/>
@@ -54091,6 +54089,15 @@
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="G23:G24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0.11811023622047245" footer="0"/>

--- a/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
+++ b/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Informes agregado\Gran agregado AG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802C83FF-1FED-4BA1-B55F-38B27F5A7B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E2424E-5D46-49F7-B6F0-2B47147206E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="598" firstSheet="2" activeTab="3" xr2:uid="{21CE8C7D-CFC7-4B7D-B46A-F41F71EC9170}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="598" xr2:uid="{21CE8C7D-CFC7-4B7D-B46A-F41F71EC9170}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="105" r:id="rId1"/>
@@ -38418,7 +38418,7 @@
       <c r="L69" s="337"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <protectedRanges>
     <protectedRange sqref="E16" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E13" name="Rango3_3_1_1_1_1_1_1_1_1_2"/>

--- a/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
+++ b/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Informes agregado\Gran agregado AG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E2424E-5D46-49F7-B6F0-2B47147206E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5B2C2D-F79F-4238-A8AA-5D1837086A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="598" xr2:uid="{21CE8C7D-CFC7-4B7D-B46A-F41F71EC9170}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="598" activeTab="3" xr2:uid="{21CE8C7D-CFC7-4B7D-B46A-F41F71EC9170}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="105" r:id="rId1"/>
@@ -38418,7 +38418,7 @@
       <c r="L69" s="337"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KjtFbqj+awez3nmatvXTUhptncqa0fiqLEcNeKt9ZefP5nQ0wKPn4zyew27CVx8kYZExrWI41Hc5CswZkRF15g==" saltValue="BBTqcofuNsnULRTF5jK1Lw==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <protectedRanges>
     <protectedRange sqref="E16" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E13" name="Rango3_3_1_1_1_1_1_1_1_1_2"/>
@@ -38772,7 +38772,7 @@
         <v>285</v>
       </c>
       <c r="H15" s="539">
-        <f>+IF(C10="Global",FORMATO!D22,FORMATO!D36)</f>
+        <f>J12</f>
         <v>0</v>
       </c>
       <c r="I15" s="444">
@@ -40340,7 +40340,7 @@
     <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="cvdp4ubDMsWVsh1DHGHdpbcF18q35cHVXHDDdyeqLp97E6eFY/Ur7+hm6xu3+y7OZtPYQGqOUCKbb/PsU984yw==" saltValue="HWvDGf1N7LVqZ81tzXJQUg==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="C47:E47"/>
     <mergeCell ref="C61:D61"/>
@@ -46655,7 +46655,7 @@
       <c r="I281" s="547"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bC7OIqzPwDP9E2RGOaQfi8uGBHN1WthlXg7X1jCAP8Dds2CjtmDMblJxZi+yuB+fPcaf7Iro/t/lXx3L+YIp7A==" saltValue="oBd54LNn75iV+UT4HFB6dA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="9">
     <mergeCell ref="B280:C280"/>
     <mergeCell ref="E280:F280"/>
@@ -47898,7 +47898,7 @@
       <c r="E69" s="700"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="v8HcRHeMe336PymyxK0HQbjdnavpBQNhAw0OesYBR/orw/5sTkn/biyS02pjlqm2xZj6/AT6jSiGZpnxACuK3Q==" saltValue="8VAfBRaTo8/OhfgdVO3wyQ==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="E28:E29"/>

--- a/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
+++ b/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Informes agregado\Gran agregado AG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5B2C2D-F79F-4238-A8AA-5D1837086A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E105B9FA-E8F0-4FDB-9F80-E71F3DF1F6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="598" activeTab="3" xr2:uid="{21CE8C7D-CFC7-4B7D-B46A-F41F71EC9170}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="598" xr2:uid="{21CE8C7D-CFC7-4B7D-B46A-F41F71EC9170}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="105" r:id="rId1"/>
@@ -305,7 +305,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="474">
   <si>
     <t>:</t>
   </si>
@@ -1950,9 +1950,6 @@
   <si>
     <t>Fecha evaluacion</t>
   </si>
-  <si>
-    <t>Global</t>
-  </si>
 </sst>
 </file>
 
@@ -3511,7 +3508,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1008">
+  <cellXfs count="1007">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
@@ -5220,10 +5217,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="8" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="164" fontId="67" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -6045,13 +6038,88 @@
     <xf numFmtId="0" fontId="42" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -6079,80 +6147,59 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="22" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="22" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6165,10 +6212,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6187,87 +6230,37 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="22" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="22" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="181" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -6426,6 +6419,78 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6466,101 +6531,23 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6570,23 +6557,35 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6605,9 +6604,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -6616,23 +6612,17 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6670,6 +6660,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="12" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="12" fontId="12" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="12" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -6682,30 +6693,6 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -6718,26 +6705,32 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="12" fontId="12" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="12" fontId="12" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="12" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -31463,18 +31456,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="9.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="727"/>
-      <c r="B1" s="728"/>
-      <c r="C1" s="729"/>
-      <c r="D1" s="729"/>
-      <c r="E1" s="729"/>
-      <c r="F1" s="729"/>
-      <c r="G1" s="729"/>
-      <c r="H1" s="729"/>
-      <c r="I1" s="730"/>
+      <c r="A1" s="726"/>
+      <c r="B1" s="727"/>
+      <c r="C1" s="728"/>
+      <c r="D1" s="728"/>
+      <c r="E1" s="728"/>
+      <c r="F1" s="728"/>
+      <c r="G1" s="728"/>
+      <c r="H1" s="728"/>
+      <c r="I1" s="729"/>
     </row>
     <row r="2" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="731"/>
+      <c r="A2" s="730"/>
       <c r="B2" s="176"/>
       <c r="C2" s="177"/>
       <c r="D2" s="177"/>
@@ -31482,14 +31475,14 @@
       <c r="F2" s="177"/>
       <c r="G2" s="177"/>
       <c r="H2" s="177"/>
-      <c r="I2" s="732"/>
+      <c r="I2" s="731"/>
       <c r="L2" s="281" t="s">
         <v>106</v>
       </c>
-      <c r="M2" s="776"/>
+      <c r="M2" s="775"/>
     </row>
     <row r="3" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="731"/>
+      <c r="A3" s="730"/>
       <c r="B3" s="176"/>
       <c r="C3" s="177"/>
       <c r="D3" s="177"/>
@@ -31497,14 +31490,14 @@
       <c r="F3" s="177"/>
       <c r="G3" s="177"/>
       <c r="H3" s="177"/>
-      <c r="I3" s="732"/>
+      <c r="I3" s="731"/>
       <c r="L3" s="281" t="s">
         <v>299</v>
       </c>
-      <c r="M3" s="777"/>
+      <c r="M3" s="776"/>
     </row>
     <row r="4" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="731"/>
+      <c r="A4" s="730"/>
       <c r="B4" s="176"/>
       <c r="C4" s="177"/>
       <c r="D4" s="177"/>
@@ -31512,177 +31505,177 @@
       <c r="F4" s="177"/>
       <c r="G4" s="177"/>
       <c r="H4" s="177"/>
-      <c r="I4" s="732"/>
+      <c r="I4" s="731"/>
       <c r="L4" s="281" t="s">
         <v>109</v>
       </c>
-      <c r="M4" s="777"/>
+      <c r="M4" s="776"/>
     </row>
     <row r="5" spans="1:14" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="733"/>
-      <c r="B5" s="734"/>
-      <c r="C5" s="734"/>
-      <c r="D5" s="734"/>
-      <c r="E5" s="734"/>
-      <c r="F5" s="734"/>
-      <c r="G5" s="734"/>
-      <c r="H5" s="734"/>
-      <c r="I5" s="735"/>
+      <c r="A5" s="732"/>
+      <c r="B5" s="733"/>
+      <c r="C5" s="733"/>
+      <c r="D5" s="733"/>
+      <c r="E5" s="733"/>
+      <c r="F5" s="733"/>
+      <c r="G5" s="733"/>
+      <c r="H5" s="733"/>
+      <c r="I5" s="734"/>
       <c r="L5" s="281" t="s">
         <v>110</v>
       </c>
-      <c r="M5" s="777"/>
+      <c r="M5" s="776"/>
     </row>
     <row r="6" spans="1:14" ht="6" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="736"/>
-      <c r="B6" s="736"/>
-      <c r="C6" s="736"/>
-      <c r="D6" s="736"/>
-      <c r="E6" s="736"/>
-      <c r="F6" s="736"/>
-      <c r="G6" s="736"/>
-      <c r="H6" s="736"/>
-      <c r="I6" s="736"/>
-      <c r="L6" s="778"/>
-      <c r="M6" s="779"/>
+      <c r="A6" s="735"/>
+      <c r="B6" s="735"/>
+      <c r="C6" s="735"/>
+      <c r="D6" s="735"/>
+      <c r="E6" s="735"/>
+      <c r="F6" s="735"/>
+      <c r="G6" s="735"/>
+      <c r="H6" s="735"/>
+      <c r="I6" s="735"/>
+      <c r="L6" s="777"/>
+      <c r="M6" s="778"/>
     </row>
     <row r="7" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="830" t="s">
+      <c r="A7" s="805" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="830"/>
-      <c r="C7" s="830"/>
-      <c r="D7" s="830"/>
-      <c r="E7" s="830"/>
-      <c r="F7" s="830"/>
-      <c r="G7" s="830"/>
-      <c r="H7" s="830"/>
-      <c r="I7" s="830"/>
+      <c r="B7" s="805"/>
+      <c r="C7" s="805"/>
+      <c r="D7" s="805"/>
+      <c r="E7" s="805"/>
+      <c r="F7" s="805"/>
+      <c r="G7" s="805"/>
+      <c r="H7" s="805"/>
+      <c r="I7" s="805"/>
       <c r="L7" s="285" t="s">
         <v>446</v>
       </c>
-      <c r="M7" s="779"/>
+      <c r="M7" s="778"/>
     </row>
     <row r="8" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="831" t="s">
+      <c r="A8" s="806" t="s">
         <v>384</v>
       </c>
-      <c r="B8" s="831"/>
-      <c r="C8" s="831"/>
-      <c r="D8" s="831"/>
-      <c r="E8" s="831"/>
-      <c r="F8" s="831"/>
-      <c r="G8" s="831"/>
-      <c r="H8" s="831"/>
-      <c r="I8" s="831"/>
+      <c r="B8" s="806"/>
+      <c r="C8" s="806"/>
+      <c r="D8" s="806"/>
+      <c r="E8" s="806"/>
+      <c r="F8" s="806"/>
+      <c r="G8" s="806"/>
+      <c r="H8" s="806"/>
+      <c r="I8" s="806"/>
       <c r="L8" s="285" t="s">
         <v>447</v>
       </c>
-      <c r="M8" s="780"/>
+      <c r="M8" s="779"/>
     </row>
     <row r="9" spans="1:14" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="726"/>
-      <c r="B9" s="726"/>
-      <c r="C9" s="726"/>
-      <c r="D9" s="726"/>
-      <c r="E9" s="726"/>
-      <c r="F9" s="726"/>
-      <c r="G9" s="726"/>
-      <c r="H9" s="726"/>
-      <c r="I9" s="726"/>
+      <c r="A9" s="725"/>
+      <c r="B9" s="725"/>
+      <c r="C9" s="725"/>
+      <c r="D9" s="725"/>
+      <c r="E9" s="725"/>
+      <c r="F9" s="725"/>
+      <c r="G9" s="725"/>
+      <c r="H9" s="725"/>
+      <c r="I9" s="725"/>
       <c r="L9" s="285" t="s">
         <v>448</v>
       </c>
-      <c r="M9" s="779"/>
+      <c r="M9" s="778"/>
     </row>
     <row r="10" spans="1:14" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="726"/>
-      <c r="B10" s="825" t="s">
+      <c r="A10" s="725"/>
+      <c r="B10" s="807" t="s">
         <v>385</v>
       </c>
-      <c r="C10" s="825"/>
-      <c r="D10" s="832" t="s">
+      <c r="C10" s="807"/>
+      <c r="D10" s="808" t="s">
         <v>386</v>
       </c>
-      <c r="E10" s="833"/>
-      <c r="F10" s="832" t="s">
+      <c r="E10" s="809"/>
+      <c r="F10" s="808" t="s">
         <v>387</v>
       </c>
-      <c r="G10" s="833"/>
-      <c r="H10" s="737" t="s">
+      <c r="G10" s="809"/>
+      <c r="H10" s="736" t="s">
         <v>388</v>
       </c>
-      <c r="I10" s="726"/>
-      <c r="L10" s="778"/>
-      <c r="M10" s="779"/>
+      <c r="I10" s="725"/>
+      <c r="L10" s="777"/>
+      <c r="M10" s="778"/>
     </row>
     <row r="11" spans="1:14" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="726"/>
-      <c r="B11" s="827"/>
-      <c r="C11" s="827"/>
-      <c r="D11" s="828"/>
-      <c r="E11" s="829"/>
-      <c r="F11" s="828"/>
-      <c r="G11" s="829"/>
-      <c r="H11" s="738"/>
-      <c r="I11" s="726"/>
+      <c r="A11" s="725"/>
+      <c r="B11" s="802"/>
+      <c r="C11" s="802"/>
+      <c r="D11" s="803"/>
+      <c r="E11" s="804"/>
+      <c r="F11" s="803"/>
+      <c r="G11" s="804"/>
+      <c r="H11" s="737"/>
+      <c r="I11" s="725"/>
       <c r="L11" s="285" t="s">
         <v>449</v>
       </c>
-      <c r="M11" s="779"/>
+      <c r="M11" s="778"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="726"/>
-      <c r="B12" s="726"/>
-      <c r="C12" s="726"/>
-      <c r="D12" s="726"/>
-      <c r="E12" s="726"/>
-      <c r="F12" s="726"/>
-      <c r="G12" s="726"/>
-      <c r="H12" s="726"/>
-      <c r="I12" s="726"/>
+      <c r="A12" s="725"/>
+      <c r="B12" s="725"/>
+      <c r="C12" s="725"/>
+      <c r="D12" s="725"/>
+      <c r="E12" s="725"/>
+      <c r="F12" s="725"/>
+      <c r="G12" s="725"/>
+      <c r="H12" s="725"/>
+      <c r="I12" s="725"/>
       <c r="L12" s="285" t="s">
         <v>450</v>
       </c>
-      <c r="M12" s="780"/>
+      <c r="M12" s="779"/>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="817" t="s">
+      <c r="A13" s="811" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="818"/>
-      <c r="C13" s="818"/>
-      <c r="D13" s="818"/>
-      <c r="E13" s="818"/>
-      <c r="F13" s="818"/>
-      <c r="G13" s="818"/>
-      <c r="H13" s="818"/>
-      <c r="I13" s="819"/>
+      <c r="B13" s="812"/>
+      <c r="C13" s="812"/>
+      <c r="D13" s="812"/>
+      <c r="E13" s="812"/>
+      <c r="F13" s="812"/>
+      <c r="G13" s="812"/>
+      <c r="H13" s="812"/>
+      <c r="I13" s="813"/>
       <c r="J13" s="166"/>
       <c r="L13" s="285" t="s">
         <v>451</v>
       </c>
-      <c r="M13" s="780"/>
+      <c r="M13" s="779"/>
       <c r="N13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="820" t="s">
+      <c r="A14" s="814" t="s">
         <v>389</v>
       </c>
-      <c r="B14" s="821"/>
-      <c r="C14" s="821"/>
-      <c r="D14" s="821"/>
-      <c r="E14" s="821"/>
-      <c r="F14" s="821"/>
-      <c r="G14" s="821"/>
-      <c r="H14" s="821"/>
-      <c r="I14" s="822"/>
+      <c r="B14" s="815"/>
+      <c r="C14" s="815"/>
+      <c r="D14" s="815"/>
+      <c r="E14" s="815"/>
+      <c r="F14" s="815"/>
+      <c r="G14" s="815"/>
+      <c r="H14" s="815"/>
+      <c r="I14" s="816"/>
       <c r="J14" s="166"/>
-      <c r="L14" s="778"/>
-      <c r="M14" s="779"/>
+      <c r="L14" s="777"/>
+      <c r="M14" s="778"/>
     </row>
     <row r="15" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="739"/>
+      <c r="A15" s="738"/>
       <c r="B15" s="195"/>
       <c r="C15" s="195"/>
       <c r="D15" s="195"/>
@@ -31695,16 +31688,16 @@
       <c r="L15" s="285" t="s">
         <v>452</v>
       </c>
-      <c r="M15" s="781"/>
+      <c r="M15" s="780"/>
     </row>
     <row r="16" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="740" t="s">
+      <c r="A16" s="739" t="s">
         <v>390</v>
       </c>
-      <c r="B16" s="804"/>
-      <c r="C16" s="804"/>
-      <c r="D16" s="804"/>
-      <c r="E16" s="804"/>
+      <c r="B16" s="817"/>
+      <c r="C16" s="817"/>
+      <c r="D16" s="817"/>
+      <c r="E16" s="817"/>
       <c r="F16" s="231"/>
       <c r="G16" s="213" t="s">
         <v>9</v>
@@ -31718,16 +31711,16 @@
       <c r="L16" s="285" t="s">
         <v>115</v>
       </c>
-      <c r="M16" s="781"/>
+      <c r="M16" s="780"/>
     </row>
     <row r="17" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="823" t="s">
+      <c r="A17" s="818" t="s">
         <v>393</v>
       </c>
-      <c r="B17" s="823"/>
-      <c r="C17" s="823"/>
-      <c r="D17" s="824"/>
-      <c r="E17" s="824"/>
+      <c r="B17" s="818"/>
+      <c r="C17" s="818"/>
+      <c r="D17" s="819"/>
+      <c r="E17" s="819"/>
       <c r="F17" s="231"/>
       <c r="G17" s="213" t="s">
         <v>11</v>
@@ -31741,21 +31734,21 @@
       <c r="L17" s="285" t="s">
         <v>116</v>
       </c>
-      <c r="M17" s="782"/>
+      <c r="M17" s="781"/>
     </row>
     <row r="18" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="740" t="s">
+      <c r="A18" s="739" t="s">
         <v>396</v>
       </c>
-      <c r="B18" s="804"/>
-      <c r="C18" s="804"/>
-      <c r="D18" s="804"/>
-      <c r="E18" s="804"/>
-      <c r="F18" s="741"/>
+      <c r="B18" s="817"/>
+      <c r="C18" s="817"/>
+      <c r="D18" s="817"/>
+      <c r="E18" s="817"/>
+      <c r="F18" s="740"/>
       <c r="G18" s="77" t="s">
         <v>397</v>
       </c>
-      <c r="H18" s="742">
+      <c r="H18" s="741">
         <v>75</v>
       </c>
       <c r="I18" s="69"/>
@@ -31766,148 +31759,148 @@
       <c r="G19" s="220" t="s">
         <v>398</v>
       </c>
-      <c r="H19" s="742">
+      <c r="H19" s="741">
         <v>63</v>
       </c>
       <c r="I19" s="69"/>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="825" t="s">
+      <c r="A20" s="807" t="s">
         <v>399</v>
       </c>
-      <c r="B20" s="825"/>
-      <c r="C20" s="825"/>
-      <c r="D20" s="825"/>
-      <c r="E20" s="825"/>
-      <c r="F20" s="743"/>
+      <c r="B20" s="807"/>
+      <c r="C20" s="807"/>
+      <c r="D20" s="807"/>
+      <c r="E20" s="807"/>
+      <c r="F20" s="742"/>
       <c r="G20" s="77" t="s">
         <v>400</v>
       </c>
-      <c r="H20" s="742">
+      <c r="H20" s="741">
         <v>50</v>
       </c>
       <c r="I20" s="69"/>
-      <c r="J20" s="774"/>
+      <c r="J20" s="773"/>
     </row>
     <row r="21" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="744" t="s">
+      <c r="A21" s="743" t="s">
         <v>401</v>
       </c>
-      <c r="B21" s="745"/>
-      <c r="C21" s="746" t="s">
+      <c r="B21" s="744"/>
+      <c r="C21" s="745" t="s">
         <v>402</v>
       </c>
-      <c r="D21" s="826"/>
-      <c r="E21" s="826"/>
-      <c r="F21" s="747"/>
+      <c r="D21" s="820"/>
+      <c r="E21" s="820"/>
+      <c r="F21" s="746"/>
       <c r="G21" s="77" t="s">
         <v>403</v>
       </c>
-      <c r="H21" s="742">
+      <c r="H21" s="741">
         <v>37.5</v>
       </c>
       <c r="I21" s="69"/>
       <c r="J21" s="166"/>
     </row>
     <row r="22" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="744" t="s">
+      <c r="A22" s="743" t="s">
         <v>404</v>
       </c>
-      <c r="B22" s="745"/>
-      <c r="C22" s="746" t="s">
+      <c r="B22" s="744"/>
+      <c r="C22" s="745" t="s">
         <v>402</v>
       </c>
-      <c r="D22" s="826"/>
-      <c r="E22" s="826"/>
-      <c r="F22" s="747"/>
+      <c r="D22" s="820"/>
+      <c r="E22" s="820"/>
+      <c r="F22" s="746"/>
       <c r="G22" s="77" t="s">
         <v>405</v>
       </c>
-      <c r="H22" s="742">
+      <c r="H22" s="741">
         <v>25</v>
       </c>
       <c r="I22" s="69"/>
     </row>
     <row r="23" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="744" t="s">
+      <c r="A23" s="743" t="s">
         <v>406</v>
       </c>
-      <c r="B23" s="745"/>
-      <c r="C23" s="746" t="s">
+      <c r="B23" s="744"/>
+      <c r="C23" s="745" t="s">
         <v>402</v>
       </c>
-      <c r="D23" s="826"/>
-      <c r="E23" s="826"/>
-      <c r="F23" s="747"/>
+      <c r="D23" s="820"/>
+      <c r="E23" s="820"/>
+      <c r="F23" s="746"/>
       <c r="G23" s="77" t="s">
         <v>407</v>
       </c>
-      <c r="H23" s="742">
+      <c r="H23" s="741">
         <v>19</v>
       </c>
       <c r="I23" s="69"/>
     </row>
     <row r="24" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="744" t="s">
+      <c r="A24" s="743" t="s">
         <v>408</v>
       </c>
-      <c r="B24" s="745"/>
-      <c r="C24" s="746" t="s">
+      <c r="B24" s="744"/>
+      <c r="C24" s="745" t="s">
         <v>402</v>
       </c>
-      <c r="D24" s="826"/>
-      <c r="E24" s="826"/>
-      <c r="F24" s="747"/>
+      <c r="D24" s="820"/>
+      <c r="E24" s="820"/>
+      <c r="F24" s="746"/>
       <c r="G24" s="220" t="s">
         <v>409</v>
       </c>
-      <c r="H24" s="742">
+      <c r="H24" s="741">
         <v>12.5</v>
       </c>
       <c r="I24" s="69"/>
     </row>
     <row r="25" spans="1:13" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
-      <c r="B25" s="743"/>
-      <c r="C25" s="748"/>
-      <c r="D25" s="743"/>
-      <c r="E25" s="743"/>
-      <c r="F25" s="743"/>
+      <c r="B25" s="742"/>
+      <c r="C25" s="747"/>
+      <c r="D25" s="742"/>
+      <c r="E25" s="742"/>
+      <c r="F25" s="742"/>
       <c r="G25" s="77" t="s">
         <v>410</v>
       </c>
-      <c r="H25" s="742">
+      <c r="H25" s="741">
         <v>9.5</v>
       </c>
       <c r="I25" s="69"/>
     </row>
     <row r="26" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="816" t="s">
+      <c r="A26" s="810" t="s">
         <v>411</v>
       </c>
-      <c r="B26" s="816"/>
-      <c r="C26" s="816"/>
-      <c r="D26" s="816"/>
-      <c r="E26" s="816"/>
+      <c r="B26" s="810"/>
+      <c r="C26" s="810"/>
+      <c r="D26" s="810"/>
+      <c r="E26" s="810"/>
       <c r="F26" s="5"/>
       <c r="G26" s="77" t="s">
         <v>412</v>
       </c>
-      <c r="H26" s="742">
+      <c r="H26" s="741">
         <v>4.75</v>
       </c>
       <c r="I26" s="69"/>
     </row>
     <row r="27" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="749" t="s">
+      <c r="A27" s="748" t="s">
         <v>401</v>
       </c>
-      <c r="B27" s="750"/>
-      <c r="C27" s="751" t="s">
+      <c r="B27" s="749"/>
+      <c r="C27" s="750" t="s">
         <v>402</v>
       </c>
-      <c r="D27" s="812"/>
-      <c r="E27" s="812"/>
+      <c r="D27" s="821"/>
+      <c r="E27" s="821"/>
       <c r="G27" s="220" t="s">
         <v>413</v>
       </c>
@@ -31917,15 +31910,15 @@
       <c r="I27" s="69"/>
     </row>
     <row r="28" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="749" t="s">
+      <c r="A28" s="748" t="s">
         <v>414</v>
       </c>
-      <c r="B28" s="752"/>
-      <c r="C28" s="753" t="s">
+      <c r="B28" s="751"/>
+      <c r="C28" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D28" s="804"/>
-      <c r="E28" s="804"/>
+      <c r="D28" s="817"/>
+      <c r="E28" s="817"/>
       <c r="G28" s="77" t="s">
         <v>415</v>
       </c>
@@ -31935,13 +31928,13 @@
       <c r="I28" s="69"/>
     </row>
     <row r="29" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="813" t="s">
+      <c r="A29" s="822" t="s">
         <v>416</v>
       </c>
-      <c r="B29" s="814"/>
-      <c r="C29" s="814"/>
-      <c r="D29" s="814"/>
-      <c r="E29" s="815"/>
+      <c r="B29" s="823"/>
+      <c r="C29" s="823"/>
+      <c r="D29" s="823"/>
+      <c r="E29" s="824"/>
       <c r="G29" s="220" t="s">
         <v>417</v>
       </c>
@@ -31952,15 +31945,15 @@
       <c r="J29" s="166"/>
     </row>
     <row r="30" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="744" t="s">
+      <c r="A30" s="743" t="s">
         <v>404</v>
       </c>
-      <c r="B30" s="754"/>
-      <c r="C30" s="753" t="s">
+      <c r="B30" s="753"/>
+      <c r="C30" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D30" s="804"/>
-      <c r="E30" s="804"/>
+      <c r="D30" s="817"/>
+      <c r="E30" s="817"/>
       <c r="G30" s="220" t="s">
         <v>161</v>
       </c>
@@ -31971,15 +31964,15 @@
       <c r="J30" s="166"/>
     </row>
     <row r="31" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="749" t="s">
+      <c r="A31" s="748" t="s">
         <v>406</v>
       </c>
-      <c r="B31" s="754"/>
-      <c r="C31" s="753" t="s">
+      <c r="B31" s="753"/>
+      <c r="C31" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D31" s="804"/>
-      <c r="E31" s="804"/>
+      <c r="D31" s="817"/>
+      <c r="E31" s="817"/>
       <c r="G31" s="220" t="s">
         <v>418</v>
       </c>
@@ -31990,13 +31983,13 @@
       <c r="J31" s="166"/>
     </row>
     <row r="32" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="813" t="s">
+      <c r="A32" s="822" t="s">
         <v>419</v>
       </c>
-      <c r="B32" s="814"/>
-      <c r="C32" s="814"/>
-      <c r="D32" s="814"/>
-      <c r="E32" s="815"/>
+      <c r="B32" s="823"/>
+      <c r="C32" s="823"/>
+      <c r="D32" s="823"/>
+      <c r="E32" s="824"/>
       <c r="G32" s="220" t="s">
         <v>420</v>
       </c>
@@ -32007,16 +32000,16 @@
       <c r="J32" s="166"/>
     </row>
     <row r="33" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="744" t="s">
+      <c r="A33" s="743" t="s">
         <v>421</v>
       </c>
-      <c r="B33" s="754"/>
-      <c r="C33" s="753" t="s">
+      <c r="B33" s="753"/>
+      <c r="C33" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D33" s="804"/>
-      <c r="E33" s="804"/>
-      <c r="F33" s="741"/>
+      <c r="D33" s="817"/>
+      <c r="E33" s="817"/>
+      <c r="F33" s="740"/>
       <c r="G33" s="220" t="s">
         <v>422</v>
       </c>
@@ -32027,15 +32020,15 @@
       <c r="J33" s="166"/>
     </row>
     <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="755" t="s">
+      <c r="A34" s="754" t="s">
         <v>423</v>
       </c>
-      <c r="C34" s="748" t="s">
+      <c r="C34" s="747" t="s">
         <v>402</v>
       </c>
-      <c r="D34" s="804"/>
-      <c r="E34" s="804"/>
-      <c r="F34" s="741"/>
+      <c r="D34" s="817"/>
+      <c r="E34" s="817"/>
+      <c r="F34" s="740"/>
       <c r="G34" s="220" t="s">
         <v>424</v>
       </c>
@@ -32046,16 +32039,16 @@
       <c r="J34" s="166"/>
     </row>
     <row r="35" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="744" t="s">
+      <c r="A35" s="743" t="s">
         <v>425</v>
       </c>
-      <c r="B35" s="754"/>
-      <c r="C35" s="753" t="s">
+      <c r="B35" s="753"/>
+      <c r="C35" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D35" s="804"/>
-      <c r="E35" s="804"/>
-      <c r="F35" s="741"/>
+      <c r="D35" s="817"/>
+      <c r="E35" s="817"/>
+      <c r="F35" s="740"/>
       <c r="G35" s="230" t="s">
         <v>34</v>
       </c>
@@ -32066,154 +32059,154 @@
       <c r="J35" s="166"/>
     </row>
     <row r="36" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="755" t="s">
+      <c r="A36" s="754" t="s">
         <v>426</v>
       </c>
-      <c r="C36" s="748" t="s">
+      <c r="C36" s="747" t="s">
         <v>402</v>
       </c>
-      <c r="D36" s="804"/>
-      <c r="E36" s="804"/>
-      <c r="F36" s="741"/>
-      <c r="H36" s="756" t="s">
+      <c r="D36" s="817"/>
+      <c r="E36" s="817"/>
+      <c r="F36" s="740"/>
+      <c r="H36" s="755" t="s">
         <v>427</v>
       </c>
       <c r="J36" s="166"/>
     </row>
     <row r="37" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="744" t="s">
+      <c r="A37" s="743" t="s">
         <v>428</v>
       </c>
-      <c r="B37" s="754"/>
-      <c r="C37" s="753" t="s">
+      <c r="B37" s="753"/>
+      <c r="C37" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D37" s="804"/>
-      <c r="E37" s="804"/>
-      <c r="F37" s="741"/>
+      <c r="D37" s="817"/>
+      <c r="E37" s="817"/>
+      <c r="F37" s="740"/>
       <c r="J37" s="166"/>
     </row>
     <row r="38" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="749" t="s">
+      <c r="A38" s="748" t="s">
         <v>429</v>
       </c>
-      <c r="B38" s="757"/>
-      <c r="C38" s="751" t="s">
+      <c r="B38" s="756"/>
+      <c r="C38" s="750" t="s">
         <v>430</v>
       </c>
-      <c r="D38" s="804"/>
-      <c r="E38" s="804"/>
-      <c r="F38" s="741"/>
-      <c r="I38" s="758"/>
+      <c r="D38" s="817"/>
+      <c r="E38" s="817"/>
+      <c r="F38" s="740"/>
+      <c r="I38" s="757"/>
       <c r="J38" s="166"/>
     </row>
     <row r="39" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="749" t="s">
+      <c r="A39" s="748" t="s">
         <v>431</v>
       </c>
-      <c r="B39" s="757"/>
-      <c r="C39" s="751" t="s">
+      <c r="B39" s="756"/>
+      <c r="C39" s="750" t="s">
         <v>402</v>
       </c>
-      <c r="D39" s="804"/>
-      <c r="E39" s="804"/>
-      <c r="F39" s="741"/>
-      <c r="G39" s="759"/>
-      <c r="H39" s="760"/>
-      <c r="I39" s="758"/>
+      <c r="D39" s="817"/>
+      <c r="E39" s="817"/>
+      <c r="F39" s="740"/>
+      <c r="G39" s="758"/>
+      <c r="H39" s="759"/>
+      <c r="I39" s="757"/>
       <c r="J39" s="166"/>
     </row>
     <row r="40" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E40" s="741"/>
-      <c r="F40" s="741"/>
-      <c r="G40" s="759"/>
-      <c r="H40" s="760"/>
-      <c r="I40" s="758"/>
+      <c r="E40" s="740"/>
+      <c r="F40" s="740"/>
+      <c r="G40" s="758"/>
+      <c r="H40" s="759"/>
+      <c r="I40" s="757"/>
       <c r="J40" s="166"/>
     </row>
     <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="805" t="s">
+      <c r="A41" s="826" t="s">
         <v>432</v>
       </c>
-      <c r="B41" s="805"/>
-      <c r="C41" s="805"/>
-      <c r="D41" s="805"/>
-      <c r="E41" s="761"/>
-      <c r="F41" s="761"/>
+      <c r="B41" s="826"/>
+      <c r="C41" s="826"/>
+      <c r="D41" s="826"/>
+      <c r="E41" s="760"/>
+      <c r="F41" s="760"/>
       <c r="J41" s="166"/>
     </row>
     <row r="42" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="762" t="s">
+      <c r="A42" s="761" t="s">
         <v>433</v>
       </c>
-      <c r="B42" s="763"/>
-      <c r="C42" s="806"/>
-      <c r="D42" s="806"/>
-      <c r="E42" s="807"/>
-      <c r="F42" s="807"/>
+      <c r="B42" s="762"/>
+      <c r="C42" s="827"/>
+      <c r="D42" s="827"/>
+      <c r="E42" s="828"/>
+      <c r="F42" s="828"/>
       <c r="J42" s="166"/>
     </row>
     <row r="43" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="762" t="s">
+      <c r="A43" s="761" t="s">
         <v>434</v>
       </c>
-      <c r="B43" s="764"/>
-      <c r="C43" s="806"/>
-      <c r="D43" s="806"/>
-      <c r="E43" s="807"/>
-      <c r="F43" s="807"/>
+      <c r="B43" s="763"/>
+      <c r="C43" s="827"/>
+      <c r="D43" s="827"/>
+      <c r="E43" s="828"/>
+      <c r="F43" s="828"/>
       <c r="J43" s="166"/>
     </row>
     <row r="44" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="765" t="s">
+      <c r="A44" s="764" t="s">
         <v>435</v>
       </c>
-      <c r="B44" s="764"/>
-      <c r="C44" s="806"/>
-      <c r="D44" s="806"/>
-      <c r="E44" s="807"/>
-      <c r="F44" s="807"/>
+      <c r="B44" s="763"/>
+      <c r="C44" s="827"/>
+      <c r="D44" s="827"/>
+      <c r="E44" s="828"/>
+      <c r="F44" s="828"/>
       <c r="J44" s="166"/>
     </row>
     <row r="45" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J45" s="166"/>
     </row>
     <row r="46" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="766" t="s">
+      <c r="A46" s="765" t="s">
         <v>436</v>
       </c>
-      <c r="B46" s="767" t="s">
+      <c r="B46" s="766" t="s">
         <v>437</v>
       </c>
-      <c r="C46" s="768"/>
-      <c r="D46" s="769"/>
+      <c r="C46" s="767"/>
+      <c r="D46" s="768"/>
       <c r="E46" s="281"/>
       <c r="F46" s="281"/>
       <c r="J46" s="166"/>
     </row>
     <row r="47" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="770" t="s">
+      <c r="A47" s="769" t="s">
         <v>438</v>
       </c>
-      <c r="B47" s="808"/>
-      <c r="C47" s="809"/>
-      <c r="D47" s="810"/>
+      <c r="B47" s="829"/>
+      <c r="C47" s="830"/>
+      <c r="D47" s="831"/>
       <c r="E47" s="247"/>
       <c r="F47" s="247"/>
-      <c r="G47" s="811" t="s">
+      <c r="G47" s="832" t="s">
         <v>439</v>
       </c>
-      <c r="H47" s="811"/>
-      <c r="I47" s="811"/>
+      <c r="H47" s="832"/>
+      <c r="I47" s="832"/>
       <c r="J47" s="166"/>
     </row>
     <row r="48" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="771" t="s">
+      <c r="A48" s="770" t="s">
         <v>440</v>
       </c>
-      <c r="B48" s="808"/>
-      <c r="C48" s="809"/>
-      <c r="D48" s="810"/>
+      <c r="B48" s="829"/>
+      <c r="C48" s="830"/>
+      <c r="D48" s="831"/>
       <c r="E48" s="247"/>
       <c r="F48" s="247"/>
       <c r="G48" s="4" t="s">
@@ -32222,7 +32215,7 @@
       <c r="J48" s="166"/>
     </row>
     <row r="49" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="772" t="s">
+      <c r="A49" s="771" t="s">
         <v>442</v>
       </c>
       <c r="E49" s="247"/>
@@ -32232,7 +32225,7 @@
       <c r="J49" s="166"/>
     </row>
     <row r="50" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="772"/>
+      <c r="A50" s="771"/>
       <c r="E50" s="247"/>
       <c r="F50" s="247"/>
       <c r="G50" s="247"/>
@@ -32240,7 +32233,7 @@
       <c r="J50" s="166"/>
     </row>
     <row r="51" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="772"/>
+      <c r="A51" s="771"/>
       <c r="E51" s="247"/>
       <c r="F51" s="247"/>
       <c r="G51" s="247"/>
@@ -32266,11 +32259,11 @@
       </c>
       <c r="B53" s="239"/>
       <c r="C53" s="239"/>
-      <c r="D53" s="773" t="s">
+      <c r="D53" s="772" t="s">
         <v>444</v>
       </c>
-      <c r="E53" s="773"/>
-      <c r="F53" s="773"/>
+      <c r="E53" s="772"/>
+      <c r="F53" s="772"/>
       <c r="G53" s="239"/>
       <c r="H53" s="239"/>
       <c r="I53" s="239"/>
@@ -32278,17 +32271,17 @@
     </row>
     <row r="54" spans="1:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="803" t="s">
+      <c r="A55" s="825" t="s">
         <v>445</v>
       </c>
-      <c r="B55" s="803"/>
-      <c r="C55" s="803"/>
-      <c r="D55" s="803"/>
-      <c r="E55" s="803"/>
-      <c r="F55" s="803"/>
-      <c r="G55" s="803"/>
-      <c r="H55" s="803"/>
-      <c r="I55" s="803"/>
+      <c r="B55" s="825"/>
+      <c r="C55" s="825"/>
+      <c r="D55" s="825"/>
+      <c r="E55" s="825"/>
+      <c r="F55" s="825"/>
+      <c r="G55" s="825"/>
+      <c r="H55" s="825"/>
+      <c r="I55" s="825"/>
     </row>
     <row r="56" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -32298,14 +32291,30 @@
     <protectedRange sqref="B15" name="Rango3_3_1_1_1_1_1_1_1_1"/>
   </protectedRanges>
   <mergeCells count="44">
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A14:I14"/>
@@ -32318,30 +32327,14 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.59055118110236227" top="0.78740157480314965" bottom="0" header="0" footer="0"/>
@@ -32394,117 +32387,117 @@
       <c r="T4" s="25"/>
     </row>
     <row r="5" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="996" t="s">
+      <c r="B5" s="974" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="997"/>
-      <c r="D5" s="997"/>
-      <c r="E5" s="997"/>
-      <c r="F5" s="998"/>
-      <c r="H5" s="996" t="s">
+      <c r="C5" s="975"/>
+      <c r="D5" s="975"/>
+      <c r="E5" s="975"/>
+      <c r="F5" s="976"/>
+      <c r="H5" s="974" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="997"/>
-      <c r="J5" s="997"/>
-      <c r="K5" s="997"/>
-      <c r="L5" s="997"/>
-      <c r="M5" s="997"/>
-      <c r="N5" s="997"/>
-      <c r="O5" s="997"/>
-      <c r="P5" s="997"/>
-      <c r="Q5" s="997"/>
-      <c r="R5" s="997"/>
-      <c r="S5" s="997"/>
-      <c r="T5" s="997"/>
-      <c r="U5" s="997"/>
-      <c r="V5" s="997"/>
-      <c r="W5" s="997"/>
-      <c r="X5" s="997"/>
-      <c r="Y5" s="997"/>
-      <c r="Z5" s="997"/>
-      <c r="AA5" s="997"/>
-      <c r="AB5" s="997"/>
-      <c r="AC5" s="997"/>
-      <c r="AD5" s="997"/>
-      <c r="AE5" s="997"/>
-      <c r="AF5" s="997"/>
-      <c r="AG5" s="997"/>
-      <c r="AH5" s="997"/>
-      <c r="AI5" s="997"/>
-      <c r="AJ5" s="997"/>
-      <c r="AK5" s="997"/>
-      <c r="AL5" s="997"/>
-      <c r="AM5" s="997"/>
-      <c r="AN5" s="997"/>
-      <c r="AO5" s="997"/>
-      <c r="AP5" s="997"/>
-      <c r="AQ5" s="997"/>
-      <c r="AR5" s="997"/>
-      <c r="AS5" s="998"/>
+      <c r="I5" s="975"/>
+      <c r="J5" s="975"/>
+      <c r="K5" s="975"/>
+      <c r="L5" s="975"/>
+      <c r="M5" s="975"/>
+      <c r="N5" s="975"/>
+      <c r="O5" s="975"/>
+      <c r="P5" s="975"/>
+      <c r="Q5" s="975"/>
+      <c r="R5" s="975"/>
+      <c r="S5" s="975"/>
+      <c r="T5" s="975"/>
+      <c r="U5" s="975"/>
+      <c r="V5" s="975"/>
+      <c r="W5" s="975"/>
+      <c r="X5" s="975"/>
+      <c r="Y5" s="975"/>
+      <c r="Z5" s="975"/>
+      <c r="AA5" s="975"/>
+      <c r="AB5" s="975"/>
+      <c r="AC5" s="975"/>
+      <c r="AD5" s="975"/>
+      <c r="AE5" s="975"/>
+      <c r="AF5" s="975"/>
+      <c r="AG5" s="975"/>
+      <c r="AH5" s="975"/>
+      <c r="AI5" s="975"/>
+      <c r="AJ5" s="975"/>
+      <c r="AK5" s="975"/>
+      <c r="AL5" s="975"/>
+      <c r="AM5" s="975"/>
+      <c r="AN5" s="975"/>
+      <c r="AO5" s="975"/>
+      <c r="AP5" s="975"/>
+      <c r="AQ5" s="975"/>
+      <c r="AR5" s="975"/>
+      <c r="AS5" s="976"/>
     </row>
     <row r="6" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="996" t="s">
+      <c r="B6" s="974" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="997"/>
-      <c r="D6" s="997"/>
-      <c r="E6" s="997"/>
-      <c r="F6" s="998"/>
-      <c r="H6" s="996" t="s">
+      <c r="C6" s="975"/>
+      <c r="D6" s="975"/>
+      <c r="E6" s="975"/>
+      <c r="F6" s="976"/>
+      <c r="H6" s="974" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="997"/>
-      <c r="J6" s="997"/>
-      <c r="K6" s="997"/>
-      <c r="L6" s="997"/>
-      <c r="M6" s="997"/>
-      <c r="N6" s="997"/>
-      <c r="O6" s="997"/>
-      <c r="P6" s="997"/>
-      <c r="Q6" s="997"/>
-      <c r="R6" s="997"/>
-      <c r="S6" s="997"/>
-      <c r="T6" s="997"/>
-      <c r="U6" s="997"/>
-      <c r="V6" s="997"/>
-      <c r="W6" s="997"/>
-      <c r="X6" s="997"/>
-      <c r="Y6" s="997"/>
-      <c r="Z6" s="997"/>
-      <c r="AA6" s="997"/>
-      <c r="AB6" s="997"/>
-      <c r="AC6" s="997"/>
-      <c r="AD6" s="997"/>
-      <c r="AE6" s="997"/>
-      <c r="AF6" s="997"/>
-      <c r="AG6" s="997"/>
-      <c r="AH6" s="997"/>
-      <c r="AI6" s="997"/>
-      <c r="AJ6" s="997"/>
-      <c r="AK6" s="997"/>
-      <c r="AL6" s="997"/>
-      <c r="AM6" s="997"/>
-      <c r="AN6" s="997"/>
-      <c r="AO6" s="997"/>
-      <c r="AP6" s="997"/>
-      <c r="AQ6" s="997"/>
-      <c r="AR6" s="997"/>
-      <c r="AS6" s="998"/>
+      <c r="I6" s="975"/>
+      <c r="J6" s="975"/>
+      <c r="K6" s="975"/>
+      <c r="L6" s="975"/>
+      <c r="M6" s="975"/>
+      <c r="N6" s="975"/>
+      <c r="O6" s="975"/>
+      <c r="P6" s="975"/>
+      <c r="Q6" s="975"/>
+      <c r="R6" s="975"/>
+      <c r="S6" s="975"/>
+      <c r="T6" s="975"/>
+      <c r="U6" s="975"/>
+      <c r="V6" s="975"/>
+      <c r="W6" s="975"/>
+      <c r="X6" s="975"/>
+      <c r="Y6" s="975"/>
+      <c r="Z6" s="975"/>
+      <c r="AA6" s="975"/>
+      <c r="AB6" s="975"/>
+      <c r="AC6" s="975"/>
+      <c r="AD6" s="975"/>
+      <c r="AE6" s="975"/>
+      <c r="AF6" s="975"/>
+      <c r="AG6" s="975"/>
+      <c r="AH6" s="975"/>
+      <c r="AI6" s="975"/>
+      <c r="AJ6" s="975"/>
+      <c r="AK6" s="975"/>
+      <c r="AL6" s="975"/>
+      <c r="AM6" s="975"/>
+      <c r="AN6" s="975"/>
+      <c r="AO6" s="975"/>
+      <c r="AP6" s="975"/>
+      <c r="AQ6" s="975"/>
+      <c r="AR6" s="975"/>
+      <c r="AS6" s="976"/>
     </row>
     <row r="7" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="976" t="s">
+      <c r="B7" s="999" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="977"/>
-      <c r="D7" s="980" t="s">
+      <c r="C7" s="1000"/>
+      <c r="D7" s="977" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="981"/>
-      <c r="F7" s="982"/>
-      <c r="H7" s="992" t="s">
+      <c r="E7" s="978"/>
+      <c r="F7" s="979"/>
+      <c r="H7" s="1003" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="993"/>
+      <c r="I7" s="1004"/>
       <c r="J7" s="30"/>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
@@ -32514,119 +32507,119 @@
       <c r="P7" s="30"/>
       <c r="Q7" s="30"/>
       <c r="R7" s="14"/>
-      <c r="S7" s="1005">
+      <c r="S7" s="989">
         <v>2</v>
       </c>
-      <c r="T7" s="1006"/>
-      <c r="U7" s="1007"/>
-      <c r="V7" s="999"/>
-      <c r="W7" s="1000"/>
-      <c r="X7" s="1001"/>
-      <c r="Y7" s="1005">
+      <c r="T7" s="990"/>
+      <c r="U7" s="991"/>
+      <c r="V7" s="995"/>
+      <c r="W7" s="996"/>
+      <c r="X7" s="997"/>
+      <c r="Y7" s="989">
         <v>1.5</v>
       </c>
-      <c r="Z7" s="1006"/>
-      <c r="AA7" s="1007"/>
-      <c r="AB7" s="999"/>
-      <c r="AC7" s="1000"/>
-      <c r="AD7" s="1001"/>
-      <c r="AE7" s="999"/>
-      <c r="AF7" s="1000"/>
-      <c r="AG7" s="1001"/>
-      <c r="AH7" s="1005">
+      <c r="Z7" s="990"/>
+      <c r="AA7" s="991"/>
+      <c r="AB7" s="995"/>
+      <c r="AC7" s="996"/>
+      <c r="AD7" s="997"/>
+      <c r="AE7" s="995"/>
+      <c r="AF7" s="996"/>
+      <c r="AG7" s="997"/>
+      <c r="AH7" s="989">
         <v>1</v>
       </c>
-      <c r="AI7" s="1006"/>
-      <c r="AJ7" s="1007"/>
-      <c r="AK7" s="999"/>
-      <c r="AL7" s="1000"/>
-      <c r="AM7" s="1001"/>
-      <c r="AN7" s="1005">
+      <c r="AI7" s="990"/>
+      <c r="AJ7" s="991"/>
+      <c r="AK7" s="995"/>
+      <c r="AL7" s="996"/>
+      <c r="AM7" s="997"/>
+      <c r="AN7" s="989">
         <v>0.75</v>
       </c>
-      <c r="AO7" s="1006"/>
-      <c r="AP7" s="1007"/>
-      <c r="AQ7" s="1005">
+      <c r="AO7" s="990"/>
+      <c r="AP7" s="991"/>
+      <c r="AQ7" s="989">
         <v>0.5</v>
       </c>
-      <c r="AR7" s="1006"/>
-      <c r="AS7" s="1007"/>
+      <c r="AR7" s="990"/>
+      <c r="AS7" s="991"/>
     </row>
     <row r="8" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="978"/>
-      <c r="C8" s="979"/>
-      <c r="D8" s="983"/>
-      <c r="E8" s="984"/>
-      <c r="F8" s="985"/>
-      <c r="H8" s="994" t="s">
+      <c r="B8" s="1001"/>
+      <c r="C8" s="1002"/>
+      <c r="D8" s="980"/>
+      <c r="E8" s="981"/>
+      <c r="F8" s="982"/>
+      <c r="H8" s="1005" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="995"/>
-      <c r="J8" s="989">
+      <c r="I8" s="1006"/>
+      <c r="J8" s="992">
         <v>1</v>
       </c>
-      <c r="K8" s="990"/>
-      <c r="L8" s="991"/>
-      <c r="M8" s="989">
+      <c r="K8" s="993"/>
+      <c r="L8" s="994"/>
+      <c r="M8" s="992">
         <v>2</v>
       </c>
-      <c r="N8" s="990"/>
-      <c r="O8" s="991"/>
-      <c r="P8" s="989">
+      <c r="N8" s="993"/>
+      <c r="O8" s="994"/>
+      <c r="P8" s="992">
         <v>3</v>
       </c>
-      <c r="Q8" s="990"/>
-      <c r="R8" s="991"/>
-      <c r="S8" s="989">
+      <c r="Q8" s="993"/>
+      <c r="R8" s="994"/>
+      <c r="S8" s="992">
         <v>357</v>
       </c>
-      <c r="T8" s="990"/>
-      <c r="U8" s="991"/>
-      <c r="V8" s="989">
+      <c r="T8" s="993"/>
+      <c r="U8" s="994"/>
+      <c r="V8" s="992">
         <v>4</v>
       </c>
-      <c r="W8" s="990"/>
-      <c r="X8" s="991"/>
-      <c r="Y8" s="989">
+      <c r="W8" s="993"/>
+      <c r="X8" s="994"/>
+      <c r="Y8" s="992">
         <v>467</v>
       </c>
-      <c r="Z8" s="990"/>
-      <c r="AA8" s="991"/>
-      <c r="AB8" s="989">
+      <c r="Z8" s="993"/>
+      <c r="AA8" s="994"/>
+      <c r="AB8" s="992">
         <v>5</v>
       </c>
-      <c r="AC8" s="990"/>
-      <c r="AD8" s="991"/>
-      <c r="AE8" s="989">
+      <c r="AC8" s="993"/>
+      <c r="AD8" s="994"/>
+      <c r="AE8" s="992">
         <v>56</v>
       </c>
-      <c r="AF8" s="990"/>
-      <c r="AG8" s="991"/>
-      <c r="AH8" s="989">
+      <c r="AF8" s="993"/>
+      <c r="AG8" s="994"/>
+      <c r="AH8" s="992">
         <v>57</v>
       </c>
-      <c r="AI8" s="990"/>
-      <c r="AJ8" s="991"/>
-      <c r="AK8" s="989">
+      <c r="AI8" s="993"/>
+      <c r="AJ8" s="994"/>
+      <c r="AK8" s="992">
         <v>6</v>
       </c>
-      <c r="AL8" s="990"/>
-      <c r="AM8" s="991"/>
-      <c r="AN8" s="989">
+      <c r="AL8" s="993"/>
+      <c r="AM8" s="994"/>
+      <c r="AN8" s="992">
         <v>67</v>
       </c>
-      <c r="AO8" s="990"/>
-      <c r="AP8" s="991"/>
-      <c r="AQ8" s="989">
+      <c r="AO8" s="993"/>
+      <c r="AP8" s="994"/>
+      <c r="AQ8" s="992">
         <v>7</v>
       </c>
-      <c r="AR8" s="990"/>
-      <c r="AS8" s="991"/>
-      <c r="AT8" s="989">
+      <c r="AR8" s="993"/>
+      <c r="AS8" s="994"/>
+      <c r="AT8" s="992">
         <v>8</v>
       </c>
-      <c r="AU8" s="990"/>
-      <c r="AV8" s="991"/>
+      <c r="AU8" s="993"/>
+      <c r="AV8" s="994"/>
     </row>
     <row r="9" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
@@ -32635,80 +32628,80 @@
       <c r="C9" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="986"/>
-      <c r="E9" s="987"/>
-      <c r="F9" s="988"/>
+      <c r="D9" s="983"/>
+      <c r="E9" s="984"/>
+      <c r="F9" s="985"/>
       <c r="H9" s="32" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="989" t="s">
+      <c r="J9" s="992" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="990"/>
-      <c r="L9" s="991"/>
-      <c r="M9" s="989" t="s">
+      <c r="K9" s="993"/>
+      <c r="L9" s="994"/>
+      <c r="M9" s="992" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="990"/>
-      <c r="O9" s="991"/>
-      <c r="P9" s="989" t="s">
+      <c r="N9" s="993"/>
+      <c r="O9" s="994"/>
+      <c r="P9" s="992" t="s">
         <v>53</v>
       </c>
-      <c r="Q9" s="990"/>
-      <c r="R9" s="991"/>
-      <c r="S9" s="989" t="s">
+      <c r="Q9" s="993"/>
+      <c r="R9" s="994"/>
+      <c r="S9" s="992" t="s">
         <v>54</v>
       </c>
-      <c r="T9" s="990"/>
-      <c r="U9" s="991"/>
-      <c r="V9" s="989" t="s">
+      <c r="T9" s="993"/>
+      <c r="U9" s="994"/>
+      <c r="V9" s="992" t="s">
         <v>55</v>
       </c>
-      <c r="W9" s="990"/>
-      <c r="X9" s="991"/>
-      <c r="Y9" s="989" t="s">
+      <c r="W9" s="993"/>
+      <c r="X9" s="994"/>
+      <c r="Y9" s="992" t="s">
         <v>56</v>
       </c>
-      <c r="Z9" s="990"/>
-      <c r="AA9" s="991"/>
-      <c r="AB9" s="989" t="s">
+      <c r="Z9" s="993"/>
+      <c r="AA9" s="994"/>
+      <c r="AB9" s="992" t="s">
         <v>57</v>
       </c>
-      <c r="AC9" s="990"/>
-      <c r="AD9" s="991"/>
-      <c r="AE9" s="989" t="s">
+      <c r="AC9" s="993"/>
+      <c r="AD9" s="994"/>
+      <c r="AE9" s="992" t="s">
         <v>58</v>
       </c>
-      <c r="AF9" s="990"/>
-      <c r="AG9" s="991"/>
-      <c r="AH9" s="989" t="s">
+      <c r="AF9" s="993"/>
+      <c r="AG9" s="994"/>
+      <c r="AH9" s="992" t="s">
         <v>59</v>
       </c>
-      <c r="AI9" s="990"/>
-      <c r="AJ9" s="991"/>
-      <c r="AK9" s="989" t="s">
+      <c r="AI9" s="993"/>
+      <c r="AJ9" s="994"/>
+      <c r="AK9" s="992" t="s">
         <v>60</v>
       </c>
-      <c r="AL9" s="990"/>
-      <c r="AM9" s="991"/>
-      <c r="AN9" s="989" t="s">
+      <c r="AL9" s="993"/>
+      <c r="AM9" s="994"/>
+      <c r="AN9" s="992" t="s">
         <v>61</v>
       </c>
-      <c r="AO9" s="990"/>
-      <c r="AP9" s="991"/>
-      <c r="AQ9" s="989" t="s">
+      <c r="AO9" s="993"/>
+      <c r="AP9" s="994"/>
+      <c r="AQ9" s="992" t="s">
         <v>62</v>
       </c>
-      <c r="AR9" s="990"/>
-      <c r="AS9" s="991"/>
-      <c r="AT9" s="989" t="s">
+      <c r="AR9" s="993"/>
+      <c r="AS9" s="994"/>
+      <c r="AT9" s="992" t="s">
         <v>63</v>
       </c>
-      <c r="AU9" s="990"/>
-      <c r="AV9" s="991"/>
+      <c r="AU9" s="993"/>
+      <c r="AV9" s="994"/>
     </row>
     <row r="10" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="33" t="s">
@@ -33840,11 +33833,11 @@
       <c r="I25" s="60">
         <v>0.75</v>
       </c>
-      <c r="J25" s="980" t="s">
+      <c r="J25" s="977" t="s">
         <v>46</v>
       </c>
-      <c r="K25" s="981"/>
-      <c r="L25" s="982"/>
+      <c r="K25" s="978"/>
+      <c r="L25" s="979"/>
       <c r="Q25" s="25"/>
       <c r="R25" s="25"/>
       <c r="S25" s="25"/>
@@ -33869,16 +33862,16 @@
       <c r="I26" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="J26" s="983"/>
-      <c r="K26" s="984"/>
-      <c r="L26" s="985"/>
+      <c r="J26" s="980"/>
+      <c r="K26" s="981"/>
+      <c r="L26" s="982"/>
       <c r="Q26" s="25"/>
       <c r="R26" s="25"/>
-      <c r="S26" s="1002" t="s">
+      <c r="S26" s="986" t="s">
         <v>43</v>
       </c>
-      <c r="T26" s="1003"/>
-      <c r="U26" s="1004"/>
+      <c r="T26" s="987"/>
+      <c r="U26" s="988"/>
       <c r="AI26" s="73">
         <v>1.5</v>
       </c>
@@ -33902,9 +33895,9 @@
         <f>H27*2.54*10</f>
         <v>25.4</v>
       </c>
-      <c r="J27" s="986"/>
-      <c r="K27" s="987"/>
-      <c r="L27" s="988"/>
+      <c r="J27" s="983"/>
+      <c r="K27" s="984"/>
+      <c r="L27" s="985"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25"/>
       <c r="S27" s="42"/>
@@ -34072,11 +34065,11 @@
       <c r="U32" s="54"/>
     </row>
     <row r="33" spans="3:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="975"/>
-      <c r="D33" s="975"/>
-      <c r="E33" s="975"/>
-      <c r="F33" s="975"/>
-      <c r="G33" s="975"/>
+      <c r="C33" s="998"/>
+      <c r="D33" s="998"/>
+      <c r="E33" s="998"/>
+      <c r="F33" s="998"/>
+      <c r="G33" s="998"/>
       <c r="H33" s="54"/>
       <c r="I33" s="54"/>
       <c r="J33" s="54"/>
@@ -34104,6 +34097,36 @@
     <row r="35" spans="3:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="D7:F9"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="AB9:AD9"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="S8:U8"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="AT8:AV8"/>
+    <mergeCell ref="AT9:AV9"/>
+    <mergeCell ref="AN8:AP8"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="AB7:AD7"/>
+    <mergeCell ref="AE7:AG7"/>
+    <mergeCell ref="AK7:AM7"/>
+    <mergeCell ref="AE8:AG8"/>
+    <mergeCell ref="AE9:AG9"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="AK8:AM8"/>
+    <mergeCell ref="AK9:AM9"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V9:X9"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="H6:AS6"/>
     <mergeCell ref="H5:AS5"/>
@@ -34120,36 +34143,6 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AB8:AD8"/>
-    <mergeCell ref="AT8:AV8"/>
-    <mergeCell ref="AT9:AV9"/>
-    <mergeCell ref="AN8:AP8"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="V7:X7"/>
-    <mergeCell ref="AB7:AD7"/>
-    <mergeCell ref="AE7:AG7"/>
-    <mergeCell ref="AK7:AM7"/>
-    <mergeCell ref="AE8:AG8"/>
-    <mergeCell ref="AE9:AG9"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="AK8:AM8"/>
-    <mergeCell ref="AK9:AM9"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="AB9:AD9"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="P9:R9"/>
-    <mergeCell ref="S8:U8"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="D7:F9"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -34258,39 +34251,39 @@
       <c r="Z5" s="315"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="834" t="s">
+      <c r="A6" s="849" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="834"/>
-      <c r="C6" s="834"/>
-      <c r="D6" s="834"/>
-      <c r="E6" s="834"/>
-      <c r="F6" s="834"/>
-      <c r="G6" s="834"/>
-      <c r="H6" s="834"/>
-      <c r="I6" s="834"/>
-      <c r="J6" s="834"/>
-      <c r="K6" s="834"/>
-      <c r="L6" s="834"/>
-      <c r="M6" s="834"/>
+      <c r="B6" s="849"/>
+      <c r="C6" s="849"/>
+      <c r="D6" s="849"/>
+      <c r="E6" s="849"/>
+      <c r="F6" s="849"/>
+      <c r="G6" s="849"/>
+      <c r="H6" s="849"/>
+      <c r="I6" s="849"/>
+      <c r="J6" s="849"/>
+      <c r="K6" s="849"/>
+      <c r="L6" s="849"/>
+      <c r="M6" s="849"/>
       <c r="Z6" s="315"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="835">
+      <c r="A7" s="850">
         <v>1</v>
       </c>
-      <c r="B7" s="835"/>
-      <c r="C7" s="835"/>
-      <c r="D7" s="835"/>
-      <c r="E7" s="835"/>
-      <c r="F7" s="835"/>
-      <c r="G7" s="835"/>
-      <c r="H7" s="835"/>
-      <c r="I7" s="835"/>
-      <c r="J7" s="835"/>
-      <c r="K7" s="835"/>
-      <c r="L7" s="835"/>
-      <c r="M7" s="835"/>
+      <c r="B7" s="850"/>
+      <c r="C7" s="850"/>
+      <c r="D7" s="850"/>
+      <c r="E7" s="850"/>
+      <c r="F7" s="850"/>
+      <c r="G7" s="850"/>
+      <c r="H7" s="850"/>
+      <c r="I7" s="850"/>
+      <c r="J7" s="850"/>
+      <c r="K7" s="850"/>
+      <c r="L7" s="850"/>
+      <c r="M7" s="850"/>
     </row>
     <row r="8" spans="1:26" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34300,7 +34293,7 @@
       <c r="B9" s="247" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="645"/>
+      <c r="C9" s="644"/>
       <c r="D9" s="318"/>
       <c r="E9" s="317"/>
       <c r="F9" s="317"/>
@@ -34333,10 +34326,10 @@
       <c r="K10" s="285" t="s">
         <v>356</v>
       </c>
-      <c r="L10" s="836">
+      <c r="L10" s="851">
         <v>1</v>
       </c>
-      <c r="M10" s="836"/>
+      <c r="M10" s="851"/>
       <c r="N10" s="320"/>
       <c r="O10" s="320"/>
       <c r="P10" s="320"/>
@@ -34368,8 +34361,8 @@
       <c r="K11" s="285" t="s">
         <v>127</v>
       </c>
-      <c r="L11" s="837"/>
-      <c r="M11" s="837"/>
+      <c r="L11" s="847"/>
+      <c r="M11" s="847"/>
       <c r="N11" s="320"/>
       <c r="O11" s="320"/>
       <c r="P11" s="320"/>
@@ -34414,7 +34407,7 @@
       <c r="Y12" s="320"/>
     </row>
     <row r="13" spans="1:26" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="648" t="s">
+      <c r="A13" s="647" t="s">
         <v>358</v>
       </c>
       <c r="B13" s="484"/>
@@ -34443,21 +34436,21 @@
       <c r="Y13" s="320"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="847" t="s">
+      <c r="A14" s="835" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="848"/>
-      <c r="C14" s="848"/>
-      <c r="D14" s="848"/>
-      <c r="E14" s="848"/>
-      <c r="F14" s="848"/>
-      <c r="G14" s="848"/>
-      <c r="H14" s="848"/>
-      <c r="I14" s="848"/>
-      <c r="J14" s="848"/>
-      <c r="K14" s="848"/>
-      <c r="L14" s="848"/>
-      <c r="M14" s="849"/>
+      <c r="B14" s="836"/>
+      <c r="C14" s="836"/>
+      <c r="D14" s="836"/>
+      <c r="E14" s="836"/>
+      <c r="F14" s="836"/>
+      <c r="G14" s="836"/>
+      <c r="H14" s="836"/>
+      <c r="I14" s="836"/>
+      <c r="J14" s="836"/>
+      <c r="K14" s="836"/>
+      <c r="L14" s="836"/>
+      <c r="M14" s="837"/>
       <c r="N14" s="320"/>
       <c r="O14" s="320"/>
       <c r="P14" s="320"/>
@@ -34472,21 +34465,21 @@
       <c r="Y14" s="320"/>
     </row>
     <row r="15" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="850" t="s">
+      <c r="A15" s="838" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="851"/>
-      <c r="C15" s="851"/>
-      <c r="D15" s="851"/>
-      <c r="E15" s="851"/>
-      <c r="F15" s="851"/>
-      <c r="G15" s="851"/>
-      <c r="H15" s="851"/>
-      <c r="I15" s="851"/>
-      <c r="J15" s="851"/>
-      <c r="K15" s="851"/>
-      <c r="L15" s="851"/>
-      <c r="M15" s="852"/>
+      <c r="B15" s="839"/>
+      <c r="C15" s="839"/>
+      <c r="D15" s="839"/>
+      <c r="E15" s="839"/>
+      <c r="F15" s="839"/>
+      <c r="G15" s="839"/>
+      <c r="H15" s="839"/>
+      <c r="I15" s="839"/>
+      <c r="J15" s="839"/>
+      <c r="K15" s="839"/>
+      <c r="L15" s="839"/>
+      <c r="M15" s="840"/>
       <c r="N15" s="320"/>
       <c r="O15" s="320"/>
       <c r="P15" s="320"/>
@@ -34561,10 +34554,10 @@
       <c r="K18" s="285" t="s">
         <v>153</v>
       </c>
-      <c r="L18" s="857">
+      <c r="L18" s="845">
         <v>1</v>
       </c>
-      <c r="M18" s="858"/>
+      <c r="M18" s="846"/>
       <c r="Y18" s="320"/>
     </row>
     <row r="19" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34583,8 +34576,8 @@
       <c r="K19" s="285" t="s">
         <v>125</v>
       </c>
-      <c r="L19" s="837"/>
-      <c r="M19" s="859"/>
+      <c r="L19" s="847"/>
+      <c r="M19" s="848"/>
       <c r="Y19" s="320"/>
     </row>
     <row r="20" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34603,8 +34596,8 @@
       <c r="K20" s="285" t="s">
         <v>126</v>
       </c>
-      <c r="L20" s="837"/>
-      <c r="M20" s="859"/>
+      <c r="L20" s="847"/>
+      <c r="M20" s="848"/>
       <c r="Y20" s="320"/>
     </row>
     <row r="21" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34659,24 +34652,24 @@
       <c r="A23" s="356"/>
       <c r="B23" s="364"/>
       <c r="C23" s="364"/>
-      <c r="D23" s="853" t="s">
+      <c r="D23" s="841" t="s">
         <v>353</v>
       </c>
-      <c r="E23" s="854"/>
-      <c r="F23" s="844" t="s">
+      <c r="E23" s="842"/>
+      <c r="F23" s="833" t="s">
         <v>276</v>
       </c>
-      <c r="G23" s="844" t="s">
+      <c r="G23" s="833" t="s">
         <v>346</v>
       </c>
-      <c r="H23" s="844" t="s">
+      <c r="H23" s="833" t="s">
         <v>275</v>
       </c>
       <c r="I23" s="337"/>
-      <c r="J23" s="839" t="s">
+      <c r="J23" s="853" t="s">
         <v>146</v>
       </c>
-      <c r="K23" s="840"/>
+      <c r="K23" s="854"/>
       <c r="L23" s="497"/>
       <c r="M23" s="357"/>
       <c r="N23" s="320"/>
@@ -34691,11 +34684,11 @@
       <c r="W23" s="320"/>
       <c r="X23" s="320"/>
       <c r="Y23" s="332"/>
-      <c r="AA23" s="855" t="s">
+      <c r="AA23" s="843" t="s">
         <v>278</v>
       </c>
-      <c r="AB23" s="856"/>
-      <c r="AC23" s="844" t="s">
+      <c r="AB23" s="844"/>
+      <c r="AC23" s="833" t="s">
         <v>275</v>
       </c>
     </row>
@@ -34709,12 +34702,12 @@
       <c r="E24" s="500" t="s">
         <v>380</v>
       </c>
-      <c r="F24" s="845"/>
-      <c r="G24" s="845"/>
-      <c r="H24" s="845"/>
+      <c r="F24" s="834"/>
+      <c r="G24" s="834"/>
+      <c r="H24" s="834"/>
       <c r="I24" s="337"/>
-      <c r="J24" s="841"/>
-      <c r="K24" s="842"/>
+      <c r="J24" s="855"/>
+      <c r="K24" s="856"/>
       <c r="L24" s="497"/>
       <c r="M24" s="358"/>
       <c r="N24" s="320"/>
@@ -34735,7 +34728,7 @@
       <c r="AB24" s="380" t="s">
         <v>12</v>
       </c>
-      <c r="AC24" s="845"/>
+      <c r="AC24" s="834"/>
     </row>
     <row r="25" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="356"/>
@@ -34931,8 +34924,8 @@
       </c>
       <c r="I28" s="337"/>
       <c r="J28" s="232"/>
-      <c r="K28" s="646"/>
-      <c r="L28" s="646"/>
+      <c r="K28" s="645"/>
+      <c r="L28" s="645"/>
       <c r="M28" s="358"/>
       <c r="N28" s="320"/>
       <c r="O28" s="360" t="s">
@@ -34986,8 +34979,8 @@
       </c>
       <c r="I29" s="337"/>
       <c r="J29" s="232"/>
-      <c r="K29" s="646"/>
-      <c r="L29" s="646"/>
+      <c r="K29" s="645"/>
+      <c r="L29" s="645"/>
       <c r="M29" s="357"/>
       <c r="N29" s="320"/>
       <c r="O29" s="360" t="s">
@@ -35041,8 +35034,8 @@
       </c>
       <c r="I30" s="337"/>
       <c r="J30" s="232"/>
-      <c r="K30" s="647"/>
-      <c r="L30" s="647"/>
+      <c r="K30" s="646"/>
+      <c r="L30" s="646"/>
       <c r="M30" s="357"/>
       <c r="N30" s="320"/>
       <c r="O30" s="320"/>
@@ -35143,7 +35136,7 @@
       <c r="J32" s="298"/>
       <c r="K32" s="298"/>
       <c r="L32" s="298"/>
-      <c r="M32" s="846"/>
+      <c r="M32" s="858"/>
       <c r="N32" s="320"/>
       <c r="O32" s="320"/>
       <c r="P32" s="320"/>
@@ -35193,7 +35186,7 @@
       <c r="J33" s="298"/>
       <c r="K33" s="298"/>
       <c r="L33" s="298"/>
-      <c r="M33" s="846"/>
+      <c r="M33" s="858"/>
       <c r="N33" s="320"/>
       <c r="O33" s="320"/>
       <c r="P33" s="320"/>
@@ -35227,9 +35220,9 @@
       <c r="E34" s="362" t="s">
         <v>377</v>
       </c>
-      <c r="F34" s="359" t="e">
+      <c r="F34" s="359" t="b">
         <f>+datos!F37</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G34" s="359" t="e">
         <f>+datos!G37</f>
@@ -35277,9 +35270,9 @@
       <c r="E35" s="303" t="s">
         <v>378</v>
       </c>
-      <c r="F35" s="359" t="e">
+      <c r="F35" s="359" t="b">
         <f>+datos!F38</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G35" s="359" t="e">
         <f>+datos!G38</f>
@@ -35327,9 +35320,9 @@
       <c r="E36" s="362" t="s">
         <v>379</v>
       </c>
-      <c r="F36" s="359" t="e">
+      <c r="F36" s="359" t="b">
         <f>+datos!F39</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G36" s="359" t="e">
         <f>+datos!G39</f>
@@ -35377,9 +35370,9 @@
       <c r="E37" s="367" t="s">
         <v>363</v>
       </c>
-      <c r="F37" s="359" t="e">
+      <c r="F37" s="359" t="b">
         <f>+datos!F40</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G37" s="359" t="e">
         <f>+datos!G40</f>
@@ -35427,9 +35420,9 @@
       <c r="E38" s="367" t="s">
         <v>364</v>
       </c>
-      <c r="F38" s="359" t="e">
+      <c r="F38" s="359" t="b">
         <f>+datos!F41</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G38" s="359" t="e">
         <f>+datos!G41</f>
@@ -35477,9 +35470,9 @@
       <c r="E39" s="367" t="s">
         <v>365</v>
       </c>
-      <c r="F39" s="359" t="e">
+      <c r="F39" s="359" t="b">
         <f>+datos!F42</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G39" s="359" t="e">
         <f>+datos!G42</f>
@@ -35527,9 +35520,9 @@
       <c r="E40" s="367" t="s">
         <v>366</v>
       </c>
-      <c r="F40" s="359" t="e">
+      <c r="F40" s="359" t="b">
         <f>+datos!F43</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G40" s="359" t="e">
         <f>+datos!G43</f>
@@ -35577,9 +35570,9 @@
       <c r="E41" s="367" t="s">
         <v>367</v>
       </c>
-      <c r="F41" s="359" t="e">
+      <c r="F41" s="359" t="b">
         <f>+datos!F44</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G41" s="359" t="e">
         <f>+datos!G44</f>
@@ -36007,7 +36000,7 @@
       <c r="Z57" s="386"/>
     </row>
     <row r="58" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="644" t="s">
+      <c r="A58" s="643" t="s">
         <v>308</v>
       </c>
       <c r="B58" s="378"/>
@@ -36025,11 +36018,11 @@
       <c r="Z58" s="386"/>
     </row>
     <row r="59" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="644" t="s">
+      <c r="A59" s="643" t="s">
         <v>295</v>
       </c>
-      <c r="B59" s="644"/>
-      <c r="C59" s="644"/>
+      <c r="B59" s="643"/>
+      <c r="C59" s="643"/>
       <c r="D59" s="319"/>
       <c r="E59" s="319"/>
       <c r="F59" s="319"/>
@@ -36055,21 +36048,21 @@
       <c r="Z59" s="480"/>
     </row>
     <row r="60" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="843" t="s">
+      <c r="A60" s="857" t="s">
         <v>296</v>
       </c>
-      <c r="B60" s="843"/>
-      <c r="C60" s="843"/>
-      <c r="D60" s="843"/>
-      <c r="E60" s="843"/>
-      <c r="F60" s="843"/>
-      <c r="G60" s="843"/>
-      <c r="H60" s="843"/>
-      <c r="I60" s="843"/>
-      <c r="J60" s="843"/>
-      <c r="K60" s="843"/>
-      <c r="L60" s="843"/>
-      <c r="M60" s="843"/>
+      <c r="B60" s="857"/>
+      <c r="C60" s="857"/>
+      <c r="D60" s="857"/>
+      <c r="E60" s="857"/>
+      <c r="F60" s="857"/>
+      <c r="G60" s="857"/>
+      <c r="H60" s="857"/>
+      <c r="I60" s="857"/>
+      <c r="J60" s="857"/>
+      <c r="K60" s="857"/>
+      <c r="L60" s="857"/>
+      <c r="M60" s="857"/>
       <c r="N60" s="483"/>
       <c r="O60" s="483"/>
       <c r="P60" s="483"/>
@@ -36085,11 +36078,11 @@
       <c r="Z60" s="483"/>
     </row>
     <row r="61" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="644" t="s">
+      <c r="A61" s="643" t="s">
         <v>297</v>
       </c>
-      <c r="B61" s="644"/>
-      <c r="C61" s="644"/>
+      <c r="B61" s="643"/>
+      <c r="C61" s="643"/>
       <c r="D61" s="319"/>
       <c r="E61" s="319"/>
       <c r="F61" s="319"/>
@@ -36115,21 +36108,21 @@
       <c r="Z61" s="480"/>
     </row>
     <row r="62" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="843" t="s">
+      <c r="A62" s="857" t="s">
         <v>355</v>
       </c>
-      <c r="B62" s="843"/>
-      <c r="C62" s="843"/>
-      <c r="D62" s="843"/>
-      <c r="E62" s="843"/>
-      <c r="F62" s="843"/>
-      <c r="G62" s="843"/>
-      <c r="H62" s="843"/>
-      <c r="I62" s="843"/>
-      <c r="J62" s="843"/>
-      <c r="K62" s="843"/>
-      <c r="L62" s="843"/>
-      <c r="M62" s="843"/>
+      <c r="B62" s="857"/>
+      <c r="C62" s="857"/>
+      <c r="D62" s="857"/>
+      <c r="E62" s="857"/>
+      <c r="F62" s="857"/>
+      <c r="G62" s="857"/>
+      <c r="H62" s="857"/>
+      <c r="I62" s="857"/>
+      <c r="J62" s="857"/>
+      <c r="K62" s="857"/>
+      <c r="L62" s="857"/>
+      <c r="M62" s="857"/>
       <c r="N62" s="319"/>
       <c r="O62" s="319"/>
       <c r="P62" s="319"/>
@@ -36200,12 +36193,12 @@
       <c r="Z64" s="482"/>
     </row>
     <row r="65" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="838" t="s">
+      <c r="A65" s="852" t="s">
         <v>362</v>
       </c>
-      <c r="B65" s="838"/>
-      <c r="C65" s="838"/>
-      <c r="D65" s="838"/>
+      <c r="B65" s="852"/>
+      <c r="C65" s="852"/>
+      <c r="D65" s="852"/>
       <c r="E65" s="337"/>
       <c r="F65" s="337"/>
       <c r="G65" s="337"/>
@@ -36287,15 +36280,6 @@
     <protectedRange sqref="D9:D10" name="Rango3_3_1_1_1_1_1_2_1_1_1"/>
   </protectedRanges>
   <mergeCells count="20">
-    <mergeCell ref="AC23:AC24"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A7:M7"/>
     <mergeCell ref="L10:M10"/>
@@ -36307,6 +36291,15 @@
     <mergeCell ref="H23:H24"/>
     <mergeCell ref="A62:M62"/>
     <mergeCell ref="M32:M33"/>
+    <mergeCell ref="AC23:AC24"/>
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -36414,37 +36407,37 @@
       <c r="Y5" s="315"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="834" t="s">
+      <c r="A6" s="849" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="834"/>
-      <c r="C6" s="834"/>
-      <c r="D6" s="834"/>
-      <c r="E6" s="834"/>
-      <c r="F6" s="834"/>
-      <c r="G6" s="834"/>
-      <c r="H6" s="834"/>
-      <c r="I6" s="834"/>
-      <c r="J6" s="834"/>
-      <c r="K6" s="834"/>
-      <c r="L6" s="834"/>
+      <c r="B6" s="849"/>
+      <c r="C6" s="849"/>
+      <c r="D6" s="849"/>
+      <c r="E6" s="849"/>
+      <c r="F6" s="849"/>
+      <c r="G6" s="849"/>
+      <c r="H6" s="849"/>
+      <c r="I6" s="849"/>
+      <c r="J6" s="849"/>
+      <c r="K6" s="849"/>
+      <c r="L6" s="849"/>
       <c r="Y6" s="315"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="860">
+      <c r="A7" s="867">
         <v>1</v>
       </c>
-      <c r="B7" s="860"/>
-      <c r="C7" s="860"/>
-      <c r="D7" s="860"/>
-      <c r="E7" s="860"/>
-      <c r="F7" s="860"/>
-      <c r="G7" s="860"/>
-      <c r="H7" s="860"/>
-      <c r="I7" s="860"/>
-      <c r="J7" s="860"/>
-      <c r="K7" s="860"/>
-      <c r="L7" s="860"/>
+      <c r="B7" s="867"/>
+      <c r="C7" s="867"/>
+      <c r="D7" s="867"/>
+      <c r="E7" s="867"/>
+      <c r="F7" s="867"/>
+      <c r="G7" s="867"/>
+      <c r="H7" s="867"/>
+      <c r="I7" s="867"/>
+      <c r="J7" s="867"/>
+      <c r="K7" s="867"/>
+      <c r="L7" s="867"/>
     </row>
     <row r="8" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36454,7 +36447,7 @@
       <c r="B9" s="247" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="645">
+      <c r="C9" s="644">
         <f>+FORMATO!M2</f>
         <v>0</v>
       </c>
@@ -36479,7 +36472,7 @@
       <c r="B10" s="247" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="645">
+      <c r="C10" s="644">
         <f>+FORMATO!M3</f>
         <v>0</v>
       </c>
@@ -36493,7 +36486,7 @@
       <c r="K10" s="285" t="s">
         <v>356</v>
       </c>
-      <c r="L10" s="724">
+      <c r="L10" s="723">
         <f>+FORMATO!M7</f>
         <v>0</v>
       </c>
@@ -36517,7 +36510,7 @@
       <c r="B11" s="247" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="645">
+      <c r="C11" s="644">
         <f>+FORMATO!M4</f>
         <v>0</v>
       </c>
@@ -36531,7 +36524,7 @@
       <c r="K11" s="285" t="s">
         <v>382</v>
       </c>
-      <c r="L11" s="724">
+      <c r="L11" s="723">
         <f>+FORMATO!M9</f>
         <v>0</v>
       </c>
@@ -36555,7 +36548,7 @@
       <c r="B12" s="247" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="645">
+      <c r="C12" s="644">
         <f>+FORMATO!M5</f>
         <v>0</v>
       </c>
@@ -36569,7 +36562,7 @@
       <c r="K12" s="285" t="s">
         <v>127</v>
       </c>
-      <c r="L12" s="702">
+      <c r="L12" s="701">
         <f>+FORMATO!M8</f>
         <v>0</v>
       </c>
@@ -36587,7 +36580,7 @@
       <c r="X12" s="320"/>
     </row>
     <row r="13" spans="1:25" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="648" t="s">
+      <c r="A13" s="647" t="s">
         <v>358</v>
       </c>
       <c r="B13" s="484"/>
@@ -36615,20 +36608,20 @@
       <c r="X13" s="320"/>
     </row>
     <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="847" t="s">
+      <c r="A14" s="835" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="848"/>
-      <c r="C14" s="848"/>
-      <c r="D14" s="848"/>
-      <c r="E14" s="848"/>
-      <c r="F14" s="848"/>
-      <c r="G14" s="848"/>
-      <c r="H14" s="848"/>
-      <c r="I14" s="848"/>
-      <c r="J14" s="848"/>
-      <c r="K14" s="848"/>
-      <c r="L14" s="849"/>
+      <c r="B14" s="836"/>
+      <c r="C14" s="836"/>
+      <c r="D14" s="836"/>
+      <c r="E14" s="836"/>
+      <c r="F14" s="836"/>
+      <c r="G14" s="836"/>
+      <c r="H14" s="836"/>
+      <c r="I14" s="836"/>
+      <c r="J14" s="836"/>
+      <c r="K14" s="836"/>
+      <c r="L14" s="837"/>
       <c r="M14" s="320"/>
       <c r="N14" s="320"/>
       <c r="O14" s="320"/>
@@ -36643,20 +36636,20 @@
       <c r="X14" s="320"/>
     </row>
     <row r="15" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="850" t="s">
+      <c r="A15" s="838" t="s">
         <v>466</v>
       </c>
-      <c r="B15" s="851"/>
-      <c r="C15" s="851"/>
-      <c r="D15" s="851"/>
-      <c r="E15" s="851"/>
-      <c r="F15" s="851"/>
-      <c r="G15" s="851"/>
-      <c r="H15" s="851"/>
-      <c r="I15" s="851"/>
-      <c r="J15" s="851"/>
-      <c r="K15" s="851"/>
-      <c r="L15" s="852"/>
+      <c r="B15" s="839"/>
+      <c r="C15" s="839"/>
+      <c r="D15" s="839"/>
+      <c r="E15" s="839"/>
+      <c r="F15" s="839"/>
+      <c r="G15" s="839"/>
+      <c r="H15" s="839"/>
+      <c r="I15" s="839"/>
+      <c r="J15" s="839"/>
+      <c r="K15" s="839"/>
+      <c r="L15" s="840"/>
       <c r="M15" s="320"/>
       <c r="N15" s="320"/>
       <c r="O15" s="320"/>
@@ -36682,7 +36675,7 @@
       <c r="I16" s="342"/>
       <c r="J16" s="343"/>
       <c r="K16" s="344"/>
-      <c r="L16" s="650"/>
+      <c r="L16" s="649"/>
       <c r="M16" s="320"/>
       <c r="N16" s="320"/>
       <c r="O16" s="320"/>
@@ -36710,7 +36703,7 @@
       <c r="I17" s="348"/>
       <c r="J17" s="348"/>
       <c r="K17" s="291"/>
-      <c r="L17" s="651"/>
+      <c r="L17" s="650"/>
       <c r="X17" s="320"/>
     </row>
     <row r="18" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36732,7 +36725,7 @@
       <c r="K18" s="285" t="s">
         <v>153</v>
       </c>
-      <c r="L18" s="725">
+      <c r="L18" s="724">
         <f>+FORMATO!M11</f>
         <v>0</v>
       </c>
@@ -36757,7 +36750,7 @@
       <c r="K19" s="285" t="s">
         <v>125</v>
       </c>
-      <c r="L19" s="704">
+      <c r="L19" s="703">
         <f>+FORMATO!M12</f>
         <v>0</v>
       </c>
@@ -36782,7 +36775,7 @@
       <c r="K20" s="285" t="s">
         <v>126</v>
       </c>
-      <c r="L20" s="704">
+      <c r="L20" s="703">
         <f>+FORMATO!M13</f>
         <v>0</v>
       </c>
@@ -36842,30 +36835,30 @@
       <c r="A23" s="356"/>
       <c r="B23" s="364"/>
       <c r="C23" s="364"/>
-      <c r="D23" s="853" t="s">
+      <c r="D23" s="841" t="s">
         <v>353</v>
       </c>
-      <c r="E23" s="854"/>
-      <c r="F23" s="844" t="s">
+      <c r="E23" s="842"/>
+      <c r="F23" s="833" t="s">
         <v>276</v>
       </c>
-      <c r="G23" s="844" t="s">
+      <c r="G23" s="833" t="s">
         <v>346</v>
       </c>
-      <c r="H23" s="844" t="s">
+      <c r="H23" s="833" t="s">
         <v>275</v>
       </c>
       <c r="I23" s="337"/>
-      <c r="J23" s="839" t="s">
+      <c r="J23" s="853" t="s">
         <v>146</v>
       </c>
-      <c r="K23" s="840"/>
-      <c r="L23" s="652"/>
+      <c r="K23" s="854"/>
+      <c r="L23" s="651"/>
       <c r="M23" s="320"/>
-      <c r="N23" s="839" t="s">
+      <c r="N23" s="853" t="s">
         <v>146</v>
       </c>
-      <c r="O23" s="840"/>
+      <c r="O23" s="854"/>
       <c r="P23" s="320"/>
       <c r="Q23" s="320"/>
       <c r="R23" s="320"/>
@@ -36875,11 +36868,11 @@
       <c r="V23" s="320"/>
       <c r="W23" s="320"/>
       <c r="X23" s="332"/>
-      <c r="Z23" s="855" t="s">
+      <c r="Z23" s="843" t="s">
         <v>278</v>
       </c>
-      <c r="AA23" s="856"/>
-      <c r="AB23" s="844" t="s">
+      <c r="AA23" s="844"/>
+      <c r="AB23" s="833" t="s">
         <v>275</v>
       </c>
     </row>
@@ -36893,16 +36886,16 @@
       <c r="E24" s="500" t="s">
         <v>380</v>
       </c>
-      <c r="F24" s="845"/>
-      <c r="G24" s="845"/>
-      <c r="H24" s="845"/>
+      <c r="F24" s="834"/>
+      <c r="G24" s="834"/>
+      <c r="H24" s="834"/>
       <c r="I24" s="337"/>
-      <c r="J24" s="841"/>
-      <c r="K24" s="842"/>
-      <c r="L24" s="652"/>
+      <c r="J24" s="855"/>
+      <c r="K24" s="856"/>
+      <c r="L24" s="651"/>
       <c r="M24" s="320"/>
-      <c r="N24" s="841"/>
-      <c r="O24" s="842"/>
+      <c r="N24" s="855"/>
+      <c r="O24" s="856"/>
       <c r="P24" s="320"/>
       <c r="Q24" s="320"/>
       <c r="R24" s="320"/>
@@ -36918,7 +36911,7 @@
       <c r="AA24" s="380" t="s">
         <v>12</v>
       </c>
-      <c r="AB24" s="845"/>
+      <c r="AB24" s="834"/>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="356"/>
@@ -36943,14 +36936,14 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I25" s="337"/>
-      <c r="J25" s="862" t="s">
+      <c r="J25" s="860" t="s">
         <v>381</v>
       </c>
-      <c r="K25" s="865" t="e">
+      <c r="K25" s="863" t="e">
         <f>+datos!I21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L25" s="653"/>
+      <c r="L25" s="652"/>
       <c r="M25" s="334"/>
       <c r="N25" s="360" t="s">
         <v>268</v>
@@ -37002,9 +36995,9 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I26" s="337"/>
-      <c r="J26" s="863"/>
-      <c r="K26" s="866"/>
-      <c r="L26" s="653"/>
+      <c r="J26" s="861"/>
+      <c r="K26" s="864"/>
+      <c r="L26" s="652"/>
       <c r="M26" s="320"/>
       <c r="N26" s="360" t="s">
         <v>269</v>
@@ -37056,9 +37049,9 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="337"/>
-      <c r="J27" s="864"/>
-      <c r="K27" s="867"/>
-      <c r="L27" s="649"/>
+      <c r="J27" s="862"/>
+      <c r="K27" s="865"/>
+      <c r="L27" s="648"/>
       <c r="M27" s="320"/>
       <c r="N27" s="360" t="s">
         <v>149</v>
@@ -37111,8 +37104,8 @@
       </c>
       <c r="I28" s="337"/>
       <c r="J28" s="232"/>
-      <c r="K28" s="646"/>
-      <c r="L28" s="654"/>
+      <c r="K28" s="645"/>
+      <c r="L28" s="653"/>
       <c r="M28" s="320"/>
       <c r="N28" s="360" t="s">
         <v>147</v>
@@ -37165,8 +37158,8 @@
       </c>
       <c r="I29" s="337"/>
       <c r="J29" s="232"/>
-      <c r="K29" s="646"/>
-      <c r="L29" s="654"/>
+      <c r="K29" s="645"/>
+      <c r="L29" s="653"/>
       <c r="M29" s="320"/>
       <c r="N29" s="360" t="s">
         <v>148</v>
@@ -37219,8 +37212,8 @@
       </c>
       <c r="I30" s="337"/>
       <c r="J30" s="232"/>
-      <c r="K30" s="647"/>
-      <c r="L30" s="655"/>
+      <c r="K30" s="646"/>
+      <c r="L30" s="654"/>
       <c r="M30" s="320"/>
       <c r="N30" s="320"/>
       <c r="O30" s="320"/>
@@ -37269,7 +37262,7 @@
       <c r="I31" s="337"/>
       <c r="J31" s="18"/>
       <c r="K31" s="18"/>
-      <c r="L31" s="656"/>
+      <c r="L31" s="655"/>
       <c r="M31" s="320"/>
       <c r="N31" s="320"/>
       <c r="O31" s="320"/>
@@ -37318,7 +37311,7 @@
       <c r="I32" s="337"/>
       <c r="J32" s="298"/>
       <c r="K32" s="298"/>
-      <c r="L32" s="657"/>
+      <c r="L32" s="656"/>
       <c r="M32" s="320"/>
       <c r="N32" s="320"/>
       <c r="O32" s="320"/>
@@ -37367,7 +37360,7 @@
       <c r="I33" s="337"/>
       <c r="J33" s="298"/>
       <c r="K33" s="298"/>
-      <c r="L33" s="657"/>
+      <c r="L33" s="656"/>
       <c r="M33" s="320"/>
       <c r="N33" s="320"/>
       <c r="O33" s="320"/>
@@ -37401,9 +37394,9 @@
       <c r="E34" s="362" t="s">
         <v>377</v>
       </c>
-      <c r="F34" s="359" t="e">
+      <c r="F34" s="359" t="b">
         <f>+datos!F37</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G34" s="359" t="e">
         <f>+datos!G37</f>
@@ -37450,9 +37443,9 @@
       <c r="E35" s="303" t="s">
         <v>378</v>
       </c>
-      <c r="F35" s="359" t="e">
+      <c r="F35" s="359" t="b">
         <f>+datos!F38</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G35" s="359" t="e">
         <f>+datos!G38</f>
@@ -37499,9 +37492,9 @@
       <c r="E36" s="362" t="s">
         <v>379</v>
       </c>
-      <c r="F36" s="359" t="e">
+      <c r="F36" s="359" t="b">
         <f>+datos!F39</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G36" s="359" t="e">
         <f>+datos!G39</f>
@@ -37548,9 +37541,9 @@
       <c r="E37" s="367" t="s">
         <v>363</v>
       </c>
-      <c r="F37" s="359" t="e">
+      <c r="F37" s="359" t="b">
         <f>+datos!F40</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G37" s="359" t="e">
         <f>+datos!G40</f>
@@ -37597,9 +37590,9 @@
       <c r="E38" s="367" t="s">
         <v>364</v>
       </c>
-      <c r="F38" s="359" t="e">
+      <c r="F38" s="359" t="b">
         <f>+datos!F41</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G38" s="359" t="e">
         <f>+datos!G41</f>
@@ -37646,9 +37639,9 @@
       <c r="E39" s="367" t="s">
         <v>365</v>
       </c>
-      <c r="F39" s="359" t="e">
+      <c r="F39" s="359" t="b">
         <f>+datos!F42</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G39" s="359" t="e">
         <f>+datos!G42</f>
@@ -37695,9 +37688,9 @@
       <c r="E40" s="367" t="s">
         <v>366</v>
       </c>
-      <c r="F40" s="359" t="e">
+      <c r="F40" s="359" t="b">
         <f>+datos!F43</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G40" s="359" t="e">
         <f>+datos!G43</f>
@@ -37744,9 +37737,9 @@
       <c r="E41" s="367" t="s">
         <v>367</v>
       </c>
-      <c r="F41" s="359" t="e">
+      <c r="F41" s="359" t="b">
         <f>+datos!F44</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G41" s="359" t="e">
         <f>+datos!G44</f>
@@ -38157,37 +38150,37 @@
       <c r="Y57" s="386"/>
     </row>
     <row r="58" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="868" t="s">
+      <c r="A58" s="866" t="s">
         <v>467</v>
       </c>
-      <c r="B58" s="868"/>
-      <c r="C58" s="868"/>
-      <c r="D58" s="868"/>
-      <c r="E58" s="868"/>
-      <c r="F58" s="868"/>
-      <c r="G58" s="868"/>
-      <c r="H58" s="868"/>
-      <c r="I58" s="868"/>
-      <c r="J58" s="868"/>
-      <c r="K58" s="868"/>
-      <c r="L58" s="868"/>
+      <c r="B58" s="866"/>
+      <c r="C58" s="866"/>
+      <c r="D58" s="866"/>
+      <c r="E58" s="866"/>
+      <c r="F58" s="866"/>
+      <c r="G58" s="866"/>
+      <c r="H58" s="866"/>
+      <c r="I58" s="866"/>
+      <c r="J58" s="866"/>
+      <c r="K58" s="866"/>
+      <c r="L58" s="866"/>
       <c r="Y58" s="386"/>
     </row>
     <row r="59" spans="1:25" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="861" t="s">
+      <c r="A59" s="859" t="s">
         <v>468</v>
       </c>
-      <c r="B59" s="861"/>
-      <c r="C59" s="861"/>
-      <c r="D59" s="861"/>
-      <c r="E59" s="861"/>
-      <c r="F59" s="861"/>
-      <c r="G59" s="861"/>
-      <c r="H59" s="861"/>
-      <c r="I59" s="861"/>
-      <c r="J59" s="861"/>
-      <c r="K59" s="861"/>
-      <c r="L59" s="861"/>
+      <c r="B59" s="859"/>
+      <c r="C59" s="859"/>
+      <c r="D59" s="859"/>
+      <c r="E59" s="859"/>
+      <c r="F59" s="859"/>
+      <c r="G59" s="859"/>
+      <c r="H59" s="859"/>
+      <c r="I59" s="859"/>
+      <c r="J59" s="859"/>
+      <c r="K59" s="859"/>
+      <c r="L59" s="859"/>
       <c r="M59" s="319"/>
       <c r="N59" s="319"/>
       <c r="O59" s="319"/>
@@ -38203,20 +38196,20 @@
       <c r="Y59" s="480"/>
     </row>
     <row r="60" spans="1:25" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="861" t="s">
+      <c r="A60" s="859" t="s">
         <v>469</v>
       </c>
-      <c r="B60" s="861"/>
-      <c r="C60" s="861"/>
-      <c r="D60" s="861"/>
-      <c r="E60" s="861"/>
-      <c r="F60" s="861"/>
-      <c r="G60" s="861"/>
-      <c r="H60" s="861"/>
-      <c r="I60" s="861"/>
-      <c r="J60" s="861"/>
-      <c r="K60" s="861"/>
-      <c r="L60" s="861"/>
+      <c r="B60" s="859"/>
+      <c r="C60" s="859"/>
+      <c r="D60" s="859"/>
+      <c r="E60" s="859"/>
+      <c r="F60" s="859"/>
+      <c r="G60" s="859"/>
+      <c r="H60" s="859"/>
+      <c r="I60" s="859"/>
+      <c r="J60" s="859"/>
+      <c r="K60" s="859"/>
+      <c r="L60" s="859"/>
       <c r="M60" s="483"/>
       <c r="N60" s="483"/>
       <c r="O60" s="483"/>
@@ -38232,20 +38225,20 @@
       <c r="Y60" s="483"/>
     </row>
     <row r="61" spans="1:25" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="861" t="s">
+      <c r="A61" s="859" t="s">
         <v>470</v>
       </c>
-      <c r="B61" s="861"/>
-      <c r="C61" s="861"/>
-      <c r="D61" s="861"/>
-      <c r="E61" s="861"/>
-      <c r="F61" s="861"/>
-      <c r="G61" s="861"/>
-      <c r="H61" s="861"/>
-      <c r="I61" s="861"/>
-      <c r="J61" s="861"/>
-      <c r="K61" s="861"/>
-      <c r="L61" s="861"/>
+      <c r="B61" s="859"/>
+      <c r="C61" s="859"/>
+      <c r="D61" s="859"/>
+      <c r="E61" s="859"/>
+      <c r="F61" s="859"/>
+      <c r="G61" s="859"/>
+      <c r="H61" s="859"/>
+      <c r="I61" s="859"/>
+      <c r="J61" s="859"/>
+      <c r="K61" s="859"/>
+      <c r="L61" s="859"/>
       <c r="M61" s="319"/>
       <c r="N61" s="319"/>
       <c r="O61" s="319"/>
@@ -38261,20 +38254,20 @@
       <c r="Y61" s="480"/>
     </row>
     <row r="62" spans="1:25" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="843" t="s">
+      <c r="A62" s="857" t="s">
         <v>471</v>
       </c>
-      <c r="B62" s="843"/>
-      <c r="C62" s="843"/>
-      <c r="D62" s="843"/>
-      <c r="E62" s="843"/>
-      <c r="F62" s="843"/>
-      <c r="G62" s="843"/>
-      <c r="H62" s="843"/>
-      <c r="I62" s="843"/>
-      <c r="J62" s="843"/>
-      <c r="K62" s="843"/>
-      <c r="L62" s="843"/>
+      <c r="B62" s="857"/>
+      <c r="C62" s="857"/>
+      <c r="D62" s="857"/>
+      <c r="E62" s="857"/>
+      <c r="F62" s="857"/>
+      <c r="G62" s="857"/>
+      <c r="H62" s="857"/>
+      <c r="I62" s="857"/>
+      <c r="J62" s="857"/>
+      <c r="K62" s="857"/>
+      <c r="L62" s="857"/>
       <c r="M62" s="319"/>
       <c r="N62" s="319"/>
       <c r="O62" s="319"/>
@@ -38344,12 +38337,12 @@
       <c r="Y64" s="482"/>
     </row>
     <row r="65" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="838" t="s">
+      <c r="A65" s="852" t="s">
         <v>472</v>
       </c>
-      <c r="B65" s="838"/>
-      <c r="C65" s="838"/>
-      <c r="D65" s="838"/>
+      <c r="B65" s="852"/>
+      <c r="C65" s="852"/>
+      <c r="D65" s="852"/>
       <c r="E65" s="337"/>
       <c r="F65" s="337"/>
       <c r="G65" s="337"/>
@@ -38357,7 +38350,7 @@
       <c r="I65" s="337"/>
       <c r="J65" s="337"/>
       <c r="K65" s="337"/>
-      <c r="L65" s="701" t="s">
+      <c r="L65" s="700" t="s">
         <v>298</v>
       </c>
     </row>
@@ -38427,6 +38420,11 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="20">
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="Z23:AA23"/>
     <mergeCell ref="AB23:AB24"/>
     <mergeCell ref="A60:L60"/>
     <mergeCell ref="A62:L62"/>
@@ -38442,11 +38440,6 @@
     <mergeCell ref="A61:L61"/>
     <mergeCell ref="A59:L59"/>
     <mergeCell ref="A58:L58"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="Z23:AA23"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
@@ -38476,148 +38469,148 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="470"/>
-      <c r="B1" s="847" t="s">
+      <c r="B1" s="835" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="848"/>
-      <c r="D1" s="848"/>
-      <c r="E1" s="848"/>
-      <c r="F1" s="848"/>
-      <c r="G1" s="848"/>
-      <c r="H1" s="848"/>
-      <c r="I1" s="848"/>
-      <c r="J1" s="848"/>
-      <c r="K1" s="848"/>
-      <c r="L1" s="849"/>
+      <c r="C1" s="836"/>
+      <c r="D1" s="836"/>
+      <c r="E1" s="836"/>
+      <c r="F1" s="836"/>
+      <c r="G1" s="836"/>
+      <c r="H1" s="836"/>
+      <c r="I1" s="836"/>
+      <c r="J1" s="836"/>
+      <c r="K1" s="836"/>
+      <c r="L1" s="837"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="470"/>
-      <c r="B2" s="850" t="s">
+      <c r="B2" s="838" t="s">
         <v>383</v>
       </c>
-      <c r="C2" s="851"/>
-      <c r="D2" s="851"/>
-      <c r="E2" s="851"/>
-      <c r="F2" s="851"/>
-      <c r="G2" s="851"/>
-      <c r="H2" s="851"/>
-      <c r="I2" s="851"/>
-      <c r="J2" s="851"/>
-      <c r="K2" s="851"/>
-      <c r="L2" s="852"/>
+      <c r="C2" s="839"/>
+      <c r="D2" s="839"/>
+      <c r="E2" s="839"/>
+      <c r="F2" s="839"/>
+      <c r="G2" s="839"/>
+      <c r="H2" s="839"/>
+      <c r="I2" s="839"/>
+      <c r="J2" s="839"/>
+      <c r="K2" s="839"/>
+      <c r="L2" s="840"/>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="470"/>
-      <c r="B3" s="721" t="s">
+      <c r="B3" s="720" t="s">
         <v>304</v>
       </c>
-      <c r="C3" s="609"/>
-      <c r="D3" s="610"/>
-      <c r="E3" s="610"/>
-      <c r="F3" s="610"/>
-      <c r="G3" s="610"/>
-      <c r="H3" s="610"/>
-      <c r="I3" s="541"/>
-      <c r="J3" s="541"/>
-      <c r="K3" s="541"/>
-      <c r="L3" s="542"/>
+      <c r="C3" s="608"/>
+      <c r="D3" s="609"/>
+      <c r="E3" s="609"/>
+      <c r="F3" s="609"/>
+      <c r="G3" s="609"/>
+      <c r="H3" s="609"/>
+      <c r="I3" s="540"/>
+      <c r="J3" s="540"/>
+      <c r="K3" s="540"/>
+      <c r="L3" s="541"/>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="470"/>
-      <c r="B4" s="722" t="s">
+      <c r="B4" s="721" t="s">
         <v>305</v>
       </c>
-      <c r="C4" s="791"/>
+      <c r="C4" s="790"/>
       <c r="D4" s="47"/>
-      <c r="E4" s="791"/>
-      <c r="F4" s="791"/>
-      <c r="G4" s="792"/>
-      <c r="H4" s="791"/>
-      <c r="I4" s="793"/>
-      <c r="J4" s="793"/>
-      <c r="K4" s="793"/>
+      <c r="E4" s="790"/>
+      <c r="F4" s="790"/>
+      <c r="G4" s="791"/>
+      <c r="H4" s="790"/>
+      <c r="I4" s="792"/>
+      <c r="J4" s="792"/>
+      <c r="K4" s="792"/>
       <c r="L4" s="490"/>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="470"/>
-      <c r="B5" s="722" t="s">
+      <c r="B5" s="721" t="s">
         <v>306</v>
       </c>
-      <c r="C5" s="791"/>
-      <c r="D5" s="794">
+      <c r="C5" s="790"/>
+      <c r="D5" s="793">
         <f>+Balanza!B8</f>
         <v>-3.2899999999999998E-6</v>
       </c>
-      <c r="E5" s="791"/>
-      <c r="F5" s="791"/>
-      <c r="G5" s="792"/>
-      <c r="H5" s="791"/>
-      <c r="I5" s="793"/>
-      <c r="J5" s="793"/>
-      <c r="K5" s="793"/>
+      <c r="E5" s="790"/>
+      <c r="F5" s="790"/>
+      <c r="G5" s="791"/>
+      <c r="H5" s="790"/>
+      <c r="I5" s="792"/>
+      <c r="J5" s="792"/>
+      <c r="K5" s="792"/>
       <c r="L5" s="490"/>
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="470"/>
-      <c r="B6" s="722" t="s">
+      <c r="B6" s="721" t="s">
         <v>104</v>
       </c>
       <c r="C6" s="47"/>
-      <c r="D6" s="795" t="str">
+      <c r="D6" s="794" t="str">
         <f>+Balanza!B12</f>
         <v>EQP-0046</v>
       </c>
-      <c r="E6" s="796"/>
-      <c r="F6" s="796"/>
+      <c r="E6" s="795"/>
+      <c r="F6" s="795"/>
       <c r="G6" s="47"/>
-      <c r="H6" s="791"/>
-      <c r="I6" s="793"/>
-      <c r="J6" s="793"/>
-      <c r="K6" s="793"/>
+      <c r="H6" s="790"/>
+      <c r="I6" s="792"/>
+      <c r="J6" s="792"/>
+      <c r="K6" s="792"/>
       <c r="L6" s="490"/>
     </row>
     <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="470"/>
-      <c r="B7" s="723" t="s">
+      <c r="B7" s="722" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="611"/>
-      <c r="D7" s="797">
+      <c r="C7" s="610"/>
+      <c r="D7" s="796">
         <v>46132</v>
       </c>
-      <c r="E7" s="612"/>
-      <c r="F7" s="612"/>
-      <c r="G7" s="613"/>
-      <c r="H7" s="613"/>
-      <c r="I7" s="789"/>
-      <c r="J7" s="789"/>
-      <c r="K7" s="789"/>
-      <c r="L7" s="790"/>
+      <c r="E7" s="611"/>
+      <c r="F7" s="611"/>
+      <c r="G7" s="612"/>
+      <c r="H7" s="612"/>
+      <c r="I7" s="788"/>
+      <c r="J7" s="788"/>
+      <c r="K7" s="788"/>
+      <c r="L7" s="789"/>
     </row>
     <row r="8" spans="1:14" ht="8.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="470"/>
       <c r="B8" s="470"/>
-      <c r="C8" s="614"/>
-      <c r="D8" s="614"/>
-      <c r="E8" s="615"/>
-      <c r="F8" s="615"/>
-      <c r="G8" s="615"/>
-      <c r="H8" s="615"/>
-      <c r="I8" s="615"/>
-      <c r="J8" s="615"/>
-      <c r="K8" s="615"/>
-      <c r="L8" s="615"/>
+      <c r="C8" s="613"/>
+      <c r="D8" s="613"/>
+      <c r="E8" s="614"/>
+      <c r="F8" s="614"/>
+      <c r="G8" s="614"/>
+      <c r="H8" s="614"/>
+      <c r="I8" s="614"/>
+      <c r="J8" s="614"/>
+      <c r="K8" s="614"/>
+      <c r="L8" s="614"/>
     </row>
     <row r="9" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="470"/>
       <c r="B9" s="439" t="s">
         <v>332</v>
       </c>
-      <c r="C9" s="884" t="s">
+      <c r="C9" s="883" t="s">
         <v>344</v>
       </c>
-      <c r="D9" s="885"/>
-      <c r="F9" s="580" t="s">
+      <c r="D9" s="884"/>
+      <c r="F9" s="579" t="s">
         <v>354</v>
       </c>
       <c r="G9" s="470"/>
@@ -38633,11 +38626,11 @@
       <c r="B10" s="439" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="884" t="s">
-        <v>474</v>
-      </c>
-      <c r="D10" s="885"/>
-      <c r="F10" s="708" t="s">
+      <c r="C10" s="883" t="s">
+        <v>344</v>
+      </c>
+      <c r="D10" s="884"/>
+      <c r="F10" s="707" t="s">
         <v>344</v>
       </c>
       <c r="G10" s="470">
@@ -38655,8 +38648,8 @@
     <row r="11" spans="1:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="470"/>
       <c r="B11" s="441"/>
-      <c r="C11" s="616"/>
-      <c r="D11" s="616"/>
+      <c r="C11" s="615"/>
+      <c r="D11" s="615"/>
       <c r="E11" s="470"/>
       <c r="F11" s="470"/>
       <c r="G11" s="470"/>
@@ -38664,43 +38657,43 @@
       <c r="I11" s="470"/>
       <c r="J11" s="470"/>
       <c r="K11" s="470"/>
-      <c r="L11" s="617"/>
+      <c r="L11" s="616"/>
       <c r="M11" s="440"/>
       <c r="N11" s="440"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="470"/>
-      <c r="B12" s="875" t="s">
+      <c r="B12" s="874" t="s">
         <v>282</v>
       </c>
-      <c r="C12" s="876"/>
-      <c r="D12" s="876"/>
-      <c r="E12" s="877"/>
+      <c r="C12" s="875"/>
+      <c r="D12" s="875"/>
+      <c r="E12" s="876"/>
       <c r="F12" s="470"/>
-      <c r="G12" s="878" t="s">
+      <c r="G12" s="877" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="879"/>
-      <c r="I12" s="880"/>
+      <c r="H12" s="878"/>
+      <c r="I12" s="879"/>
       <c r="J12" s="470"/>
       <c r="K12" s="470"/>
-      <c r="L12" s="617"/>
+      <c r="L12" s="616"/>
       <c r="M12" s="440"/>
       <c r="N12" s="440"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="470"/>
-      <c r="B13" s="618"/>
-      <c r="C13" s="543" t="s">
+      <c r="B13" s="617"/>
+      <c r="C13" s="542" t="s">
         <v>280</v>
       </c>
-      <c r="D13" s="543" t="s">
+      <c r="D13" s="542" t="s">
         <v>257</v>
       </c>
-      <c r="E13" s="543" t="s">
+      <c r="E13" s="542" t="s">
         <v>281</v>
       </c>
-      <c r="F13" s="617"/>
+      <c r="F13" s="616"/>
       <c r="G13" s="473"/>
       <c r="H13" s="474" t="s">
         <v>283</v>
@@ -38710,31 +38703,31 @@
       </c>
       <c r="J13" s="470"/>
       <c r="K13" s="470"/>
-      <c r="L13" s="617"/>
+      <c r="L13" s="616"/>
       <c r="M13" s="440"/>
       <c r="N13" s="440"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="581" t="s">
+      <c r="B14" s="580" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="561">
+      <c r="C14" s="560">
         <f>+FORMATO!D30</f>
         <v>0</v>
       </c>
-      <c r="D14" s="562">
+      <c r="D14" s="561">
         <f>C14+($D$5*C14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="563">
+      <c r="E14" s="562">
         <f>D14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="619">
+      <c r="F14" s="618">
         <f>SUM(E28:E45)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="582" t="s">
+      <c r="G14" s="581" t="s">
         <v>284</v>
       </c>
       <c r="H14" s="538">
@@ -38745,64 +38738,64 @@
         <f>H14+($D$5*H14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="617"/>
-      <c r="K14" s="617"/>
-      <c r="L14" s="617"/>
+      <c r="J14" s="616"/>
+      <c r="K14" s="616"/>
+      <c r="L14" s="616"/>
       <c r="M14" s="443"/>
       <c r="N14" s="440"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="583" t="s">
+      <c r="B15" s="582" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="564">
+      <c r="C15" s="563">
         <f>+FORMATO!D33</f>
         <v>0</v>
       </c>
-      <c r="D15" s="565">
+      <c r="D15" s="564">
         <f>C15+($D$5*C15)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="566" t="e">
+      <c r="E15" s="565" t="e">
         <f>D15/(1+I16/100)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F15" s="620"/>
-      <c r="G15" s="584" t="s">
+      <c r="F15" s="619"/>
+      <c r="G15" s="583" t="s">
         <v>285</v>
       </c>
-      <c r="H15" s="539">
-        <f>J12</f>
+      <c r="H15" s="538">
+        <f>+IF(C11="Global",FORMATO!D22,FORMATO!D36)</f>
         <v>0</v>
       </c>
       <c r="I15" s="444">
         <f>H15+($D$5*H15)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="617"/>
-      <c r="K15" s="622"/>
-      <c r="L15" s="622"/>
+      <c r="J15" s="616"/>
+      <c r="K15" s="621"/>
+      <c r="L15" s="621"/>
       <c r="M15" s="445"/>
       <c r="N15" s="440"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="585" t="s">
+      <c r="B16" s="584" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="447"/>
       <c r="D16" s="448"/>
-      <c r="E16" s="560" t="e">
+      <c r="E16" s="559" t="e">
         <f>SUM(E14:E15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F16" s="621">
+      <c r="F16" s="620" t="b">
         <f>IF(C10="Global",H15,IF(C10="Fraccionada",E16))</f>
         <v>0</v>
       </c>
-      <c r="G16" s="586" t="s">
+      <c r="G16" s="585" t="s">
         <v>286</v>
       </c>
-      <c r="H16" s="587" t="e">
+      <c r="H16" s="586" t="e">
         <f>((H14-H15)/H15)*100</f>
         <v>#DIV/0!</v>
       </c>
@@ -38810,13 +38803,13 @@
         <f>((I14-I15)/I15)*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J16" s="617"/>
-      <c r="K16" s="622"/>
-      <c r="L16" s="617"/>
+      <c r="J16" s="616"/>
+      <c r="K16" s="621"/>
+      <c r="L16" s="616"/>
       <c r="M16" s="445"/>
     </row>
     <row r="17" spans="1:22" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="623"/>
+      <c r="A17" s="622"/>
       <c r="B17" s="470"/>
       <c r="C17" s="470"/>
       <c r="D17" s="470"/>
@@ -38825,37 +38818,37 @@
       <c r="G17" s="470"/>
       <c r="H17" s="470"/>
       <c r="I17" s="470"/>
-      <c r="J17" s="617"/>
-      <c r="K17" s="622"/>
-      <c r="L17" s="617"/>
+      <c r="J17" s="616"/>
+      <c r="K17" s="621"/>
+      <c r="L17" s="616"/>
       <c r="M17" s="440"/>
     </row>
     <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="623"/>
-      <c r="B18" s="875" t="s">
+      <c r="A18" s="622"/>
+      <c r="B18" s="874" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="876"/>
-      <c r="D18" s="876"/>
-      <c r="E18" s="877"/>
+      <c r="C18" s="875"/>
+      <c r="D18" s="875"/>
+      <c r="E18" s="876"/>
       <c r="F18" s="470"/>
       <c r="G18" s="470"/>
-      <c r="H18" s="882" t="s">
+      <c r="H18" s="881" t="s">
         <v>146</v>
       </c>
-      <c r="I18" s="883"/>
-      <c r="J18" s="617"/>
-      <c r="K18" s="622"/>
-      <c r="L18" s="617"/>
+      <c r="I18" s="882"/>
+      <c r="J18" s="616"/>
+      <c r="K18" s="621"/>
+      <c r="L18" s="616"/>
     </row>
     <row r="19" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="623"/>
+      <c r="A19" s="622"/>
       <c r="B19" s="452" t="s">
         <v>290</v>
       </c>
       <c r="C19" s="475"/>
       <c r="D19" s="475"/>
-      <c r="E19" s="453">
+      <c r="E19" s="453" t="b">
         <f>IF(C9="Grueso",F14,F16)</f>
         <v>0</v>
       </c>
@@ -38868,21 +38861,21 @@
         <f>IF(C9="Fino","- -",T39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J19" s="617"/>
+      <c r="J19" s="616"/>
       <c r="K19" s="471"/>
-      <c r="L19" s="617"/>
+      <c r="L19" s="616"/>
       <c r="N19" s="440"/>
     </row>
     <row r="20" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="623"/>
+      <c r="A20" s="622"/>
       <c r="B20" s="455" t="s">
         <v>289</v>
       </c>
       <c r="C20" s="456"/>
       <c r="D20" s="456"/>
-      <c r="E20" s="457" t="str">
+      <c r="E20" s="457" t="b">
         <f>IF(C10="Global","--",IF(C10="Fraccionada",I15))</f>
-        <v>--</v>
+        <v>0</v>
       </c>
       <c r="F20" s="470"/>
       <c r="G20" s="470"/>
@@ -38895,20 +38888,20 @@
       </c>
       <c r="J20" s="470"/>
       <c r="K20" s="470"/>
-      <c r="L20" s="624"/>
+      <c r="L20" s="623"/>
     </row>
     <row r="21" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="451"/>
-      <c r="B21" s="588" t="s">
+      <c r="B21" s="587" t="s">
         <v>303</v>
       </c>
-      <c r="C21" s="589"/>
-      <c r="D21" s="589"/>
+      <c r="C21" s="588"/>
+      <c r="D21" s="588"/>
       <c r="E21" s="537">
         <f>+IF(C10="Global",FORMATO!D24,FORMATO!D39)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="775"/>
+      <c r="F21" s="774"/>
       <c r="G21" s="470"/>
       <c r="H21" s="458" t="s">
         <v>37</v>
@@ -38919,15 +38912,15 @@
       </c>
       <c r="J21" s="470"/>
       <c r="K21" s="470"/>
-      <c r="L21" s="617"/>
+      <c r="L21" s="616"/>
     </row>
     <row r="22" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="623"/>
+      <c r="A22" s="622"/>
       <c r="B22" s="455" t="s">
         <v>302</v>
       </c>
-      <c r="C22" s="625"/>
-      <c r="D22" s="625"/>
+      <c r="C22" s="624"/>
+      <c r="D22" s="624"/>
       <c r="E22" s="457">
         <f>IF(C10="Global",SUM(E28:E45),SUM(E37:E45))</f>
         <v>0</v>
@@ -38946,13 +38939,13 @@
       <c r="L22" s="470"/>
     </row>
     <row r="23" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="623"/>
+      <c r="A23" s="622"/>
       <c r="B23" s="460" t="s">
         <v>287</v>
       </c>
-      <c r="C23" s="626"/>
-      <c r="D23" s="626"/>
-      <c r="E23" s="627">
+      <c r="C23" s="625"/>
+      <c r="D23" s="625"/>
+      <c r="E23" s="626">
         <f>ABS(E21-E22)</f>
         <v>0</v>
       </c>
@@ -38970,17 +38963,17 @@
       <c r="L23" s="470"/>
     </row>
     <row r="24" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="623"/>
+      <c r="A24" s="622"/>
       <c r="B24" s="446" t="s">
         <v>301</v>
       </c>
-      <c r="C24" s="628"/>
-      <c r="D24" s="628"/>
-      <c r="E24" s="629" t="e">
+      <c r="C24" s="627"/>
+      <c r="D24" s="627"/>
+      <c r="E24" s="628" t="e">
         <f>E23/E21*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F24" s="630" t="e">
+      <c r="F24" s="629" t="e">
         <f>+IF(E24&lt;=0.3,"cumple","no cumple")</f>
         <v>#DIV/0!</v>
       </c>
@@ -38997,11 +38990,11 @@
       <c r="L24" s="470"/>
     </row>
     <row r="25" spans="1:22" ht="8.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="623"/>
+      <c r="A25" s="622"/>
       <c r="B25" s="477"/>
       <c r="C25" s="470"/>
       <c r="D25" s="470"/>
-      <c r="E25" s="631"/>
+      <c r="E25" s="630"/>
       <c r="F25" s="470"/>
       <c r="G25" s="488"/>
       <c r="H25" s="489"/>
@@ -39011,33 +39004,33 @@
       <c r="L25" s="470"/>
     </row>
     <row r="26" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="632"/>
-      <c r="B26" s="881" t="s">
+      <c r="A26" s="631"/>
+      <c r="B26" s="880" t="s">
         <v>278</v>
       </c>
-      <c r="C26" s="881"/>
-      <c r="D26" s="633" t="s">
+      <c r="C26" s="880"/>
+      <c r="D26" s="632" t="s">
         <v>277</v>
       </c>
-      <c r="E26" s="874" t="s">
+      <c r="E26" s="873" t="s">
         <v>100</v>
       </c>
-      <c r="F26" s="872" t="s">
+      <c r="F26" s="871" t="s">
         <v>288</v>
       </c>
-      <c r="G26" s="872" t="s">
+      <c r="G26" s="871" t="s">
         <v>345</v>
       </c>
-      <c r="H26" s="872" t="s">
+      <c r="H26" s="871" t="s">
         <v>275</v>
       </c>
       <c r="I26" s="470"/>
       <c r="J26" s="470"/>
-      <c r="K26" s="634"/>
-      <c r="L26" s="634"/>
+      <c r="K26" s="633"/>
+      <c r="L26" s="633"/>
     </row>
     <row r="27" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="635"/>
+      <c r="A27" s="634"/>
       <c r="B27" s="476" t="s">
         <v>267</v>
       </c>
@@ -39047,34 +39040,34 @@
       <c r="D27" s="476" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="874"/>
-      <c r="F27" s="873"/>
-      <c r="G27" s="873"/>
-      <c r="H27" s="873"/>
+      <c r="E27" s="873"/>
+      <c r="F27" s="872"/>
+      <c r="G27" s="872"/>
+      <c r="H27" s="872"/>
       <c r="I27" s="470"/>
-      <c r="J27" s="636"/>
-      <c r="K27" s="634"/>
-      <c r="L27" s="634"/>
-      <c r="M27" s="709"/>
-      <c r="N27" s="710"/>
-      <c r="O27" s="710"/>
-      <c r="P27" s="710"/>
-      <c r="Q27" s="710"/>
-      <c r="R27" s="710"/>
-      <c r="S27" s="710"/>
-      <c r="T27" s="710"/>
-      <c r="U27" s="710"/>
-      <c r="V27" s="711"/>
+      <c r="J27" s="635"/>
+      <c r="K27" s="633"/>
+      <c r="L27" s="633"/>
+      <c r="M27" s="708"/>
+      <c r="N27" s="709"/>
+      <c r="O27" s="709"/>
+      <c r="P27" s="709"/>
+      <c r="Q27" s="709"/>
+      <c r="R27" s="709"/>
+      <c r="S27" s="709"/>
+      <c r="T27" s="709"/>
+      <c r="U27" s="709"/>
+      <c r="V27" s="710"/>
     </row>
     <row r="28" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="635"/>
+      <c r="A28" s="634"/>
       <c r="B28" s="465">
         <v>3</v>
       </c>
       <c r="C28" s="462">
         <v>75</v>
       </c>
-      <c r="D28" s="540">
+      <c r="D28" s="539">
         <f>+FORMATO!I18</f>
         <v>0</v>
       </c>
@@ -39098,50 +39091,50 @@
       <c r="J28" s="470"/>
       <c r="K28" s="470"/>
       <c r="L28" s="470"/>
-      <c r="M28" s="712"/>
-      <c r="N28" s="590" t="e">
+      <c r="M28" s="711"/>
+      <c r="N28" s="589" t="e">
         <f t="shared" ref="N28:N36" si="1">IF(G28&gt;=5,1,0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O28" s="590" t="e">
+      <c r="O28" s="589" t="e">
         <f>IF(N28=0,1,-0.5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P28" s="590" t="e">
+      <c r="P28" s="589" t="e">
         <f>O28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q28" s="591">
+      <c r="Q28" s="590">
         <f t="shared" ref="Q28:Q36" si="2">+B28</f>
         <v>3</v>
       </c>
-      <c r="R28" s="590">
+      <c r="R28" s="589">
         <f t="shared" ref="R28:R34" si="3">IF(D28&lt;100,1,0)</f>
         <v>1</v>
       </c>
-      <c r="S28" s="590" t="e">
+      <c r="S28" s="589" t="e">
         <f t="shared" ref="S28:S36" si="4">IF(H28=100,1,-0.5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T28" s="590" t="e">
+      <c r="T28" s="589" t="e">
         <f>S28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U28" s="591">
+      <c r="U28" s="590">
         <f>+Q28</f>
         <v>3</v>
       </c>
-      <c r="V28" s="713"/>
+      <c r="V28" s="712"/>
     </row>
     <row r="29" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="623"/>
+      <c r="A29" s="622"/>
       <c r="B29" s="466">
         <v>2.5</v>
       </c>
       <c r="C29" s="462">
         <v>63</v>
       </c>
-      <c r="D29" s="540">
+      <c r="D29" s="539">
         <f>+FORMATO!I19</f>
         <v>0</v>
       </c>
@@ -39165,50 +39158,50 @@
       <c r="J29" s="470"/>
       <c r="K29" s="470"/>
       <c r="L29" s="470"/>
-      <c r="M29" s="712"/>
-      <c r="N29" s="590" t="e">
+      <c r="M29" s="711"/>
+      <c r="N29" s="589" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="590" t="e">
+      <c r="O29" s="589" t="e">
         <f t="shared" ref="O29:O36" si="8">IF(N29=0,1,-0.5)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P29" s="590" t="e">
+      <c r="P29" s="589" t="e">
         <f t="shared" ref="P29:P36" si="9">P28+O29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q29" s="591">
+      <c r="Q29" s="590">
         <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
-      <c r="R29" s="590">
+      <c r="R29" s="589">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S29" s="590" t="e">
+      <c r="S29" s="589" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T29" s="590" t="e">
+      <c r="T29" s="589" t="e">
         <f t="shared" ref="T29:T36" si="10">T28+S29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U29" s="591">
+      <c r="U29" s="590">
         <f t="shared" ref="U29:U36" si="11">+Q29</f>
         <v>2.5</v>
       </c>
-      <c r="V29" s="713"/>
+      <c r="V29" s="712"/>
     </row>
     <row r="30" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="623"/>
+      <c r="A30" s="622"/>
       <c r="B30" s="465">
         <v>2</v>
       </c>
       <c r="C30" s="462">
         <v>50</v>
       </c>
-      <c r="D30" s="540">
+      <c r="D30" s="539">
         <f>+FORMATO!I20</f>
         <v>0</v>
       </c>
@@ -39232,50 +39225,50 @@
       <c r="J30" s="470"/>
       <c r="K30" s="470"/>
       <c r="L30" s="470"/>
-      <c r="M30" s="712"/>
-      <c r="N30" s="590" t="e">
+      <c r="M30" s="711"/>
+      <c r="N30" s="589" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O30" s="590" t="e">
+      <c r="O30" s="589" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P30" s="590" t="e">
+      <c r="P30" s="589" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q30" s="591">
+      <c r="Q30" s="590">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="R30" s="590">
+      <c r="R30" s="589">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S30" s="590" t="e">
+      <c r="S30" s="589" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T30" s="590" t="e">
+      <c r="T30" s="589" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U30" s="591">
+      <c r="U30" s="590">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
-      <c r="V30" s="713"/>
+      <c r="V30" s="712"/>
     </row>
     <row r="31" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="623"/>
+      <c r="A31" s="622"/>
       <c r="B31" s="466">
         <v>1.5</v>
       </c>
       <c r="C31" s="467">
         <v>37.5</v>
       </c>
-      <c r="D31" s="540">
+      <c r="D31" s="539">
         <f>+FORMATO!I21</f>
         <v>0</v>
       </c>
@@ -39299,50 +39292,50 @@
       <c r="J31" s="470"/>
       <c r="K31" s="470"/>
       <c r="L31" s="470"/>
-      <c r="M31" s="712"/>
-      <c r="N31" s="590" t="e">
+      <c r="M31" s="711"/>
+      <c r="N31" s="589" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O31" s="590" t="e">
+      <c r="O31" s="589" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P31" s="590" t="e">
+      <c r="P31" s="589" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q31" s="591">
+      <c r="Q31" s="590">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="R31" s="590">
+      <c r="R31" s="589">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S31" s="590" t="e">
+      <c r="S31" s="589" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T31" s="590" t="e">
+      <c r="T31" s="589" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U31" s="591">
+      <c r="U31" s="590">
         <f t="shared" si="11"/>
         <v>1.5</v>
       </c>
-      <c r="V31" s="713"/>
+      <c r="V31" s="712"/>
     </row>
     <row r="32" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="623"/>
+      <c r="A32" s="622"/>
       <c r="B32" s="465">
         <v>1</v>
       </c>
       <c r="C32" s="462">
         <v>25</v>
       </c>
-      <c r="D32" s="540">
+      <c r="D32" s="539">
         <f>+FORMATO!I22</f>
         <v>0</v>
       </c>
@@ -39366,50 +39359,50 @@
       <c r="J32" s="470"/>
       <c r="K32" s="470"/>
       <c r="L32" s="470"/>
-      <c r="M32" s="712"/>
-      <c r="N32" s="590" t="e">
+      <c r="M32" s="711"/>
+      <c r="N32" s="589" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O32" s="590" t="e">
+      <c r="O32" s="589" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P32" s="590" t="e">
+      <c r="P32" s="589" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q32" s="591">
+      <c r="Q32" s="590">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="R32" s="590">
+      <c r="R32" s="589">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S32" s="590" t="e">
+      <c r="S32" s="589" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T32" s="590" t="e">
+      <c r="T32" s="589" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U32" s="591">
+      <c r="U32" s="590">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="V32" s="713"/>
+      <c r="V32" s="712"/>
     </row>
     <row r="33" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="623"/>
+      <c r="A33" s="622"/>
       <c r="B33" s="466">
         <v>0.75</v>
       </c>
       <c r="C33" s="462">
         <v>19</v>
       </c>
-      <c r="D33" s="540">
+      <c r="D33" s="539">
         <f>+FORMATO!I23</f>
         <v>0</v>
       </c>
@@ -39433,50 +39426,50 @@
       <c r="J33" s="470"/>
       <c r="K33" s="470"/>
       <c r="L33" s="470"/>
-      <c r="M33" s="712"/>
-      <c r="N33" s="590" t="e">
+      <c r="M33" s="711"/>
+      <c r="N33" s="589" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O33" s="590" t="e">
+      <c r="O33" s="589" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P33" s="590" t="e">
+      <c r="P33" s="589" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q33" s="592">
+      <c r="Q33" s="591">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="R33" s="590">
+      <c r="R33" s="589">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S33" s="590" t="e">
+      <c r="S33" s="589" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T33" s="590" t="e">
+      <c r="T33" s="589" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U33" s="592">
+      <c r="U33" s="591">
         <f t="shared" si="11"/>
         <v>0.75</v>
       </c>
-      <c r="V33" s="713"/>
+      <c r="V33" s="712"/>
     </row>
     <row r="34" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="623"/>
+      <c r="A34" s="622"/>
       <c r="B34" s="466">
         <v>0.5</v>
       </c>
       <c r="C34" s="467">
         <v>12.5</v>
       </c>
-      <c r="D34" s="540">
+      <c r="D34" s="539">
         <f>+FORMATO!I24</f>
         <v>0</v>
       </c>
@@ -39496,54 +39489,54 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I34" s="638"/>
+      <c r="I34" s="637"/>
       <c r="J34" s="470"/>
       <c r="K34" s="470"/>
       <c r="L34" s="470"/>
-      <c r="M34" s="712"/>
-      <c r="N34" s="590" t="e">
+      <c r="M34" s="711"/>
+      <c r="N34" s="589" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O34" s="590" t="e">
+      <c r="O34" s="589" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P34" s="590" t="e">
+      <c r="P34" s="589" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q34" s="592">
+      <c r="Q34" s="591">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="R34" s="590">
+      <c r="R34" s="589">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="S34" s="590" t="e">
+      <c r="S34" s="589" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T34" s="590" t="e">
+      <c r="T34" s="589" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U34" s="592">
+      <c r="U34" s="591">
         <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
-      <c r="V34" s="713"/>
+      <c r="V34" s="712"/>
     </row>
     <row r="35" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="623"/>
+      <c r="A35" s="622"/>
       <c r="B35" s="466">
         <v>0.375</v>
       </c>
       <c r="C35" s="467">
         <v>9.5</v>
       </c>
-      <c r="D35" s="540">
+      <c r="D35" s="539">
         <f>+FORMATO!I25</f>
         <v>0</v>
       </c>
@@ -39567,47 +39560,47 @@
       <c r="J35" s="470"/>
       <c r="K35" s="470"/>
       <c r="L35" s="470"/>
-      <c r="M35" s="712"/>
-      <c r="N35" s="590" t="e">
+      <c r="M35" s="711"/>
+      <c r="N35" s="589" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O35" s="590" t="e">
+      <c r="O35" s="589" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P35" s="590" t="e">
+      <c r="P35" s="589" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q35" s="592">
+      <c r="Q35" s="591">
         <f t="shared" si="2"/>
         <v>0.375</v>
       </c>
-      <c r="R35" s="590"/>
-      <c r="S35" s="590" t="e">
+      <c r="R35" s="589"/>
+      <c r="S35" s="589" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T35" s="590" t="e">
+      <c r="T35" s="589" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U35" s="592">
+      <c r="U35" s="591">
         <f t="shared" si="11"/>
         <v>0.375</v>
       </c>
-      <c r="V35" s="713"/>
+      <c r="V35" s="712"/>
     </row>
     <row r="36" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="623"/>
+      <c r="A36" s="622"/>
       <c r="B36" s="465" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="461">
         <v>4.75</v>
       </c>
-      <c r="D36" s="540">
+      <c r="D36" s="539">
         <f>+FORMATO!I26</f>
         <v>0</v>
       </c>
@@ -39631,47 +39624,47 @@
       <c r="J36" s="470"/>
       <c r="K36" s="470"/>
       <c r="L36" s="470"/>
-      <c r="M36" s="712"/>
-      <c r="N36" s="590" t="e">
+      <c r="M36" s="711"/>
+      <c r="N36" s="589" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O36" s="590" t="e">
+      <c r="O36" s="589" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P36" s="590" t="e">
+      <c r="P36" s="589" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q36" s="591" t="str">
+      <c r="Q36" s="590" t="str">
         <f t="shared" si="2"/>
         <v>No4</v>
       </c>
-      <c r="R36" s="590"/>
-      <c r="S36" s="590" t="e">
+      <c r="R36" s="589"/>
+      <c r="S36" s="589" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T36" s="590" t="e">
+      <c r="T36" s="589" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U36" s="591" t="str">
+      <c r="U36" s="590" t="str">
         <f t="shared" si="11"/>
         <v>No4</v>
       </c>
-      <c r="V36" s="713"/>
+      <c r="V36" s="712"/>
     </row>
     <row r="37" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="623"/>
+      <c r="A37" s="622"/>
       <c r="B37" s="465">
         <v>8</v>
       </c>
       <c r="C37" s="461">
         <v>2.36</v>
       </c>
-      <c r="D37" s="540">
+      <c r="D37" s="539">
         <f>+FORMATO!I27</f>
         <v>0</v>
       </c>
@@ -39679,9 +39672,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F37" s="501" t="e">
+      <c r="F37" s="501" t="b">
         <f>IF($C$10="Fraccionada",E37*$H$36/E$20,IF($C$10="Global",E37/$E$19*100))</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G37" s="502" t="e">
         <f t="shared" si="12"/>
@@ -39692,32 +39685,32 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I37" s="470"/>
-      <c r="J37" s="640"/>
+      <c r="J37" s="639"/>
       <c r="K37" s="470"/>
       <c r="L37" s="470"/>
-      <c r="M37" s="712"/>
-      <c r="N37" s="590" t="e">
+      <c r="M37" s="711"/>
+      <c r="N37" s="589" t="e">
         <f>SUM(N28:N36)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O37" s="590"/>
-      <c r="P37" s="590"/>
-      <c r="Q37" s="591"/>
-      <c r="R37" s="590"/>
-      <c r="S37" s="590"/>
-      <c r="T37" s="590"/>
-      <c r="U37" s="591"/>
-      <c r="V37" s="713"/>
+      <c r="O37" s="589"/>
+      <c r="P37" s="589"/>
+      <c r="Q37" s="590"/>
+      <c r="R37" s="589"/>
+      <c r="S37" s="589"/>
+      <c r="T37" s="589"/>
+      <c r="U37" s="590"/>
+      <c r="V37" s="712"/>
     </row>
     <row r="38" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="623"/>
+      <c r="A38" s="622"/>
       <c r="B38" s="465">
         <v>10</v>
       </c>
       <c r="C38" s="462">
         <v>2</v>
       </c>
-      <c r="D38" s="540">
+      <c r="D38" s="539">
         <f>+FORMATO!I28</f>
         <v>0</v>
       </c>
@@ -39725,9 +39718,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F38" s="501" t="e">
+      <c r="F38" s="501" t="b">
         <f>IF($C$10="Fraccionada",E38*$H$36/E$20,IF($C$10="Global",E38/$E$19*100))</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G38" s="502" t="e">
         <f>+G37+F38</f>
@@ -39741,36 +39734,36 @@
       <c r="J38" s="470"/>
       <c r="K38" s="470"/>
       <c r="L38" s="470"/>
-      <c r="M38" s="712"/>
-      <c r="N38" s="714"/>
-      <c r="O38" s="590" t="s">
+      <c r="M38" s="711"/>
+      <c r="N38" s="713"/>
+      <c r="O38" s="589" t="s">
         <v>72</v>
       </c>
-      <c r="P38" s="590" t="e">
+      <c r="P38" s="589" t="e">
         <f>MAX(P28:P36)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q38" s="714"/>
-      <c r="R38" s="715"/>
-      <c r="S38" s="590" t="s">
+      <c r="Q38" s="713"/>
+      <c r="R38" s="714"/>
+      <c r="S38" s="589" t="s">
         <v>72</v>
       </c>
-      <c r="T38" s="590" t="e">
+      <c r="T38" s="589" t="e">
         <f>MAX(T28:T36)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U38" s="715"/>
-      <c r="V38" s="713"/>
+      <c r="U38" s="714"/>
+      <c r="V38" s="712"/>
     </row>
     <row r="39" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="623"/>
+      <c r="A39" s="622"/>
       <c r="B39" s="465">
         <v>16</v>
       </c>
       <c r="C39" s="461">
         <v>1.18</v>
       </c>
-      <c r="D39" s="540">
+      <c r="D39" s="539">
         <f>+FORMATO!I29</f>
         <v>0</v>
       </c>
@@ -39778,9 +39771,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F39" s="501" t="e">
+      <c r="F39" s="501" t="b">
         <f t="shared" ref="F39:F45" si="13">IF($C$10="Fraccionada",E39*$H$36/E$20,IF($C$10="Global",E39/$E$19*100))</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G39" s="502" t="e">
         <f t="shared" si="12"/>
@@ -39794,36 +39787,36 @@
       <c r="J39" s="470"/>
       <c r="K39" s="470"/>
       <c r="L39" s="470"/>
-      <c r="M39" s="712"/>
-      <c r="N39" s="714"/>
-      <c r="O39" s="590" t="s">
+      <c r="M39" s="711"/>
+      <c r="N39" s="713"/>
+      <c r="O39" s="589" t="s">
         <v>65</v>
       </c>
-      <c r="P39" s="590" t="e">
+      <c r="P39" s="589" t="e">
         <f>IF(N37=0,"&lt;No .4",VLOOKUP(1,N28:Q36,4,0))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q39" s="714"/>
-      <c r="R39" s="715"/>
-      <c r="S39" s="590" t="s">
+      <c r="Q39" s="713"/>
+      <c r="R39" s="714"/>
+      <c r="S39" s="589" t="s">
         <v>73</v>
       </c>
-      <c r="T39" s="590" t="e">
+      <c r="T39" s="589" t="e">
         <f>VLOOKUP(T38,T28:U36,2,0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U39" s="715"/>
-      <c r="V39" s="713"/>
+      <c r="U39" s="714"/>
+      <c r="V39" s="712"/>
     </row>
     <row r="40" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="623"/>
+      <c r="A40" s="622"/>
       <c r="B40" s="465">
         <v>30</v>
       </c>
       <c r="C40" s="468">
         <v>0.6</v>
       </c>
-      <c r="D40" s="540">
+      <c r="D40" s="539">
         <f>+FORMATO!I30</f>
         <v>0</v>
       </c>
@@ -39831,9 +39824,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F40" s="501" t="e">
+      <c r="F40" s="501" t="b">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G40" s="502" t="e">
         <f t="shared" si="12"/>
@@ -39844,23 +39837,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I40" s="470"/>
-      <c r="J40" s="634"/>
+      <c r="J40" s="633"/>
       <c r="K40" s="470"/>
       <c r="L40" s="470"/>
-      <c r="M40" s="716"/>
-      <c r="N40" s="717"/>
-      <c r="Q40" s="717"/>
-      <c r="V40" s="713"/>
+      <c r="M40" s="715"/>
+      <c r="N40" s="716"/>
+      <c r="Q40" s="716"/>
+      <c r="V40" s="712"/>
     </row>
     <row r="41" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="623"/>
+      <c r="A41" s="622"/>
       <c r="B41" s="465">
         <v>40</v>
       </c>
       <c r="C41" s="468">
         <v>0.42499999999999999</v>
       </c>
-      <c r="D41" s="540">
+      <c r="D41" s="539">
         <f>+FORMATO!I31</f>
         <v>0</v>
       </c>
@@ -39868,9 +39861,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F41" s="501" t="e">
+      <c r="F41" s="501" t="b">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G41" s="502" t="e">
         <f t="shared" si="12"/>
@@ -39881,29 +39874,29 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I41" s="470"/>
-      <c r="J41" s="634"/>
+      <c r="J41" s="633"/>
       <c r="K41" s="83"/>
       <c r="L41" s="85"/>
-      <c r="M41" s="718"/>
-      <c r="N41" s="719"/>
-      <c r="O41" s="719"/>
-      <c r="P41" s="719"/>
-      <c r="Q41" s="719"/>
-      <c r="R41" s="719"/>
-      <c r="S41" s="719"/>
-      <c r="T41" s="719"/>
-      <c r="U41" s="719"/>
-      <c r="V41" s="720"/>
+      <c r="M41" s="717"/>
+      <c r="N41" s="718"/>
+      <c r="O41" s="718"/>
+      <c r="P41" s="718"/>
+      <c r="Q41" s="718"/>
+      <c r="R41" s="718"/>
+      <c r="S41" s="718"/>
+      <c r="T41" s="718"/>
+      <c r="U41" s="718"/>
+      <c r="V41" s="719"/>
     </row>
     <row r="42" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="623"/>
+      <c r="A42" s="622"/>
       <c r="B42" s="465">
         <v>50</v>
       </c>
       <c r="C42" s="468">
         <v>0.3</v>
       </c>
-      <c r="D42" s="540">
+      <c r="D42" s="539">
         <f>+FORMATO!I32</f>
         <v>0</v>
       </c>
@@ -39911,9 +39904,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F42" s="501" t="e">
+      <c r="F42" s="501" t="b">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G42" s="502" t="e">
         <f t="shared" si="12"/>
@@ -39924,19 +39917,19 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I42" s="470"/>
-      <c r="J42" s="617"/>
-      <c r="K42" s="617"/>
+      <c r="J42" s="616"/>
+      <c r="K42" s="616"/>
       <c r="L42" s="470"/>
     </row>
     <row r="43" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="623"/>
+      <c r="A43" s="622"/>
       <c r="B43" s="465">
         <v>100</v>
       </c>
       <c r="C43" s="468">
         <v>0.15</v>
       </c>
-      <c r="D43" s="540">
+      <c r="D43" s="539">
         <f>+FORMATO!I33</f>
         <v>0</v>
       </c>
@@ -39944,9 +39937,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F43" s="501" t="e">
+      <c r="F43" s="501" t="b">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G43" s="502" t="e">
         <f t="shared" si="12"/>
@@ -39957,19 +39950,19 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I43" s="470"/>
-      <c r="J43" s="617"/>
-      <c r="K43" s="639"/>
-      <c r="L43" s="617"/>
+      <c r="J43" s="616"/>
+      <c r="K43" s="638"/>
+      <c r="L43" s="616"/>
     </row>
     <row r="44" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="623"/>
+      <c r="A44" s="622"/>
       <c r="B44" s="465">
         <v>200</v>
       </c>
       <c r="C44" s="468">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="D44" s="540">
+      <c r="D44" s="539">
         <f>+FORMATO!I34</f>
         <v>0</v>
       </c>
@@ -39977,9 +39970,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F44" s="501" t="e">
+      <c r="F44" s="501" t="b">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G44" s="502" t="e">
         <f t="shared" si="12"/>
@@ -39990,17 +39983,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I44" s="470"/>
-      <c r="J44" s="640"/>
-      <c r="K44" s="622"/>
-      <c r="L44" s="617"/>
+      <c r="J44" s="639"/>
+      <c r="K44" s="621"/>
+      <c r="L44" s="616"/>
     </row>
     <row r="45" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="623"/>
-      <c r="B45" s="637" t="s">
+      <c r="A45" s="622"/>
+      <c r="B45" s="636" t="s">
         <v>34</v>
       </c>
       <c r="C45" s="465"/>
-      <c r="D45" s="540">
+      <c r="D45" s="539">
         <f>+FORMATO!I35</f>
         <v>0</v>
       </c>
@@ -40008,9 +40001,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F45" s="501" t="e">
+      <c r="F45" s="501" t="b">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="G45" s="502" t="e">
         <f>+G44+H44</f>
@@ -40018,32 +40011,32 @@
       </c>
       <c r="H45" s="501"/>
       <c r="I45" s="470"/>
-      <c r="J45" s="617"/>
-      <c r="K45" s="622"/>
-      <c r="L45" s="641"/>
+      <c r="J45" s="616"/>
+      <c r="K45" s="621"/>
+      <c r="L45" s="640"/>
     </row>
     <row r="46" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="623"/>
+      <c r="A46" s="622"/>
       <c r="B46" s="477"/>
       <c r="C46" s="477"/>
       <c r="D46" s="464"/>
       <c r="E46" s="477"/>
-      <c r="F46" s="642"/>
-      <c r="G46" s="642"/>
-      <c r="H46" s="643"/>
-      <c r="I46" s="617"/>
-      <c r="J46" s="617"/>
-      <c r="K46" s="622"/>
-      <c r="L46" s="617"/>
+      <c r="F46" s="641"/>
+      <c r="G46" s="641"/>
+      <c r="H46" s="642"/>
+      <c r="I46" s="616"/>
+      <c r="J46" s="616"/>
+      <c r="K46" s="621"/>
+      <c r="L46" s="616"/>
     </row>
     <row r="47" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="451"/>
       <c r="B47" s="464"/>
-      <c r="C47" s="869" t="s">
+      <c r="C47" s="868" t="s">
         <v>293</v>
       </c>
-      <c r="D47" s="869"/>
-      <c r="E47" s="869"/>
+      <c r="D47" s="868"/>
+      <c r="E47" s="868"/>
       <c r="H47" s="469"/>
       <c r="I47" s="440"/>
       <c r="J47" s="440"/>
@@ -40053,7 +40046,7 @@
     <row r="48" spans="1:22" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="451"/>
       <c r="B48" s="464"/>
-      <c r="C48" s="593" t="s">
+      <c r="C48" s="592" t="s">
         <v>258</v>
       </c>
       <c r="D48" s="479" t="s">
@@ -40067,14 +40060,14 @@
     <row r="49" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="451"/>
       <c r="B49" s="464"/>
-      <c r="C49" s="594">
+      <c r="C49" s="593">
         <v>0.375</v>
       </c>
-      <c r="D49" s="595">
+      <c r="D49" s="594">
         <v>1000</v>
       </c>
-      <c r="E49" s="540"/>
-      <c r="G49" s="596"/>
+      <c r="E49" s="539"/>
+      <c r="G49" s="595"/>
       <c r="H49" s="464"/>
       <c r="I49" s="440"/>
       <c r="J49" s="440"/>
@@ -40083,14 +40076,14 @@
     <row r="50" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="451"/>
       <c r="B50" s="454"/>
-      <c r="C50" s="594">
+      <c r="C50" s="593">
         <v>0.5</v>
       </c>
-      <c r="D50" s="595">
+      <c r="D50" s="594">
         <v>2000</v>
       </c>
-      <c r="E50" s="540"/>
-      <c r="G50" s="596"/>
+      <c r="E50" s="539"/>
+      <c r="G50" s="595"/>
       <c r="H50" s="464"/>
       <c r="I50" s="440"/>
       <c r="J50" s="440"/>
@@ -40099,13 +40092,13 @@
     <row r="51" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="451"/>
       <c r="B51" s="454"/>
-      <c r="C51" s="594">
+      <c r="C51" s="593">
         <v>0.75</v>
       </c>
-      <c r="D51" s="595">
+      <c r="D51" s="594">
         <v>5000</v>
       </c>
-      <c r="E51" s="540"/>
+      <c r="E51" s="539"/>
       <c r="G51" s="464"/>
       <c r="H51" s="464"/>
       <c r="I51" s="440"/>
@@ -40116,13 +40109,13 @@
     <row r="52" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="451"/>
       <c r="B52" s="454"/>
-      <c r="C52" s="594">
+      <c r="C52" s="593">
         <v>1</v>
       </c>
-      <c r="D52" s="595">
+      <c r="D52" s="594">
         <v>10000</v>
       </c>
-      <c r="E52" s="540"/>
+      <c r="E52" s="539"/>
       <c r="G52" s="464"/>
       <c r="H52" s="464"/>
       <c r="I52" s="440"/>
@@ -40132,13 +40125,13 @@
     </row>
     <row r="53" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="454"/>
-      <c r="C53" s="594">
+      <c r="C53" s="593">
         <v>1.5</v>
       </c>
-      <c r="D53" s="595">
+      <c r="D53" s="594">
         <v>15000</v>
       </c>
-      <c r="E53" s="540"/>
+      <c r="E53" s="539"/>
       <c r="G53" s="464"/>
       <c r="H53" s="464"/>
       <c r="I53" s="440"/>
@@ -40148,13 +40141,13 @@
     </row>
     <row r="54" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="454"/>
-      <c r="C54" s="594">
+      <c r="C54" s="593">
         <v>2</v>
       </c>
-      <c r="D54" s="595">
+      <c r="D54" s="594">
         <v>20000</v>
       </c>
-      <c r="E54" s="540"/>
+      <c r="E54" s="539"/>
       <c r="G54" s="464"/>
       <c r="H54" s="464"/>
       <c r="I54" s="440"/>
@@ -40164,13 +40157,13 @@
     </row>
     <row r="55" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="454"/>
-      <c r="C55" s="594">
+      <c r="C55" s="593">
         <v>2.5</v>
       </c>
-      <c r="D55" s="595">
+      <c r="D55" s="594">
         <v>35000</v>
       </c>
-      <c r="E55" s="540"/>
+      <c r="E55" s="539"/>
       <c r="H55" s="464"/>
       <c r="I55" s="440"/>
       <c r="J55" s="440"/>
@@ -40179,13 +40172,13 @@
     </row>
     <row r="56" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="454"/>
-      <c r="C56" s="597">
+      <c r="C56" s="596">
         <v>3</v>
       </c>
-      <c r="D56" s="598">
+      <c r="D56" s="597">
         <v>60000</v>
       </c>
-      <c r="E56" s="540"/>
+      <c r="E56" s="539"/>
       <c r="H56" s="464"/>
       <c r="I56" s="440"/>
       <c r="J56" s="440"/>
@@ -40194,11 +40187,11 @@
     </row>
     <row r="57" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="454"/>
-      <c r="C57" s="599"/>
-      <c r="D57" s="600" t="s">
+      <c r="C57" s="598"/>
+      <c r="D57" s="599" t="s">
         <v>150</v>
       </c>
-      <c r="E57" s="601" t="str">
+      <c r="E57" s="600" t="str">
         <f>IF(AND(E49="",E50="",E51="",E52="",E53="",E54="",E55="",E56=""),"",IF(E49&lt;&gt;"","3/8",IF(E50&lt;&gt;"","1/2",IF(E51&lt;&gt;"","3/4",IF(E52&lt;&gt;"","1",IF(E53&lt;&gt;"","1 1/2",IF(E54&lt;&gt;"","2",IF(E55&lt;&gt;"","2 1/2","3"))))))))</f>
         <v/>
       </c>
@@ -40210,11 +40203,11 @@
     </row>
     <row r="58" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="454"/>
-      <c r="C58" s="602"/>
-      <c r="D58" s="603" t="s">
+      <c r="C58" s="601"/>
+      <c r="D58" s="602" t="s">
         <v>151</v>
       </c>
-      <c r="E58" s="604" t="str">
+      <c r="E58" s="603" t="str">
         <f>IF(E57="","",IF(E57="3",60000,IF(E57="2 1/2",35000,IF(E57="2",20000,IF(E57="1 1/2",15000,IF(E57="1",10000,IF(E57="3/4",5000,IF(E57="1/2",2000,1000))))))))</f>
         <v/>
       </c>
@@ -40227,15 +40220,15 @@
     </row>
     <row r="59" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="454"/>
-      <c r="C59" s="605"/>
-      <c r="D59" s="606" t="s">
+      <c r="C59" s="604"/>
+      <c r="D59" s="605" t="s">
         <v>152</v>
       </c>
-      <c r="E59" s="607" t="e">
+      <c r="E59" s="606" t="e">
         <f>IF(E16="","",IF(AND(E49="",E50="",E51="",E52="",E53="",E54="",E55="",E56=""),"Falta Especificar Tmax",IF(E16="","",IF(E16&gt;=E58,"Cumple","No cumple- Repetir ensayo"))))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G59" s="608"/>
+      <c r="G59" s="607"/>
       <c r="I59" s="440"/>
       <c r="J59" s="440"/>
       <c r="K59" s="440"/>
@@ -40254,13 +40247,13 @@
     </row>
     <row r="61" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="454"/>
-      <c r="C61" s="870" t="s">
+      <c r="C61" s="869" t="s">
         <v>294</v>
       </c>
-      <c r="D61" s="871"/>
-      <c r="E61" s="607" t="str">
+      <c r="D61" s="870"/>
+      <c r="E61" s="606" t="str">
         <f>IF(E19&gt;=300,"Cumple","No cumple")</f>
-        <v>No cumple</v>
+        <v>Cumple</v>
       </c>
       <c r="I61" s="440"/>
       <c r="J61" s="440"/>
@@ -40340,7 +40333,7 @@
     <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cvdp4ubDMsWVsh1DHGHdpbcF18q35cHVXHDDdyeqLp97E6eFY/Ur7+hm6xu3+y7OZtPYQGqOUCKbb/PsU984yw==" saltValue="HWvDGf1N7LVqZ81tzXJQUg==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TNSh9Anr1QAwo+Wu7s6k6M95M9SOg/Gy/xVzI3YskQB47xYzcUrVU9oMmMALZnEQFevVwRVapT4xI+pocclfog==" saltValue="QcweydN+0uFY4Pu1YTEyCA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="C47:E47"/>
     <mergeCell ref="C61:D61"/>
@@ -40399,17 +40392,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="899"/>
-      <c r="B1" s="890" t="s">
+      <c r="A1" s="898"/>
+      <c r="B1" s="889" t="s">
         <v>234</v>
       </c>
-      <c r="C1" s="891"/>
-      <c r="D1" s="891"/>
-      <c r="E1" s="891"/>
-      <c r="F1" s="891"/>
-      <c r="G1" s="891"/>
-      <c r="H1" s="891"/>
-      <c r="I1" s="892"/>
+      <c r="C1" s="890"/>
+      <c r="D1" s="890"/>
+      <c r="E1" s="890"/>
+      <c r="F1" s="890"/>
+      <c r="G1" s="890"/>
+      <c r="H1" s="890"/>
+      <c r="I1" s="891"/>
       <c r="J1" s="400" t="s">
         <v>233</v>
       </c>
@@ -40418,15 +40411,15 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="900"/>
-      <c r="B2" s="893"/>
-      <c r="C2" s="894"/>
-      <c r="D2" s="894"/>
-      <c r="E2" s="894"/>
-      <c r="F2" s="894"/>
-      <c r="G2" s="894"/>
-      <c r="H2" s="894"/>
-      <c r="I2" s="895"/>
+      <c r="A2" s="899"/>
+      <c r="B2" s="892"/>
+      <c r="C2" s="893"/>
+      <c r="D2" s="893"/>
+      <c r="E2" s="893"/>
+      <c r="F2" s="893"/>
+      <c r="G2" s="893"/>
+      <c r="H2" s="893"/>
+      <c r="I2" s="894"/>
       <c r="J2" s="400" t="s">
         <v>231</v>
       </c>
@@ -40435,32 +40428,32 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="900"/>
-      <c r="B3" s="893"/>
-      <c r="C3" s="894"/>
-      <c r="D3" s="894"/>
-      <c r="E3" s="894"/>
-      <c r="F3" s="894"/>
-      <c r="G3" s="894"/>
-      <c r="H3" s="894"/>
-      <c r="I3" s="895"/>
+      <c r="A3" s="899"/>
+      <c r="B3" s="892"/>
+      <c r="C3" s="893"/>
+      <c r="D3" s="893"/>
+      <c r="E3" s="893"/>
+      <c r="F3" s="893"/>
+      <c r="G3" s="893"/>
+      <c r="H3" s="893"/>
+      <c r="I3" s="894"/>
       <c r="J3" s="400" t="s">
         <v>230</v>
       </c>
-      <c r="K3" s="785">
+      <c r="K3" s="784">
         <v>46146</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="901"/>
-      <c r="B4" s="896"/>
-      <c r="C4" s="897"/>
-      <c r="D4" s="897"/>
-      <c r="E4" s="897"/>
-      <c r="F4" s="897"/>
-      <c r="G4" s="897"/>
-      <c r="H4" s="897"/>
-      <c r="I4" s="898"/>
+      <c r="A4" s="900"/>
+      <c r="B4" s="895"/>
+      <c r="C4" s="896"/>
+      <c r="D4" s="896"/>
+      <c r="E4" s="896"/>
+      <c r="F4" s="896"/>
+      <c r="G4" s="896"/>
+      <c r="H4" s="896"/>
+      <c r="I4" s="897"/>
       <c r="J4" s="400" t="s">
         <v>229</v>
       </c>
@@ -40469,13 +40462,13 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="575" t="s">
+      <c r="A6" s="574" t="s">
         <v>227</v>
       </c>
-      <c r="B6" s="576" t="s">
+      <c r="B6" s="575" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="577"/>
+      <c r="C6" s="576"/>
       <c r="D6" s="402"/>
       <c r="E6" s="402"/>
       <c r="F6" s="402"/>
@@ -40486,13 +40479,13 @@
       <c r="K6" s="398"/>
     </row>
     <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="575" t="s">
+      <c r="A7" s="574" t="s">
         <v>226</v>
       </c>
-      <c r="B7" s="576" t="s">
+      <c r="B7" s="575" t="s">
         <v>352</v>
       </c>
-      <c r="C7" s="577"/>
+      <c r="C7" s="576"/>
       <c r="D7" s="402"/>
       <c r="E7" s="402"/>
       <c r="F7" s="402"/>
@@ -40503,13 +40496,13 @@
       <c r="K7" s="398"/>
     </row>
     <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="575" t="s">
+      <c r="A8" s="574" t="s">
         <v>225</v>
       </c>
-      <c r="B8" s="576" t="s">
+      <c r="B8" s="575" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="577"/>
+      <c r="C8" s="576"/>
       <c r="D8" s="402"/>
       <c r="E8" s="402"/>
       <c r="F8" s="402"/>
@@ -40520,13 +40513,13 @@
       <c r="K8" s="398"/>
     </row>
     <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="578" t="s">
+      <c r="A9" s="577" t="s">
         <v>463</v>
       </c>
-      <c r="B9" s="576" t="s">
+      <c r="B9" s="575" t="s">
         <v>272</v>
       </c>
-      <c r="C9" s="577"/>
+      <c r="C9" s="576"/>
       <c r="D9" s="402"/>
       <c r="E9" s="402"/>
       <c r="F9" s="402"/>
@@ -40565,14 +40558,14 @@
       <c r="K12" s="491"/>
     </row>
     <row r="13" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="572" t="s">
+      <c r="A13" s="571" t="s">
         <v>310</v>
       </c>
       <c r="B13" s="503"/>
       <c r="C13" s="399"/>
       <c r="D13" s="491"/>
       <c r="E13" s="491"/>
-      <c r="F13" s="572" t="s">
+      <c r="F13" s="571" t="s">
         <v>311</v>
       </c>
       <c r="G13" s="491"/>
@@ -40595,7 +40588,7 @@
       <c r="K14" s="491"/>
     </row>
     <row r="15" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A15" s="573" t="s">
+      <c r="A15" s="572" t="s">
         <v>349</v>
       </c>
       <c r="B15" s="503"/>
@@ -40610,7 +40603,7 @@
       <c r="K15" s="491"/>
     </row>
     <row r="16" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A16" s="573" t="s">
+      <c r="A16" s="572" t="s">
         <v>350</v>
       </c>
       <c r="B16" s="503"/>
@@ -40625,7 +40618,7 @@
       <c r="K16" s="491"/>
     </row>
     <row r="17" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="573" t="s">
+      <c r="A17" s="572" t="s">
         <v>351</v>
       </c>
       <c r="B17" s="491"/>
@@ -40653,7 +40646,7 @@
       <c r="K18" s="491"/>
     </row>
     <row r="19" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="572" t="s">
+      <c r="A19" s="571" t="s">
         <v>313</v>
       </c>
       <c r="B19" s="491"/>
@@ -40681,7 +40674,7 @@
       <c r="K20" s="491"/>
     </row>
     <row r="21" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A21" s="574" t="s">
+      <c r="A21" s="573" t="s">
         <v>315</v>
       </c>
       <c r="B21" s="491"/>
@@ -40696,7 +40689,7 @@
       <c r="K21" s="491"/>
     </row>
     <row r="22" spans="1:11" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A22" s="574" t="s">
+      <c r="A22" s="573" t="s">
         <v>316</v>
       </c>
       <c r="B22" s="491"/>
@@ -40869,17 +40862,17 @@
       <c r="K34" s="491"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="889" t="s">
+      <c r="A35" s="888" t="s">
         <v>465</v>
       </c>
-      <c r="B35" s="889"/>
-      <c r="C35" s="889"/>
-      <c r="D35" s="889"/>
-      <c r="E35" s="889"/>
-      <c r="F35" s="889"/>
-      <c r="G35" s="889"/>
-      <c r="H35" s="889"/>
-      <c r="I35" s="889"/>
+      <c r="B35" s="888"/>
+      <c r="C35" s="888"/>
+      <c r="D35" s="888"/>
+      <c r="E35" s="888"/>
+      <c r="F35" s="888"/>
+      <c r="G35" s="888"/>
+      <c r="H35" s="888"/>
+      <c r="I35" s="888"/>
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997" x14ac:dyDescent="0.25">
       <c r="A36" s="397" t="s">
@@ -40909,7 +40902,7 @@
       <c r="I36" s="397" t="s">
         <v>219</v>
       </c>
-      <c r="N36" s="569"/>
+      <c r="N36" s="568"/>
     </row>
     <row r="37" spans="1:14" ht="12" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="387"/>
@@ -40959,7 +40952,7 @@
       <c r="J39" s="387"/>
     </row>
     <row r="40" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="568" t="s">
+      <c r="A40" s="567" t="s">
         <v>321</v>
       </c>
       <c r="B40" s="525">
@@ -41067,7 +41060,7 @@
       <c r="A44" s="403" t="s">
         <v>189</v>
       </c>
-      <c r="B44" s="417">
+      <c r="B44" s="417" t="b">
         <f>+Balanza!$C$26</f>
         <v>0</v>
       </c>
@@ -41385,7 +41378,7 @@
       <c r="A58" s="403" t="s">
         <v>189</v>
       </c>
-      <c r="B58" s="417">
+      <c r="B58" s="417" t="b">
         <f>+Balanza!$C$26</f>
         <v>0</v>
       </c>
@@ -41703,7 +41696,7 @@
       <c r="A72" s="403" t="s">
         <v>189</v>
       </c>
-      <c r="B72" s="417">
+      <c r="B72" s="417" t="b">
         <f>+Balanza!$C$26</f>
         <v>0</v>
       </c>
@@ -42021,7 +42014,7 @@
       <c r="A86" s="403" t="s">
         <v>189</v>
       </c>
-      <c r="B86" s="417">
+      <c r="B86" s="417" t="b">
         <f>+Balanza!$C$26</f>
         <v>0</v>
       </c>
@@ -42339,7 +42332,7 @@
       <c r="A100" s="403" t="s">
         <v>189</v>
       </c>
-      <c r="B100" s="417">
+      <c r="B100" s="417" t="b">
         <f>+Balanza!$C$26</f>
         <v>0</v>
       </c>
@@ -42653,7 +42646,7 @@
       <c r="A114" s="403" t="s">
         <v>189</v>
       </c>
-      <c r="B114" s="417">
+      <c r="B114" s="417" t="b">
         <f>+Balanza!$C$26</f>
         <v>0</v>
       </c>
@@ -42971,7 +42964,7 @@
       <c r="A128" s="403" t="s">
         <v>189</v>
       </c>
-      <c r="B128" s="417">
+      <c r="B128" s="417" t="b">
         <f>+Balanza!$C$26</f>
         <v>0</v>
       </c>
@@ -43289,7 +43282,7 @@
       <c r="A142" s="403" t="s">
         <v>189</v>
       </c>
-      <c r="B142" s="417">
+      <c r="B142" s="417" t="b">
         <f>+Balanza!$C$26</f>
         <v>0</v>
       </c>
@@ -43607,7 +43600,7 @@
       <c r="A156" s="403" t="s">
         <v>189</v>
       </c>
-      <c r="B156" s="417">
+      <c r="B156" s="417" t="b">
         <f>+Balanza!$C$26</f>
         <v>0</v>
       </c>
@@ -43783,7 +43776,7 @@
     <row r="163" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="516" t="str">
         <f>+datos!C10</f>
-        <v>Global</v>
+        <v>-</v>
       </c>
       <c r="H163" s="390" t="s">
         <v>318</v>
@@ -43949,7 +43942,7 @@
         <f>IF($A$163="Fraccionada","M Fraccion Fino (g)","M total (g)")</f>
         <v>M total (g)</v>
       </c>
-      <c r="B170" s="417">
+      <c r="B170" s="417" t="b">
         <f>IF($A$163="Fraccionada",datos!E20,datos!E19)</f>
         <v>0</v>
       </c>
@@ -44292,7 +44285,7 @@
         <f>IF($A$163="Fraccionada","M Fraccion Fino (g)","M total (g)")</f>
         <v>M total (g)</v>
       </c>
-      <c r="B184" s="417">
+      <c r="B184" s="417" t="b">
         <f>IF($A$163="Fraccionada",datos!E20,datos!E19)</f>
         <v>0</v>
       </c>
@@ -44645,7 +44638,7 @@
         <f>IF($A$163="Fraccionada","M Fraccion Fino (g)","M total (g)")</f>
         <v>M total (g)</v>
       </c>
-      <c r="B198" s="417">
+      <c r="B198" s="417" t="b">
         <f>IF($A$163="Fraccionada",datos!$E$20,datos!$E$19)</f>
         <v>0</v>
       </c>
@@ -44998,7 +44991,7 @@
         <f>IF($A$163="Fraccionada","M Fraccion Fino (g)","M total (g)")</f>
         <v>M total (g)</v>
       </c>
-      <c r="B212" s="417">
+      <c r="B212" s="417" t="b">
         <f>IF($A$163="Fraccionada",datos!$E$20,datos!$E$19)</f>
         <v>0</v>
       </c>
@@ -45351,7 +45344,7 @@
         <f>IF($A$163="Fraccionada","M Fraccion Fino (g)","M total (g)")</f>
         <v>M total (g)</v>
       </c>
-      <c r="B226" s="417">
+      <c r="B226" s="417" t="b">
         <f>IF($A$163="Fraccionada",datos!$E$20,datos!$E$19)</f>
         <v>0</v>
       </c>
@@ -45704,7 +45697,7 @@
         <f>IF($A$163="Fraccionada","M Fraccion Fino (g)","M total (g)")</f>
         <v>M total (g)</v>
       </c>
-      <c r="B240" s="417">
+      <c r="B240" s="417" t="b">
         <f>IF($A$163="Fraccionada",datos!$E$20,datos!$E$19)</f>
         <v>0</v>
       </c>
@@ -46057,7 +46050,7 @@
         <f>IF($A$163="Fraccionada","M Fraccion Fino (g)","M total (g)")</f>
         <v>M total (g)</v>
       </c>
-      <c r="B254" s="417">
+      <c r="B254" s="417" t="b">
         <f>IF($A$163="Fraccionada",datos!$E$20,datos!$E$19)</f>
         <v>0</v>
       </c>
@@ -46246,7 +46239,7 @@
       <c r="A262" s="426" t="s">
         <v>191</v>
       </c>
-      <c r="B262" s="570" t="e">
+      <c r="B262" s="569" t="e">
         <f>IF($A$163="Fraccionada",$B$179*(1-(B264/B268)),(1-(B264/B268))*100)</f>
         <v>#DIV/0!</v>
       </c>
@@ -46259,7 +46252,7 @@
         <f>IF($A$163="fraccionada",SQRT(G264*G264+(G272*G272)+(G268*G268)+(G274*G274)+(G263*G263)),SQRT(G264*G264+G268*G268+G272*G272+G274*G274))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I262" s="571" t="str">
+      <c r="I262" s="570" t="str">
         <f>IF(B264=0,"---",(H262*2))</f>
         <v>---</v>
       </c>
@@ -46410,7 +46403,7 @@
         <f>IF($A$163="Fraccionada","M Fraccion Fino (g)","M total (g)")</f>
         <v>M total (g)</v>
       </c>
-      <c r="B268" s="417">
+      <c r="B268" s="417" t="b">
         <f>IF($A$163="Fraccionada",datos!$E$20,datos!$E$19)</f>
         <v>0</v>
       </c>
@@ -46595,64 +46588,64 @@
       <c r="J274" s="387"/>
     </row>
     <row r="278" spans="1:10" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A278" s="786" t="s">
+      <c r="A278" s="785" t="s">
         <v>457</v>
       </c>
-      <c r="B278" s="902" t="s">
+      <c r="B278" s="901" t="s">
         <v>458</v>
       </c>
-      <c r="C278" s="903"/>
-      <c r="D278" s="787"/>
-      <c r="E278" s="904" t="s">
+      <c r="C278" s="902"/>
+      <c r="D278" s="786"/>
+      <c r="E278" s="903" t="s">
         <v>459</v>
       </c>
-      <c r="F278" s="904"/>
-      <c r="G278" s="905" t="s">
+      <c r="F278" s="903"/>
+      <c r="G278" s="904" t="s">
         <v>460</v>
       </c>
-      <c r="H278" s="906"/>
-      <c r="I278" s="547"/>
+      <c r="H278" s="905"/>
+      <c r="I278" s="546"/>
     </row>
     <row r="279" spans="1:10" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A279" s="547"/>
-      <c r="B279" s="547"/>
-      <c r="C279" s="547"/>
-      <c r="D279" s="547"/>
-      <c r="E279" s="547"/>
-      <c r="F279" s="547"/>
-      <c r="G279" s="547"/>
-      <c r="H279" s="547"/>
-      <c r="I279" s="547"/>
+      <c r="A279" s="546"/>
+      <c r="B279" s="546"/>
+      <c r="C279" s="546"/>
+      <c r="D279" s="546"/>
+      <c r="E279" s="546"/>
+      <c r="F279" s="546"/>
+      <c r="G279" s="546"/>
+      <c r="H279" s="546"/>
+      <c r="I279" s="546"/>
     </row>
     <row r="280" spans="1:10" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A280" s="788" t="s">
+      <c r="A280" s="787" t="s">
         <v>461</v>
       </c>
-      <c r="B280" s="886">
+      <c r="B280" s="885">
         <v>44944</v>
       </c>
-      <c r="C280" s="887"/>
-      <c r="D280" s="547"/>
-      <c r="E280" s="888" t="s">
+      <c r="C280" s="886"/>
+      <c r="D280" s="546"/>
+      <c r="E280" s="887" t="s">
         <v>462</v>
       </c>
-      <c r="F280" s="888"/>
-      <c r="G280" s="886">
+      <c r="F280" s="887"/>
+      <c r="G280" s="885">
         <v>44944</v>
       </c>
-      <c r="H280" s="887"/>
-      <c r="I280" s="547"/>
+      <c r="H280" s="886"/>
+      <c r="I280" s="546"/>
     </row>
     <row r="281" spans="1:10" ht="13.2" x14ac:dyDescent="0.2">
-      <c r="A281" s="547"/>
-      <c r="B281" s="547"/>
-      <c r="C281" s="547"/>
-      <c r="D281" s="547"/>
-      <c r="E281" s="547"/>
-      <c r="F281" s="547"/>
-      <c r="G281" s="547"/>
-      <c r="H281" s="547"/>
-      <c r="I281" s="547"/>
+      <c r="A281" s="546"/>
+      <c r="B281" s="546"/>
+      <c r="C281" s="546"/>
+      <c r="D281" s="546"/>
+      <c r="E281" s="546"/>
+      <c r="F281" s="546"/>
+      <c r="G281" s="546"/>
+      <c r="H281" s="546"/>
+      <c r="I281" s="546"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="bC7OIqzPwDP9E2RGOaQfi8uGBHN1WthlXg7X1jCAP8Dds2CjtmDMblJxZi+yuB+fPcaf7Iro/t/lXx3L+YIp7A==" saltValue="oBd54LNn75iV+UT4HFB6dA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
@@ -46678,969 +46671,969 @@
   <dimension ref="A7:T69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="660"/>
-    <col min="2" max="3" width="12.5546875" style="660" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="660"/>
-    <col min="5" max="6" width="13.6640625" style="660" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" style="660" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" style="660"/>
-    <col min="9" max="9" width="11.88671875" style="660" customWidth="1"/>
-    <col min="10" max="16384" width="11.5546875" style="660"/>
+    <col min="1" max="1" width="11.5546875" style="659"/>
+    <col min="2" max="3" width="12.5546875" style="659" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="659"/>
+    <col min="5" max="6" width="13.6640625" style="659" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" style="659" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" style="659"/>
+    <col min="9" max="9" width="11.88671875" style="659" customWidth="1"/>
+    <col min="10" max="16384" width="11.5546875" style="659"/>
   </cols>
   <sheetData>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="658" t="s">
+      <c r="A7" s="657" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="659"/>
-      <c r="C7" s="659"/>
-      <c r="D7" s="547"/>
-      <c r="E7" s="547"/>
-      <c r="F7" s="547"/>
-      <c r="G7" s="547"/>
+      <c r="B7" s="658"/>
+      <c r="C7" s="658"/>
+      <c r="D7" s="546"/>
+      <c r="E7" s="546"/>
+      <c r="F7" s="546"/>
+      <c r="G7" s="546"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="783" t="s">
+      <c r="A8" s="782" t="s">
         <v>306</v>
       </c>
-      <c r="B8" s="706">
+      <c r="B8" s="705">
         <v>-3.2899999999999998E-6</v>
       </c>
       <c r="C8" s="491"/>
       <c r="D8" s="491"/>
       <c r="E8" s="270"/>
-      <c r="F8" s="547"/>
-      <c r="G8" s="547"/>
-      <c r="M8" s="662"/>
-      <c r="N8" s="662"/>
-      <c r="O8" s="662"/>
-      <c r="P8" s="662"/>
-      <c r="Q8" s="662"/>
-      <c r="R8" s="662"/>
-      <c r="S8" s="662"/>
-      <c r="T8" s="662"/>
+      <c r="F8" s="546"/>
+      <c r="G8" s="546"/>
+      <c r="M8" s="661"/>
+      <c r="N8" s="661"/>
+      <c r="O8" s="661"/>
+      <c r="P8" s="661"/>
+      <c r="Q8" s="661"/>
+      <c r="R8" s="661"/>
+      <c r="S8" s="661"/>
+      <c r="T8" s="661"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="492" t="s">
         <v>178</v>
       </c>
-      <c r="B9" s="705">
+      <c r="B9" s="704">
         <v>4.1599999999999996E-3</v>
       </c>
-      <c r="C9" s="706">
+      <c r="C9" s="705">
         <v>2.4299999999999999E-10</v>
       </c>
       <c r="D9" s="491"/>
       <c r="E9" s="270"/>
-      <c r="F9" s="547"/>
-      <c r="G9" s="547"/>
+      <c r="F9" s="546"/>
+      <c r="G9" s="546"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="492" t="s">
         <v>453</v>
       </c>
-      <c r="B10" s="707" t="s">
+      <c r="B10" s="706" t="s">
         <v>454</v>
       </c>
-      <c r="C10" s="705"/>
+      <c r="C10" s="704"/>
       <c r="D10" s="491"/>
       <c r="E10" s="270"/>
-      <c r="F10" s="547"/>
-      <c r="G10" s="547"/>
+      <c r="F10" s="546"/>
+      <c r="G10" s="546"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="492" t="s">
         <v>183</v>
       </c>
-      <c r="B11" s="707">
+      <c r="B11" s="706">
         <v>0.1</v>
       </c>
-      <c r="C11" s="705" t="s">
+      <c r="C11" s="704" t="s">
         <v>402</v>
       </c>
       <c r="D11" s="270"/>
       <c r="E11" s="270"/>
-      <c r="F11" s="547"/>
-      <c r="G11" s="547"/>
+      <c r="F11" s="546"/>
+      <c r="G11" s="546"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="492" t="s">
         <v>455</v>
       </c>
-      <c r="B12" s="705" t="s">
+      <c r="B12" s="704" t="s">
         <v>154</v>
       </c>
       <c r="C12" s="491"/>
       <c r="D12" s="270"/>
       <c r="E12" s="270"/>
-      <c r="F12" s="547"/>
-      <c r="G12" s="547"/>
+      <c r="F12" s="546"/>
+      <c r="G12" s="546"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="492" t="s">
         <v>456</v>
       </c>
       <c r="B13" s="270"/>
-      <c r="C13" s="784">
+      <c r="C13" s="783">
         <v>46132</v>
       </c>
       <c r="D13" s="270"/>
       <c r="E13" s="270"/>
-      <c r="F13" s="547"/>
-      <c r="G13" s="547"/>
+      <c r="F13" s="546"/>
+      <c r="G13" s="546"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="495"/>
-      <c r="B14" s="661"/>
-      <c r="C14" s="547"/>
-      <c r="D14" s="547"/>
-      <c r="E14" s="547"/>
-      <c r="F14" s="547"/>
-      <c r="G14" s="547"/>
+      <c r="B14" s="660"/>
+      <c r="C14" s="546"/>
+      <c r="D14" s="546"/>
+      <c r="E14" s="546"/>
+      <c r="F14" s="546"/>
+      <c r="G14" s="546"/>
     </row>
     <row r="15" spans="1:20" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="665" t="s">
+      <c r="A15" s="664" t="s">
         <v>270</v>
       </c>
-      <c r="B15" s="664" t="s">
+      <c r="B15" s="663" t="s">
         <v>343</v>
       </c>
-      <c r="C15" s="665">
+      <c r="C15" s="664">
         <v>20</v>
       </c>
-      <c r="D15" s="665">
+      <c r="D15" s="664">
         <v>200</v>
       </c>
-      <c r="E15" s="665">
+      <c r="E15" s="664">
         <v>500</v>
       </c>
-      <c r="F15" s="665">
+      <c r="F15" s="664">
         <v>1000</v>
       </c>
-      <c r="G15" s="665">
+      <c r="G15" s="664">
         <v>5000</v>
       </c>
-      <c r="H15" s="665">
+      <c r="H15" s="664">
         <v>10000</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="666"/>
-      <c r="B16" s="667"/>
-      <c r="C16" s="668"/>
-      <c r="D16" s="703"/>
-      <c r="E16" s="703"/>
-      <c r="F16" s="703"/>
-      <c r="G16" s="703"/>
-      <c r="H16" s="703"/>
+      <c r="A16" s="665"/>
+      <c r="B16" s="666"/>
+      <c r="C16" s="667"/>
+      <c r="D16" s="702"/>
+      <c r="E16" s="702"/>
+      <c r="F16" s="702"/>
+      <c r="G16" s="702"/>
+      <c r="H16" s="702"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="666"/>
-      <c r="B17" s="667"/>
-      <c r="C17" s="668"/>
-      <c r="D17" s="703"/>
-      <c r="E17" s="703"/>
-      <c r="F17" s="703"/>
-      <c r="G17" s="703"/>
-      <c r="H17" s="703"/>
+      <c r="A17" s="665"/>
+      <c r="B17" s="666"/>
+      <c r="C17" s="667"/>
+      <c r="D17" s="702"/>
+      <c r="E17" s="702"/>
+      <c r="F17" s="702"/>
+      <c r="G17" s="702"/>
+      <c r="H17" s="702"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="547"/>
-      <c r="B18" s="547"/>
-      <c r="C18" s="547"/>
-      <c r="D18" s="547"/>
-      <c r="E18" s="547"/>
-      <c r="F18" s="547"/>
-      <c r="G18" s="547"/>
+      <c r="A18" s="546"/>
+      <c r="B18" s="546"/>
+      <c r="C18" s="546"/>
+      <c r="D18" s="546"/>
+      <c r="E18" s="546"/>
+      <c r="F18" s="546"/>
+      <c r="G18" s="546"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="664"/>
-      <c r="B19" s="663" t="s">
+      <c r="A19" s="663"/>
+      <c r="B19" s="662" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="669">
+      <c r="C19" s="668">
         <v>0</v>
       </c>
-      <c r="D19" s="669">
+      <c r="D19" s="668">
         <v>0</v>
       </c>
-      <c r="E19" s="669">
+      <c r="E19" s="668">
         <v>0</v>
       </c>
-      <c r="F19" s="669">
+      <c r="F19" s="668">
         <v>0</v>
       </c>
-      <c r="G19" s="669">
+      <c r="G19" s="668">
         <v>0</v>
       </c>
-      <c r="H19" s="669">
+      <c r="H19" s="668">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:15" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="911" t="s">
+      <c r="C21" s="910" t="s">
         <v>164</v>
       </c>
-      <c r="D21" s="912"/>
-      <c r="E21" s="912"/>
-      <c r="F21" s="912"/>
-      <c r="G21" s="912"/>
-      <c r="H21" s="913"/>
+      <c r="D21" s="911"/>
+      <c r="E21" s="911"/>
+      <c r="F21" s="911"/>
+      <c r="G21" s="911"/>
+      <c r="H21" s="912"/>
     </row>
     <row r="22" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="914"/>
-      <c r="D22" s="915"/>
-      <c r="E22" s="915"/>
-      <c r="F22" s="915"/>
-      <c r="G22" s="915"/>
-      <c r="H22" s="916"/>
-      <c r="J22" s="670"/>
-      <c r="K22" s="671" t="s">
+      <c r="C22" s="913"/>
+      <c r="D22" s="914"/>
+      <c r="E22" s="914"/>
+      <c r="F22" s="914"/>
+      <c r="G22" s="914"/>
+      <c r="H22" s="915"/>
+      <c r="J22" s="669"/>
+      <c r="K22" s="670" t="s">
         <v>165</v>
       </c>
-      <c r="L22" s="671"/>
-      <c r="M22" s="671"/>
-      <c r="N22" s="671"/>
-      <c r="O22" s="672"/>
+      <c r="L22" s="670"/>
+      <c r="M22" s="670"/>
+      <c r="N22" s="670"/>
+      <c r="O22" s="671"/>
     </row>
     <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="673">
+      <c r="C23" s="672">
         <f t="shared" ref="C23:H23" si="0">+C15</f>
         <v>20</v>
       </c>
-      <c r="D23" s="674">
+      <c r="D23" s="673">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="E23" s="674">
+      <c r="E23" s="673">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="F23" s="674">
+      <c r="F23" s="673">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="G23" s="674">
+      <c r="G23" s="673">
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
-      <c r="H23" s="675">
+      <c r="H23" s="674">
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
-      <c r="J23" s="676"/>
-      <c r="O23" s="677"/>
+      <c r="J23" s="675"/>
+      <c r="O23" s="676"/>
     </row>
     <row r="24" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="678">
+      <c r="C24" s="677">
         <f t="shared" ref="C24:H24" si="1">C19</f>
         <v>0</v>
       </c>
-      <c r="D24" s="679">
+      <c r="D24" s="678">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E24" s="679">
+      <c r="E24" s="678">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F24" s="679">
+      <c r="F24" s="678">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G24" s="679">
+      <c r="G24" s="678">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H24" s="680">
+      <c r="H24" s="679">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J24" s="676"/>
-      <c r="K24" s="547" t="s">
+      <c r="J24" s="675"/>
+      <c r="K24" s="546" t="s">
         <v>166</v>
       </c>
-      <c r="L24" s="547"/>
-      <c r="M24" s="548">
+      <c r="L24" s="546"/>
+      <c r="M24" s="547">
         <v>44628</v>
       </c>
-      <c r="N24" s="548"/>
-      <c r="O24" s="677"/>
+      <c r="N24" s="547"/>
+      <c r="O24" s="676"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="494"/>
       <c r="B25" s="495"/>
-      <c r="J25" s="676"/>
-      <c r="O25" s="677"/>
+      <c r="J25" s="675"/>
+      <c r="O25" s="676"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="681"/>
-      <c r="B26" s="682" t="s">
+      <c r="A26" s="680"/>
+      <c r="B26" s="681" t="s">
         <v>174</v>
       </c>
-      <c r="C26" s="559">
+      <c r="C26" s="558" t="b">
         <f>+datos!E19</f>
         <v>0</v>
       </c>
-      <c r="D26" s="669">
+      <c r="D26" s="668">
         <f>IF(C26&lt;=$C$23,$C$24,IF(AND(C26&gt;$C$23,C26&lt;=$D$23),$D$24,IF(AND(C26&gt;$D$23,C26&lt;=$E$23),$E$24,IF(AND(C26&gt;$E$23,C26&lt;=$F$23),$F$24,IF(AND(C26&gt;$F$23,C26&lt;=$G$23),$G$24,IF(AND(C26&gt;$G$23,C26&lt;=$H$23),$H$24,$H$24))))))</f>
         <v>0</v>
       </c>
-      <c r="J26" s="676"/>
-      <c r="O26" s="677"/>
+      <c r="J26" s="675"/>
+      <c r="O26" s="676"/>
     </row>
     <row r="27" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="683" t="str">
+      <c r="B27" s="682" t="str">
         <f>+datos!C10</f>
-        <v>Global</v>
-      </c>
-      <c r="C27" s="684" t="str">
+        <v>-</v>
+      </c>
+      <c r="C27" s="683" t="b">
         <f>+datos!E20</f>
-        <v>--</v>
-      </c>
-      <c r="D27" s="685">
+        <v>0</v>
+      </c>
+      <c r="D27" s="684">
         <f>IF(C27&lt;=$C$23,$C$24,IF(AND(C27&gt;$C$23,C27&lt;=$D$23),$D$24,IF(AND(C27&gt;$D$23,C27&lt;=$E$23),$E$24,IF(AND(C27&gt;$E$23,C27&lt;=$F$23),$F$24,IF(AND(C27&gt;$F$23,C27&lt;=$G$23),$G$24,IF(AND(C27&gt;$G$23,C27&lt;=$H$23),$H$24,$H$24))))))</f>
         <v>0</v>
       </c>
-      <c r="J27" s="676"/>
-      <c r="K27" s="549" t="s">
+      <c r="J27" s="675"/>
+      <c r="K27" s="548" t="s">
         <v>167</v>
       </c>
-      <c r="L27" s="550" t="s">
+      <c r="L27" s="549" t="s">
         <v>168</v>
       </c>
-      <c r="M27" s="663" t="s">
+      <c r="M27" s="662" t="s">
         <v>169</v>
       </c>
-      <c r="N27" s="686"/>
-      <c r="O27" s="677"/>
+      <c r="N27" s="685"/>
+      <c r="O27" s="676"/>
     </row>
     <row r="28" spans="1:15" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="907" t="s">
+      <c r="B28" s="906" t="s">
         <v>317</v>
       </c>
-      <c r="C28" s="917" t="s">
+      <c r="C28" s="916" t="s">
         <v>341</v>
       </c>
-      <c r="D28" s="917" t="s">
+      <c r="D28" s="916" t="s">
         <v>320</v>
       </c>
-      <c r="E28" s="909" t="s">
+      <c r="E28" s="908" t="s">
         <v>319</v>
       </c>
-      <c r="G28" s="919"/>
-      <c r="H28" s="919"/>
-      <c r="J28" s="676"/>
-      <c r="K28" s="551" t="s">
+      <c r="G28" s="918"/>
+      <c r="H28" s="918"/>
+      <c r="J28" s="675"/>
+      <c r="K28" s="550" t="s">
         <v>170</v>
       </c>
-      <c r="L28" s="552">
+      <c r="L28" s="551">
         <f>M28/1000</f>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M28" s="687">
+      <c r="M28" s="686">
         <v>18</v>
       </c>
-      <c r="N28" s="688" t="s">
+      <c r="N28" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O28" s="677"/>
+      <c r="O28" s="676"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="681"/>
-      <c r="B29" s="908"/>
-      <c r="C29" s="918"/>
-      <c r="D29" s="918"/>
-      <c r="E29" s="910"/>
-      <c r="G29" s="919"/>
-      <c r="H29" s="919"/>
-      <c r="J29" s="676"/>
-      <c r="K29" s="551" t="s">
+      <c r="A29" s="680"/>
+      <c r="B29" s="907"/>
+      <c r="C29" s="917"/>
+      <c r="D29" s="917"/>
+      <c r="E29" s="909"/>
+      <c r="G29" s="918"/>
+      <c r="H29" s="918"/>
+      <c r="J29" s="675"/>
+      <c r="K29" s="550" t="s">
         <v>236</v>
       </c>
-      <c r="L29" s="552">
+      <c r="L29" s="551">
         <f t="shared" ref="L29:L34" si="2">M29/1000</f>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M29" s="664">
+      <c r="M29" s="663">
         <v>18</v>
       </c>
-      <c r="N29" s="688" t="s">
+      <c r="N29" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O29" s="677"/>
+      <c r="O29" s="676"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="681"/>
-      <c r="B30" s="544" t="s">
+      <c r="A30" s="680"/>
+      <c r="B30" s="543" t="s">
         <v>170</v>
       </c>
-      <c r="C30" s="689">
+      <c r="C30" s="688">
         <f>+datos!E28</f>
         <v>0</v>
       </c>
-      <c r="D30" s="689">
+      <c r="D30" s="688">
         <f>C30</f>
         <v>0</v>
       </c>
-      <c r="E30" s="690">
+      <c r="E30" s="689">
         <f>IF(D30&lt;=$C$23,$C$24,IF(AND(D30&gt;$C$23,D30&lt;=$D$23),$D$24,IF(AND(D30&gt;$D$23,D30&lt;=$E$23),$E$24,IF(AND(D30&gt;$E$23,D30&lt;=$F$23),$F$24,IF(AND(D30&gt;$F$23,D30&lt;=$G$23),$G$24,IF(AND(D30&gt;$G$23,D30&lt;=$H$23),$H$24,$H$24))))))</f>
         <v>0</v>
       </c>
-      <c r="G30" s="691"/>
-      <c r="H30" s="692"/>
-      <c r="J30" s="681"/>
-      <c r="K30" s="551" t="s">
+      <c r="G30" s="690"/>
+      <c r="H30" s="691"/>
+      <c r="J30" s="680"/>
+      <c r="K30" s="550" t="s">
         <v>172</v>
       </c>
-      <c r="L30" s="552">
+      <c r="L30" s="551">
         <f t="shared" si="2"/>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M30" s="664">
+      <c r="M30" s="663">
         <v>18</v>
       </c>
-      <c r="N30" s="688" t="s">
+      <c r="N30" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O30" s="677"/>
+      <c r="O30" s="676"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="681"/>
-      <c r="B31" s="544" t="s">
+      <c r="A31" s="680"/>
+      <c r="B31" s="543" t="s">
         <v>236</v>
       </c>
-      <c r="C31" s="689">
+      <c r="C31" s="688">
         <f>+datos!E29</f>
         <v>0</v>
       </c>
-      <c r="D31" s="689">
+      <c r="D31" s="688">
         <f t="shared" ref="D31:D38" si="3">D30+C31</f>
         <v>0</v>
       </c>
-      <c r="E31" s="690">
+      <c r="E31" s="689">
         <f t="shared" ref="E31:E46" si="4">IF(D31&lt;=$C$23,$C$24,IF(AND(D31&gt;$C$23,D31&lt;=$D$23),$D$24,IF(AND(D31&gt;$D$23,D31&lt;=$E$23),$E$24,IF(AND(D31&gt;$E$23,D31&lt;=$F$23),$F$24,IF(AND(D31&gt;$F$23,D31&lt;=$G$23),$G$24,IF(AND(D31&gt;$G$23,D31&lt;=$H$23),$H$24,$H$24))))))</f>
         <v>0</v>
       </c>
-      <c r="G31" s="691"/>
-      <c r="H31" s="692"/>
-      <c r="J31" s="681"/>
-      <c r="K31" s="551" t="s">
+      <c r="G31" s="690"/>
+      <c r="H31" s="691"/>
+      <c r="J31" s="680"/>
+      <c r="K31" s="550" t="s">
         <v>173</v>
       </c>
-      <c r="L31" s="552">
+      <c r="L31" s="551">
         <f t="shared" si="2"/>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M31" s="664">
+      <c r="M31" s="663">
         <v>18</v>
       </c>
-      <c r="N31" s="688" t="s">
+      <c r="N31" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O31" s="677"/>
+      <c r="O31" s="676"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="681"/>
-      <c r="B32" s="544" t="s">
+      <c r="A32" s="680"/>
+      <c r="B32" s="543" t="s">
         <v>172</v>
       </c>
-      <c r="C32" s="689">
+      <c r="C32" s="688">
         <f>+datos!E30</f>
         <v>0</v>
       </c>
-      <c r="D32" s="689">
+      <c r="D32" s="688">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E32" s="690">
+      <c r="E32" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G32" s="691"/>
-      <c r="H32" s="692"/>
-      <c r="J32" s="681"/>
-      <c r="K32" s="551" t="s">
+      <c r="G32" s="690"/>
+      <c r="H32" s="691"/>
+      <c r="J32" s="680"/>
+      <c r="K32" s="550" t="s">
         <v>175</v>
       </c>
-      <c r="L32" s="552">
+      <c r="L32" s="551">
         <f t="shared" si="2"/>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M32" s="664">
+      <c r="M32" s="663">
         <v>18</v>
       </c>
-      <c r="N32" s="688" t="s">
+      <c r="N32" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O32" s="677"/>
+      <c r="O32" s="676"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="681"/>
-      <c r="B33" s="544" t="s">
+      <c r="A33" s="680"/>
+      <c r="B33" s="543" t="s">
         <v>173</v>
       </c>
-      <c r="C33" s="689">
+      <c r="C33" s="688">
         <f>+datos!E31</f>
         <v>0</v>
       </c>
-      <c r="D33" s="689">
+      <c r="D33" s="688">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E33" s="690">
+      <c r="E33" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G33" s="691"/>
-      <c r="H33" s="692"/>
-      <c r="J33" s="681"/>
-      <c r="K33" s="551" t="s">
+      <c r="G33" s="690"/>
+      <c r="H33" s="691"/>
+      <c r="J33" s="680"/>
+      <c r="K33" s="550" t="s">
         <v>18</v>
       </c>
-      <c r="L33" s="552">
+      <c r="L33" s="551">
         <f t="shared" si="2"/>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M33" s="664">
+      <c r="M33" s="663">
         <v>18</v>
       </c>
-      <c r="N33" s="688" t="s">
+      <c r="N33" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O33" s="677"/>
+      <c r="O33" s="676"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="681"/>
-      <c r="B34" s="544" t="s">
+      <c r="A34" s="680"/>
+      <c r="B34" s="543" t="s">
         <v>175</v>
       </c>
-      <c r="C34" s="689">
+      <c r="C34" s="688">
         <f>+datos!E32</f>
         <v>0</v>
       </c>
-      <c r="D34" s="689">
+      <c r="D34" s="688">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E34" s="690">
+      <c r="E34" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G34" s="691"/>
-      <c r="H34" s="692"/>
-      <c r="J34" s="681"/>
-      <c r="K34" s="551" t="s">
+      <c r="G34" s="690"/>
+      <c r="H34" s="691"/>
+      <c r="J34" s="680"/>
+      <c r="K34" s="550" t="s">
         <v>32</v>
       </c>
-      <c r="L34" s="552">
+      <c r="L34" s="551">
         <f t="shared" si="2"/>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M34" s="664">
+      <c r="M34" s="663">
         <v>18</v>
       </c>
-      <c r="N34" s="688" t="s">
+      <c r="N34" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O34" s="677"/>
+      <c r="O34" s="676"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="681"/>
-      <c r="B35" s="544" t="s">
+      <c r="A35" s="680"/>
+      <c r="B35" s="543" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="689">
+      <c r="C35" s="688">
         <f>+datos!E33</f>
         <v>0</v>
       </c>
-      <c r="D35" s="689">
+      <c r="D35" s="688">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E35" s="690">
+      <c r="E35" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G35" s="691"/>
-      <c r="H35" s="692"/>
-      <c r="J35" s="681"/>
-      <c r="K35" s="551" t="s">
+      <c r="G35" s="690"/>
+      <c r="H35" s="691"/>
+      <c r="J35" s="680"/>
+      <c r="K35" s="550" t="s">
         <v>19</v>
       </c>
-      <c r="L35" s="552">
+      <c r="L35" s="551">
         <f t="shared" ref="L35:L44" si="5">M35/1000</f>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M35" s="664">
+      <c r="M35" s="663">
         <v>18</v>
       </c>
-      <c r="N35" s="688" t="s">
+      <c r="N35" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O35" s="677"/>
+      <c r="O35" s="676"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="681"/>
-      <c r="B36" s="544" t="s">
+      <c r="A36" s="680"/>
+      <c r="B36" s="543" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="689">
+      <c r="C36" s="688">
         <f>+datos!E34</f>
         <v>0</v>
       </c>
-      <c r="D36" s="689">
+      <c r="D36" s="688">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E36" s="690">
+      <c r="E36" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G36" s="691"/>
-      <c r="H36" s="692"/>
-      <c r="J36" s="681"/>
-      <c r="K36" s="551" t="s">
+      <c r="G36" s="690"/>
+      <c r="H36" s="691"/>
+      <c r="J36" s="680"/>
+      <c r="K36" s="550" t="s">
         <v>155</v>
       </c>
-      <c r="L36" s="552">
+      <c r="L36" s="551">
         <f t="shared" si="5"/>
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="M36" s="664">
+      <c r="M36" s="663">
         <v>18</v>
       </c>
-      <c r="N36" s="688" t="s">
+      <c r="N36" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O36" s="677"/>
+      <c r="O36" s="676"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="681"/>
-      <c r="B37" s="544" t="s">
+      <c r="A37" s="680"/>
+      <c r="B37" s="543" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="689">
+      <c r="C37" s="688">
         <f>+datos!E35</f>
         <v>0</v>
       </c>
-      <c r="D37" s="689">
+      <c r="D37" s="688">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E37" s="690">
+      <c r="E37" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G37" s="691"/>
-      <c r="H37" s="692"/>
-      <c r="J37" s="681"/>
-      <c r="K37" s="551" t="s">
+      <c r="G37" s="690"/>
+      <c r="H37" s="691"/>
+      <c r="J37" s="680"/>
+      <c r="K37" s="550" t="s">
         <v>156</v>
       </c>
-      <c r="L37" s="552">
+      <c r="L37" s="551">
         <f t="shared" si="5"/>
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="M37" s="664">
+      <c r="M37" s="663">
         <v>6.5</v>
       </c>
-      <c r="N37" s="688" t="s">
+      <c r="N37" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O37" s="677"/>
+      <c r="O37" s="676"/>
     </row>
     <row r="38" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="681"/>
-      <c r="B38" s="545" t="s">
+      <c r="A38" s="680"/>
+      <c r="B38" s="544" t="s">
         <v>155</v>
       </c>
-      <c r="C38" s="693">
+      <c r="C38" s="692">
         <f>+datos!E36</f>
         <v>0</v>
       </c>
-      <c r="D38" s="693">
+      <c r="D38" s="692">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E38" s="694">
+      <c r="E38" s="693">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G38" s="691"/>
-      <c r="H38" s="692"/>
-      <c r="J38" s="681"/>
-      <c r="K38" s="551" t="s">
+      <c r="G38" s="690"/>
+      <c r="H38" s="691"/>
+      <c r="J38" s="680"/>
+      <c r="K38" s="550" t="s">
         <v>160</v>
       </c>
-      <c r="L38" s="552">
+      <c r="L38" s="551">
         <f t="shared" si="5"/>
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="M38" s="664">
+      <c r="M38" s="663">
         <v>11</v>
       </c>
-      <c r="N38" s="688" t="s">
+      <c r="N38" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O38" s="677"/>
+      <c r="O38" s="676"/>
     </row>
     <row r="39" spans="1:15" ht="13.8" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="681"/>
-      <c r="B39" s="546" t="s">
+      <c r="A39" s="680"/>
+      <c r="B39" s="545" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="695">
+      <c r="C39" s="694">
         <f>+datos!E37</f>
         <v>0</v>
       </c>
-      <c r="D39" s="695">
+      <c r="D39" s="694">
         <f>IF(B27="Fraccionada",C39,D38+C39)</f>
         <v>0</v>
       </c>
-      <c r="E39" s="696">
+      <c r="E39" s="695">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G39" s="691"/>
-      <c r="H39" s="692"/>
-      <c r="J39" s="681"/>
-      <c r="K39" s="551" t="s">
+      <c r="G39" s="690"/>
+      <c r="H39" s="691"/>
+      <c r="J39" s="680"/>
+      <c r="K39" s="550" t="s">
         <v>157</v>
       </c>
-      <c r="L39" s="552">
+      <c r="L39" s="551">
         <f t="shared" si="5"/>
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="M39" s="664">
+      <c r="M39" s="663">
         <v>5.4</v>
       </c>
-      <c r="N39" s="688" t="s">
+      <c r="N39" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O39" s="677"/>
+      <c r="O39" s="676"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="681"/>
-      <c r="B40" s="544" t="s">
+      <c r="A40" s="680"/>
+      <c r="B40" s="543" t="s">
         <v>160</v>
       </c>
-      <c r="C40" s="689">
+      <c r="C40" s="688">
         <f>+datos!E38</f>
         <v>0</v>
       </c>
-      <c r="D40" s="689">
+      <c r="D40" s="688">
         <f t="shared" ref="D40:D46" si="6">D39+C40</f>
         <v>0</v>
       </c>
-      <c r="E40" s="690">
+      <c r="E40" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G40" s="691"/>
-      <c r="H40" s="692"/>
-      <c r="J40" s="681"/>
-      <c r="K40" s="551" t="s">
+      <c r="G40" s="690"/>
+      <c r="H40" s="691"/>
+      <c r="J40" s="680"/>
+      <c r="K40" s="550" t="s">
         <v>237</v>
       </c>
-      <c r="L40" s="552">
+      <c r="L40" s="551">
         <f t="shared" si="5"/>
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="M40" s="664">
+      <c r="M40" s="663">
         <v>3.5</v>
       </c>
-      <c r="N40" s="688" t="s">
+      <c r="N40" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O40" s="677"/>
+      <c r="O40" s="676"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="681"/>
-      <c r="B41" s="544" t="s">
+      <c r="A41" s="680"/>
+      <c r="B41" s="543" t="s">
         <v>157</v>
       </c>
-      <c r="C41" s="689">
+      <c r="C41" s="688">
         <f>+datos!E39</f>
         <v>0</v>
       </c>
-      <c r="D41" s="689">
+      <c r="D41" s="688">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E41" s="690">
+      <c r="E41" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G41" s="691"/>
-      <c r="H41" s="692"/>
-      <c r="J41" s="681"/>
-      <c r="K41" s="551" t="s">
+      <c r="G41" s="690"/>
+      <c r="H41" s="691"/>
+      <c r="J41" s="680"/>
+      <c r="K41" s="550" t="s">
         <v>162</v>
       </c>
-      <c r="L41" s="552">
+      <c r="L41" s="551">
         <f t="shared" si="5"/>
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="M41" s="664">
+      <c r="M41" s="663">
         <v>2.7</v>
       </c>
-      <c r="N41" s="688" t="s">
+      <c r="N41" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O41" s="677"/>
+      <c r="O41" s="676"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="681"/>
-      <c r="B42" s="544" t="s">
+      <c r="A42" s="680"/>
+      <c r="B42" s="543" t="s">
         <v>161</v>
       </c>
-      <c r="C42" s="689">
+      <c r="C42" s="688">
         <f>+datos!E40</f>
         <v>0</v>
       </c>
-      <c r="D42" s="689">
+      <c r="D42" s="688">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E42" s="690">
+      <c r="E42" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G42" s="691"/>
-      <c r="H42" s="692"/>
-      <c r="J42" s="681"/>
-      <c r="K42" s="551" t="s">
+      <c r="G42" s="690"/>
+      <c r="H42" s="691"/>
+      <c r="J42" s="680"/>
+      <c r="K42" s="550" t="s">
         <v>158</v>
       </c>
-      <c r="L42" s="552">
+      <c r="L42" s="551">
         <f t="shared" si="5"/>
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="M42" s="664">
+      <c r="M42" s="663">
         <v>2.5</v>
       </c>
-      <c r="N42" s="688" t="s">
+      <c r="N42" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O42" s="677"/>
+      <c r="O42" s="676"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="681"/>
-      <c r="B43" s="544" t="s">
+      <c r="A43" s="680"/>
+      <c r="B43" s="543" t="s">
         <v>162</v>
       </c>
-      <c r="C43" s="689">
+      <c r="C43" s="688">
         <f>+datos!E41</f>
         <v>0</v>
       </c>
-      <c r="D43" s="689">
+      <c r="D43" s="688">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E43" s="690">
+      <c r="E43" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G43" s="691"/>
-      <c r="H43" s="692"/>
-      <c r="J43" s="681"/>
-      <c r="K43" s="551" t="s">
+      <c r="G43" s="690"/>
+      <c r="H43" s="691"/>
+      <c r="J43" s="680"/>
+      <c r="K43" s="550" t="s">
         <v>159</v>
       </c>
-      <c r="L43" s="552">
+      <c r="L43" s="551">
         <f t="shared" si="5"/>
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="M43" s="664">
+      <c r="M43" s="663">
         <v>1.3</v>
       </c>
-      <c r="N43" s="688" t="s">
+      <c r="N43" s="687" t="s">
         <v>171</v>
       </c>
-      <c r="O43" s="677"/>
+      <c r="O43" s="676"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="681"/>
-      <c r="B44" s="544" t="s">
+      <c r="A44" s="680"/>
+      <c r="B44" s="543" t="s">
         <v>158</v>
       </c>
-      <c r="C44" s="689">
+      <c r="C44" s="688">
         <f>+datos!E42</f>
         <v>0</v>
       </c>
-      <c r="D44" s="689">
+      <c r="D44" s="688">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E44" s="690">
+      <c r="E44" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G44" s="691"/>
-      <c r="H44" s="692"/>
-      <c r="J44" s="681"/>
-      <c r="K44" s="551" t="s">
+      <c r="G44" s="690"/>
+      <c r="H44" s="691"/>
+      <c r="J44" s="680"/>
+      <c r="K44" s="550" t="s">
         <v>163</v>
       </c>
-      <c r="L44" s="552">
+      <c r="L44" s="551">
         <f t="shared" si="5"/>
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="M44" s="664">
+      <c r="M44" s="663">
         <v>1.3</v>
       </c>
-      <c r="N44" s="697"/>
-      <c r="O44" s="677"/>
+      <c r="N44" s="696"/>
+      <c r="O44" s="676"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="681"/>
-      <c r="B45" s="544" t="s">
+      <c r="A45" s="680"/>
+      <c r="B45" s="543" t="s">
         <v>159</v>
       </c>
-      <c r="C45" s="689">
+      <c r="C45" s="688">
         <f>+datos!E43</f>
         <v>0</v>
       </c>
-      <c r="D45" s="689">
+      <c r="D45" s="688">
         <f>D44+C45</f>
         <v>0</v>
       </c>
-      <c r="E45" s="690">
+      <c r="E45" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G45" s="691"/>
-      <c r="H45" s="692"/>
-      <c r="J45" s="681"/>
-      <c r="O45" s="677"/>
+      <c r="G45" s="690"/>
+      <c r="H45" s="691"/>
+      <c r="J45" s="680"/>
+      <c r="O45" s="676"/>
     </row>
     <row r="46" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="681"/>
-      <c r="B46" s="545" t="s">
+      <c r="A46" s="680"/>
+      <c r="B46" s="544" t="s">
         <v>163</v>
       </c>
-      <c r="C46" s="693">
+      <c r="C46" s="692">
         <f>+datos!E44</f>
         <v>0</v>
       </c>
-      <c r="D46" s="693">
+      <c r="D46" s="692">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E46" s="690">
+      <c r="E46" s="689">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G46" s="691"/>
-      <c r="H46" s="692"/>
-      <c r="J46" s="553"/>
-      <c r="K46" s="554"/>
-      <c r="L46" s="554"/>
-      <c r="M46" s="554"/>
-      <c r="N46" s="554"/>
-      <c r="O46" s="698"/>
+      <c r="G46" s="690"/>
+      <c r="H46" s="691"/>
+      <c r="J46" s="552"/>
+      <c r="K46" s="553"/>
+      <c r="L46" s="553"/>
+      <c r="M46" s="553"/>
+      <c r="N46" s="553"/>
+      <c r="O46" s="697"/>
     </row>
     <row r="47" spans="1:15" ht="13.8" thickTop="1" x14ac:dyDescent="0.25">
       <c r="H47" s="493"/>
@@ -47649,253 +47642,253 @@
       <c r="H48" s="493"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="801" t="s">
+      <c r="B49" s="800" t="s">
         <v>176</v>
       </c>
-      <c r="C49" s="802"/>
-      <c r="H49" s="555"/>
+      <c r="C49" s="801"/>
+      <c r="H49" s="554"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="799" t="s">
+      <c r="B50" s="798" t="s">
         <v>473</v>
       </c>
-      <c r="D50" s="800">
+      <c r="D50" s="799">
         <v>46142</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="53.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="556" t="s">
+      <c r="A52" s="555" t="s">
         <v>167</v>
       </c>
-      <c r="B52" s="798" t="s">
+      <c r="B52" s="797" t="s">
         <v>347</v>
       </c>
-      <c r="C52" s="567" t="s">
+      <c r="C52" s="566" t="s">
         <v>271</v>
       </c>
-      <c r="D52" s="579"/>
-      <c r="E52" s="557"/>
+      <c r="D52" s="578"/>
+      <c r="E52" s="556"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="558" t="s">
+      <c r="A53" s="557" t="s">
         <v>170</v>
       </c>
-      <c r="B53" s="699">
+      <c r="B53" s="698">
         <v>0</v>
       </c>
-      <c r="C53" s="699">
+      <c r="C53" s="698">
         <v>0</v>
       </c>
-      <c r="D53" s="700"/>
-      <c r="E53" s="700"/>
+      <c r="D53" s="699"/>
+      <c r="E53" s="699"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="558" t="s">
+      <c r="A54" s="557" t="s">
         <v>236</v>
       </c>
-      <c r="B54" s="699">
+      <c r="B54" s="698">
         <v>0</v>
       </c>
-      <c r="C54" s="699">
+      <c r="C54" s="698">
         <v>0</v>
       </c>
-      <c r="D54" s="700"/>
-      <c r="E54" s="700"/>
+      <c r="D54" s="699"/>
+      <c r="E54" s="699"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="558" t="s">
+      <c r="A55" s="557" t="s">
         <v>172</v>
       </c>
-      <c r="B55" s="699">
+      <c r="B55" s="698">
         <v>0</v>
       </c>
-      <c r="C55" s="699">
+      <c r="C55" s="698">
         <v>0</v>
       </c>
-      <c r="D55" s="700"/>
-      <c r="E55" s="700"/>
+      <c r="D55" s="699"/>
+      <c r="E55" s="699"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="558" t="s">
+      <c r="A56" s="557" t="s">
         <v>173</v>
       </c>
-      <c r="B56" s="699">
+      <c r="B56" s="698">
         <v>0</v>
       </c>
-      <c r="C56" s="699">
+      <c r="C56" s="698">
         <v>0</v>
       </c>
-      <c r="D56" s="700"/>
-      <c r="E56" s="700"/>
+      <c r="D56" s="699"/>
+      <c r="E56" s="699"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="558" t="s">
+      <c r="A57" s="557" t="s">
         <v>175</v>
       </c>
-      <c r="B57" s="699">
+      <c r="B57" s="698">
         <v>0</v>
       </c>
-      <c r="C57" s="699">
+      <c r="C57" s="698">
         <v>0</v>
       </c>
-      <c r="D57" s="700"/>
-      <c r="E57" s="700"/>
+      <c r="D57" s="699"/>
+      <c r="E57" s="699"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="558" t="s">
+      <c r="A58" s="557" t="s">
         <v>18</v>
       </c>
-      <c r="B58" s="699">
+      <c r="B58" s="698">
         <v>0</v>
       </c>
-      <c r="C58" s="699">
+      <c r="C58" s="698">
         <v>0</v>
       </c>
-      <c r="D58" s="700"/>
-      <c r="E58" s="700"/>
+      <c r="D58" s="699"/>
+      <c r="E58" s="699"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="558" t="s">
+      <c r="A59" s="557" t="s">
         <v>32</v>
       </c>
-      <c r="B59" s="699">
+      <c r="B59" s="698">
         <v>0</v>
       </c>
-      <c r="C59" s="699">
+      <c r="C59" s="698">
         <v>0</v>
       </c>
-      <c r="D59" s="700"/>
-      <c r="E59" s="700"/>
+      <c r="D59" s="699"/>
+      <c r="E59" s="699"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="558" t="s">
+      <c r="A60" s="557" t="s">
         <v>19</v>
       </c>
-      <c r="B60" s="699">
+      <c r="B60" s="698">
         <v>0</v>
       </c>
-      <c r="C60" s="699">
+      <c r="C60" s="698">
         <v>0</v>
       </c>
-      <c r="D60" s="700"/>
-      <c r="E60" s="700"/>
+      <c r="D60" s="699"/>
+      <c r="E60" s="699"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="558" t="s">
+      <c r="A61" s="557" t="s">
         <v>155</v>
       </c>
-      <c r="B61" s="699">
+      <c r="B61" s="698">
         <v>7.8102205558218438E-2</v>
       </c>
-      <c r="C61" s="699">
+      <c r="C61" s="698">
         <v>8.2494332399335443E-2</v>
       </c>
-      <c r="D61" s="700"/>
-      <c r="E61" s="700"/>
+      <c r="D61" s="699"/>
+      <c r="E61" s="699"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="558" t="s">
+      <c r="A62" s="557" t="s">
         <v>156</v>
       </c>
-      <c r="B62" s="699">
+      <c r="B62" s="698">
         <v>0.24270886010920917</v>
       </c>
-      <c r="C62" s="699">
+      <c r="C62" s="698">
         <v>0.24465262833019497</v>
       </c>
-      <c r="D62" s="700"/>
-      <c r="E62" s="700"/>
+      <c r="D62" s="699"/>
+      <c r="E62" s="699"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="558" t="s">
+      <c r="A63" s="557" t="s">
         <v>160</v>
       </c>
-      <c r="B63" s="699">
+      <c r="B63" s="698">
         <v>0.32081881115367472</v>
       </c>
-      <c r="C63" s="699">
+      <c r="C63" s="698">
         <v>0.34618670168438298</v>
       </c>
-      <c r="D63" s="700"/>
-      <c r="E63" s="700"/>
+      <c r="D63" s="699"/>
+      <c r="E63" s="699"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="558" t="s">
+      <c r="A64" s="557" t="s">
         <v>157</v>
       </c>
-      <c r="B64" s="699">
+      <c r="B64" s="698">
         <v>0.53458571667600707</v>
       </c>
-      <c r="C64" s="699">
+      <c r="C64" s="698">
         <v>0.57717227286380801</v>
       </c>
-      <c r="D64" s="700"/>
-      <c r="E64" s="700"/>
+      <c r="D64" s="699"/>
+      <c r="E64" s="699"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="558" t="s">
+      <c r="A65" s="557" t="s">
         <v>237</v>
       </c>
-      <c r="B65" s="699">
+      <c r="B65" s="698">
         <v>0.48239791708632423</v>
       </c>
-      <c r="C65" s="699">
+      <c r="C65" s="698">
         <v>0.64464161334682302</v>
       </c>
-      <c r="D65" s="700"/>
-      <c r="E65" s="700"/>
+      <c r="D65" s="699"/>
+      <c r="E65" s="699"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="558" t="s">
+      <c r="A66" s="557" t="s">
         <v>162</v>
       </c>
-      <c r="B66" s="699">
+      <c r="B66" s="698">
         <v>0.34208544824232401</v>
       </c>
-      <c r="C66" s="699">
+      <c r="C66" s="698">
         <v>0.36037631614706434</v>
       </c>
-      <c r="D66" s="700"/>
-      <c r="E66" s="700"/>
+      <c r="D66" s="699"/>
+      <c r="E66" s="699"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="558" t="s">
+      <c r="A67" s="557" t="s">
         <v>158</v>
       </c>
-      <c r="B67" s="699">
+      <c r="B67" s="698">
         <v>0.45392671715941679</v>
       </c>
-      <c r="C67" s="699">
+      <c r="C67" s="698">
         <v>0.51407100842544873</v>
       </c>
-      <c r="D67" s="700"/>
-      <c r="E67" s="700"/>
+      <c r="D67" s="699"/>
+      <c r="E67" s="699"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="558" t="s">
+      <c r="A68" s="557" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="699">
+      <c r="B68" s="698">
         <v>0.24282402392218505</v>
       </c>
-      <c r="C68" s="699">
+      <c r="C68" s="698">
         <v>0.25127048276239239</v>
       </c>
-      <c r="D68" s="700"/>
-      <c r="E68" s="700"/>
+      <c r="D68" s="699"/>
+      <c r="E68" s="699"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="558" t="s">
+      <c r="A69" s="557" t="s">
         <v>163</v>
       </c>
-      <c r="B69" s="699">
+      <c r="B69" s="698">
         <v>0.31355805092132405</v>
       </c>
-      <c r="C69" s="699">
+      <c r="C69" s="698">
         <v>0.32233975414555627</v>
       </c>
-      <c r="D69" s="700"/>
-      <c r="E69" s="700"/>
+      <c r="D69" s="699"/>
+      <c r="E69" s="699"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="v8HcRHeMe336PymyxK0HQbjdnavpBQNhAw0OesYBR/orw/5sTkn/biyS02pjlqm2xZj6/AT6jSiGZpnxACuK3Q==" saltValue="8VAfBRaTo8/OhfgdVO3wyQ==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
@@ -47952,35 +47945,35 @@
       <c r="K4" s="87"/>
     </row>
     <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="933" t="s">
+      <c r="A5" s="920" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="933"/>
-      <c r="C5" s="933"/>
-      <c r="D5" s="933"/>
-      <c r="E5" s="933"/>
-      <c r="F5" s="933"/>
-      <c r="G5" s="933"/>
-      <c r="H5" s="933"/>
-      <c r="I5" s="933"/>
-      <c r="J5" s="933"/>
-      <c r="K5" s="933"/>
+      <c r="B5" s="920"/>
+      <c r="C5" s="920"/>
+      <c r="D5" s="920"/>
+      <c r="E5" s="920"/>
+      <c r="F5" s="920"/>
+      <c r="G5" s="920"/>
+      <c r="H5" s="920"/>
+      <c r="I5" s="920"/>
+      <c r="J5" s="920"/>
+      <c r="K5" s="920"/>
     </row>
     <row r="6" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="940">
+      <c r="A6" s="927">
         <f>+K12</f>
         <v>32</v>
       </c>
-      <c r="B6" s="940"/>
-      <c r="C6" s="940"/>
-      <c r="D6" s="940"/>
-      <c r="E6" s="940"/>
-      <c r="F6" s="940"/>
-      <c r="G6" s="940"/>
-      <c r="H6" s="940"/>
-      <c r="I6" s="940"/>
-      <c r="J6" s="940"/>
-      <c r="K6" s="940"/>
+      <c r="B6" s="927"/>
+      <c r="C6" s="927"/>
+      <c r="D6" s="927"/>
+      <c r="E6" s="927"/>
+      <c r="F6" s="927"/>
+      <c r="G6" s="927"/>
+      <c r="H6" s="927"/>
+      <c r="I6" s="927"/>
+      <c r="J6" s="927"/>
+      <c r="K6" s="927"/>
       <c r="S6" s="259" t="s">
         <v>101</v>
       </c>
@@ -48057,10 +48050,10 @@
       <c r="S9" s="275" t="s">
         <v>105</v>
       </c>
-      <c r="T9" s="944">
+      <c r="T9" s="931">
         <v>44090</v>
       </c>
-      <c r="U9" s="944"/>
+      <c r="U9" s="931"/>
       <c r="V9" s="276"/>
       <c r="W9" s="277"/>
       <c r="X9" s="276"/>
@@ -48205,19 +48198,19 @@
       <c r="S13" s="86"/>
     </row>
     <row r="14" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="941" t="s">
+      <c r="A14" s="928" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="942"/>
-      <c r="C14" s="942"/>
-      <c r="D14" s="942"/>
-      <c r="E14" s="942"/>
-      <c r="F14" s="942"/>
-      <c r="G14" s="942"/>
-      <c r="H14" s="942"/>
-      <c r="I14" s="942"/>
-      <c r="J14" s="942"/>
-      <c r="K14" s="943"/>
+      <c r="B14" s="929"/>
+      <c r="C14" s="929"/>
+      <c r="D14" s="929"/>
+      <c r="E14" s="929"/>
+      <c r="F14" s="929"/>
+      <c r="G14" s="929"/>
+      <c r="H14" s="929"/>
+      <c r="I14" s="929"/>
+      <c r="J14" s="929"/>
+      <c r="K14" s="930"/>
       <c r="L14" s="87"/>
       <c r="M14" s="87"/>
       <c r="P14" s="86"/>
@@ -48226,19 +48219,19 @@
       <c r="S14" s="86"/>
     </row>
     <row r="15" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="948" t="s">
+      <c r="A15" s="935" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="949"/>
-      <c r="C15" s="949"/>
-      <c r="D15" s="949"/>
-      <c r="E15" s="949"/>
-      <c r="F15" s="949"/>
-      <c r="G15" s="949"/>
-      <c r="H15" s="949"/>
-      <c r="I15" s="949"/>
-      <c r="J15" s="949"/>
-      <c r="K15" s="950"/>
+      <c r="B15" s="936"/>
+      <c r="C15" s="936"/>
+      <c r="D15" s="936"/>
+      <c r="E15" s="936"/>
+      <c r="F15" s="936"/>
+      <c r="G15" s="936"/>
+      <c r="H15" s="936"/>
+      <c r="I15" s="936"/>
+      <c r="J15" s="936"/>
+      <c r="K15" s="937"/>
       <c r="L15" s="87"/>
       <c r="M15" s="87"/>
       <c r="P15" s="86"/>
@@ -48266,17 +48259,17 @@
       <c r="S16" s="86"/>
     </row>
     <row r="17" spans="1:27" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="938" t="s">
+      <c r="A17" s="925" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="939"/>
-      <c r="C17" s="939"/>
-      <c r="D17" s="939"/>
-      <c r="E17" s="939"/>
-      <c r="F17" s="939"/>
-      <c r="G17" s="939"/>
-      <c r="H17" s="939"/>
-      <c r="I17" s="939"/>
+      <c r="B17" s="926"/>
+      <c r="C17" s="926"/>
+      <c r="D17" s="926"/>
+      <c r="E17" s="926"/>
+      <c r="F17" s="926"/>
+      <c r="G17" s="926"/>
+      <c r="H17" s="926"/>
+      <c r="I17" s="926"/>
       <c r="J17" s="1"/>
       <c r="K17" s="199"/>
       <c r="L17" s="87"/>
@@ -48344,23 +48337,23 @@
       <c r="Q19" s="86"/>
       <c r="R19" s="86"/>
       <c r="S19" s="86"/>
-      <c r="U19" s="921" t="s">
+      <c r="U19" s="939" t="s">
         <v>9</v>
       </c>
-      <c r="V19" s="922"/>
-      <c r="W19" s="932" t="s">
+      <c r="V19" s="940"/>
+      <c r="W19" s="919" t="s">
         <v>100</v>
       </c>
-      <c r="X19" s="844" t="s">
+      <c r="X19" s="833" t="s">
         <v>45</v>
       </c>
-      <c r="Y19" s="844" t="s">
+      <c r="Y19" s="833" t="s">
         <v>41</v>
       </c>
-      <c r="Z19" s="844" t="s">
+      <c r="Z19" s="833" t="s">
         <v>42</v>
       </c>
-      <c r="AA19" s="844" t="s">
+      <c r="AA19" s="833" t="s">
         <v>43</v>
       </c>
     </row>
@@ -48398,11 +48391,11 @@
       <c r="V20" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="W20" s="932"/>
-      <c r="X20" s="845"/>
-      <c r="Y20" s="845"/>
-      <c r="Z20" s="845"/>
-      <c r="AA20" s="845"/>
+      <c r="W20" s="919"/>
+      <c r="X20" s="834"/>
+      <c r="Y20" s="834"/>
+      <c r="Z20" s="834"/>
+      <c r="AA20" s="834"/>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="288" t="s">
@@ -48495,27 +48488,27 @@
     </row>
     <row r="23" spans="1:27" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="140"/>
-      <c r="B23" s="921" t="s">
+      <c r="B23" s="939" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="922"/>
-      <c r="D23" s="844" t="s">
+      <c r="C23" s="940"/>
+      <c r="D23" s="833" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="844" t="s">
+      <c r="E23" s="833" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="844" t="s">
+      <c r="F23" s="833" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="844" t="s">
+      <c r="G23" s="833" t="s">
         <v>43</v>
       </c>
       <c r="H23" s="138"/>
-      <c r="I23" s="926" t="s">
+      <c r="I23" s="944" t="s">
         <v>36</v>
       </c>
-      <c r="J23" s="927"/>
+      <c r="J23" s="945"/>
       <c r="K23" s="139"/>
       <c r="L23" s="91"/>
       <c r="M23" s="91"/>
@@ -48556,16 +48549,16 @@
       <c r="C24" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="845"/>
-      <c r="E24" s="845"/>
-      <c r="F24" s="845"/>
-      <c r="G24" s="845"/>
+      <c r="D24" s="834"/>
+      <c r="E24" s="834"/>
+      <c r="F24" s="834"/>
+      <c r="G24" s="834"/>
       <c r="H24" s="156"/>
-      <c r="I24" s="929">
+      <c r="I24" s="947">
         <f>+Q23</f>
         <v>23983.979695431473</v>
       </c>
-      <c r="J24" s="930"/>
+      <c r="J24" s="948"/>
       <c r="K24" s="139"/>
       <c r="L24" s="91"/>
       <c r="M24" s="91"/>
@@ -48679,10 +48672,10 @@
       </c>
       <c r="G26" s="97"/>
       <c r="H26" s="142"/>
-      <c r="I26" s="928" t="s">
+      <c r="I26" s="946" t="s">
         <v>92</v>
       </c>
-      <c r="J26" s="928"/>
+      <c r="J26" s="946"/>
       <c r="K26" s="143"/>
       <c r="L26" s="91"/>
       <c r="M26" s="91"/>
@@ -48933,16 +48926,16 @@
         <v>57.746817294661284</v>
       </c>
       <c r="H30" s="142"/>
-      <c r="I30" s="937"/>
-      <c r="J30" s="937"/>
+      <c r="I30" s="924"/>
+      <c r="J30" s="924"/>
       <c r="K30" s="143"/>
       <c r="L30" s="91"/>
-      <c r="M30" s="945" t="s">
+      <c r="M30" s="932" t="s">
         <v>74</v>
       </c>
-      <c r="N30" s="946"/>
-      <c r="O30" s="946"/>
-      <c r="P30" s="947"/>
+      <c r="N30" s="933"/>
+      <c r="O30" s="933"/>
+      <c r="P30" s="934"/>
       <c r="T30" s="99"/>
       <c r="U30" s="93" t="s">
         <v>88</v>
@@ -48995,16 +48988,16 @@
         <v>38.462771103509866</v>
       </c>
       <c r="H31" s="142"/>
-      <c r="I31" s="937"/>
-      <c r="J31" s="937"/>
+      <c r="I31" s="924"/>
+      <c r="J31" s="924"/>
       <c r="K31" s="143"/>
       <c r="L31" s="91"/>
-      <c r="M31" s="934" t="s">
+      <c r="M31" s="921" t="s">
         <v>82</v>
       </c>
-      <c r="N31" s="935"/>
-      <c r="O31" s="935"/>
-      <c r="P31" s="936"/>
+      <c r="N31" s="922"/>
+      <c r="O31" s="922"/>
+      <c r="P31" s="923"/>
       <c r="T31" s="99"/>
       <c r="U31" s="147" t="s">
         <v>90</v>
@@ -49169,11 +49162,11 @@
         <f t="shared" ref="U34:U42" si="10">+T34</f>
         <v>25.4</v>
       </c>
-      <c r="Z34" s="923" t="s">
+      <c r="Z34" s="941" t="s">
         <v>89</v>
       </c>
-      <c r="AA34" s="924"/>
-      <c r="AB34" s="924"/>
+      <c r="AA34" s="942"/>
+      <c r="AB34" s="942"/>
     </row>
     <row r="35" spans="1:28" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="140"/>
@@ -49737,14 +49730,14 @@
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="925"/>
-      <c r="E57" s="925"/>
-      <c r="F57" s="925"/>
-      <c r="G57" s="925"/>
-      <c r="H57" s="925"/>
-      <c r="I57" s="925"/>
-      <c r="J57" s="925"/>
-      <c r="K57" s="925"/>
+      <c r="D57" s="943"/>
+      <c r="E57" s="943"/>
+      <c r="F57" s="943"/>
+      <c r="G57" s="943"/>
+      <c r="H57" s="943"/>
+      <c r="I57" s="943"/>
+      <c r="J57" s="943"/>
+      <c r="K57" s="943"/>
       <c r="M57" s="91"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
@@ -49810,19 +49803,19 @@
       <c r="W59" s="4"/>
     </row>
     <row r="60" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="931" t="s">
+      <c r="A60" s="949" t="s">
         <v>122</v>
       </c>
-      <c r="B60" s="931"/>
-      <c r="C60" s="931"/>
-      <c r="D60" s="931"/>
-      <c r="E60" s="931"/>
-      <c r="F60" s="931"/>
-      <c r="G60" s="931"/>
-      <c r="H60" s="931"/>
-      <c r="I60" s="931"/>
-      <c r="J60" s="931"/>
-      <c r="K60" s="931"/>
+      <c r="B60" s="949"/>
+      <c r="C60" s="949"/>
+      <c r="D60" s="949"/>
+      <c r="E60" s="949"/>
+      <c r="F60" s="949"/>
+      <c r="G60" s="949"/>
+      <c r="H60" s="949"/>
+      <c r="I60" s="949"/>
+      <c r="J60" s="949"/>
+      <c r="K60" s="949"/>
       <c r="M60" s="91"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
@@ -49843,12 +49836,12 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="920" t="s">
+      <c r="H61" s="938" t="s">
         <v>123</v>
       </c>
-      <c r="I61" s="920"/>
-      <c r="J61" s="920"/>
-      <c r="K61" s="920"/>
+      <c r="I61" s="938"/>
+      <c r="J61" s="938"/>
+      <c r="K61" s="938"/>
       <c r="M61" s="91"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
@@ -50197,20 +50190,6 @@
     <protectedRange sqref="C9:C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="30">
-    <mergeCell ref="Z19:Z20"/>
-    <mergeCell ref="AA19:AA20"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="M30:P30"/>
-    <mergeCell ref="A15:K15"/>
     <mergeCell ref="H61:K61"/>
     <mergeCell ref="U19:V19"/>
     <mergeCell ref="X19:X20"/>
@@ -50227,6 +50206,20 @@
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="F23:F24"/>
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="A15:K15"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -50347,35 +50340,35 @@
       <c r="X6" s="178"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="933" t="s">
+      <c r="A7" s="920" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="933"/>
-      <c r="C7" s="933"/>
-      <c r="D7" s="933"/>
-      <c r="E7" s="933"/>
-      <c r="F7" s="933"/>
-      <c r="G7" s="933"/>
-      <c r="H7" s="933"/>
-      <c r="I7" s="933"/>
-      <c r="J7" s="933"/>
-      <c r="K7" s="933"/>
+      <c r="B7" s="920"/>
+      <c r="C7" s="920"/>
+      <c r="D7" s="920"/>
+      <c r="E7" s="920"/>
+      <c r="F7" s="920"/>
+      <c r="G7" s="920"/>
+      <c r="H7" s="920"/>
+      <c r="I7" s="920"/>
+      <c r="J7" s="920"/>
+      <c r="K7" s="920"/>
       <c r="X7" s="178"/>
     </row>
     <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="960">
+      <c r="A8" s="956">
         <v>1</v>
       </c>
-      <c r="B8" s="960"/>
-      <c r="C8" s="960"/>
-      <c r="D8" s="960"/>
-      <c r="E8" s="960"/>
-      <c r="F8" s="960"/>
-      <c r="G8" s="960"/>
-      <c r="H8" s="960"/>
-      <c r="I8" s="960"/>
-      <c r="J8" s="960"/>
-      <c r="K8" s="960"/>
+      <c r="B8" s="956"/>
+      <c r="C8" s="956"/>
+      <c r="D8" s="956"/>
+      <c r="E8" s="956"/>
+      <c r="F8" s="956"/>
+      <c r="G8" s="956"/>
+      <c r="H8" s="956"/>
+      <c r="I8" s="956"/>
+      <c r="J8" s="956"/>
+      <c r="K8" s="956"/>
       <c r="X8" s="178"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -50451,15 +50444,15 @@
       <c r="K13" s="308">
         <v>43845</v>
       </c>
-      <c r="M13" s="921" t="s">
+      <c r="M13" s="939" t="s">
         <v>9</v>
       </c>
-      <c r="N13" s="922"/>
-      <c r="O13" s="953" t="s">
+      <c r="N13" s="940"/>
+      <c r="O13" s="959" t="s">
         <v>69</v>
       </c>
-      <c r="P13" s="954"/>
-      <c r="Q13" s="955"/>
+      <c r="P13" s="960"/>
+      <c r="Q13" s="961"/>
       <c r="W13" s="178"/>
       <c r="X13" s="178"/>
     </row>
@@ -50483,26 +50476,26 @@
       <c r="N14" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="O14" s="956"/>
-      <c r="P14" s="957"/>
-      <c r="Q14" s="958"/>
+      <c r="O14" s="962"/>
+      <c r="P14" s="963"/>
+      <c r="Q14" s="964"/>
       <c r="W14" s="178"/>
       <c r="X14" s="178"/>
     </row>
     <row r="15" spans="1:24" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="941" t="s">
+      <c r="A15" s="928" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="942"/>
-      <c r="C15" s="942"/>
-      <c r="D15" s="942"/>
-      <c r="E15" s="942"/>
-      <c r="F15" s="942"/>
-      <c r="G15" s="942"/>
-      <c r="H15" s="942"/>
-      <c r="I15" s="942"/>
-      <c r="J15" s="942"/>
-      <c r="K15" s="943"/>
+      <c r="B15" s="929"/>
+      <c r="C15" s="929"/>
+      <c r="D15" s="929"/>
+      <c r="E15" s="929"/>
+      <c r="F15" s="929"/>
+      <c r="G15" s="929"/>
+      <c r="H15" s="929"/>
+      <c r="I15" s="929"/>
+      <c r="J15" s="929"/>
+      <c r="K15" s="930"/>
       <c r="M15" s="77" t="s">
         <v>19</v>
       </c>
@@ -50516,19 +50509,19 @@
       <c r="X15" s="178"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="948" t="s">
+      <c r="A16" s="935" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="949"/>
-      <c r="C16" s="949"/>
-      <c r="D16" s="949"/>
-      <c r="E16" s="949"/>
-      <c r="F16" s="949"/>
-      <c r="G16" s="949"/>
-      <c r="H16" s="949"/>
-      <c r="I16" s="949"/>
-      <c r="J16" s="949"/>
-      <c r="K16" s="950"/>
+      <c r="B16" s="936"/>
+      <c r="C16" s="936"/>
+      <c r="D16" s="936"/>
+      <c r="E16" s="936"/>
+      <c r="F16" s="936"/>
+      <c r="G16" s="936"/>
+      <c r="H16" s="936"/>
+      <c r="I16" s="936"/>
+      <c r="J16" s="936"/>
+      <c r="K16" s="937"/>
       <c r="L16" s="18"/>
       <c r="M16" s="77" t="s">
         <v>20</v>
@@ -50567,17 +50560,17 @@
       <c r="X17" s="178"/>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="938" t="s">
+      <c r="A18" s="925" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="939"/>
-      <c r="C18" s="939"/>
-      <c r="D18" s="939"/>
-      <c r="E18" s="939"/>
-      <c r="F18" s="939"/>
-      <c r="G18" s="939"/>
-      <c r="H18" s="939"/>
-      <c r="I18" s="939"/>
+      <c r="B18" s="926"/>
+      <c r="C18" s="926"/>
+      <c r="D18" s="926"/>
+      <c r="E18" s="926"/>
+      <c r="F18" s="926"/>
+      <c r="G18" s="926"/>
+      <c r="H18" s="926"/>
+      <c r="I18" s="926"/>
       <c r="J18" s="291"/>
       <c r="K18" s="292"/>
       <c r="M18" s="77">
@@ -50726,15 +50719,15 @@
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
       <c r="K24" s="144"/>
-      <c r="M24" s="921" t="s">
+      <c r="M24" s="939" t="s">
         <v>71</v>
       </c>
-      <c r="N24" s="922"/>
+      <c r="N24" s="940"/>
       <c r="O24" s="294"/>
-      <c r="P24" s="951">
+      <c r="P24" s="957">
         <v>762</v>
       </c>
-      <c r="Q24" s="952"/>
+      <c r="Q24" s="958"/>
       <c r="R24" s="202"/>
       <c r="S24" s="202"/>
       <c r="V24" s="201"/>
@@ -50743,33 +50736,33 @@
     </row>
     <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20"/>
-      <c r="B25" s="921" t="s">
+      <c r="B25" s="939" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="922"/>
-      <c r="D25" s="844" t="s">
+      <c r="C25" s="940"/>
+      <c r="D25" s="833" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="844" t="s">
+      <c r="E25" s="833" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="844" t="s">
+      <c r="F25" s="833" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="844" t="s">
+      <c r="G25" s="833" t="s">
         <v>43</v>
       </c>
       <c r="H25" s="209"/>
-      <c r="I25" s="926" t="s">
+      <c r="I25" s="944" t="s">
         <v>36</v>
       </c>
-      <c r="J25" s="927"/>
+      <c r="J25" s="945"/>
       <c r="K25" s="144"/>
       <c r="M25" s="210" t="s">
         <v>9</v>
       </c>
       <c r="N25" s="211"/>
-      <c r="O25" s="932" t="s">
+      <c r="O25" s="919" t="s">
         <v>100</v>
       </c>
       <c r="P25" s="212" t="s">
@@ -50796,16 +50789,16 @@
       <c r="C26" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="845"/>
-      <c r="E26" s="845"/>
-      <c r="F26" s="845"/>
-      <c r="G26" s="845"/>
+      <c r="D26" s="834"/>
+      <c r="E26" s="834"/>
+      <c r="F26" s="834"/>
+      <c r="G26" s="834"/>
       <c r="H26" s="209"/>
-      <c r="I26" s="929">
+      <c r="I26" s="947">
         <f>+P24</f>
         <v>762</v>
       </c>
-      <c r="J26" s="930"/>
+      <c r="J26" s="948"/>
       <c r="K26" s="144"/>
       <c r="M26" s="213" t="s">
         <v>11</v>
@@ -50813,7 +50806,7 @@
       <c r="N26" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="O26" s="932"/>
+      <c r="O26" s="919"/>
       <c r="P26" s="187" t="s">
         <v>28</v>
       </c>
@@ -50913,10 +50906,10 @@
         <v>#REF!</v>
       </c>
       <c r="H28" s="218"/>
-      <c r="I28" s="962" t="s">
+      <c r="I28" s="951" t="s">
         <v>37</v>
       </c>
-      <c r="J28" s="963"/>
+      <c r="J28" s="952"/>
       <c r="K28" s="144"/>
       <c r="M28" s="220" t="s">
         <v>31</v>
@@ -50972,11 +50965,11 @@
         <v>#REF!</v>
       </c>
       <c r="H29" s="218"/>
-      <c r="I29" s="964" t="e">
+      <c r="I29" s="953" t="e">
         <f>(R30+R32+R34+R36+R37+R39+R40+R42+R43)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="J29" s="965"/>
+      <c r="J29" s="954"/>
       <c r="K29" s="144"/>
       <c r="M29" s="220" t="s">
         <v>15</v>
@@ -51092,8 +51085,8 @@
         <v>#REF!</v>
       </c>
       <c r="H31" s="218"/>
-      <c r="I31" s="937"/>
-      <c r="J31" s="937"/>
+      <c r="I31" s="924"/>
+      <c r="J31" s="924"/>
       <c r="K31" s="144"/>
       <c r="L31" s="19"/>
       <c r="M31" s="220" t="s">
@@ -51150,8 +51143,8 @@
         <v>#REF!</v>
       </c>
       <c r="H32" s="218"/>
-      <c r="I32" s="937"/>
-      <c r="J32" s="937"/>
+      <c r="I32" s="924"/>
+      <c r="J32" s="924"/>
       <c r="K32" s="144"/>
       <c r="L32" s="19"/>
       <c r="M32" s="220" t="s">
@@ -51208,8 +51201,8 @@
         <v>#REF!</v>
       </c>
       <c r="H33" s="218"/>
-      <c r="I33" s="959"/>
-      <c r="J33" s="959"/>
+      <c r="I33" s="955"/>
+      <c r="J33" s="955"/>
       <c r="K33" s="144"/>
       <c r="L33" s="19"/>
       <c r="M33" s="220" t="s">
@@ -52027,10 +52020,10 @@
       <c r="W54" s="275" t="s">
         <v>105</v>
       </c>
-      <c r="X54" s="944">
+      <c r="X54" s="931">
         <v>44090</v>
       </c>
-      <c r="Y54" s="944"/>
+      <c r="Y54" s="931"/>
       <c r="Z54" s="276"/>
       <c r="AA54" s="277"/>
       <c r="AB54" s="276"/>
@@ -52059,19 +52052,19 @@
       <c r="X57" s="178"/>
     </row>
     <row r="58" spans="1:33" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="961" t="s">
+      <c r="A58" s="950" t="s">
         <v>120</v>
       </c>
-      <c r="B58" s="961"/>
-      <c r="C58" s="961"/>
-      <c r="D58" s="961"/>
-      <c r="E58" s="961"/>
-      <c r="F58" s="961"/>
-      <c r="G58" s="961"/>
-      <c r="H58" s="961"/>
-      <c r="I58" s="961"/>
-      <c r="J58" s="961"/>
-      <c r="K58" s="961"/>
+      <c r="B58" s="950"/>
+      <c r="C58" s="950"/>
+      <c r="D58" s="950"/>
+      <c r="E58" s="950"/>
+      <c r="F58" s="950"/>
+      <c r="G58" s="950"/>
+      <c r="H58" s="950"/>
+      <c r="I58" s="950"/>
+      <c r="J58" s="950"/>
+      <c r="K58" s="950"/>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" s="310" t="s">
@@ -52089,19 +52082,19 @@
       <c r="K59" s="311"/>
     </row>
     <row r="60" spans="1:33" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="961" t="s">
+      <c r="A60" s="950" t="s">
         <v>122</v>
       </c>
-      <c r="B60" s="961"/>
-      <c r="C60" s="961"/>
-      <c r="D60" s="961"/>
-      <c r="E60" s="961"/>
-      <c r="F60" s="961"/>
-      <c r="G60" s="961"/>
-      <c r="H60" s="961"/>
-      <c r="I60" s="961"/>
-      <c r="J60" s="961"/>
-      <c r="K60" s="961"/>
+      <c r="B60" s="950"/>
+      <c r="C60" s="950"/>
+      <c r="D60" s="950"/>
+      <c r="E60" s="950"/>
+      <c r="F60" s="950"/>
+      <c r="G60" s="950"/>
+      <c r="H60" s="950"/>
+      <c r="I60" s="950"/>
+      <c r="J60" s="950"/>
+      <c r="K60" s="950"/>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B63" s="5"/>
@@ -52135,21 +52128,6 @@
     <protectedRange sqref="B10:B11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="25">
-    <mergeCell ref="X54:Y54"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A18:I18"/>
     <mergeCell ref="M24:N24"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="F25:F26"/>
@@ -52160,6 +52138,21 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="X54:Y54"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="I31:J31"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -52242,35 +52235,35 @@
       <c r="H4" s="177"/>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="933" t="s">
+      <c r="A5" s="920" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="933"/>
-      <c r="C5" s="933"/>
-      <c r="D5" s="933"/>
-      <c r="E5" s="933"/>
-      <c r="F5" s="933"/>
-      <c r="G5" s="933"/>
-      <c r="H5" s="933"/>
-      <c r="I5" s="933"/>
-      <c r="J5" s="933"/>
-      <c r="K5" s="933"/>
+      <c r="B5" s="920"/>
+      <c r="C5" s="920"/>
+      <c r="D5" s="920"/>
+      <c r="E5" s="920"/>
+      <c r="F5" s="920"/>
+      <c r="G5" s="920"/>
+      <c r="H5" s="920"/>
+      <c r="I5" s="920"/>
+      <c r="J5" s="920"/>
+      <c r="K5" s="920"/>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="940">
+      <c r="A6" s="927">
         <f>+K12</f>
         <v>44</v>
       </c>
-      <c r="B6" s="940"/>
-      <c r="C6" s="940"/>
-      <c r="D6" s="940"/>
-      <c r="E6" s="940"/>
-      <c r="F6" s="940"/>
-      <c r="G6" s="940"/>
-      <c r="H6" s="940"/>
-      <c r="I6" s="940"/>
-      <c r="J6" s="940"/>
-      <c r="K6" s="940"/>
+      <c r="B6" s="927"/>
+      <c r="C6" s="927"/>
+      <c r="D6" s="927"/>
+      <c r="E6" s="927"/>
+      <c r="F6" s="927"/>
+      <c r="G6" s="927"/>
+      <c r="H6" s="927"/>
+      <c r="I6" s="927"/>
+      <c r="J6" s="927"/>
+      <c r="K6" s="927"/>
       <c r="Q6" s="259" t="s">
         <v>101</v>
       </c>
@@ -52336,10 +52329,10 @@
       <c r="Q9" s="275" t="s">
         <v>105</v>
       </c>
-      <c r="R9" s="944">
+      <c r="R9" s="931">
         <v>44090</v>
       </c>
-      <c r="S9" s="944"/>
+      <c r="S9" s="931"/>
       <c r="T9" s="276"/>
       <c r="U9" s="277"/>
       <c r="V9" s="276"/>
@@ -52420,37 +52413,37 @@
       <c r="U13" s="3"/>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="941" t="s">
+      <c r="A14" s="928" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="942"/>
-      <c r="C14" s="942"/>
-      <c r="D14" s="942"/>
-      <c r="E14" s="942"/>
-      <c r="F14" s="942"/>
-      <c r="G14" s="942"/>
-      <c r="H14" s="942"/>
-      <c r="I14" s="942"/>
-      <c r="J14" s="942"/>
-      <c r="K14" s="943"/>
+      <c r="B14" s="929"/>
+      <c r="C14" s="929"/>
+      <c r="D14" s="929"/>
+      <c r="E14" s="929"/>
+      <c r="F14" s="929"/>
+      <c r="G14" s="929"/>
+      <c r="H14" s="929"/>
+      <c r="I14" s="929"/>
+      <c r="J14" s="929"/>
+      <c r="K14" s="930"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
       <c r="U14" s="70"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="948" t="s">
+      <c r="A15" s="935" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="949"/>
-      <c r="C15" s="949"/>
-      <c r="D15" s="949"/>
-      <c r="E15" s="949"/>
-      <c r="F15" s="949"/>
-      <c r="G15" s="949"/>
-      <c r="H15" s="949"/>
-      <c r="I15" s="949"/>
-      <c r="J15" s="949"/>
-      <c r="K15" s="950"/>
+      <c r="B15" s="936"/>
+      <c r="C15" s="936"/>
+      <c r="D15" s="936"/>
+      <c r="E15" s="936"/>
+      <c r="F15" s="936"/>
+      <c r="G15" s="936"/>
+      <c r="H15" s="936"/>
+      <c r="I15" s="936"/>
+      <c r="J15" s="936"/>
+      <c r="K15" s="937"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
       <c r="U15" s="71"/>
@@ -52472,17 +52465,17 @@
       <c r="U16" s="70"/>
     </row>
     <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="938" t="s">
+      <c r="A17" s="925" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="939"/>
-      <c r="C17" s="939"/>
-      <c r="D17" s="939"/>
-      <c r="E17" s="939"/>
-      <c r="F17" s="939"/>
-      <c r="G17" s="939"/>
-      <c r="H17" s="939"/>
-      <c r="I17" s="939"/>
+      <c r="B17" s="926"/>
+      <c r="C17" s="926"/>
+      <c r="D17" s="926"/>
+      <c r="E17" s="926"/>
+      <c r="F17" s="926"/>
+      <c r="G17" s="926"/>
+      <c r="H17" s="926"/>
+      <c r="I17" s="926"/>
       <c r="J17" s="291" t="s">
         <v>124</v>
       </c>
@@ -52578,16 +52571,16 @@
       <c r="I22" s="242"/>
       <c r="J22" s="18"/>
       <c r="K22" s="243"/>
-      <c r="M22" s="966" t="s">
+      <c r="M22" s="967" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="967"/>
+      <c r="N22" s="968"/>
       <c r="O22" s="280"/>
-      <c r="P22" s="968">
+      <c r="P22" s="969">
         <f>SUM(O25:O42)</f>
         <v>9543.9950657520003</v>
       </c>
-      <c r="Q22" s="952"/>
+      <c r="Q22" s="958"/>
       <c r="R22" s="77" t="s">
         <v>73</v>
       </c>
@@ -52602,33 +52595,33 @@
     </row>
     <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
-      <c r="B23" s="974" t="s">
+      <c r="B23" s="965" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="974"/>
-      <c r="D23" s="971" t="s">
+      <c r="C23" s="965"/>
+      <c r="D23" s="966" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="971" t="s">
+      <c r="E23" s="966" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="971" t="s">
+      <c r="F23" s="966" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="971" t="s">
+      <c r="G23" s="966" t="s">
         <v>43</v>
       </c>
       <c r="H23" s="18"/>
-      <c r="I23" s="926" t="s">
+      <c r="I23" s="944" t="s">
         <v>36</v>
       </c>
-      <c r="J23" s="927"/>
+      <c r="J23" s="945"/>
       <c r="K23" s="144"/>
       <c r="M23" s="67" t="s">
         <v>9</v>
       </c>
       <c r="N23" s="68"/>
-      <c r="O23" s="932" t="s">
+      <c r="O23" s="919" t="s">
         <v>100</v>
       </c>
       <c r="P23" s="9" t="s">
@@ -52659,16 +52652,16 @@
       <c r="C24" s="244" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="971"/>
-      <c r="E24" s="971"/>
-      <c r="F24" s="971"/>
-      <c r="G24" s="971"/>
+      <c r="D24" s="966"/>
+      <c r="E24" s="966"/>
+      <c r="F24" s="966"/>
+      <c r="G24" s="966"/>
       <c r="H24" s="245"/>
-      <c r="I24" s="929">
+      <c r="I24" s="947">
         <f>+P22</f>
         <v>9543.9950657520003</v>
       </c>
-      <c r="J24" s="930"/>
+      <c r="J24" s="948"/>
       <c r="K24" s="144"/>
       <c r="M24" s="65" t="s">
         <v>11</v>
@@ -52676,7 +52669,7 @@
       <c r="N24" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O24" s="932"/>
+      <c r="O24" s="919"/>
       <c r="P24" s="10" t="s">
         <v>28</v>
       </c>
@@ -52797,10 +52790,10 @@
         <v>100</v>
       </c>
       <c r="H26" s="245"/>
-      <c r="I26" s="962" t="s">
+      <c r="I26" s="951" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="963"/>
+      <c r="J26" s="952"/>
       <c r="K26" s="144"/>
       <c r="M26" s="74">
         <v>2.5</v>
@@ -53036,10 +53029,10 @@
         <v>98.973176865046099</v>
       </c>
       <c r="H29" s="245"/>
-      <c r="I29" s="962" t="s">
+      <c r="I29" s="951" t="s">
         <v>65</v>
       </c>
-      <c r="J29" s="963"/>
+      <c r="J29" s="952"/>
       <c r="K29" s="144"/>
       <c r="L29" s="19"/>
       <c r="M29" s="74">
@@ -53117,11 +53110,11 @@
         <v>44.991617770326911</v>
       </c>
       <c r="H30" s="245"/>
-      <c r="I30" s="969">
+      <c r="I30" s="970">
         <f>+Z38</f>
         <v>0.5</v>
       </c>
-      <c r="J30" s="970"/>
+      <c r="J30" s="971"/>
       <c r="K30" s="144"/>
       <c r="L30" s="19"/>
       <c r="M30" s="74">
@@ -53278,8 +53271,8 @@
         <v>0.20955574182733017</v>
       </c>
       <c r="H32" s="245"/>
-      <c r="I32" s="937"/>
-      <c r="J32" s="937"/>
+      <c r="I32" s="924"/>
+      <c r="J32" s="924"/>
       <c r="K32" s="144"/>
       <c r="L32" s="19"/>
       <c r="M32" s="74">
@@ -53357,8 +53350,8 @@
         <v>0</v>
       </c>
       <c r="H33" s="245"/>
-      <c r="I33" s="937"/>
-      <c r="J33" s="937"/>
+      <c r="I33" s="924"/>
+      <c r="J33" s="924"/>
       <c r="K33" s="144"/>
       <c r="L33" s="19"/>
       <c r="M33" s="74">
@@ -53431,8 +53424,8 @@
       </c>
       <c r="G34" s="303"/>
       <c r="H34" s="245"/>
-      <c r="I34" s="959"/>
-      <c r="J34" s="959"/>
+      <c r="I34" s="955"/>
+      <c r="J34" s="955"/>
       <c r="K34" s="144"/>
       <c r="L34" s="19"/>
       <c r="M34" s="23" t="s">
@@ -54080,27 +54073,27 @@
       <c r="K54" s="297"/>
     </row>
     <row r="55" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="931" t="s">
+      <c r="A55" s="949" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="931"/>
-      <c r="C55" s="931"/>
-      <c r="D55" s="931"/>
-      <c r="E55" s="931"/>
-      <c r="F55" s="931"/>
-      <c r="G55" s="931"/>
-      <c r="H55" s="931"/>
-      <c r="I55" s="931"/>
-      <c r="J55" s="931"/>
-      <c r="K55" s="931"/>
+      <c r="B55" s="949"/>
+      <c r="C55" s="949"/>
+      <c r="D55" s="949"/>
+      <c r="E55" s="949"/>
+      <c r="F55" s="949"/>
+      <c r="G55" s="949"/>
+      <c r="H55" s="949"/>
+      <c r="I55" s="949"/>
+      <c r="J55" s="949"/>
+      <c r="K55" s="949"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="H56" s="920" t="s">
+      <c r="H56" s="938" t="s">
         <v>123</v>
       </c>
-      <c r="I56" s="920"/>
-      <c r="J56" s="920"/>
-      <c r="K56" s="920"/>
+      <c r="I56" s="938"/>
+      <c r="J56" s="938"/>
+      <c r="K56" s="938"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -54110,15 +54103,6 @@
     <protectedRange sqref="B9:B10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="25">
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="G23:G24"/>
     <mergeCell ref="A55:K55"/>
     <mergeCell ref="H56:K56"/>
     <mergeCell ref="O23:O24"/>
@@ -54135,6 +54119,15 @@
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="G23:G24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0.11811023622047245" footer="0"/>

--- a/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
+++ b/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Informes agregado\Gran agregado AG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E105B9FA-E8F0-4FDB-9F80-E71F3DF1F6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F596B52-0D5A-4903-9853-7278EA5BE0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="598" xr2:uid="{21CE8C7D-CFC7-4B7D-B46A-F41F71EC9170}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="598" activeTab="3" xr2:uid="{21CE8C7D-CFC7-4B7D-B46A-F41F71EC9170}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="105" r:id="rId1"/>
@@ -6038,6 +6038,93 @@
     <xf numFmtId="0" fontId="42" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6054,103 +6141,52 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6193,74 +6229,38 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="22" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="181" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -6419,6 +6419,46 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -6491,44 +6531,36 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -6549,44 +6581,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6604,6 +6598,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -6612,6 +6609,84 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -6624,40 +6699,16 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6680,57 +6731,6 @@
     <xf numFmtId="12" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -31540,34 +31540,34 @@
       <c r="M6" s="778"/>
     </row>
     <row r="7" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="805" t="s">
+      <c r="A7" s="829" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="805"/>
-      <c r="C7" s="805"/>
-      <c r="D7" s="805"/>
-      <c r="E7" s="805"/>
-      <c r="F7" s="805"/>
-      <c r="G7" s="805"/>
-      <c r="H7" s="805"/>
-      <c r="I7" s="805"/>
+      <c r="B7" s="829"/>
+      <c r="C7" s="829"/>
+      <c r="D7" s="829"/>
+      <c r="E7" s="829"/>
+      <c r="F7" s="829"/>
+      <c r="G7" s="829"/>
+      <c r="H7" s="829"/>
+      <c r="I7" s="829"/>
       <c r="L7" s="285" t="s">
         <v>446</v>
       </c>
       <c r="M7" s="778"/>
     </row>
     <row r="8" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="806" t="s">
+      <c r="A8" s="830" t="s">
         <v>384</v>
       </c>
-      <c r="B8" s="806"/>
-      <c r="C8" s="806"/>
-      <c r="D8" s="806"/>
-      <c r="E8" s="806"/>
-      <c r="F8" s="806"/>
-      <c r="G8" s="806"/>
-      <c r="H8" s="806"/>
-      <c r="I8" s="806"/>
+      <c r="B8" s="830"/>
+      <c r="C8" s="830"/>
+      <c r="D8" s="830"/>
+      <c r="E8" s="830"/>
+      <c r="F8" s="830"/>
+      <c r="G8" s="830"/>
+      <c r="H8" s="830"/>
+      <c r="I8" s="830"/>
       <c r="L8" s="285" t="s">
         <v>447</v>
       </c>
@@ -31590,18 +31590,18 @@
     </row>
     <row r="10" spans="1:14" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="725"/>
-      <c r="B10" s="807" t="s">
+      <c r="B10" s="824" t="s">
         <v>385</v>
       </c>
-      <c r="C10" s="807"/>
-      <c r="D10" s="808" t="s">
+      <c r="C10" s="824"/>
+      <c r="D10" s="831" t="s">
         <v>386</v>
       </c>
-      <c r="E10" s="809"/>
-      <c r="F10" s="808" t="s">
+      <c r="E10" s="832"/>
+      <c r="F10" s="831" t="s">
         <v>387</v>
       </c>
-      <c r="G10" s="809"/>
+      <c r="G10" s="832"/>
       <c r="H10" s="736" t="s">
         <v>388</v>
       </c>
@@ -31611,12 +31611,12 @@
     </row>
     <row r="11" spans="1:14" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="725"/>
-      <c r="B11" s="802"/>
-      <c r="C11" s="802"/>
-      <c r="D11" s="803"/>
-      <c r="E11" s="804"/>
-      <c r="F11" s="803"/>
-      <c r="G11" s="804"/>
+      <c r="B11" s="826"/>
+      <c r="C11" s="826"/>
+      <c r="D11" s="827"/>
+      <c r="E11" s="828"/>
+      <c r="F11" s="827"/>
+      <c r="G11" s="828"/>
       <c r="H11" s="737"/>
       <c r="I11" s="725"/>
       <c r="L11" s="285" t="s">
@@ -31640,17 +31640,17 @@
       <c r="M12" s="779"/>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="811" t="s">
+      <c r="A13" s="816" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="812"/>
-      <c r="C13" s="812"/>
-      <c r="D13" s="812"/>
-      <c r="E13" s="812"/>
-      <c r="F13" s="812"/>
-      <c r="G13" s="812"/>
-      <c r="H13" s="812"/>
-      <c r="I13" s="813"/>
+      <c r="B13" s="817"/>
+      <c r="C13" s="817"/>
+      <c r="D13" s="817"/>
+      <c r="E13" s="817"/>
+      <c r="F13" s="817"/>
+      <c r="G13" s="817"/>
+      <c r="H13" s="817"/>
+      <c r="I13" s="818"/>
       <c r="J13" s="166"/>
       <c r="L13" s="285" t="s">
         <v>451</v>
@@ -31659,17 +31659,17 @@
       <c r="N13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="814" t="s">
+      <c r="A14" s="819" t="s">
         <v>389</v>
       </c>
-      <c r="B14" s="815"/>
-      <c r="C14" s="815"/>
-      <c r="D14" s="815"/>
-      <c r="E14" s="815"/>
-      <c r="F14" s="815"/>
-      <c r="G14" s="815"/>
-      <c r="H14" s="815"/>
-      <c r="I14" s="816"/>
+      <c r="B14" s="820"/>
+      <c r="C14" s="820"/>
+      <c r="D14" s="820"/>
+      <c r="E14" s="820"/>
+      <c r="F14" s="820"/>
+      <c r="G14" s="820"/>
+      <c r="H14" s="820"/>
+      <c r="I14" s="821"/>
       <c r="J14" s="166"/>
       <c r="L14" s="777"/>
       <c r="M14" s="778"/>
@@ -31694,10 +31694,10 @@
       <c r="A16" s="739" t="s">
         <v>390</v>
       </c>
-      <c r="B16" s="817"/>
-      <c r="C16" s="817"/>
-      <c r="D16" s="817"/>
-      <c r="E16" s="817"/>
+      <c r="B16" s="803"/>
+      <c r="C16" s="803"/>
+      <c r="D16" s="803"/>
+      <c r="E16" s="803"/>
       <c r="F16" s="231"/>
       <c r="G16" s="213" t="s">
         <v>9</v>
@@ -31714,13 +31714,13 @@
       <c r="M16" s="780"/>
     </row>
     <row r="17" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="818" t="s">
+      <c r="A17" s="822" t="s">
         <v>393</v>
       </c>
-      <c r="B17" s="818"/>
-      <c r="C17" s="818"/>
-      <c r="D17" s="819"/>
-      <c r="E17" s="819"/>
+      <c r="B17" s="822"/>
+      <c r="C17" s="822"/>
+      <c r="D17" s="823"/>
+      <c r="E17" s="823"/>
       <c r="F17" s="231"/>
       <c r="G17" s="213" t="s">
         <v>11</v>
@@ -31740,10 +31740,10 @@
       <c r="A18" s="739" t="s">
         <v>396</v>
       </c>
-      <c r="B18" s="817"/>
-      <c r="C18" s="817"/>
-      <c r="D18" s="817"/>
-      <c r="E18" s="817"/>
+      <c r="B18" s="803"/>
+      <c r="C18" s="803"/>
+      <c r="D18" s="803"/>
+      <c r="E18" s="803"/>
       <c r="F18" s="740"/>
       <c r="G18" s="77" t="s">
         <v>397</v>
@@ -31765,13 +31765,13 @@
       <c r="I19" s="69"/>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="807" t="s">
+      <c r="A20" s="824" t="s">
         <v>399</v>
       </c>
-      <c r="B20" s="807"/>
-      <c r="C20" s="807"/>
-      <c r="D20" s="807"/>
-      <c r="E20" s="807"/>
+      <c r="B20" s="824"/>
+      <c r="C20" s="824"/>
+      <c r="D20" s="824"/>
+      <c r="E20" s="824"/>
       <c r="F20" s="742"/>
       <c r="G20" s="77" t="s">
         <v>400</v>
@@ -31790,8 +31790,8 @@
       <c r="C21" s="745" t="s">
         <v>402</v>
       </c>
-      <c r="D21" s="820"/>
-      <c r="E21" s="820"/>
+      <c r="D21" s="825"/>
+      <c r="E21" s="825"/>
       <c r="F21" s="746"/>
       <c r="G21" s="77" t="s">
         <v>403</v>
@@ -31810,8 +31810,8 @@
       <c r="C22" s="745" t="s">
         <v>402</v>
       </c>
-      <c r="D22" s="820"/>
-      <c r="E22" s="820"/>
+      <c r="D22" s="825"/>
+      <c r="E22" s="825"/>
       <c r="F22" s="746"/>
       <c r="G22" s="77" t="s">
         <v>405</v>
@@ -31829,8 +31829,8 @@
       <c r="C23" s="745" t="s">
         <v>402</v>
       </c>
-      <c r="D23" s="820"/>
-      <c r="E23" s="820"/>
+      <c r="D23" s="825"/>
+      <c r="E23" s="825"/>
       <c r="F23" s="746"/>
       <c r="G23" s="77" t="s">
         <v>407</v>
@@ -31848,8 +31848,8 @@
       <c r="C24" s="745" t="s">
         <v>402</v>
       </c>
-      <c r="D24" s="820"/>
-      <c r="E24" s="820"/>
+      <c r="D24" s="825"/>
+      <c r="E24" s="825"/>
       <c r="F24" s="746"/>
       <c r="G24" s="220" t="s">
         <v>409</v>
@@ -31875,13 +31875,13 @@
       <c r="I25" s="69"/>
     </row>
     <row r="26" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="810" t="s">
+      <c r="A26" s="815" t="s">
         <v>411</v>
       </c>
-      <c r="B26" s="810"/>
-      <c r="C26" s="810"/>
-      <c r="D26" s="810"/>
-      <c r="E26" s="810"/>
+      <c r="B26" s="815"/>
+      <c r="C26" s="815"/>
+      <c r="D26" s="815"/>
+      <c r="E26" s="815"/>
       <c r="F26" s="5"/>
       <c r="G26" s="77" t="s">
         <v>412</v>
@@ -31899,8 +31899,8 @@
       <c r="C27" s="750" t="s">
         <v>402</v>
       </c>
-      <c r="D27" s="821"/>
-      <c r="E27" s="821"/>
+      <c r="D27" s="811"/>
+      <c r="E27" s="811"/>
       <c r="G27" s="220" t="s">
         <v>413</v>
       </c>
@@ -31917,8 +31917,8 @@
       <c r="C28" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D28" s="817"/>
-      <c r="E28" s="817"/>
+      <c r="D28" s="803"/>
+      <c r="E28" s="803"/>
       <c r="G28" s="77" t="s">
         <v>415</v>
       </c>
@@ -31928,13 +31928,13 @@
       <c r="I28" s="69"/>
     </row>
     <row r="29" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="822" t="s">
+      <c r="A29" s="812" t="s">
         <v>416</v>
       </c>
-      <c r="B29" s="823"/>
-      <c r="C29" s="823"/>
-      <c r="D29" s="823"/>
-      <c r="E29" s="824"/>
+      <c r="B29" s="813"/>
+      <c r="C29" s="813"/>
+      <c r="D29" s="813"/>
+      <c r="E29" s="814"/>
       <c r="G29" s="220" t="s">
         <v>417</v>
       </c>
@@ -31952,8 +31952,8 @@
       <c r="C30" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D30" s="817"/>
-      <c r="E30" s="817"/>
+      <c r="D30" s="803"/>
+      <c r="E30" s="803"/>
       <c r="G30" s="220" t="s">
         <v>161</v>
       </c>
@@ -31971,8 +31971,8 @@
       <c r="C31" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D31" s="817"/>
-      <c r="E31" s="817"/>
+      <c r="D31" s="803"/>
+      <c r="E31" s="803"/>
       <c r="G31" s="220" t="s">
         <v>418</v>
       </c>
@@ -31983,13 +31983,13 @@
       <c r="J31" s="166"/>
     </row>
     <row r="32" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="822" t="s">
+      <c r="A32" s="812" t="s">
         <v>419</v>
       </c>
-      <c r="B32" s="823"/>
-      <c r="C32" s="823"/>
-      <c r="D32" s="823"/>
-      <c r="E32" s="824"/>
+      <c r="B32" s="813"/>
+      <c r="C32" s="813"/>
+      <c r="D32" s="813"/>
+      <c r="E32" s="814"/>
       <c r="G32" s="220" t="s">
         <v>420</v>
       </c>
@@ -32007,8 +32007,8 @@
       <c r="C33" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D33" s="817"/>
-      <c r="E33" s="817"/>
+      <c r="D33" s="803"/>
+      <c r="E33" s="803"/>
       <c r="F33" s="740"/>
       <c r="G33" s="220" t="s">
         <v>422</v>
@@ -32026,8 +32026,8 @@
       <c r="C34" s="747" t="s">
         <v>402</v>
       </c>
-      <c r="D34" s="817"/>
-      <c r="E34" s="817"/>
+      <c r="D34" s="803"/>
+      <c r="E34" s="803"/>
       <c r="F34" s="740"/>
       <c r="G34" s="220" t="s">
         <v>424</v>
@@ -32046,8 +32046,8 @@
       <c r="C35" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D35" s="817"/>
-      <c r="E35" s="817"/>
+      <c r="D35" s="803"/>
+      <c r="E35" s="803"/>
       <c r="F35" s="740"/>
       <c r="G35" s="230" t="s">
         <v>34</v>
@@ -32065,8 +32065,8 @@
       <c r="C36" s="747" t="s">
         <v>402</v>
       </c>
-      <c r="D36" s="817"/>
-      <c r="E36" s="817"/>
+      <c r="D36" s="803"/>
+      <c r="E36" s="803"/>
       <c r="F36" s="740"/>
       <c r="H36" s="755" t="s">
         <v>427</v>
@@ -32081,8 +32081,8 @@
       <c r="C37" s="752" t="s">
         <v>402</v>
       </c>
-      <c r="D37" s="817"/>
-      <c r="E37" s="817"/>
+      <c r="D37" s="803"/>
+      <c r="E37" s="803"/>
       <c r="F37" s="740"/>
       <c r="J37" s="166"/>
     </row>
@@ -32094,8 +32094,8 @@
       <c r="C38" s="750" t="s">
         <v>430</v>
       </c>
-      <c r="D38" s="817"/>
-      <c r="E38" s="817"/>
+      <c r="D38" s="803"/>
+      <c r="E38" s="803"/>
       <c r="F38" s="740"/>
       <c r="I38" s="757"/>
       <c r="J38" s="166"/>
@@ -32108,8 +32108,8 @@
       <c r="C39" s="750" t="s">
         <v>402</v>
       </c>
-      <c r="D39" s="817"/>
-      <c r="E39" s="817"/>
+      <c r="D39" s="803"/>
+      <c r="E39" s="803"/>
       <c r="F39" s="740"/>
       <c r="G39" s="758"/>
       <c r="H39" s="759"/>
@@ -32125,12 +32125,12 @@
       <c r="J40" s="166"/>
     </row>
     <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="826" t="s">
+      <c r="A41" s="804" t="s">
         <v>432</v>
       </c>
-      <c r="B41" s="826"/>
-      <c r="C41" s="826"/>
-      <c r="D41" s="826"/>
+      <c r="B41" s="804"/>
+      <c r="C41" s="804"/>
+      <c r="D41" s="804"/>
       <c r="E41" s="760"/>
       <c r="F41" s="760"/>
       <c r="J41" s="166"/>
@@ -32140,10 +32140,10 @@
         <v>433</v>
       </c>
       <c r="B42" s="762"/>
-      <c r="C42" s="827"/>
-      <c r="D42" s="827"/>
-      <c r="E42" s="828"/>
-      <c r="F42" s="828"/>
+      <c r="C42" s="805"/>
+      <c r="D42" s="805"/>
+      <c r="E42" s="806"/>
+      <c r="F42" s="806"/>
       <c r="J42" s="166"/>
     </row>
     <row r="43" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -32151,10 +32151,10 @@
         <v>434</v>
       </c>
       <c r="B43" s="763"/>
-      <c r="C43" s="827"/>
-      <c r="D43" s="827"/>
-      <c r="E43" s="828"/>
-      <c r="F43" s="828"/>
+      <c r="C43" s="805"/>
+      <c r="D43" s="805"/>
+      <c r="E43" s="806"/>
+      <c r="F43" s="806"/>
       <c r="J43" s="166"/>
     </row>
     <row r="44" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -32162,10 +32162,10 @@
         <v>435</v>
       </c>
       <c r="B44" s="763"/>
-      <c r="C44" s="827"/>
-      <c r="D44" s="827"/>
-      <c r="E44" s="828"/>
-      <c r="F44" s="828"/>
+      <c r="C44" s="805"/>
+      <c r="D44" s="805"/>
+      <c r="E44" s="806"/>
+      <c r="F44" s="806"/>
       <c r="J44" s="166"/>
     </row>
     <row r="45" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -32188,25 +32188,25 @@
       <c r="A47" s="769" t="s">
         <v>438</v>
       </c>
-      <c r="B47" s="829"/>
-      <c r="C47" s="830"/>
-      <c r="D47" s="831"/>
+      <c r="B47" s="807"/>
+      <c r="C47" s="808"/>
+      <c r="D47" s="809"/>
       <c r="E47" s="247"/>
       <c r="F47" s="247"/>
-      <c r="G47" s="832" t="s">
+      <c r="G47" s="810" t="s">
         <v>439</v>
       </c>
-      <c r="H47" s="832"/>
-      <c r="I47" s="832"/>
+      <c r="H47" s="810"/>
+      <c r="I47" s="810"/>
       <c r="J47" s="166"/>
     </row>
     <row r="48" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="770" t="s">
         <v>440</v>
       </c>
-      <c r="B48" s="829"/>
-      <c r="C48" s="830"/>
-      <c r="D48" s="831"/>
+      <c r="B48" s="807"/>
+      <c r="C48" s="808"/>
+      <c r="D48" s="809"/>
       <c r="E48" s="247"/>
       <c r="F48" s="247"/>
       <c r="G48" s="4" t="s">
@@ -32271,17 +32271,17 @@
     </row>
     <row r="54" spans="1:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="825" t="s">
+      <c r="A55" s="802" t="s">
         <v>445</v>
       </c>
-      <c r="B55" s="825"/>
-      <c r="C55" s="825"/>
-      <c r="D55" s="825"/>
-      <c r="E55" s="825"/>
-      <c r="F55" s="825"/>
-      <c r="G55" s="825"/>
-      <c r="H55" s="825"/>
-      <c r="I55" s="825"/>
+      <c r="B55" s="802"/>
+      <c r="C55" s="802"/>
+      <c r="D55" s="802"/>
+      <c r="E55" s="802"/>
+      <c r="F55" s="802"/>
+      <c r="G55" s="802"/>
+      <c r="H55" s="802"/>
+      <c r="I55" s="802"/>
     </row>
     <row r="56" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -32291,6 +32291,38 @@
     <protectedRange sqref="B15" name="Rango3_3_1_1_1_1_1_1_1_1"/>
   </protectedRanges>
   <mergeCells count="44">
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
     <mergeCell ref="A55:I55"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="A41:D41"/>
@@ -32303,38 +32335,6 @@
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="G47:I47"/>
     <mergeCell ref="B48:D48"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.59055118110236227" top="0.78740157480314965" bottom="0" header="0" footer="0"/>
@@ -32387,117 +32387,117 @@
       <c r="T4" s="25"/>
     </row>
     <row r="5" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="974" t="s">
+      <c r="B5" s="995" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="975"/>
-      <c r="D5" s="975"/>
-      <c r="E5" s="975"/>
-      <c r="F5" s="976"/>
-      <c r="H5" s="974" t="s">
+      <c r="C5" s="996"/>
+      <c r="D5" s="996"/>
+      <c r="E5" s="996"/>
+      <c r="F5" s="997"/>
+      <c r="H5" s="995" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="975"/>
-      <c r="J5" s="975"/>
-      <c r="K5" s="975"/>
-      <c r="L5" s="975"/>
-      <c r="M5" s="975"/>
-      <c r="N5" s="975"/>
-      <c r="O5" s="975"/>
-      <c r="P5" s="975"/>
-      <c r="Q5" s="975"/>
-      <c r="R5" s="975"/>
-      <c r="S5" s="975"/>
-      <c r="T5" s="975"/>
-      <c r="U5" s="975"/>
-      <c r="V5" s="975"/>
-      <c r="W5" s="975"/>
-      <c r="X5" s="975"/>
-      <c r="Y5" s="975"/>
-      <c r="Z5" s="975"/>
-      <c r="AA5" s="975"/>
-      <c r="AB5" s="975"/>
-      <c r="AC5" s="975"/>
-      <c r="AD5" s="975"/>
-      <c r="AE5" s="975"/>
-      <c r="AF5" s="975"/>
-      <c r="AG5" s="975"/>
-      <c r="AH5" s="975"/>
-      <c r="AI5" s="975"/>
-      <c r="AJ5" s="975"/>
-      <c r="AK5" s="975"/>
-      <c r="AL5" s="975"/>
-      <c r="AM5" s="975"/>
-      <c r="AN5" s="975"/>
-      <c r="AO5" s="975"/>
-      <c r="AP5" s="975"/>
-      <c r="AQ5" s="975"/>
-      <c r="AR5" s="975"/>
-      <c r="AS5" s="976"/>
+      <c r="I5" s="996"/>
+      <c r="J5" s="996"/>
+      <c r="K5" s="996"/>
+      <c r="L5" s="996"/>
+      <c r="M5" s="996"/>
+      <c r="N5" s="996"/>
+      <c r="O5" s="996"/>
+      <c r="P5" s="996"/>
+      <c r="Q5" s="996"/>
+      <c r="R5" s="996"/>
+      <c r="S5" s="996"/>
+      <c r="T5" s="996"/>
+      <c r="U5" s="996"/>
+      <c r="V5" s="996"/>
+      <c r="W5" s="996"/>
+      <c r="X5" s="996"/>
+      <c r="Y5" s="996"/>
+      <c r="Z5" s="996"/>
+      <c r="AA5" s="996"/>
+      <c r="AB5" s="996"/>
+      <c r="AC5" s="996"/>
+      <c r="AD5" s="996"/>
+      <c r="AE5" s="996"/>
+      <c r="AF5" s="996"/>
+      <c r="AG5" s="996"/>
+      <c r="AH5" s="996"/>
+      <c r="AI5" s="996"/>
+      <c r="AJ5" s="996"/>
+      <c r="AK5" s="996"/>
+      <c r="AL5" s="996"/>
+      <c r="AM5" s="996"/>
+      <c r="AN5" s="996"/>
+      <c r="AO5" s="996"/>
+      <c r="AP5" s="996"/>
+      <c r="AQ5" s="996"/>
+      <c r="AR5" s="996"/>
+      <c r="AS5" s="997"/>
     </row>
     <row r="6" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="974" t="s">
+      <c r="B6" s="995" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="975"/>
-      <c r="D6" s="975"/>
-      <c r="E6" s="975"/>
-      <c r="F6" s="976"/>
-      <c r="H6" s="974" t="s">
+      <c r="C6" s="996"/>
+      <c r="D6" s="996"/>
+      <c r="E6" s="996"/>
+      <c r="F6" s="997"/>
+      <c r="H6" s="995" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="975"/>
-      <c r="J6" s="975"/>
-      <c r="K6" s="975"/>
-      <c r="L6" s="975"/>
-      <c r="M6" s="975"/>
-      <c r="N6" s="975"/>
-      <c r="O6" s="975"/>
-      <c r="P6" s="975"/>
-      <c r="Q6" s="975"/>
-      <c r="R6" s="975"/>
-      <c r="S6" s="975"/>
-      <c r="T6" s="975"/>
-      <c r="U6" s="975"/>
-      <c r="V6" s="975"/>
-      <c r="W6" s="975"/>
-      <c r="X6" s="975"/>
-      <c r="Y6" s="975"/>
-      <c r="Z6" s="975"/>
-      <c r="AA6" s="975"/>
-      <c r="AB6" s="975"/>
-      <c r="AC6" s="975"/>
-      <c r="AD6" s="975"/>
-      <c r="AE6" s="975"/>
-      <c r="AF6" s="975"/>
-      <c r="AG6" s="975"/>
-      <c r="AH6" s="975"/>
-      <c r="AI6" s="975"/>
-      <c r="AJ6" s="975"/>
-      <c r="AK6" s="975"/>
-      <c r="AL6" s="975"/>
-      <c r="AM6" s="975"/>
-      <c r="AN6" s="975"/>
-      <c r="AO6" s="975"/>
-      <c r="AP6" s="975"/>
-      <c r="AQ6" s="975"/>
-      <c r="AR6" s="975"/>
-      <c r="AS6" s="976"/>
+      <c r="I6" s="996"/>
+      <c r="J6" s="996"/>
+      <c r="K6" s="996"/>
+      <c r="L6" s="996"/>
+      <c r="M6" s="996"/>
+      <c r="N6" s="996"/>
+      <c r="O6" s="996"/>
+      <c r="P6" s="996"/>
+      <c r="Q6" s="996"/>
+      <c r="R6" s="996"/>
+      <c r="S6" s="996"/>
+      <c r="T6" s="996"/>
+      <c r="U6" s="996"/>
+      <c r="V6" s="996"/>
+      <c r="W6" s="996"/>
+      <c r="X6" s="996"/>
+      <c r="Y6" s="996"/>
+      <c r="Z6" s="996"/>
+      <c r="AA6" s="996"/>
+      <c r="AB6" s="996"/>
+      <c r="AC6" s="996"/>
+      <c r="AD6" s="996"/>
+      <c r="AE6" s="996"/>
+      <c r="AF6" s="996"/>
+      <c r="AG6" s="996"/>
+      <c r="AH6" s="996"/>
+      <c r="AI6" s="996"/>
+      <c r="AJ6" s="996"/>
+      <c r="AK6" s="996"/>
+      <c r="AL6" s="996"/>
+      <c r="AM6" s="996"/>
+      <c r="AN6" s="996"/>
+      <c r="AO6" s="996"/>
+      <c r="AP6" s="996"/>
+      <c r="AQ6" s="996"/>
+      <c r="AR6" s="996"/>
+      <c r="AS6" s="997"/>
     </row>
     <row r="7" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="999" t="s">
+      <c r="B7" s="975" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1000"/>
-      <c r="D7" s="977" t="s">
+      <c r="C7" s="976"/>
+      <c r="D7" s="979" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="978"/>
-      <c r="F7" s="979"/>
-      <c r="H7" s="1003" t="s">
+      <c r="E7" s="980"/>
+      <c r="F7" s="981"/>
+      <c r="H7" s="991" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="1004"/>
+      <c r="I7" s="992"/>
       <c r="J7" s="30"/>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
@@ -32507,119 +32507,119 @@
       <c r="P7" s="30"/>
       <c r="Q7" s="30"/>
       <c r="R7" s="14"/>
-      <c r="S7" s="989">
+      <c r="S7" s="1004">
         <v>2</v>
       </c>
-      <c r="T7" s="990"/>
-      <c r="U7" s="991"/>
-      <c r="V7" s="995"/>
-      <c r="W7" s="996"/>
-      <c r="X7" s="997"/>
-      <c r="Y7" s="989">
+      <c r="T7" s="1005"/>
+      <c r="U7" s="1006"/>
+      <c r="V7" s="998"/>
+      <c r="W7" s="999"/>
+      <c r="X7" s="1000"/>
+      <c r="Y7" s="1004">
         <v>1.5</v>
       </c>
-      <c r="Z7" s="990"/>
-      <c r="AA7" s="991"/>
-      <c r="AB7" s="995"/>
-      <c r="AC7" s="996"/>
-      <c r="AD7" s="997"/>
-      <c r="AE7" s="995"/>
-      <c r="AF7" s="996"/>
-      <c r="AG7" s="997"/>
-      <c r="AH7" s="989">
+      <c r="Z7" s="1005"/>
+      <c r="AA7" s="1006"/>
+      <c r="AB7" s="998"/>
+      <c r="AC7" s="999"/>
+      <c r="AD7" s="1000"/>
+      <c r="AE7" s="998"/>
+      <c r="AF7" s="999"/>
+      <c r="AG7" s="1000"/>
+      <c r="AH7" s="1004">
         <v>1</v>
       </c>
-      <c r="AI7" s="990"/>
-      <c r="AJ7" s="991"/>
-      <c r="AK7" s="995"/>
-      <c r="AL7" s="996"/>
-      <c r="AM7" s="997"/>
-      <c r="AN7" s="989">
+      <c r="AI7" s="1005"/>
+      <c r="AJ7" s="1006"/>
+      <c r="AK7" s="998"/>
+      <c r="AL7" s="999"/>
+      <c r="AM7" s="1000"/>
+      <c r="AN7" s="1004">
         <v>0.75</v>
       </c>
-      <c r="AO7" s="990"/>
-      <c r="AP7" s="991"/>
-      <c r="AQ7" s="989">
+      <c r="AO7" s="1005"/>
+      <c r="AP7" s="1006"/>
+      <c r="AQ7" s="1004">
         <v>0.5</v>
       </c>
-      <c r="AR7" s="990"/>
-      <c r="AS7" s="991"/>
+      <c r="AR7" s="1005"/>
+      <c r="AS7" s="1006"/>
     </row>
     <row r="8" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="1001"/>
-      <c r="C8" s="1002"/>
-      <c r="D8" s="980"/>
-      <c r="E8" s="981"/>
-      <c r="F8" s="982"/>
-      <c r="H8" s="1005" t="s">
+      <c r="B8" s="977"/>
+      <c r="C8" s="978"/>
+      <c r="D8" s="982"/>
+      <c r="E8" s="983"/>
+      <c r="F8" s="984"/>
+      <c r="H8" s="993" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="1006"/>
-      <c r="J8" s="992">
+      <c r="I8" s="994"/>
+      <c r="J8" s="988">
         <v>1</v>
       </c>
-      <c r="K8" s="993"/>
-      <c r="L8" s="994"/>
-      <c r="M8" s="992">
+      <c r="K8" s="989"/>
+      <c r="L8" s="990"/>
+      <c r="M8" s="988">
         <v>2</v>
       </c>
-      <c r="N8" s="993"/>
-      <c r="O8" s="994"/>
-      <c r="P8" s="992">
+      <c r="N8" s="989"/>
+      <c r="O8" s="990"/>
+      <c r="P8" s="988">
         <v>3</v>
       </c>
-      <c r="Q8" s="993"/>
-      <c r="R8" s="994"/>
-      <c r="S8" s="992">
+      <c r="Q8" s="989"/>
+      <c r="R8" s="990"/>
+      <c r="S8" s="988">
         <v>357</v>
       </c>
-      <c r="T8" s="993"/>
-      <c r="U8" s="994"/>
-      <c r="V8" s="992">
+      <c r="T8" s="989"/>
+      <c r="U8" s="990"/>
+      <c r="V8" s="988">
         <v>4</v>
       </c>
-      <c r="W8" s="993"/>
-      <c r="X8" s="994"/>
-      <c r="Y8" s="992">
+      <c r="W8" s="989"/>
+      <c r="X8" s="990"/>
+      <c r="Y8" s="988">
         <v>467</v>
       </c>
-      <c r="Z8" s="993"/>
-      <c r="AA8" s="994"/>
-      <c r="AB8" s="992">
+      <c r="Z8" s="989"/>
+      <c r="AA8" s="990"/>
+      <c r="AB8" s="988">
         <v>5</v>
       </c>
-      <c r="AC8" s="993"/>
-      <c r="AD8" s="994"/>
-      <c r="AE8" s="992">
+      <c r="AC8" s="989"/>
+      <c r="AD8" s="990"/>
+      <c r="AE8" s="988">
         <v>56</v>
       </c>
-      <c r="AF8" s="993"/>
-      <c r="AG8" s="994"/>
-      <c r="AH8" s="992">
+      <c r="AF8" s="989"/>
+      <c r="AG8" s="990"/>
+      <c r="AH8" s="988">
         <v>57</v>
       </c>
-      <c r="AI8" s="993"/>
-      <c r="AJ8" s="994"/>
-      <c r="AK8" s="992">
+      <c r="AI8" s="989"/>
+      <c r="AJ8" s="990"/>
+      <c r="AK8" s="988">
         <v>6</v>
       </c>
-      <c r="AL8" s="993"/>
-      <c r="AM8" s="994"/>
-      <c r="AN8" s="992">
+      <c r="AL8" s="989"/>
+      <c r="AM8" s="990"/>
+      <c r="AN8" s="988">
         <v>67</v>
       </c>
-      <c r="AO8" s="993"/>
-      <c r="AP8" s="994"/>
-      <c r="AQ8" s="992">
+      <c r="AO8" s="989"/>
+      <c r="AP8" s="990"/>
+      <c r="AQ8" s="988">
         <v>7</v>
       </c>
-      <c r="AR8" s="993"/>
-      <c r="AS8" s="994"/>
-      <c r="AT8" s="992">
+      <c r="AR8" s="989"/>
+      <c r="AS8" s="990"/>
+      <c r="AT8" s="988">
         <v>8</v>
       </c>
-      <c r="AU8" s="993"/>
-      <c r="AV8" s="994"/>
+      <c r="AU8" s="989"/>
+      <c r="AV8" s="990"/>
     </row>
     <row r="9" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
@@ -32628,80 +32628,80 @@
       <c r="C9" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="983"/>
-      <c r="E9" s="984"/>
-      <c r="F9" s="985"/>
+      <c r="D9" s="985"/>
+      <c r="E9" s="986"/>
+      <c r="F9" s="987"/>
       <c r="H9" s="32" t="s">
         <v>11</v>
       </c>
       <c r="I9" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="992" t="s">
+      <c r="J9" s="988" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="993"/>
-      <c r="L9" s="994"/>
-      <c r="M9" s="992" t="s">
+      <c r="K9" s="989"/>
+      <c r="L9" s="990"/>
+      <c r="M9" s="988" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="993"/>
-      <c r="O9" s="994"/>
-      <c r="P9" s="992" t="s">
+      <c r="N9" s="989"/>
+      <c r="O9" s="990"/>
+      <c r="P9" s="988" t="s">
         <v>53</v>
       </c>
-      <c r="Q9" s="993"/>
-      <c r="R9" s="994"/>
-      <c r="S9" s="992" t="s">
+      <c r="Q9" s="989"/>
+      <c r="R9" s="990"/>
+      <c r="S9" s="988" t="s">
         <v>54</v>
       </c>
-      <c r="T9" s="993"/>
-      <c r="U9" s="994"/>
-      <c r="V9" s="992" t="s">
+      <c r="T9" s="989"/>
+      <c r="U9" s="990"/>
+      <c r="V9" s="988" t="s">
         <v>55</v>
       </c>
-      <c r="W9" s="993"/>
-      <c r="X9" s="994"/>
-      <c r="Y9" s="992" t="s">
+      <c r="W9" s="989"/>
+      <c r="X9" s="990"/>
+      <c r="Y9" s="988" t="s">
         <v>56</v>
       </c>
-      <c r="Z9" s="993"/>
-      <c r="AA9" s="994"/>
-      <c r="AB9" s="992" t="s">
+      <c r="Z9" s="989"/>
+      <c r="AA9" s="990"/>
+      <c r="AB9" s="988" t="s">
         <v>57</v>
       </c>
-      <c r="AC9" s="993"/>
-      <c r="AD9" s="994"/>
-      <c r="AE9" s="992" t="s">
+      <c r="AC9" s="989"/>
+      <c r="AD9" s="990"/>
+      <c r="AE9" s="988" t="s">
         <v>58</v>
       </c>
-      <c r="AF9" s="993"/>
-      <c r="AG9" s="994"/>
-      <c r="AH9" s="992" t="s">
+      <c r="AF9" s="989"/>
+      <c r="AG9" s="990"/>
+      <c r="AH9" s="988" t="s">
         <v>59</v>
       </c>
-      <c r="AI9" s="993"/>
-      <c r="AJ9" s="994"/>
-      <c r="AK9" s="992" t="s">
+      <c r="AI9" s="989"/>
+      <c r="AJ9" s="990"/>
+      <c r="AK9" s="988" t="s">
         <v>60</v>
       </c>
-      <c r="AL9" s="993"/>
-      <c r="AM9" s="994"/>
-      <c r="AN9" s="992" t="s">
+      <c r="AL9" s="989"/>
+      <c r="AM9" s="990"/>
+      <c r="AN9" s="988" t="s">
         <v>61</v>
       </c>
-      <c r="AO9" s="993"/>
-      <c r="AP9" s="994"/>
-      <c r="AQ9" s="992" t="s">
+      <c r="AO9" s="989"/>
+      <c r="AP9" s="990"/>
+      <c r="AQ9" s="988" t="s">
         <v>62</v>
       </c>
-      <c r="AR9" s="993"/>
-      <c r="AS9" s="994"/>
-      <c r="AT9" s="992" t="s">
+      <c r="AR9" s="989"/>
+      <c r="AS9" s="990"/>
+      <c r="AT9" s="988" t="s">
         <v>63</v>
       </c>
-      <c r="AU9" s="993"/>
-      <c r="AV9" s="994"/>
+      <c r="AU9" s="989"/>
+      <c r="AV9" s="990"/>
     </row>
     <row r="10" spans="2:55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="33" t="s">
@@ -33833,11 +33833,11 @@
       <c r="I25" s="60">
         <v>0.75</v>
       </c>
-      <c r="J25" s="977" t="s">
+      <c r="J25" s="979" t="s">
         <v>46</v>
       </c>
-      <c r="K25" s="978"/>
-      <c r="L25" s="979"/>
+      <c r="K25" s="980"/>
+      <c r="L25" s="981"/>
       <c r="Q25" s="25"/>
       <c r="R25" s="25"/>
       <c r="S25" s="25"/>
@@ -33862,16 +33862,16 @@
       <c r="I26" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="J26" s="980"/>
-      <c r="K26" s="981"/>
-      <c r="L26" s="982"/>
+      <c r="J26" s="982"/>
+      <c r="K26" s="983"/>
+      <c r="L26" s="984"/>
       <c r="Q26" s="25"/>
       <c r="R26" s="25"/>
-      <c r="S26" s="986" t="s">
+      <c r="S26" s="1001" t="s">
         <v>43</v>
       </c>
-      <c r="T26" s="987"/>
-      <c r="U26" s="988"/>
+      <c r="T26" s="1002"/>
+      <c r="U26" s="1003"/>
       <c r="AI26" s="73">
         <v>1.5</v>
       </c>
@@ -33895,9 +33895,9 @@
         <f>H27*2.54*10</f>
         <v>25.4</v>
       </c>
-      <c r="J27" s="983"/>
-      <c r="K27" s="984"/>
-      <c r="L27" s="985"/>
+      <c r="J27" s="985"/>
+      <c r="K27" s="986"/>
+      <c r="L27" s="987"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25"/>
       <c r="S27" s="42"/>
@@ -34065,11 +34065,11 @@
       <c r="U32" s="54"/>
     </row>
     <row r="33" spans="3:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="998"/>
-      <c r="D33" s="998"/>
-      <c r="E33" s="998"/>
-      <c r="F33" s="998"/>
-      <c r="G33" s="998"/>
+      <c r="C33" s="974"/>
+      <c r="D33" s="974"/>
+      <c r="E33" s="974"/>
+      <c r="F33" s="974"/>
+      <c r="G33" s="974"/>
       <c r="H33" s="54"/>
       <c r="I33" s="54"/>
       <c r="J33" s="54"/>
@@ -34097,20 +34097,22 @@
     <row r="35" spans="3:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="D7:F9"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="AB9:AD9"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="P9:R9"/>
-    <mergeCell ref="S8:U8"/>
-    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H6:AS6"/>
+    <mergeCell ref="H5:AS5"/>
+    <mergeCell ref="J25:L27"/>
+    <mergeCell ref="S26:U26"/>
+    <mergeCell ref="S7:U7"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="AH7:AJ7"/>
+    <mergeCell ref="AN7:AP7"/>
+    <mergeCell ref="AQ7:AS7"/>
+    <mergeCell ref="AN9:AP9"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ9:AS9"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AT8:AV8"/>
     <mergeCell ref="AT9:AV9"/>
     <mergeCell ref="AN8:AP8"/>
@@ -34127,22 +34129,20 @@
     <mergeCell ref="AK9:AM9"/>
     <mergeCell ref="V8:X8"/>
     <mergeCell ref="V9:X9"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H6:AS6"/>
-    <mergeCell ref="H5:AS5"/>
-    <mergeCell ref="J25:L27"/>
-    <mergeCell ref="S26:U26"/>
-    <mergeCell ref="S7:U7"/>
-    <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="AH7:AJ7"/>
-    <mergeCell ref="AN7:AP7"/>
-    <mergeCell ref="AQ7:AS7"/>
-    <mergeCell ref="AN9:AP9"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ9:AS9"/>
-    <mergeCell ref="Y8:AA8"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="AB8:AD8"/>
+    <mergeCell ref="AB9:AD9"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="S8:U8"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="D7:F9"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -34251,39 +34251,39 @@
       <c r="Z5" s="315"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="849" t="s">
+      <c r="A6" s="833" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="849"/>
-      <c r="C6" s="849"/>
-      <c r="D6" s="849"/>
-      <c r="E6" s="849"/>
-      <c r="F6" s="849"/>
-      <c r="G6" s="849"/>
-      <c r="H6" s="849"/>
-      <c r="I6" s="849"/>
-      <c r="J6" s="849"/>
-      <c r="K6" s="849"/>
-      <c r="L6" s="849"/>
-      <c r="M6" s="849"/>
+      <c r="B6" s="833"/>
+      <c r="C6" s="833"/>
+      <c r="D6" s="833"/>
+      <c r="E6" s="833"/>
+      <c r="F6" s="833"/>
+      <c r="G6" s="833"/>
+      <c r="H6" s="833"/>
+      <c r="I6" s="833"/>
+      <c r="J6" s="833"/>
+      <c r="K6" s="833"/>
+      <c r="L6" s="833"/>
+      <c r="M6" s="833"/>
       <c r="Z6" s="315"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="850">
+      <c r="A7" s="834">
         <v>1</v>
       </c>
-      <c r="B7" s="850"/>
-      <c r="C7" s="850"/>
-      <c r="D7" s="850"/>
-      <c r="E7" s="850"/>
-      <c r="F7" s="850"/>
-      <c r="G7" s="850"/>
-      <c r="H7" s="850"/>
-      <c r="I7" s="850"/>
-      <c r="J7" s="850"/>
-      <c r="K7" s="850"/>
-      <c r="L7" s="850"/>
-      <c r="M7" s="850"/>
+      <c r="B7" s="834"/>
+      <c r="C7" s="834"/>
+      <c r="D7" s="834"/>
+      <c r="E7" s="834"/>
+      <c r="F7" s="834"/>
+      <c r="G7" s="834"/>
+      <c r="H7" s="834"/>
+      <c r="I7" s="834"/>
+      <c r="J7" s="834"/>
+      <c r="K7" s="834"/>
+      <c r="L7" s="834"/>
+      <c r="M7" s="834"/>
     </row>
     <row r="8" spans="1:26" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34326,10 +34326,10 @@
       <c r="K10" s="285" t="s">
         <v>356</v>
       </c>
-      <c r="L10" s="851">
+      <c r="L10" s="835">
         <v>1</v>
       </c>
-      <c r="M10" s="851"/>
+      <c r="M10" s="835"/>
       <c r="N10" s="320"/>
       <c r="O10" s="320"/>
       <c r="P10" s="320"/>
@@ -34361,8 +34361,8 @@
       <c r="K11" s="285" t="s">
         <v>127</v>
       </c>
-      <c r="L11" s="847"/>
-      <c r="M11" s="847"/>
+      <c r="L11" s="836"/>
+      <c r="M11" s="836"/>
       <c r="N11" s="320"/>
       <c r="O11" s="320"/>
       <c r="P11" s="320"/>
@@ -34436,21 +34436,21 @@
       <c r="Y13" s="320"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="835" t="s">
+      <c r="A14" s="846" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="836"/>
-      <c r="C14" s="836"/>
-      <c r="D14" s="836"/>
-      <c r="E14" s="836"/>
-      <c r="F14" s="836"/>
-      <c r="G14" s="836"/>
-      <c r="H14" s="836"/>
-      <c r="I14" s="836"/>
-      <c r="J14" s="836"/>
-      <c r="K14" s="836"/>
-      <c r="L14" s="836"/>
-      <c r="M14" s="837"/>
+      <c r="B14" s="847"/>
+      <c r="C14" s="847"/>
+      <c r="D14" s="847"/>
+      <c r="E14" s="847"/>
+      <c r="F14" s="847"/>
+      <c r="G14" s="847"/>
+      <c r="H14" s="847"/>
+      <c r="I14" s="847"/>
+      <c r="J14" s="847"/>
+      <c r="K14" s="847"/>
+      <c r="L14" s="847"/>
+      <c r="M14" s="848"/>
       <c r="N14" s="320"/>
       <c r="O14" s="320"/>
       <c r="P14" s="320"/>
@@ -34465,21 +34465,21 @@
       <c r="Y14" s="320"/>
     </row>
     <row r="15" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="838" t="s">
+      <c r="A15" s="849" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="839"/>
-      <c r="C15" s="839"/>
-      <c r="D15" s="839"/>
-      <c r="E15" s="839"/>
-      <c r="F15" s="839"/>
-      <c r="G15" s="839"/>
-      <c r="H15" s="839"/>
-      <c r="I15" s="839"/>
-      <c r="J15" s="839"/>
-      <c r="K15" s="839"/>
-      <c r="L15" s="839"/>
-      <c r="M15" s="840"/>
+      <c r="B15" s="850"/>
+      <c r="C15" s="850"/>
+      <c r="D15" s="850"/>
+      <c r="E15" s="850"/>
+      <c r="F15" s="850"/>
+      <c r="G15" s="850"/>
+      <c r="H15" s="850"/>
+      <c r="I15" s="850"/>
+      <c r="J15" s="850"/>
+      <c r="K15" s="850"/>
+      <c r="L15" s="850"/>
+      <c r="M15" s="851"/>
       <c r="N15" s="320"/>
       <c r="O15" s="320"/>
       <c r="P15" s="320"/>
@@ -34554,10 +34554,10 @@
       <c r="K18" s="285" t="s">
         <v>153</v>
       </c>
-      <c r="L18" s="845">
+      <c r="L18" s="856">
         <v>1</v>
       </c>
-      <c r="M18" s="846"/>
+      <c r="M18" s="857"/>
       <c r="Y18" s="320"/>
     </row>
     <row r="19" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34576,8 +34576,8 @@
       <c r="K19" s="285" t="s">
         <v>125</v>
       </c>
-      <c r="L19" s="847"/>
-      <c r="M19" s="848"/>
+      <c r="L19" s="836"/>
+      <c r="M19" s="858"/>
       <c r="Y19" s="320"/>
     </row>
     <row r="20" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34596,8 +34596,8 @@
       <c r="K20" s="285" t="s">
         <v>126</v>
       </c>
-      <c r="L20" s="847"/>
-      <c r="M20" s="848"/>
+      <c r="L20" s="836"/>
+      <c r="M20" s="858"/>
       <c r="Y20" s="320"/>
     </row>
     <row r="21" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34652,24 +34652,24 @@
       <c r="A23" s="356"/>
       <c r="B23" s="364"/>
       <c r="C23" s="364"/>
-      <c r="D23" s="841" t="s">
+      <c r="D23" s="852" t="s">
         <v>353</v>
       </c>
-      <c r="E23" s="842"/>
-      <c r="F23" s="833" t="s">
+      <c r="E23" s="853"/>
+      <c r="F23" s="843" t="s">
         <v>276</v>
       </c>
-      <c r="G23" s="833" t="s">
+      <c r="G23" s="843" t="s">
         <v>346</v>
       </c>
-      <c r="H23" s="833" t="s">
+      <c r="H23" s="843" t="s">
         <v>275</v>
       </c>
       <c r="I23" s="337"/>
-      <c r="J23" s="853" t="s">
+      <c r="J23" s="838" t="s">
         <v>146</v>
       </c>
-      <c r="K23" s="854"/>
+      <c r="K23" s="839"/>
       <c r="L23" s="497"/>
       <c r="M23" s="357"/>
       <c r="N23" s="320"/>
@@ -34684,11 +34684,11 @@
       <c r="W23" s="320"/>
       <c r="X23" s="320"/>
       <c r="Y23" s="332"/>
-      <c r="AA23" s="843" t="s">
+      <c r="AA23" s="854" t="s">
         <v>278</v>
       </c>
-      <c r="AB23" s="844"/>
-      <c r="AC23" s="833" t="s">
+      <c r="AB23" s="855"/>
+      <c r="AC23" s="843" t="s">
         <v>275</v>
       </c>
     </row>
@@ -34702,12 +34702,12 @@
       <c r="E24" s="500" t="s">
         <v>380</v>
       </c>
-      <c r="F24" s="834"/>
-      <c r="G24" s="834"/>
-      <c r="H24" s="834"/>
+      <c r="F24" s="844"/>
+      <c r="G24" s="844"/>
+      <c r="H24" s="844"/>
       <c r="I24" s="337"/>
-      <c r="J24" s="855"/>
-      <c r="K24" s="856"/>
+      <c r="J24" s="840"/>
+      <c r="K24" s="841"/>
       <c r="L24" s="497"/>
       <c r="M24" s="358"/>
       <c r="N24" s="320"/>
@@ -34728,7 +34728,7 @@
       <c r="AB24" s="380" t="s">
         <v>12</v>
       </c>
-      <c r="AC24" s="834"/>
+      <c r="AC24" s="844"/>
     </row>
     <row r="25" spans="1:29" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="356"/>
@@ -35136,7 +35136,7 @@
       <c r="J32" s="298"/>
       <c r="K32" s="298"/>
       <c r="L32" s="298"/>
-      <c r="M32" s="858"/>
+      <c r="M32" s="845"/>
       <c r="N32" s="320"/>
       <c r="O32" s="320"/>
       <c r="P32" s="320"/>
@@ -35186,7 +35186,7 @@
       <c r="J33" s="298"/>
       <c r="K33" s="298"/>
       <c r="L33" s="298"/>
-      <c r="M33" s="858"/>
+      <c r="M33" s="845"/>
       <c r="N33" s="320"/>
       <c r="O33" s="320"/>
       <c r="P33" s="320"/>
@@ -36048,21 +36048,21 @@
       <c r="Z59" s="480"/>
     </row>
     <row r="60" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="857" t="s">
+      <c r="A60" s="842" t="s">
         <v>296</v>
       </c>
-      <c r="B60" s="857"/>
-      <c r="C60" s="857"/>
-      <c r="D60" s="857"/>
-      <c r="E60" s="857"/>
-      <c r="F60" s="857"/>
-      <c r="G60" s="857"/>
-      <c r="H60" s="857"/>
-      <c r="I60" s="857"/>
-      <c r="J60" s="857"/>
-      <c r="K60" s="857"/>
-      <c r="L60" s="857"/>
-      <c r="M60" s="857"/>
+      <c r="B60" s="842"/>
+      <c r="C60" s="842"/>
+      <c r="D60" s="842"/>
+      <c r="E60" s="842"/>
+      <c r="F60" s="842"/>
+      <c r="G60" s="842"/>
+      <c r="H60" s="842"/>
+      <c r="I60" s="842"/>
+      <c r="J60" s="842"/>
+      <c r="K60" s="842"/>
+      <c r="L60" s="842"/>
+      <c r="M60" s="842"/>
       <c r="N60" s="483"/>
       <c r="O60" s="483"/>
       <c r="P60" s="483"/>
@@ -36108,21 +36108,21 @@
       <c r="Z61" s="480"/>
     </row>
     <row r="62" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="857" t="s">
+      <c r="A62" s="842" t="s">
         <v>355</v>
       </c>
-      <c r="B62" s="857"/>
-      <c r="C62" s="857"/>
-      <c r="D62" s="857"/>
-      <c r="E62" s="857"/>
-      <c r="F62" s="857"/>
-      <c r="G62" s="857"/>
-      <c r="H62" s="857"/>
-      <c r="I62" s="857"/>
-      <c r="J62" s="857"/>
-      <c r="K62" s="857"/>
-      <c r="L62" s="857"/>
-      <c r="M62" s="857"/>
+      <c r="B62" s="842"/>
+      <c r="C62" s="842"/>
+      <c r="D62" s="842"/>
+      <c r="E62" s="842"/>
+      <c r="F62" s="842"/>
+      <c r="G62" s="842"/>
+      <c r="H62" s="842"/>
+      <c r="I62" s="842"/>
+      <c r="J62" s="842"/>
+      <c r="K62" s="842"/>
+      <c r="L62" s="842"/>
+      <c r="M62" s="842"/>
       <c r="N62" s="319"/>
       <c r="O62" s="319"/>
       <c r="P62" s="319"/>
@@ -36193,12 +36193,12 @@
       <c r="Z64" s="482"/>
     </row>
     <row r="65" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="852" t="s">
+      <c r="A65" s="837" t="s">
         <v>362</v>
       </c>
-      <c r="B65" s="852"/>
-      <c r="C65" s="852"/>
-      <c r="D65" s="852"/>
+      <c r="B65" s="837"/>
+      <c r="C65" s="837"/>
+      <c r="D65" s="837"/>
       <c r="E65" s="337"/>
       <c r="F65" s="337"/>
       <c r="G65" s="337"/>
@@ -36280,6 +36280,15 @@
     <protectedRange sqref="D9:D10" name="Rango3_3_1_1_1_1_1_2_1_1_1"/>
   </protectedRanges>
   <mergeCells count="20">
+    <mergeCell ref="AC23:AC24"/>
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
     <mergeCell ref="A6:M6"/>
     <mergeCell ref="A7:M7"/>
     <mergeCell ref="L10:M10"/>
@@ -36291,15 +36300,6 @@
     <mergeCell ref="H23:H24"/>
     <mergeCell ref="A62:M62"/>
     <mergeCell ref="M32:M33"/>
-    <mergeCell ref="AC23:AC24"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -36407,37 +36407,37 @@
       <c r="Y5" s="315"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="849" t="s">
+      <c r="A6" s="833" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="849"/>
-      <c r="C6" s="849"/>
-      <c r="D6" s="849"/>
-      <c r="E6" s="849"/>
-      <c r="F6" s="849"/>
-      <c r="G6" s="849"/>
-      <c r="H6" s="849"/>
-      <c r="I6" s="849"/>
-      <c r="J6" s="849"/>
-      <c r="K6" s="849"/>
-      <c r="L6" s="849"/>
+      <c r="B6" s="833"/>
+      <c r="C6" s="833"/>
+      <c r="D6" s="833"/>
+      <c r="E6" s="833"/>
+      <c r="F6" s="833"/>
+      <c r="G6" s="833"/>
+      <c r="H6" s="833"/>
+      <c r="I6" s="833"/>
+      <c r="J6" s="833"/>
+      <c r="K6" s="833"/>
+      <c r="L6" s="833"/>
       <c r="Y6" s="315"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="867">
+      <c r="A7" s="859">
         <v>1</v>
       </c>
-      <c r="B7" s="867"/>
-      <c r="C7" s="867"/>
-      <c r="D7" s="867"/>
-      <c r="E7" s="867"/>
-      <c r="F7" s="867"/>
-      <c r="G7" s="867"/>
-      <c r="H7" s="867"/>
-      <c r="I7" s="867"/>
-      <c r="J7" s="867"/>
-      <c r="K7" s="867"/>
-      <c r="L7" s="867"/>
+      <c r="B7" s="859"/>
+      <c r="C7" s="859"/>
+      <c r="D7" s="859"/>
+      <c r="E7" s="859"/>
+      <c r="F7" s="859"/>
+      <c r="G7" s="859"/>
+      <c r="H7" s="859"/>
+      <c r="I7" s="859"/>
+      <c r="J7" s="859"/>
+      <c r="K7" s="859"/>
+      <c r="L7" s="859"/>
     </row>
     <row r="8" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36608,20 +36608,20 @@
       <c r="X13" s="320"/>
     </row>
     <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="835" t="s">
+      <c r="A14" s="846" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="836"/>
-      <c r="C14" s="836"/>
-      <c r="D14" s="836"/>
-      <c r="E14" s="836"/>
-      <c r="F14" s="836"/>
-      <c r="G14" s="836"/>
-      <c r="H14" s="836"/>
-      <c r="I14" s="836"/>
-      <c r="J14" s="836"/>
-      <c r="K14" s="836"/>
-      <c r="L14" s="837"/>
+      <c r="B14" s="847"/>
+      <c r="C14" s="847"/>
+      <c r="D14" s="847"/>
+      <c r="E14" s="847"/>
+      <c r="F14" s="847"/>
+      <c r="G14" s="847"/>
+      <c r="H14" s="847"/>
+      <c r="I14" s="847"/>
+      <c r="J14" s="847"/>
+      <c r="K14" s="847"/>
+      <c r="L14" s="848"/>
       <c r="M14" s="320"/>
       <c r="N14" s="320"/>
       <c r="O14" s="320"/>
@@ -36636,20 +36636,20 @@
       <c r="X14" s="320"/>
     </row>
     <row r="15" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="838" t="s">
+      <c r="A15" s="849" t="s">
         <v>466</v>
       </c>
-      <c r="B15" s="839"/>
-      <c r="C15" s="839"/>
-      <c r="D15" s="839"/>
-      <c r="E15" s="839"/>
-      <c r="F15" s="839"/>
-      <c r="G15" s="839"/>
-      <c r="H15" s="839"/>
-      <c r="I15" s="839"/>
-      <c r="J15" s="839"/>
-      <c r="K15" s="839"/>
-      <c r="L15" s="840"/>
+      <c r="B15" s="850"/>
+      <c r="C15" s="850"/>
+      <c r="D15" s="850"/>
+      <c r="E15" s="850"/>
+      <c r="F15" s="850"/>
+      <c r="G15" s="850"/>
+      <c r="H15" s="850"/>
+      <c r="I15" s="850"/>
+      <c r="J15" s="850"/>
+      <c r="K15" s="850"/>
+      <c r="L15" s="851"/>
       <c r="M15" s="320"/>
       <c r="N15" s="320"/>
       <c r="O15" s="320"/>
@@ -36835,30 +36835,30 @@
       <c r="A23" s="356"/>
       <c r="B23" s="364"/>
       <c r="C23" s="364"/>
-      <c r="D23" s="841" t="s">
+      <c r="D23" s="852" t="s">
         <v>353</v>
       </c>
-      <c r="E23" s="842"/>
-      <c r="F23" s="833" t="s">
+      <c r="E23" s="853"/>
+      <c r="F23" s="843" t="s">
         <v>276</v>
       </c>
-      <c r="G23" s="833" t="s">
+      <c r="G23" s="843" t="s">
         <v>346</v>
       </c>
-      <c r="H23" s="833" t="s">
+      <c r="H23" s="843" t="s">
         <v>275</v>
       </c>
       <c r="I23" s="337"/>
-      <c r="J23" s="853" t="s">
+      <c r="J23" s="838" t="s">
         <v>146</v>
       </c>
-      <c r="K23" s="854"/>
+      <c r="K23" s="839"/>
       <c r="L23" s="651"/>
       <c r="M23" s="320"/>
-      <c r="N23" s="853" t="s">
+      <c r="N23" s="838" t="s">
         <v>146</v>
       </c>
-      <c r="O23" s="854"/>
+      <c r="O23" s="839"/>
       <c r="P23" s="320"/>
       <c r="Q23" s="320"/>
       <c r="R23" s="320"/>
@@ -36868,11 +36868,11 @@
       <c r="V23" s="320"/>
       <c r="W23" s="320"/>
       <c r="X23" s="332"/>
-      <c r="Z23" s="843" t="s">
+      <c r="Z23" s="854" t="s">
         <v>278</v>
       </c>
-      <c r="AA23" s="844"/>
-      <c r="AB23" s="833" t="s">
+      <c r="AA23" s="855"/>
+      <c r="AB23" s="843" t="s">
         <v>275</v>
       </c>
     </row>
@@ -36886,16 +36886,16 @@
       <c r="E24" s="500" t="s">
         <v>380</v>
       </c>
-      <c r="F24" s="834"/>
-      <c r="G24" s="834"/>
-      <c r="H24" s="834"/>
+      <c r="F24" s="844"/>
+      <c r="G24" s="844"/>
+      <c r="H24" s="844"/>
       <c r="I24" s="337"/>
-      <c r="J24" s="855"/>
-      <c r="K24" s="856"/>
+      <c r="J24" s="840"/>
+      <c r="K24" s="841"/>
       <c r="L24" s="651"/>
       <c r="M24" s="320"/>
-      <c r="N24" s="855"/>
-      <c r="O24" s="856"/>
+      <c r="N24" s="840"/>
+      <c r="O24" s="841"/>
       <c r="P24" s="320"/>
       <c r="Q24" s="320"/>
       <c r="R24" s="320"/>
@@ -36911,7 +36911,7 @@
       <c r="AA24" s="380" t="s">
         <v>12</v>
       </c>
-      <c r="AB24" s="834"/>
+      <c r="AB24" s="844"/>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="356"/>
@@ -36936,10 +36936,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I25" s="337"/>
-      <c r="J25" s="860" t="s">
+      <c r="J25" s="861" t="s">
         <v>381</v>
       </c>
-      <c r="K25" s="863" t="e">
+      <c r="K25" s="864" t="e">
         <f>+datos!I21</f>
         <v>#DIV/0!</v>
       </c>
@@ -36995,8 +36995,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I26" s="337"/>
-      <c r="J26" s="861"/>
-      <c r="K26" s="864"/>
+      <c r="J26" s="862"/>
+      <c r="K26" s="865"/>
       <c r="L26" s="652"/>
       <c r="M26" s="320"/>
       <c r="N26" s="360" t="s">
@@ -37049,8 +37049,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="337"/>
-      <c r="J27" s="862"/>
-      <c r="K27" s="865"/>
+      <c r="J27" s="863"/>
+      <c r="K27" s="866"/>
       <c r="L27" s="648"/>
       <c r="M27" s="320"/>
       <c r="N27" s="360" t="s">
@@ -38150,37 +38150,37 @@
       <c r="Y57" s="386"/>
     </row>
     <row r="58" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="866" t="s">
+      <c r="A58" s="867" t="s">
         <v>467</v>
       </c>
-      <c r="B58" s="866"/>
-      <c r="C58" s="866"/>
-      <c r="D58" s="866"/>
-      <c r="E58" s="866"/>
-      <c r="F58" s="866"/>
-      <c r="G58" s="866"/>
-      <c r="H58" s="866"/>
-      <c r="I58" s="866"/>
-      <c r="J58" s="866"/>
-      <c r="K58" s="866"/>
-      <c r="L58" s="866"/>
+      <c r="B58" s="867"/>
+      <c r="C58" s="867"/>
+      <c r="D58" s="867"/>
+      <c r="E58" s="867"/>
+      <c r="F58" s="867"/>
+      <c r="G58" s="867"/>
+      <c r="H58" s="867"/>
+      <c r="I58" s="867"/>
+      <c r="J58" s="867"/>
+      <c r="K58" s="867"/>
+      <c r="L58" s="867"/>
       <c r="Y58" s="386"/>
     </row>
     <row r="59" spans="1:25" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="859" t="s">
+      <c r="A59" s="860" t="s">
         <v>468</v>
       </c>
-      <c r="B59" s="859"/>
-      <c r="C59" s="859"/>
-      <c r="D59" s="859"/>
-      <c r="E59" s="859"/>
-      <c r="F59" s="859"/>
-      <c r="G59" s="859"/>
-      <c r="H59" s="859"/>
-      <c r="I59" s="859"/>
-      <c r="J59" s="859"/>
-      <c r="K59" s="859"/>
-      <c r="L59" s="859"/>
+      <c r="B59" s="860"/>
+      <c r="C59" s="860"/>
+      <c r="D59" s="860"/>
+      <c r="E59" s="860"/>
+      <c r="F59" s="860"/>
+      <c r="G59" s="860"/>
+      <c r="H59" s="860"/>
+      <c r="I59" s="860"/>
+      <c r="J59" s="860"/>
+      <c r="K59" s="860"/>
+      <c r="L59" s="860"/>
       <c r="M59" s="319"/>
       <c r="N59" s="319"/>
       <c r="O59" s="319"/>
@@ -38196,20 +38196,20 @@
       <c r="Y59" s="480"/>
     </row>
     <row r="60" spans="1:25" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="859" t="s">
+      <c r="A60" s="860" t="s">
         <v>469</v>
       </c>
-      <c r="B60" s="859"/>
-      <c r="C60" s="859"/>
-      <c r="D60" s="859"/>
-      <c r="E60" s="859"/>
-      <c r="F60" s="859"/>
-      <c r="G60" s="859"/>
-      <c r="H60" s="859"/>
-      <c r="I60" s="859"/>
-      <c r="J60" s="859"/>
-      <c r="K60" s="859"/>
-      <c r="L60" s="859"/>
+      <c r="B60" s="860"/>
+      <c r="C60" s="860"/>
+      <c r="D60" s="860"/>
+      <c r="E60" s="860"/>
+      <c r="F60" s="860"/>
+      <c r="G60" s="860"/>
+      <c r="H60" s="860"/>
+      <c r="I60" s="860"/>
+      <c r="J60" s="860"/>
+      <c r="K60" s="860"/>
+      <c r="L60" s="860"/>
       <c r="M60" s="483"/>
       <c r="N60" s="483"/>
       <c r="O60" s="483"/>
@@ -38225,20 +38225,20 @@
       <c r="Y60" s="483"/>
     </row>
     <row r="61" spans="1:25" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="859" t="s">
+      <c r="A61" s="860" t="s">
         <v>470</v>
       </c>
-      <c r="B61" s="859"/>
-      <c r="C61" s="859"/>
-      <c r="D61" s="859"/>
-      <c r="E61" s="859"/>
-      <c r="F61" s="859"/>
-      <c r="G61" s="859"/>
-      <c r="H61" s="859"/>
-      <c r="I61" s="859"/>
-      <c r="J61" s="859"/>
-      <c r="K61" s="859"/>
-      <c r="L61" s="859"/>
+      <c r="B61" s="860"/>
+      <c r="C61" s="860"/>
+      <c r="D61" s="860"/>
+      <c r="E61" s="860"/>
+      <c r="F61" s="860"/>
+      <c r="G61" s="860"/>
+      <c r="H61" s="860"/>
+      <c r="I61" s="860"/>
+      <c r="J61" s="860"/>
+      <c r="K61" s="860"/>
+      <c r="L61" s="860"/>
       <c r="M61" s="319"/>
       <c r="N61" s="319"/>
       <c r="O61" s="319"/>
@@ -38254,20 +38254,20 @@
       <c r="Y61" s="480"/>
     </row>
     <row r="62" spans="1:25" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="857" t="s">
+      <c r="A62" s="842" t="s">
         <v>471</v>
       </c>
-      <c r="B62" s="857"/>
-      <c r="C62" s="857"/>
-      <c r="D62" s="857"/>
-      <c r="E62" s="857"/>
-      <c r="F62" s="857"/>
-      <c r="G62" s="857"/>
-      <c r="H62" s="857"/>
-      <c r="I62" s="857"/>
-      <c r="J62" s="857"/>
-      <c r="K62" s="857"/>
-      <c r="L62" s="857"/>
+      <c r="B62" s="842"/>
+      <c r="C62" s="842"/>
+      <c r="D62" s="842"/>
+      <c r="E62" s="842"/>
+      <c r="F62" s="842"/>
+      <c r="G62" s="842"/>
+      <c r="H62" s="842"/>
+      <c r="I62" s="842"/>
+      <c r="J62" s="842"/>
+      <c r="K62" s="842"/>
+      <c r="L62" s="842"/>
       <c r="M62" s="319"/>
       <c r="N62" s="319"/>
       <c r="O62" s="319"/>
@@ -38337,12 +38337,12 @@
       <c r="Y64" s="482"/>
     </row>
     <row r="65" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="852" t="s">
+      <c r="A65" s="837" t="s">
         <v>472</v>
       </c>
-      <c r="B65" s="852"/>
-      <c r="C65" s="852"/>
-      <c r="D65" s="852"/>
+      <c r="B65" s="837"/>
+      <c r="C65" s="837"/>
+      <c r="D65" s="837"/>
       <c r="E65" s="337"/>
       <c r="F65" s="337"/>
       <c r="G65" s="337"/>
@@ -38420,11 +38420,6 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="20">
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="Z23:AA23"/>
     <mergeCell ref="AB23:AB24"/>
     <mergeCell ref="A60:L60"/>
     <mergeCell ref="A62:L62"/>
@@ -38440,6 +38435,11 @@
     <mergeCell ref="A61:L61"/>
     <mergeCell ref="A59:L59"/>
     <mergeCell ref="A58:L58"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="Z23:AA23"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0" footer="0"/>
@@ -38469,35 +38469,35 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="470"/>
-      <c r="B1" s="835" t="s">
+      <c r="B1" s="846" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="836"/>
-      <c r="D1" s="836"/>
-      <c r="E1" s="836"/>
-      <c r="F1" s="836"/>
-      <c r="G1" s="836"/>
-      <c r="H1" s="836"/>
-      <c r="I1" s="836"/>
-      <c r="J1" s="836"/>
-      <c r="K1" s="836"/>
-      <c r="L1" s="837"/>
+      <c r="C1" s="847"/>
+      <c r="D1" s="847"/>
+      <c r="E1" s="847"/>
+      <c r="F1" s="847"/>
+      <c r="G1" s="847"/>
+      <c r="H1" s="847"/>
+      <c r="I1" s="847"/>
+      <c r="J1" s="847"/>
+      <c r="K1" s="847"/>
+      <c r="L1" s="848"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="470"/>
-      <c r="B2" s="838" t="s">
+      <c r="B2" s="849" t="s">
         <v>383</v>
       </c>
-      <c r="C2" s="839"/>
-      <c r="D2" s="839"/>
-      <c r="E2" s="839"/>
-      <c r="F2" s="839"/>
-      <c r="G2" s="839"/>
-      <c r="H2" s="839"/>
-      <c r="I2" s="839"/>
-      <c r="J2" s="839"/>
-      <c r="K2" s="839"/>
-      <c r="L2" s="840"/>
+      <c r="C2" s="850"/>
+      <c r="D2" s="850"/>
+      <c r="E2" s="850"/>
+      <c r="F2" s="850"/>
+      <c r="G2" s="850"/>
+      <c r="H2" s="850"/>
+      <c r="I2" s="850"/>
+      <c r="J2" s="850"/>
+      <c r="K2" s="850"/>
+      <c r="L2" s="851"/>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="470"/>
@@ -38765,7 +38765,7 @@
         <v>285</v>
       </c>
       <c r="H15" s="538">
-        <f>+IF(C11="Global",FORMATO!D22,FORMATO!D36)</f>
+        <f>+IF(C10="Global",FORMATO!D22,FORMATO!D36)</f>
         <v>0</v>
       </c>
       <c r="I15" s="444">
@@ -40333,7 +40333,7 @@
     <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TNSh9Anr1QAwo+Wu7s6k6M95M9SOg/Gy/xVzI3YskQB47xYzcUrVU9oMmMALZnEQFevVwRVapT4xI+pocclfog==" saltValue="QcweydN+0uFY4Pu1YTEyCA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PhSjsJrvoH6nY17GGGXQbM6919a0pS0xFYS8BjkTuVmW528wUwejdzF3ex+AFMUD6QoE8jLqA43PhA/Jz5a1lw==" saltValue="q1DYuEWj9QoKvOAlnxc1DA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="C47:E47"/>
     <mergeCell ref="C61:D61"/>
@@ -47945,35 +47945,35 @@
       <c r="K4" s="87"/>
     </row>
     <row r="5" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="920" t="s">
+      <c r="A5" s="932" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="920"/>
-      <c r="C5" s="920"/>
-      <c r="D5" s="920"/>
-      <c r="E5" s="920"/>
-      <c r="F5" s="920"/>
-      <c r="G5" s="920"/>
-      <c r="H5" s="920"/>
-      <c r="I5" s="920"/>
-      <c r="J5" s="920"/>
-      <c r="K5" s="920"/>
+      <c r="B5" s="932"/>
+      <c r="C5" s="932"/>
+      <c r="D5" s="932"/>
+      <c r="E5" s="932"/>
+      <c r="F5" s="932"/>
+      <c r="G5" s="932"/>
+      <c r="H5" s="932"/>
+      <c r="I5" s="932"/>
+      <c r="J5" s="932"/>
+      <c r="K5" s="932"/>
     </row>
     <row r="6" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="927">
+      <c r="A6" s="939">
         <f>+K12</f>
         <v>32</v>
       </c>
-      <c r="B6" s="927"/>
-      <c r="C6" s="927"/>
-      <c r="D6" s="927"/>
-      <c r="E6" s="927"/>
-      <c r="F6" s="927"/>
-      <c r="G6" s="927"/>
-      <c r="H6" s="927"/>
-      <c r="I6" s="927"/>
-      <c r="J6" s="927"/>
-      <c r="K6" s="927"/>
+      <c r="B6" s="939"/>
+      <c r="C6" s="939"/>
+      <c r="D6" s="939"/>
+      <c r="E6" s="939"/>
+      <c r="F6" s="939"/>
+      <c r="G6" s="939"/>
+      <c r="H6" s="939"/>
+      <c r="I6" s="939"/>
+      <c r="J6" s="939"/>
+      <c r="K6" s="939"/>
       <c r="S6" s="259" t="s">
         <v>101</v>
       </c>
@@ -48050,10 +48050,10 @@
       <c r="S9" s="275" t="s">
         <v>105</v>
       </c>
-      <c r="T9" s="931">
+      <c r="T9" s="943">
         <v>44090</v>
       </c>
-      <c r="U9" s="931"/>
+      <c r="U9" s="943"/>
       <c r="V9" s="276"/>
       <c r="W9" s="277"/>
       <c r="X9" s="276"/>
@@ -48198,19 +48198,19 @@
       <c r="S13" s="86"/>
     </row>
     <row r="14" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="928" t="s">
+      <c r="A14" s="940" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="929"/>
-      <c r="C14" s="929"/>
-      <c r="D14" s="929"/>
-      <c r="E14" s="929"/>
-      <c r="F14" s="929"/>
-      <c r="G14" s="929"/>
-      <c r="H14" s="929"/>
-      <c r="I14" s="929"/>
-      <c r="J14" s="929"/>
-      <c r="K14" s="930"/>
+      <c r="B14" s="941"/>
+      <c r="C14" s="941"/>
+      <c r="D14" s="941"/>
+      <c r="E14" s="941"/>
+      <c r="F14" s="941"/>
+      <c r="G14" s="941"/>
+      <c r="H14" s="941"/>
+      <c r="I14" s="941"/>
+      <c r="J14" s="941"/>
+      <c r="K14" s="942"/>
       <c r="L14" s="87"/>
       <c r="M14" s="87"/>
       <c r="P14" s="86"/>
@@ -48219,19 +48219,19 @@
       <c r="S14" s="86"/>
     </row>
     <row r="15" spans="1:31" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="935" t="s">
+      <c r="A15" s="947" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="936"/>
-      <c r="C15" s="936"/>
-      <c r="D15" s="936"/>
-      <c r="E15" s="936"/>
-      <c r="F15" s="936"/>
-      <c r="G15" s="936"/>
-      <c r="H15" s="936"/>
-      <c r="I15" s="936"/>
-      <c r="J15" s="936"/>
-      <c r="K15" s="937"/>
+      <c r="B15" s="948"/>
+      <c r="C15" s="948"/>
+      <c r="D15" s="948"/>
+      <c r="E15" s="948"/>
+      <c r="F15" s="948"/>
+      <c r="G15" s="948"/>
+      <c r="H15" s="948"/>
+      <c r="I15" s="948"/>
+      <c r="J15" s="948"/>
+      <c r="K15" s="949"/>
       <c r="L15" s="87"/>
       <c r="M15" s="87"/>
       <c r="P15" s="86"/>
@@ -48259,17 +48259,17 @@
       <c r="S16" s="86"/>
     </row>
     <row r="17" spans="1:27" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="925" t="s">
+      <c r="A17" s="937" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="926"/>
-      <c r="C17" s="926"/>
-      <c r="D17" s="926"/>
-      <c r="E17" s="926"/>
-      <c r="F17" s="926"/>
-      <c r="G17" s="926"/>
-      <c r="H17" s="926"/>
-      <c r="I17" s="926"/>
+      <c r="B17" s="938"/>
+      <c r="C17" s="938"/>
+      <c r="D17" s="938"/>
+      <c r="E17" s="938"/>
+      <c r="F17" s="938"/>
+      <c r="G17" s="938"/>
+      <c r="H17" s="938"/>
+      <c r="I17" s="938"/>
       <c r="J17" s="1"/>
       <c r="K17" s="199"/>
       <c r="L17" s="87"/>
@@ -48337,23 +48337,23 @@
       <c r="Q19" s="86"/>
       <c r="R19" s="86"/>
       <c r="S19" s="86"/>
-      <c r="U19" s="939" t="s">
+      <c r="U19" s="920" t="s">
         <v>9</v>
       </c>
-      <c r="V19" s="940"/>
-      <c r="W19" s="919" t="s">
+      <c r="V19" s="921"/>
+      <c r="W19" s="931" t="s">
         <v>100</v>
       </c>
-      <c r="X19" s="833" t="s">
+      <c r="X19" s="843" t="s">
         <v>45</v>
       </c>
-      <c r="Y19" s="833" t="s">
+      <c r="Y19" s="843" t="s">
         <v>41</v>
       </c>
-      <c r="Z19" s="833" t="s">
+      <c r="Z19" s="843" t="s">
         <v>42</v>
       </c>
-      <c r="AA19" s="833" t="s">
+      <c r="AA19" s="843" t="s">
         <v>43</v>
       </c>
     </row>
@@ -48391,11 +48391,11 @@
       <c r="V20" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="W20" s="919"/>
-      <c r="X20" s="834"/>
-      <c r="Y20" s="834"/>
-      <c r="Z20" s="834"/>
-      <c r="AA20" s="834"/>
+      <c r="W20" s="931"/>
+      <c r="X20" s="844"/>
+      <c r="Y20" s="844"/>
+      <c r="Z20" s="844"/>
+      <c r="AA20" s="844"/>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="288" t="s">
@@ -48488,27 +48488,27 @@
     </row>
     <row r="23" spans="1:27" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="140"/>
-      <c r="B23" s="939" t="s">
+      <c r="B23" s="920" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="940"/>
-      <c r="D23" s="833" t="s">
+      <c r="C23" s="921"/>
+      <c r="D23" s="843" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="833" t="s">
+      <c r="E23" s="843" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="833" t="s">
+      <c r="F23" s="843" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="833" t="s">
+      <c r="G23" s="843" t="s">
         <v>43</v>
       </c>
       <c r="H23" s="138"/>
-      <c r="I23" s="944" t="s">
+      <c r="I23" s="925" t="s">
         <v>36</v>
       </c>
-      <c r="J23" s="945"/>
+      <c r="J23" s="926"/>
       <c r="K23" s="139"/>
       <c r="L23" s="91"/>
       <c r="M23" s="91"/>
@@ -48549,16 +48549,16 @@
       <c r="C24" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="834"/>
-      <c r="E24" s="834"/>
-      <c r="F24" s="834"/>
-      <c r="G24" s="834"/>
+      <c r="D24" s="844"/>
+      <c r="E24" s="844"/>
+      <c r="F24" s="844"/>
+      <c r="G24" s="844"/>
       <c r="H24" s="156"/>
-      <c r="I24" s="947">
+      <c r="I24" s="928">
         <f>+Q23</f>
         <v>23983.979695431473</v>
       </c>
-      <c r="J24" s="948"/>
+      <c r="J24" s="929"/>
       <c r="K24" s="139"/>
       <c r="L24" s="91"/>
       <c r="M24" s="91"/>
@@ -48672,10 +48672,10 @@
       </c>
       <c r="G26" s="97"/>
       <c r="H26" s="142"/>
-      <c r="I26" s="946" t="s">
+      <c r="I26" s="927" t="s">
         <v>92</v>
       </c>
-      <c r="J26" s="946"/>
+      <c r="J26" s="927"/>
       <c r="K26" s="143"/>
       <c r="L26" s="91"/>
       <c r="M26" s="91"/>
@@ -48926,16 +48926,16 @@
         <v>57.746817294661284</v>
       </c>
       <c r="H30" s="142"/>
-      <c r="I30" s="924"/>
-      <c r="J30" s="924"/>
+      <c r="I30" s="936"/>
+      <c r="J30" s="936"/>
       <c r="K30" s="143"/>
       <c r="L30" s="91"/>
-      <c r="M30" s="932" t="s">
+      <c r="M30" s="944" t="s">
         <v>74</v>
       </c>
-      <c r="N30" s="933"/>
-      <c r="O30" s="933"/>
-      <c r="P30" s="934"/>
+      <c r="N30" s="945"/>
+      <c r="O30" s="945"/>
+      <c r="P30" s="946"/>
       <c r="T30" s="99"/>
       <c r="U30" s="93" t="s">
         <v>88</v>
@@ -48988,16 +48988,16 @@
         <v>38.462771103509866</v>
       </c>
       <c r="H31" s="142"/>
-      <c r="I31" s="924"/>
-      <c r="J31" s="924"/>
+      <c r="I31" s="936"/>
+      <c r="J31" s="936"/>
       <c r="K31" s="143"/>
       <c r="L31" s="91"/>
-      <c r="M31" s="921" t="s">
+      <c r="M31" s="933" t="s">
         <v>82</v>
       </c>
-      <c r="N31" s="922"/>
-      <c r="O31" s="922"/>
-      <c r="P31" s="923"/>
+      <c r="N31" s="934"/>
+      <c r="O31" s="934"/>
+      <c r="P31" s="935"/>
       <c r="T31" s="99"/>
       <c r="U31" s="147" t="s">
         <v>90</v>
@@ -49162,11 +49162,11 @@
         <f t="shared" ref="U34:U42" si="10">+T34</f>
         <v>25.4</v>
       </c>
-      <c r="Z34" s="941" t="s">
+      <c r="Z34" s="922" t="s">
         <v>89</v>
       </c>
-      <c r="AA34" s="942"/>
-      <c r="AB34" s="942"/>
+      <c r="AA34" s="923"/>
+      <c r="AB34" s="923"/>
     </row>
     <row r="35" spans="1:28" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="140"/>
@@ -49730,14 +49730,14 @@
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="943"/>
-      <c r="E57" s="943"/>
-      <c r="F57" s="943"/>
-      <c r="G57" s="943"/>
-      <c r="H57" s="943"/>
-      <c r="I57" s="943"/>
-      <c r="J57" s="943"/>
-      <c r="K57" s="943"/>
+      <c r="D57" s="924"/>
+      <c r="E57" s="924"/>
+      <c r="F57" s="924"/>
+      <c r="G57" s="924"/>
+      <c r="H57" s="924"/>
+      <c r="I57" s="924"/>
+      <c r="J57" s="924"/>
+      <c r="K57" s="924"/>
       <c r="M57" s="91"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
@@ -49803,19 +49803,19 @@
       <c r="W59" s="4"/>
     </row>
     <row r="60" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="949" t="s">
+      <c r="A60" s="930" t="s">
         <v>122</v>
       </c>
-      <c r="B60" s="949"/>
-      <c r="C60" s="949"/>
-      <c r="D60" s="949"/>
-      <c r="E60" s="949"/>
-      <c r="F60" s="949"/>
-      <c r="G60" s="949"/>
-      <c r="H60" s="949"/>
-      <c r="I60" s="949"/>
-      <c r="J60" s="949"/>
-      <c r="K60" s="949"/>
+      <c r="B60" s="930"/>
+      <c r="C60" s="930"/>
+      <c r="D60" s="930"/>
+      <c r="E60" s="930"/>
+      <c r="F60" s="930"/>
+      <c r="G60" s="930"/>
+      <c r="H60" s="930"/>
+      <c r="I60" s="930"/>
+      <c r="J60" s="930"/>
+      <c r="K60" s="930"/>
       <c r="M60" s="91"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
@@ -49836,12 +49836,12 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-      <c r="H61" s="938" t="s">
+      <c r="H61" s="919" t="s">
         <v>123</v>
       </c>
-      <c r="I61" s="938"/>
-      <c r="J61" s="938"/>
-      <c r="K61" s="938"/>
+      <c r="I61" s="919"/>
+      <c r="J61" s="919"/>
+      <c r="K61" s="919"/>
       <c r="M61" s="91"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
@@ -50190,6 +50190,20 @@
     <protectedRange sqref="C9:C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="30">
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="A15:K15"/>
     <mergeCell ref="H61:K61"/>
     <mergeCell ref="U19:V19"/>
     <mergeCell ref="X19:X20"/>
@@ -50206,20 +50220,6 @@
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="F23:F24"/>
-    <mergeCell ref="Z19:Z20"/>
-    <mergeCell ref="AA19:AA20"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="M30:P30"/>
-    <mergeCell ref="A15:K15"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -50340,35 +50340,35 @@
       <c r="X6" s="178"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="920" t="s">
+      <c r="A7" s="932" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="920"/>
-      <c r="C7" s="920"/>
-      <c r="D7" s="920"/>
-      <c r="E7" s="920"/>
-      <c r="F7" s="920"/>
-      <c r="G7" s="920"/>
-      <c r="H7" s="920"/>
-      <c r="I7" s="920"/>
-      <c r="J7" s="920"/>
-      <c r="K7" s="920"/>
+      <c r="B7" s="932"/>
+      <c r="C7" s="932"/>
+      <c r="D7" s="932"/>
+      <c r="E7" s="932"/>
+      <c r="F7" s="932"/>
+      <c r="G7" s="932"/>
+      <c r="H7" s="932"/>
+      <c r="I7" s="932"/>
+      <c r="J7" s="932"/>
+      <c r="K7" s="932"/>
       <c r="X7" s="178"/>
     </row>
     <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="956">
+      <c r="A8" s="959">
         <v>1</v>
       </c>
-      <c r="B8" s="956"/>
-      <c r="C8" s="956"/>
-      <c r="D8" s="956"/>
-      <c r="E8" s="956"/>
-      <c r="F8" s="956"/>
-      <c r="G8" s="956"/>
-      <c r="H8" s="956"/>
-      <c r="I8" s="956"/>
-      <c r="J8" s="956"/>
-      <c r="K8" s="956"/>
+      <c r="B8" s="959"/>
+      <c r="C8" s="959"/>
+      <c r="D8" s="959"/>
+      <c r="E8" s="959"/>
+      <c r="F8" s="959"/>
+      <c r="G8" s="959"/>
+      <c r="H8" s="959"/>
+      <c r="I8" s="959"/>
+      <c r="J8" s="959"/>
+      <c r="K8" s="959"/>
       <c r="X8" s="178"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -50444,15 +50444,15 @@
       <c r="K13" s="308">
         <v>43845</v>
       </c>
-      <c r="M13" s="939" t="s">
+      <c r="M13" s="920" t="s">
         <v>9</v>
       </c>
-      <c r="N13" s="940"/>
-      <c r="O13" s="959" t="s">
+      <c r="N13" s="921"/>
+      <c r="O13" s="952" t="s">
         <v>69</v>
       </c>
-      <c r="P13" s="960"/>
-      <c r="Q13" s="961"/>
+      <c r="P13" s="953"/>
+      <c r="Q13" s="954"/>
       <c r="W13" s="178"/>
       <c r="X13" s="178"/>
     </row>
@@ -50476,26 +50476,26 @@
       <c r="N14" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="O14" s="962"/>
-      <c r="P14" s="963"/>
-      <c r="Q14" s="964"/>
+      <c r="O14" s="955"/>
+      <c r="P14" s="956"/>
+      <c r="Q14" s="957"/>
       <c r="W14" s="178"/>
       <c r="X14" s="178"/>
     </row>
     <row r="15" spans="1:24" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="928" t="s">
+      <c r="A15" s="940" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="929"/>
-      <c r="C15" s="929"/>
-      <c r="D15" s="929"/>
-      <c r="E15" s="929"/>
-      <c r="F15" s="929"/>
-      <c r="G15" s="929"/>
-      <c r="H15" s="929"/>
-      <c r="I15" s="929"/>
-      <c r="J15" s="929"/>
-      <c r="K15" s="930"/>
+      <c r="B15" s="941"/>
+      <c r="C15" s="941"/>
+      <c r="D15" s="941"/>
+      <c r="E15" s="941"/>
+      <c r="F15" s="941"/>
+      <c r="G15" s="941"/>
+      <c r="H15" s="941"/>
+      <c r="I15" s="941"/>
+      <c r="J15" s="941"/>
+      <c r="K15" s="942"/>
       <c r="M15" s="77" t="s">
         <v>19</v>
       </c>
@@ -50509,19 +50509,19 @@
       <c r="X15" s="178"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="935" t="s">
+      <c r="A16" s="947" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="936"/>
-      <c r="C16" s="936"/>
-      <c r="D16" s="936"/>
-      <c r="E16" s="936"/>
-      <c r="F16" s="936"/>
-      <c r="G16" s="936"/>
-      <c r="H16" s="936"/>
-      <c r="I16" s="936"/>
-      <c r="J16" s="936"/>
-      <c r="K16" s="937"/>
+      <c r="B16" s="948"/>
+      <c r="C16" s="948"/>
+      <c r="D16" s="948"/>
+      <c r="E16" s="948"/>
+      <c r="F16" s="948"/>
+      <c r="G16" s="948"/>
+      <c r="H16" s="948"/>
+      <c r="I16" s="948"/>
+      <c r="J16" s="948"/>
+      <c r="K16" s="949"/>
       <c r="L16" s="18"/>
       <c r="M16" s="77" t="s">
         <v>20</v>
@@ -50560,17 +50560,17 @@
       <c r="X17" s="178"/>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="925" t="s">
+      <c r="A18" s="937" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="926"/>
-      <c r="C18" s="926"/>
-      <c r="D18" s="926"/>
-      <c r="E18" s="926"/>
-      <c r="F18" s="926"/>
-      <c r="G18" s="926"/>
-      <c r="H18" s="926"/>
-      <c r="I18" s="926"/>
+      <c r="B18" s="938"/>
+      <c r="C18" s="938"/>
+      <c r="D18" s="938"/>
+      <c r="E18" s="938"/>
+      <c r="F18" s="938"/>
+      <c r="G18" s="938"/>
+      <c r="H18" s="938"/>
+      <c r="I18" s="938"/>
       <c r="J18" s="291"/>
       <c r="K18" s="292"/>
       <c r="M18" s="77">
@@ -50719,15 +50719,15 @@
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
       <c r="K24" s="144"/>
-      <c r="M24" s="939" t="s">
+      <c r="M24" s="920" t="s">
         <v>71</v>
       </c>
-      <c r="N24" s="940"/>
+      <c r="N24" s="921"/>
       <c r="O24" s="294"/>
-      <c r="P24" s="957">
+      <c r="P24" s="950">
         <v>762</v>
       </c>
-      <c r="Q24" s="958"/>
+      <c r="Q24" s="951"/>
       <c r="R24" s="202"/>
       <c r="S24" s="202"/>
       <c r="V24" s="201"/>
@@ -50736,33 +50736,33 @@
     </row>
     <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20"/>
-      <c r="B25" s="939" t="s">
+      <c r="B25" s="920" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="940"/>
-      <c r="D25" s="833" t="s">
+      <c r="C25" s="921"/>
+      <c r="D25" s="843" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="833" t="s">
+      <c r="E25" s="843" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="833" t="s">
+      <c r="F25" s="843" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="833" t="s">
+      <c r="G25" s="843" t="s">
         <v>43</v>
       </c>
       <c r="H25" s="209"/>
-      <c r="I25" s="944" t="s">
+      <c r="I25" s="925" t="s">
         <v>36</v>
       </c>
-      <c r="J25" s="945"/>
+      <c r="J25" s="926"/>
       <c r="K25" s="144"/>
       <c r="M25" s="210" t="s">
         <v>9</v>
       </c>
       <c r="N25" s="211"/>
-      <c r="O25" s="919" t="s">
+      <c r="O25" s="931" t="s">
         <v>100</v>
       </c>
       <c r="P25" s="212" t="s">
@@ -50789,16 +50789,16 @@
       <c r="C26" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="834"/>
-      <c r="E26" s="834"/>
-      <c r="F26" s="834"/>
-      <c r="G26" s="834"/>
+      <c r="D26" s="844"/>
+      <c r="E26" s="844"/>
+      <c r="F26" s="844"/>
+      <c r="G26" s="844"/>
       <c r="H26" s="209"/>
-      <c r="I26" s="947">
+      <c r="I26" s="928">
         <f>+P24</f>
         <v>762</v>
       </c>
-      <c r="J26" s="948"/>
+      <c r="J26" s="929"/>
       <c r="K26" s="144"/>
       <c r="M26" s="213" t="s">
         <v>11</v>
@@ -50806,7 +50806,7 @@
       <c r="N26" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="O26" s="919"/>
+      <c r="O26" s="931"/>
       <c r="P26" s="187" t="s">
         <v>28</v>
       </c>
@@ -50906,10 +50906,10 @@
         <v>#REF!</v>
       </c>
       <c r="H28" s="218"/>
-      <c r="I28" s="951" t="s">
+      <c r="I28" s="961" t="s">
         <v>37</v>
       </c>
-      <c r="J28" s="952"/>
+      <c r="J28" s="962"/>
       <c r="K28" s="144"/>
       <c r="M28" s="220" t="s">
         <v>31</v>
@@ -50965,11 +50965,11 @@
         <v>#REF!</v>
       </c>
       <c r="H29" s="218"/>
-      <c r="I29" s="953" t="e">
+      <c r="I29" s="963" t="e">
         <f>(R30+R32+R34+R36+R37+R39+R40+R42+R43)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="J29" s="954"/>
+      <c r="J29" s="964"/>
       <c r="K29" s="144"/>
       <c r="M29" s="220" t="s">
         <v>15</v>
@@ -51085,8 +51085,8 @@
         <v>#REF!</v>
       </c>
       <c r="H31" s="218"/>
-      <c r="I31" s="924"/>
-      <c r="J31" s="924"/>
+      <c r="I31" s="936"/>
+      <c r="J31" s="936"/>
       <c r="K31" s="144"/>
       <c r="L31" s="19"/>
       <c r="M31" s="220" t="s">
@@ -51143,8 +51143,8 @@
         <v>#REF!</v>
       </c>
       <c r="H32" s="218"/>
-      <c r="I32" s="924"/>
-      <c r="J32" s="924"/>
+      <c r="I32" s="936"/>
+      <c r="J32" s="936"/>
       <c r="K32" s="144"/>
       <c r="L32" s="19"/>
       <c r="M32" s="220" t="s">
@@ -51201,8 +51201,8 @@
         <v>#REF!</v>
       </c>
       <c r="H33" s="218"/>
-      <c r="I33" s="955"/>
-      <c r="J33" s="955"/>
+      <c r="I33" s="958"/>
+      <c r="J33" s="958"/>
       <c r="K33" s="144"/>
       <c r="L33" s="19"/>
       <c r="M33" s="220" t="s">
@@ -52020,10 +52020,10 @@
       <c r="W54" s="275" t="s">
         <v>105</v>
       </c>
-      <c r="X54" s="931">
+      <c r="X54" s="943">
         <v>44090</v>
       </c>
-      <c r="Y54" s="931"/>
+      <c r="Y54" s="943"/>
       <c r="Z54" s="276"/>
       <c r="AA54" s="277"/>
       <c r="AB54" s="276"/>
@@ -52052,19 +52052,19 @@
       <c r="X57" s="178"/>
     </row>
     <row r="58" spans="1:33" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="950" t="s">
+      <c r="A58" s="960" t="s">
         <v>120</v>
       </c>
-      <c r="B58" s="950"/>
-      <c r="C58" s="950"/>
-      <c r="D58" s="950"/>
-      <c r="E58" s="950"/>
-      <c r="F58" s="950"/>
-      <c r="G58" s="950"/>
-      <c r="H58" s="950"/>
-      <c r="I58" s="950"/>
-      <c r="J58" s="950"/>
-      <c r="K58" s="950"/>
+      <c r="B58" s="960"/>
+      <c r="C58" s="960"/>
+      <c r="D58" s="960"/>
+      <c r="E58" s="960"/>
+      <c r="F58" s="960"/>
+      <c r="G58" s="960"/>
+      <c r="H58" s="960"/>
+      <c r="I58" s="960"/>
+      <c r="J58" s="960"/>
+      <c r="K58" s="960"/>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" s="310" t="s">
@@ -52082,19 +52082,19 @@
       <c r="K59" s="311"/>
     </row>
     <row r="60" spans="1:33" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="950" t="s">
+      <c r="A60" s="960" t="s">
         <v>122</v>
       </c>
-      <c r="B60" s="950"/>
-      <c r="C60" s="950"/>
-      <c r="D60" s="950"/>
-      <c r="E60" s="950"/>
-      <c r="F60" s="950"/>
-      <c r="G60" s="950"/>
-      <c r="H60" s="950"/>
-      <c r="I60" s="950"/>
-      <c r="J60" s="950"/>
-      <c r="K60" s="950"/>
+      <c r="B60" s="960"/>
+      <c r="C60" s="960"/>
+      <c r="D60" s="960"/>
+      <c r="E60" s="960"/>
+      <c r="F60" s="960"/>
+      <c r="G60" s="960"/>
+      <c r="H60" s="960"/>
+      <c r="I60" s="960"/>
+      <c r="J60" s="960"/>
+      <c r="K60" s="960"/>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B63" s="5"/>
@@ -52128,6 +52128,21 @@
     <protectedRange sqref="B10:B11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="25">
+    <mergeCell ref="X54:Y54"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A18:I18"/>
     <mergeCell ref="M24:N24"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="F25:F26"/>
@@ -52138,21 +52153,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="X54:Y54"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="I31:J31"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -52235,35 +52235,35 @@
       <c r="H4" s="177"/>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="920" t="s">
+      <c r="A5" s="932" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="920"/>
-      <c r="C5" s="920"/>
-      <c r="D5" s="920"/>
-      <c r="E5" s="920"/>
-      <c r="F5" s="920"/>
-      <c r="G5" s="920"/>
-      <c r="H5" s="920"/>
-      <c r="I5" s="920"/>
-      <c r="J5" s="920"/>
-      <c r="K5" s="920"/>
+      <c r="B5" s="932"/>
+      <c r="C5" s="932"/>
+      <c r="D5" s="932"/>
+      <c r="E5" s="932"/>
+      <c r="F5" s="932"/>
+      <c r="G5" s="932"/>
+      <c r="H5" s="932"/>
+      <c r="I5" s="932"/>
+      <c r="J5" s="932"/>
+      <c r="K5" s="932"/>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="927">
+      <c r="A6" s="939">
         <f>+K12</f>
         <v>44</v>
       </c>
-      <c r="B6" s="927"/>
-      <c r="C6" s="927"/>
-      <c r="D6" s="927"/>
-      <c r="E6" s="927"/>
-      <c r="F6" s="927"/>
-      <c r="G6" s="927"/>
-      <c r="H6" s="927"/>
-      <c r="I6" s="927"/>
-      <c r="J6" s="927"/>
-      <c r="K6" s="927"/>
+      <c r="B6" s="939"/>
+      <c r="C6" s="939"/>
+      <c r="D6" s="939"/>
+      <c r="E6" s="939"/>
+      <c r="F6" s="939"/>
+      <c r="G6" s="939"/>
+      <c r="H6" s="939"/>
+      <c r="I6" s="939"/>
+      <c r="J6" s="939"/>
+      <c r="K6" s="939"/>
       <c r="Q6" s="259" t="s">
         <v>101</v>
       </c>
@@ -52329,10 +52329,10 @@
       <c r="Q9" s="275" t="s">
         <v>105</v>
       </c>
-      <c r="R9" s="931">
+      <c r="R9" s="943">
         <v>44090</v>
       </c>
-      <c r="S9" s="931"/>
+      <c r="S9" s="943"/>
       <c r="T9" s="276"/>
       <c r="U9" s="277"/>
       <c r="V9" s="276"/>
@@ -52413,37 +52413,37 @@
       <c r="U13" s="3"/>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="928" t="s">
+      <c r="A14" s="940" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="929"/>
-      <c r="C14" s="929"/>
-      <c r="D14" s="929"/>
-      <c r="E14" s="929"/>
-      <c r="F14" s="929"/>
-      <c r="G14" s="929"/>
-      <c r="H14" s="929"/>
-      <c r="I14" s="929"/>
-      <c r="J14" s="929"/>
-      <c r="K14" s="930"/>
+      <c r="B14" s="941"/>
+      <c r="C14" s="941"/>
+      <c r="D14" s="941"/>
+      <c r="E14" s="941"/>
+      <c r="F14" s="941"/>
+      <c r="G14" s="941"/>
+      <c r="H14" s="941"/>
+      <c r="I14" s="941"/>
+      <c r="J14" s="941"/>
+      <c r="K14" s="942"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
       <c r="U14" s="70"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="935" t="s">
+      <c r="A15" s="947" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="936"/>
-      <c r="C15" s="936"/>
-      <c r="D15" s="936"/>
-      <c r="E15" s="936"/>
-      <c r="F15" s="936"/>
-      <c r="G15" s="936"/>
-      <c r="H15" s="936"/>
-      <c r="I15" s="936"/>
-      <c r="J15" s="936"/>
-      <c r="K15" s="937"/>
+      <c r="B15" s="948"/>
+      <c r="C15" s="948"/>
+      <c r="D15" s="948"/>
+      <c r="E15" s="948"/>
+      <c r="F15" s="948"/>
+      <c r="G15" s="948"/>
+      <c r="H15" s="948"/>
+      <c r="I15" s="948"/>
+      <c r="J15" s="948"/>
+      <c r="K15" s="949"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
       <c r="U15" s="71"/>
@@ -52465,17 +52465,17 @@
       <c r="U16" s="70"/>
     </row>
     <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="925" t="s">
+      <c r="A17" s="937" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="926"/>
-      <c r="C17" s="926"/>
-      <c r="D17" s="926"/>
-      <c r="E17" s="926"/>
-      <c r="F17" s="926"/>
-      <c r="G17" s="926"/>
-      <c r="H17" s="926"/>
-      <c r="I17" s="926"/>
+      <c r="B17" s="938"/>
+      <c r="C17" s="938"/>
+      <c r="D17" s="938"/>
+      <c r="E17" s="938"/>
+      <c r="F17" s="938"/>
+      <c r="G17" s="938"/>
+      <c r="H17" s="938"/>
+      <c r="I17" s="938"/>
       <c r="J17" s="291" t="s">
         <v>124</v>
       </c>
@@ -52571,16 +52571,16 @@
       <c r="I22" s="242"/>
       <c r="J22" s="18"/>
       <c r="K22" s="243"/>
-      <c r="M22" s="967" t="s">
+      <c r="M22" s="965" t="s">
         <v>71</v>
       </c>
-      <c r="N22" s="968"/>
+      <c r="N22" s="966"/>
       <c r="O22" s="280"/>
-      <c r="P22" s="969">
+      <c r="P22" s="967">
         <f>SUM(O25:O42)</f>
         <v>9543.9950657520003</v>
       </c>
-      <c r="Q22" s="958"/>
+      <c r="Q22" s="951"/>
       <c r="R22" s="77" t="s">
         <v>73</v>
       </c>
@@ -52595,33 +52595,33 @@
     </row>
     <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
-      <c r="B23" s="965" t="s">
+      <c r="B23" s="973" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="965"/>
-      <c r="D23" s="966" t="s">
+      <c r="C23" s="973"/>
+      <c r="D23" s="970" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="966" t="s">
+      <c r="E23" s="970" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="966" t="s">
+      <c r="F23" s="970" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="966" t="s">
+      <c r="G23" s="970" t="s">
         <v>43</v>
       </c>
       <c r="H23" s="18"/>
-      <c r="I23" s="944" t="s">
+      <c r="I23" s="925" t="s">
         <v>36</v>
       </c>
-      <c r="J23" s="945"/>
+      <c r="J23" s="926"/>
       <c r="K23" s="144"/>
       <c r="M23" s="67" t="s">
         <v>9</v>
       </c>
       <c r="N23" s="68"/>
-      <c r="O23" s="919" t="s">
+      <c r="O23" s="931" t="s">
         <v>100</v>
       </c>
       <c r="P23" s="9" t="s">
@@ -52652,16 +52652,16 @@
       <c r="C24" s="244" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="966"/>
-      <c r="E24" s="966"/>
-      <c r="F24" s="966"/>
-      <c r="G24" s="966"/>
+      <c r="D24" s="970"/>
+      <c r="E24" s="970"/>
+      <c r="F24" s="970"/>
+      <c r="G24" s="970"/>
       <c r="H24" s="245"/>
-      <c r="I24" s="947">
+      <c r="I24" s="928">
         <f>+P22</f>
         <v>9543.9950657520003</v>
       </c>
-      <c r="J24" s="948"/>
+      <c r="J24" s="929"/>
       <c r="K24" s="144"/>
       <c r="M24" s="65" t="s">
         <v>11</v>
@@ -52669,7 +52669,7 @@
       <c r="N24" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O24" s="919"/>
+      <c r="O24" s="931"/>
       <c r="P24" s="10" t="s">
         <v>28</v>
       </c>
@@ -52790,10 +52790,10 @@
         <v>100</v>
       </c>
       <c r="H26" s="245"/>
-      <c r="I26" s="951" t="s">
+      <c r="I26" s="961" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="952"/>
+      <c r="J26" s="962"/>
       <c r="K26" s="144"/>
       <c r="M26" s="74">
         <v>2.5</v>
@@ -52870,11 +52870,11 @@
         <v>100</v>
       </c>
       <c r="H27" s="245"/>
-      <c r="I27" s="972">
+      <c r="I27" s="971">
         <f>(R28+R30+R32+R34+R35+R37+R38+R40+R41)/100</f>
         <v>6.8505867560771163</v>
       </c>
-      <c r="J27" s="973"/>
+      <c r="J27" s="972"/>
       <c r="K27" s="144"/>
       <c r="M27" s="74">
         <v>2</v>
@@ -53029,10 +53029,10 @@
         <v>98.973176865046099</v>
       </c>
       <c r="H29" s="245"/>
-      <c r="I29" s="951" t="s">
+      <c r="I29" s="961" t="s">
         <v>65</v>
       </c>
-      <c r="J29" s="952"/>
+      <c r="J29" s="962"/>
       <c r="K29" s="144"/>
       <c r="L29" s="19"/>
       <c r="M29" s="74">
@@ -53110,11 +53110,11 @@
         <v>44.991617770326911</v>
       </c>
       <c r="H30" s="245"/>
-      <c r="I30" s="970">
+      <c r="I30" s="968">
         <f>+Z38</f>
         <v>0.5</v>
       </c>
-      <c r="J30" s="971"/>
+      <c r="J30" s="969"/>
       <c r="K30" s="144"/>
       <c r="L30" s="19"/>
       <c r="M30" s="74">
@@ -53271,8 +53271,8 @@
         <v>0.20955574182733017</v>
       </c>
       <c r="H32" s="245"/>
-      <c r="I32" s="924"/>
-      <c r="J32" s="924"/>
+      <c r="I32" s="936"/>
+      <c r="J32" s="936"/>
       <c r="K32" s="144"/>
       <c r="L32" s="19"/>
       <c r="M32" s="74">
@@ -53350,8 +53350,8 @@
         <v>0</v>
       </c>
       <c r="H33" s="245"/>
-      <c r="I33" s="924"/>
-      <c r="J33" s="924"/>
+      <c r="I33" s="936"/>
+      <c r="J33" s="936"/>
       <c r="K33" s="144"/>
       <c r="L33" s="19"/>
       <c r="M33" s="74">
@@ -53424,8 +53424,8 @@
       </c>
       <c r="G34" s="303"/>
       <c r="H34" s="245"/>
-      <c r="I34" s="955"/>
-      <c r="J34" s="955"/>
+      <c r="I34" s="958"/>
+      <c r="J34" s="958"/>
       <c r="K34" s="144"/>
       <c r="L34" s="19"/>
       <c r="M34" s="23" t="s">
@@ -54073,27 +54073,27 @@
       <c r="K54" s="297"/>
     </row>
     <row r="55" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="949" t="s">
+      <c r="A55" s="930" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="949"/>
-      <c r="C55" s="949"/>
-      <c r="D55" s="949"/>
-      <c r="E55" s="949"/>
-      <c r="F55" s="949"/>
-      <c r="G55" s="949"/>
-      <c r="H55" s="949"/>
-      <c r="I55" s="949"/>
-      <c r="J55" s="949"/>
-      <c r="K55" s="949"/>
+      <c r="B55" s="930"/>
+      <c r="C55" s="930"/>
+      <c r="D55" s="930"/>
+      <c r="E55" s="930"/>
+      <c r="F55" s="930"/>
+      <c r="G55" s="930"/>
+      <c r="H55" s="930"/>
+      <c r="I55" s="930"/>
+      <c r="J55" s="930"/>
+      <c r="K55" s="930"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="H56" s="938" t="s">
+      <c r="H56" s="919" t="s">
         <v>123</v>
       </c>
-      <c r="I56" s="938"/>
-      <c r="J56" s="938"/>
-      <c r="K56" s="938"/>
+      <c r="I56" s="919"/>
+      <c r="J56" s="919"/>
+      <c r="K56" s="919"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -54103,6 +54103,15 @@
     <protectedRange sqref="B9:B10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="25">
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="G23:G24"/>
     <mergeCell ref="A55:K55"/>
     <mergeCell ref="H56:K56"/>
     <mergeCell ref="O23:O24"/>
@@ -54119,15 +54128,6 @@
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="G23:G24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.59055118110236227" bottom="0" header="0.11811023622047245" footer="0"/>

--- a/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
+++ b/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
@@ -31617,7 +31617,11 @@
       <c r="E11" s="828"/>
       <c r="F11" s="827"/>
       <c r="G11" s="828"/>
-      <c r="H11" s="737"/>
+      <c r="H11" s="737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I11" s="725"/>
       <c r="L11" s="285" t="s">
         <v>449</v>
@@ -38606,8 +38610,10 @@
       <c r="B9" s="439" t="s">
         <v>332</v>
       </c>
-      <c r="C9" s="883" t="s">
-        <v>344</v>
+      <c r="C9" s="883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D9" s="884"/>
       <c r="F9" s="579" t="s">
@@ -38626,12 +38632,16 @@
       <c r="B10" s="439" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="883" t="s">
-        <v>344</v>
+      <c r="C10" s="883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D10" s="884"/>
-      <c r="F10" s="707" t="s">
-        <v>344</v>
+      <c r="F10" s="707" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G10" s="470">
         <f>+FORMATO!H11</f>

--- a/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
+++ b/app/templates/informes/Informes agregado/Gran agregado AG/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
@@ -38643,10 +38643,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="470">
-        <f>+FORMATO!H11</f>
-        <v>0</v>
-      </c>
+      <c r="G10" s="470"/>
       <c r="H10" s="470"/>
       <c r="I10" s="470"/>
       <c r="J10" s="470"/>
